--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -5207,7 +5207,7 @@
         <v>1.409</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-06 05:35:23</t>
+          <t>2026-09-06 05:42:24</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -5008,7 +5008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5129,25 +5129,45 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>book_value</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>price_to_book</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>earnings_growth</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>shares_outstanding</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -5183,19 +5203,19 @@
         <v>5945953</v>
       </c>
       <c r="I2" t="n">
-        <v>10444459</v>
+        <v>10375558</v>
       </c>
       <c r="J2" t="n">
         <v>181837381632</v>
       </c>
       <c r="K2" t="n">
-        <v>22.077568</v>
+        <v>21.713402</v>
       </c>
       <c r="L2" t="n">
         <v>14.0888405</v>
       </c>
       <c r="M2" t="n">
-        <v>4.77</v>
+        <v>4.85</v>
       </c>
       <c r="N2" t="n">
         <v>119.05</v>
@@ -5231,29 +5251,41 @@
       <c r="W2" t="n">
         <v>0.709</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>63.602</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.6557654</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.483</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1726686902</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>https://thewaltdisneycompany.com</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>The Walt Disney Company operates as an entertainment company in Americas, Europe, and the Asia Pacific. It operates in three segments: Entertainment, Sports, and Experiences. The company produces and distributes film and television content under the ABC Television Network, Disney, Freeform, FX, Fox, National Geographic, and Star brand television channels, as well as ABC television stations and A+E television networks; and produces original content under the Disney Branded Television, FX Productions, Lucasfilm, Marvel, National Geographic Studios, Pixar, Searchlight Pictures, Twentieth Century Studios, 20th Television, and Walt Disney Pictures banners. It also provides direct-to-consumer streaming services through Disney+, Disney+ Hotstar, and Hulu; sports-related video streaming content through ESPN, ESPN on ABC, ESPN+ DTC, and Star; sale/licensing of film and episodic content to television and video-on-demand services; theatrical, home entertainment, and music distribution services; DVD and Blu-ray discs, electronic home video licenses, and VOD rental services; staging and licensing of live entertainment events; and post-production services. In addition, the company operates theme parks and resorts, such as Walt Disney World Resort, Disneyland Resort, Disneyland Paris, Hong Kong Disneyland Resort, Shanghai Disney Resort, Disney Cruise Line, Disney Vacation Club, National Geographic Expeditions, and Adventures by Disney, as well as Aulani, a Disney resort and spa in Hawaii. Further, it licenses its intellectual property (IP) to a third party that owns and operates Tokyo Disney Resort; licenses trade names, characters, visual, literary, and other IP for use on merchandise, published materials, and games; operates a direct-to-home satellite distribution platform; sells branded merchandise through retail, online, and wholesale businesses; and develops and publishes books, comic books, and magazines. The company was founded in 1923 and is based in Burbank, California.</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2026-09-06 05:42:24</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-09-06 16:10:27</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -5285,7 +5285,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:10:27</t>
+          <t>2026-09-06 16:25:03</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -5285,7 +5285,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:25:03</t>
+          <t>2026-09-06 16:34:58</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -5285,7 +5285,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:34:58</t>
+          <t>2026-09-06 16:49:31</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -5229,15 +5229,11 @@
       <c r="Q2" t="n">
         <v>1.42</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="R2" t="n">
+        <v>0.08699000599999999</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.19301</v>
       </c>
       <c r="T2" t="n">
         <v>0.0801</v>
@@ -5285,7 +5281,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:31</t>
+          <t>2026-09-06 17:00:02</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -5008,7 +5008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5149,25 +5149,40 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>total_revenue</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -5259,29 +5274,38 @@
       <c r="AA2" t="n">
         <v>1726686902</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>98860998656</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>229503401984</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>20963000320</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Entertainment</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://thewaltdisneycompany.com</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>The Walt Disney Company operates as an entertainment company in Americas, Europe, and the Asia Pacific. It operates in three segments: Entertainment, Sports, and Experiences. The company produces and distributes film and television content under the ABC Television Network, Disney, Freeform, FX, Fox, National Geographic, and Star brand television channels, as well as ABC television stations and A+E television networks; and produces original content under the Disney Branded Television, FX Productions, Lucasfilm, Marvel, National Geographic Studios, Pixar, Searchlight Pictures, Twentieth Century Studios, 20th Television, and Walt Disney Pictures banners. It also provides direct-to-consumer streaming services through Disney+, Disney+ Hotstar, and Hulu; sports-related video streaming content through ESPN, ESPN on ABC, ESPN+ DTC, and Star; sale/licensing of film and episodic content to television and video-on-demand services; theatrical, home entertainment, and music distribution services; DVD and Blu-ray discs, electronic home video licenses, and VOD rental services; staging and licensing of live entertainment events; and post-production services. In addition, the company operates theme parks and resorts, such as Walt Disney World Resort, Disneyland Resort, Disneyland Paris, Hong Kong Disneyland Resort, Shanghai Disney Resort, Disney Cruise Line, Disney Vacation Club, National Geographic Expeditions, and Adventures by Disney, as well as Aulani, a Disney resort and spa in Hawaii. Further, it licenses its intellectual property (IP) to a third party that owns and operates Tokyo Disney Resort; licenses trade names, characters, visual, literary, and other IP for use on merchandise, published materials, and games; operates a direct-to-home satellite distribution platform; sells branded merchandise through retail, online, and wholesale businesses; and develops and publishes books, comic books, and magazines. The company was founded in 1923 and is based in Burbank, California.</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>2026-09-06 17:00:02</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:21:07</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -5305,7 +5305,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:21:07</t>
+          <t>2026-09-06 22:42:02</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -5305,7 +5305,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:42:02</t>
+          <t>2026-09-06 22:59:56</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46239</v>
+        <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>101.9899978637695</v>
+        <v>117.2127468064064</v>
       </c>
       <c r="C2" t="n">
-        <v>103.2099990844727</v>
+        <v>118.0703240854676</v>
       </c>
       <c r="D2" t="n">
-        <v>99.69000244140625</v>
+        <v>116.0200110716605</v>
       </c>
       <c r="E2" t="n">
-        <v>101.7600021362305</v>
+        <v>116.2270202636719</v>
       </c>
       <c r="F2" t="n">
-        <v>20809000</v>
+        <v>6669100</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>45908</v>
       </c>
       <c r="B3" t="n">
-        <v>102.5400009155273</v>
+        <v>116.2763011496704</v>
       </c>
       <c r="C3" t="n">
-        <v>104.7300033569336</v>
+        <v>117.1831677568228</v>
       </c>
       <c r="D3" t="n">
-        <v>102.5199966430664</v>
+        <v>115.0737135738613</v>
       </c>
       <c r="E3" t="n">
-        <v>104.6800003051758</v>
+        <v>117.1437377929688</v>
       </c>
       <c r="F3" t="n">
-        <v>14047200</v>
+        <v>6450700</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46241</v>
+        <v>45909</v>
       </c>
       <c r="B4" t="n">
-        <v>104.4199981689453</v>
+        <v>116.8381638958523</v>
       </c>
       <c r="C4" t="n">
-        <v>105.25</v>
+        <v>117.3507459007291</v>
       </c>
       <c r="D4" t="n">
-        <v>103.6999969482422</v>
+        <v>115.5468645536568</v>
       </c>
       <c r="E4" t="n">
-        <v>104.9100036621094</v>
+        <v>115.6947250366211</v>
       </c>
       <c r="F4" t="n">
-        <v>10929700</v>
+        <v>5444300</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46244</v>
+        <v>45910</v>
       </c>
       <c r="B5" t="n">
-        <v>104.6100006103516</v>
+        <v>115.1821434099858</v>
       </c>
       <c r="C5" t="n">
-        <v>104.8000030517578</v>
+        <v>115.8327265289666</v>
       </c>
       <c r="D5" t="n">
-        <v>102.8000030517578</v>
+        <v>112.8656875709264</v>
       </c>
       <c r="E5" t="n">
-        <v>103.1800003051758</v>
+        <v>114.1372756958008</v>
       </c>
       <c r="F5" t="n">
-        <v>8631900</v>
+        <v>7484900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46245</v>
+        <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>102.9499969482422</v>
+        <v>113.8021202611286</v>
       </c>
       <c r="C6" t="n">
-        <v>104.0899963378906</v>
+        <v>115.4975710271905</v>
       </c>
       <c r="D6" t="n">
-        <v>102.7900009155273</v>
+        <v>112.9938248401568</v>
       </c>
       <c r="E6" t="n">
-        <v>103.5299987792969</v>
+        <v>115.4088592529297</v>
       </c>
       <c r="F6" t="n">
-        <v>6781600</v>
+        <v>8399100</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46246</v>
+        <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>103.2900009155273</v>
+        <v>114.6005610358709</v>
       </c>
       <c r="C7" t="n">
-        <v>103.6800003051758</v>
+        <v>115.3398558853256</v>
       </c>
       <c r="D7" t="n">
-        <v>102.0299987792969</v>
+        <v>113.4571147255429</v>
       </c>
       <c r="E7" t="n">
-        <v>103.2200012207031</v>
+        <v>114.3048400878906</v>
       </c>
       <c r="F7" t="n">
-        <v>6717500</v>
+        <v>7640900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46247</v>
+        <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>103.8000030517578</v>
+        <v>114.45269990472</v>
       </c>
       <c r="C8" t="n">
-        <v>104.9400024414062</v>
+        <v>115.0835642376594</v>
       </c>
       <c r="D8" t="n">
-        <v>103.4599990844727</v>
+        <v>113.3585429321699</v>
       </c>
       <c r="E8" t="n">
-        <v>104.8000030517578</v>
+        <v>113.9696960449219</v>
       </c>
       <c r="F8" t="n">
-        <v>7100000</v>
+        <v>7150900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46248</v>
+        <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>104.9899978637695</v>
+        <v>113.8021196226455</v>
       </c>
       <c r="C9" t="n">
-        <v>107.1100006103516</v>
+        <v>114.1964117205285</v>
       </c>
       <c r="D9" t="n">
-        <v>104.9100036621094</v>
+        <v>113.0726841298844</v>
       </c>
       <c r="E9" t="n">
-        <v>106.8499984741211</v>
+        <v>113.5852661132812</v>
       </c>
       <c r="F9" t="n">
-        <v>8176900</v>
+        <v>6844900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46251</v>
+        <v>45917</v>
       </c>
       <c r="B10" t="n">
-        <v>106.3300018310547</v>
+        <v>113.5951227912625</v>
       </c>
       <c r="C10" t="n">
-        <v>106.6399993896484</v>
+        <v>114.9948601742622</v>
       </c>
       <c r="D10" t="n">
-        <v>103.4599990844727</v>
+        <v>113.5754115697539</v>
       </c>
       <c r="E10" t="n">
-        <v>103.5</v>
+        <v>114.4428482055664</v>
       </c>
       <c r="F10" t="n">
-        <v>7635000</v>
+        <v>7333900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46252</v>
+        <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>104.1900024414062</v>
+        <v>113.6838432123518</v>
       </c>
       <c r="C11" t="n">
-        <v>105.2099990844727</v>
+        <v>114.1274171453944</v>
       </c>
       <c r="D11" t="n">
-        <v>103.629997253418</v>
+        <v>112.4221144494342</v>
       </c>
       <c r="E11" t="n">
-        <v>103.9499969482422</v>
+        <v>113.2205505371094</v>
       </c>
       <c r="F11" t="n">
-        <v>6149900</v>
+        <v>9460500</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46253</v>
+        <v>45919</v>
       </c>
       <c r="B12" t="n">
-        <v>104.0599975585938</v>
+        <v>112.9642523554146</v>
       </c>
       <c r="C12" t="n">
-        <v>107.0599975585938</v>
+        <v>112.9642523554146</v>
       </c>
       <c r="D12" t="n">
-        <v>103.9599990844727</v>
+        <v>110.3323644761722</v>
       </c>
       <c r="E12" t="n">
-        <v>106.9300003051758</v>
+        <v>112.1362457275391</v>
       </c>
       <c r="F12" t="n">
-        <v>8046100</v>
+        <v>23398400</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46254</v>
+        <v>45922</v>
       </c>
       <c r="B13" t="n">
-        <v>106.879997253418</v>
+        <v>110.1647924763258</v>
       </c>
       <c r="C13" t="n">
-        <v>108.6900024414062</v>
+        <v>112.0080961635035</v>
       </c>
       <c r="D13" t="n">
-        <v>106.4199981689453</v>
+        <v>109.9282127085895</v>
       </c>
       <c r="E13" t="n">
-        <v>107.3199996948242</v>
+        <v>110.953369140625</v>
       </c>
       <c r="F13" t="n">
-        <v>7971500</v>
+        <v>15479800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46255</v>
+        <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>107.5699996948242</v>
+        <v>111.111089276602</v>
       </c>
       <c r="C14" t="n">
-        <v>108.4100036621094</v>
+        <v>111.9982446066948</v>
       </c>
       <c r="D14" t="n">
-        <v>106.9700012207031</v>
+        <v>110.0070729190981</v>
       </c>
       <c r="E14" t="n">
-        <v>107.7799987792969</v>
+        <v>110.6477966308594</v>
       </c>
       <c r="F14" t="n">
-        <v>6840800</v>
+        <v>13145000</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46258</v>
+        <v>45924</v>
       </c>
       <c r="B15" t="n">
-        <v>108.3899993896484</v>
+        <v>110.8055211263376</v>
       </c>
       <c r="C15" t="n">
-        <v>111.870002746582</v>
+        <v>112.5206831561622</v>
       </c>
       <c r="D15" t="n">
-        <v>108.0800018310547</v>
+        <v>110.5985119402154</v>
       </c>
       <c r="E15" t="n">
-        <v>110.6100006103516</v>
+        <v>111.8109588623047</v>
       </c>
       <c r="F15" t="n">
-        <v>12658400</v>
+        <v>8755200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46259</v>
+        <v>45925</v>
       </c>
       <c r="B16" t="n">
-        <v>110.5</v>
+        <v>111.1012331951749</v>
       </c>
       <c r="C16" t="n">
-        <v>111.5999984741211</v>
+        <v>112.4221106191933</v>
       </c>
       <c r="D16" t="n">
-        <v>109.7600021362305</v>
+        <v>111.0420920115833</v>
       </c>
       <c r="E16" t="n">
-        <v>111.25</v>
+        <v>111.3772354125977</v>
       </c>
       <c r="F16" t="n">
-        <v>6747100</v>
+        <v>6365500</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46260</v>
+        <v>45926</v>
       </c>
       <c r="B17" t="n">
-        <v>111.3000030517578</v>
+        <v>111.5152366513407</v>
       </c>
       <c r="C17" t="n">
-        <v>111.5199966430664</v>
+        <v>111.9489587195086</v>
       </c>
       <c r="D17" t="n">
-        <v>109.4499969482422</v>
+        <v>111.1505226581053</v>
       </c>
       <c r="E17" t="n">
-        <v>109.629997253418</v>
+        <v>111.8503875732422</v>
       </c>
       <c r="F17" t="n">
-        <v>8524600</v>
+        <v>6145700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46261</v>
+        <v>45929</v>
       </c>
       <c r="B18" t="n">
-        <v>108.7799987792969</v>
+        <v>111.8503861885936</v>
       </c>
       <c r="C18" t="n">
-        <v>108.870002746582</v>
+        <v>113.3684058878927</v>
       </c>
       <c r="D18" t="n">
-        <v>106.7399978637695</v>
+        <v>111.7123850814297</v>
       </c>
       <c r="E18" t="n">
-        <v>106.8199996948242</v>
+        <v>113.1416854858398</v>
       </c>
       <c r="F18" t="n">
-        <v>8699500</v>
+        <v>9304100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46262</v>
+        <v>45930</v>
       </c>
       <c r="B19" t="n">
-        <v>107.25</v>
+        <v>112.8952551010659</v>
       </c>
       <c r="C19" t="n">
-        <v>108.1999969482422</v>
+        <v>113.2402578727591</v>
       </c>
       <c r="D19" t="n">
-        <v>107.0299987792969</v>
+        <v>111.7222381568123</v>
       </c>
       <c r="E19" t="n">
-        <v>108.0999984741211</v>
+        <v>112.8656845092773</v>
       </c>
       <c r="F19" t="n">
-        <v>5465900</v>
+        <v>9303700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46265</v>
+        <v>45931</v>
       </c>
       <c r="B20" t="n">
-        <v>107.7799987792969</v>
+        <v>112.4516824751333</v>
       </c>
       <c r="C20" t="n">
-        <v>108.0899963378906</v>
+        <v>114.4034167605612</v>
       </c>
       <c r="D20" t="n">
-        <v>106.9700012207031</v>
+        <v>111.1800943701441</v>
       </c>
       <c r="E20" t="n">
-        <v>107.5500030517578</v>
+        <v>111.3378067016602</v>
       </c>
       <c r="F20" t="n">
-        <v>8728700</v>
+        <v>9736300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46266</v>
+        <v>45932</v>
       </c>
       <c r="B21" t="n">
-        <v>107.2399978637695</v>
+        <v>111.3673895222522</v>
       </c>
       <c r="C21" t="n">
-        <v>108.9499969482422</v>
+        <v>111.5546724538137</v>
       </c>
       <c r="D21" t="n">
-        <v>106.1399993896484</v>
+        <v>109.1987865883829</v>
       </c>
       <c r="E21" t="n">
-        <v>106.2200012207031</v>
+        <v>110.5393753051758</v>
       </c>
       <c r="F21" t="n">
-        <v>7033700</v>
+        <v>8695100</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46267</v>
+        <v>45933</v>
       </c>
       <c r="B22" t="n">
-        <v>106.7099990844727</v>
+        <v>110.4407994688091</v>
       </c>
       <c r="C22" t="n">
-        <v>108.9899978637695</v>
+        <v>111.9489598311001</v>
       </c>
       <c r="D22" t="n">
-        <v>106.3300018310547</v>
+        <v>109.9676474333371</v>
       </c>
       <c r="E22" t="n">
-        <v>107.9800033569336</v>
+        <v>110.8646621704102</v>
       </c>
       <c r="F22" t="n">
-        <v>7555300</v>
+        <v>7148400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46268</v>
+        <v>45936</v>
       </c>
       <c r="B23" t="n">
-        <v>108.620002746582</v>
+        <v>111.0815219633868</v>
       </c>
       <c r="C23" t="n">
-        <v>109.1999969482422</v>
+        <v>111.4955252894808</v>
       </c>
       <c r="D23" t="n">
-        <v>106.9000015258789</v>
+        <v>109.8592156856383</v>
       </c>
       <c r="E23" t="n">
-        <v>107.1600036621094</v>
+        <v>111.1406631469727</v>
       </c>
       <c r="F23" t="n">
-        <v>6241300</v>
+        <v>6141200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,27 +1041,5981 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B24" t="n">
+        <v>111.0223763857341</v>
+      </c>
+      <c r="C24" t="n">
+        <v>111.7813900254436</v>
+      </c>
+      <c r="D24" t="n">
+        <v>110.20422908127</v>
+      </c>
+      <c r="E24" t="n">
+        <v>110.9238052368164</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5409800</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B25" t="n">
+        <v>111.1998048136618</v>
+      </c>
+      <c r="C25" t="n">
+        <v>111.584237549633</v>
+      </c>
+      <c r="D25" t="n">
+        <v>110.0563659765542</v>
+      </c>
+      <c r="E25" t="n">
+        <v>110.2929382324219</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7074400</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B26" t="n">
+        <v>110.2239394253812</v>
+      </c>
+      <c r="C26" t="n">
+        <v>111.3870970225426</v>
+      </c>
+      <c r="D26" t="n">
+        <v>109.2973540878383</v>
+      </c>
+      <c r="E26" t="n">
+        <v>109.4057846069336</v>
+      </c>
+      <c r="F26" t="n">
+        <v>6502400</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B27" t="n">
+        <v>109.9380737221385</v>
+      </c>
+      <c r="C27" t="n">
+        <v>111.0716606845381</v>
+      </c>
+      <c r="D27" t="n">
+        <v>107.5526174321997</v>
+      </c>
+      <c r="E27" t="n">
+        <v>107.631477355957</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9635200</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B28" t="n">
+        <v>108.8143424328862</v>
+      </c>
+      <c r="C28" t="n">
+        <v>109.3762062096973</v>
+      </c>
+      <c r="D28" t="n">
+        <v>107.8187566106434</v>
+      </c>
+      <c r="E28" t="n">
+        <v>108.6960525512695</v>
+      </c>
+      <c r="F28" t="n">
+        <v>7435100</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B29" t="n">
+        <v>108.0849128268841</v>
+      </c>
+      <c r="C29" t="n">
+        <v>110.2436487598859</v>
+      </c>
+      <c r="D29" t="n">
+        <v>107.641331387133</v>
+      </c>
+      <c r="E29" t="n">
+        <v>109.5832138061523</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7898000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B30" t="n">
+        <v>109.8789291603083</v>
+      </c>
+      <c r="C30" t="n">
+        <v>111.0716572685961</v>
+      </c>
+      <c r="D30" t="n">
+        <v>109.5536376251855</v>
+      </c>
+      <c r="E30" t="n">
+        <v>110.1155014038086</v>
+      </c>
+      <c r="F30" t="n">
+        <v>7012600</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B31" t="n">
+        <v>110.1943638011324</v>
+      </c>
+      <c r="C31" t="n">
+        <v>110.4900772320282</v>
+      </c>
+      <c r="D31" t="n">
+        <v>106.9611821588295</v>
+      </c>
+      <c r="E31" t="n">
+        <v>108.3116226196289</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7531200</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B32" t="n">
+        <v>108.1736289318545</v>
+      </c>
+      <c r="C32" t="n">
+        <v>109.8690797923661</v>
+      </c>
+      <c r="D32" t="n">
+        <v>107.8779154806818</v>
+      </c>
+      <c r="E32" t="n">
+        <v>109.0903549194336</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10090500</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B33" t="n">
+        <v>109.4452125270959</v>
+      </c>
+      <c r="C33" t="n">
+        <v>110.6478000651592</v>
+      </c>
+      <c r="D33" t="n">
+        <v>109.0213498295899</v>
+      </c>
+      <c r="E33" t="n">
+        <v>110.3619384765625</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8047500</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B34" t="n">
+        <v>110.6477986393913</v>
+      </c>
+      <c r="C34" t="n">
+        <v>112.9051132067436</v>
+      </c>
+      <c r="D34" t="n">
+        <v>110.4407969786948</v>
+      </c>
+      <c r="E34" t="n">
+        <v>112.6685409545898</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8163200</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B35" t="n">
+        <v>112.3728242428528</v>
+      </c>
+      <c r="C35" t="n">
+        <v>112.6488264675382</v>
+      </c>
+      <c r="D35" t="n">
+        <v>111.3673864928563</v>
+      </c>
+      <c r="E35" t="n">
+        <v>111.4659576416016</v>
+      </c>
+      <c r="F35" t="n">
+        <v>7569200</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B36" t="n">
+        <v>111.5546728695406</v>
+      </c>
+      <c r="C36" t="n">
+        <v>112.2052560082749</v>
+      </c>
+      <c r="D36" t="n">
+        <v>110.3028034487141</v>
+      </c>
+      <c r="E36" t="n">
+        <v>111.4166717529297</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6945400</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B37" t="n">
+        <v>111.6138166065038</v>
+      </c>
+      <c r="C37" t="n">
+        <v>112.0278199378997</v>
+      </c>
+      <c r="D37" t="n">
+        <v>109.9972182029886</v>
+      </c>
+      <c r="E37" t="n">
+        <v>110.0859375</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6235200</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B38" t="n">
+        <v>110.34222664747</v>
+      </c>
+      <c r="C38" t="n">
+        <v>110.992802225815</v>
+      </c>
+      <c r="D38" t="n">
+        <v>109.721214140304</v>
+      </c>
+      <c r="E38" t="n">
+        <v>110.7365112304688</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6029600</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>110.3126569642538</v>
+      </c>
+      <c r="C39" t="n">
+        <v>110.8745207722</v>
+      </c>
+      <c r="D39" t="n">
+        <v>109.8690755239826</v>
+      </c>
+      <c r="E39" t="n">
+        <v>110.0563659667969</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6839400</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B40" t="n">
+        <v>109.59306628145</v>
+      </c>
+      <c r="C40" t="n">
+        <v>109.9380690325516</v>
+      </c>
+      <c r="D40" t="n">
+        <v>108.4397681475551</v>
+      </c>
+      <c r="E40" t="n">
+        <v>108.6664810180664</v>
+      </c>
+      <c r="F40" t="n">
+        <v>7097100</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B41" t="n">
+        <v>108.5580608670909</v>
+      </c>
+      <c r="C41" t="n">
+        <v>111.9588219337512</v>
+      </c>
+      <c r="D41" t="n">
+        <v>107.9863451909205</v>
+      </c>
+      <c r="E41" t="n">
+        <v>110.24365234375</v>
+      </c>
+      <c r="F41" t="n">
+        <v>8311300</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B42" t="n">
+        <v>109.98736338598</v>
+      </c>
+      <c r="C42" t="n">
+        <v>111.485664339403</v>
+      </c>
+      <c r="D42" t="n">
+        <v>108.9523475649108</v>
+      </c>
+      <c r="E42" t="n">
+        <v>111.0125198364258</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8700600</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B43" t="n">
+        <v>110.9435236572715</v>
+      </c>
+      <c r="C43" t="n">
+        <v>111.1998071396153</v>
+      </c>
+      <c r="D43" t="n">
+        <v>109.4452151242777</v>
+      </c>
+      <c r="E43" t="n">
+        <v>110.519660949707</v>
+      </c>
+      <c r="F43" t="n">
+        <v>8542300</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B44" t="n">
+        <v>109.3860659107013</v>
+      </c>
+      <c r="C44" t="n">
+        <v>110.1943613029524</v>
+      </c>
+      <c r="D44" t="n">
+        <v>109.0607743756439</v>
+      </c>
+      <c r="E44" t="n">
+        <v>109.8789291381836</v>
+      </c>
+      <c r="F44" t="n">
+        <v>7950100</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B45" t="n">
+        <v>109.7606408126771</v>
+      </c>
+      <c r="C45" t="n">
+        <v>110.3717939308002</v>
+      </c>
+      <c r="D45" t="n">
+        <v>109.0213459609701</v>
+      </c>
+      <c r="E45" t="n">
+        <v>109.7705001831055</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5746000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B46" t="n">
+        <v>109.5832124067878</v>
+      </c>
+      <c r="C46" t="n">
+        <v>110.115505615394</v>
+      </c>
+      <c r="D46" t="n">
+        <v>107.6216187917271</v>
+      </c>
+      <c r="E46" t="n">
+        <v>108.9129180908203</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10291800</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B47" t="n">
+        <v>108.6862030385313</v>
+      </c>
+      <c r="C47" t="n">
+        <v>109.8395012072324</v>
+      </c>
+      <c r="D47" t="n">
+        <v>108.4693420111524</v>
+      </c>
+      <c r="E47" t="n">
+        <v>109.1593475341797</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8782100</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B48" t="n">
+        <v>109.5635011857433</v>
+      </c>
+      <c r="C48" t="n">
+        <v>111.1800920323978</v>
+      </c>
+      <c r="D48" t="n">
+        <v>109.4452112992212</v>
+      </c>
+      <c r="E48" t="n">
+        <v>110.637939453125</v>
+      </c>
+      <c r="F48" t="n">
+        <v>9158700</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B49" t="n">
+        <v>111.0420979461576</v>
+      </c>
+      <c r="C49" t="n">
+        <v>113.3289832533765</v>
+      </c>
+      <c r="D49" t="n">
+        <v>110.8153775294455</v>
+      </c>
+      <c r="E49" t="n">
+        <v>113.210693359375</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9713300</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B50" t="n">
+        <v>112.9346801407027</v>
+      </c>
+      <c r="C50" t="n">
+        <v>115.4187075091099</v>
+      </c>
+      <c r="D50" t="n">
+        <v>112.7572490772096</v>
+      </c>
+      <c r="E50" t="n">
+        <v>114.984992980957</v>
+      </c>
+      <c r="F50" t="n">
+        <v>15248700</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B51" t="n">
+        <v>107.3357644371155</v>
+      </c>
+      <c r="C51" t="n">
+        <v>107.7990571232513</v>
+      </c>
+      <c r="D51" t="n">
+        <v>103.4125769427048</v>
+      </c>
+      <c r="E51" t="n">
+        <v>106.0740356445312</v>
+      </c>
+      <c r="F51" t="n">
+        <v>44045400</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B52" t="n">
+        <v>105.9853145518839</v>
+      </c>
+      <c r="C52" t="n">
+        <v>107.1780502864732</v>
+      </c>
+      <c r="D52" t="n">
+        <v>103.7970079445177</v>
+      </c>
+      <c r="E52" t="n">
+        <v>104.2898712158203</v>
+      </c>
+      <c r="F52" t="n">
+        <v>16691400</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B53" t="n">
+        <v>104.2405758139031</v>
+      </c>
+      <c r="C53" t="n">
+        <v>106.1331688606407</v>
+      </c>
+      <c r="D53" t="n">
+        <v>103.6195708355819</v>
+      </c>
+      <c r="E53" t="n">
+        <v>104.1814346313477</v>
+      </c>
+      <c r="F53" t="n">
+        <v>12296400</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B54" t="n">
+        <v>103.5998505812639</v>
+      </c>
+      <c r="C54" t="n">
+        <v>105.5515923025468</v>
+      </c>
+      <c r="D54" t="n">
+        <v>103.501279438279</v>
+      </c>
+      <c r="E54" t="n">
+        <v>104.7630081176758</v>
+      </c>
+      <c r="F54" t="n">
+        <v>11796200</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B55" t="n">
+        <v>104.5658729007312</v>
+      </c>
+      <c r="C55" t="n">
+        <v>106.0543145575675</v>
+      </c>
+      <c r="D55" t="n">
+        <v>102.5944198257724</v>
+      </c>
+      <c r="E55" t="n">
+        <v>103.1759948730469</v>
+      </c>
+      <c r="F55" t="n">
+        <v>12790000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B56" t="n">
+        <v>103.8660034269339</v>
+      </c>
+      <c r="C56" t="n">
+        <v>104.2898661203646</v>
+      </c>
+      <c r="D56" t="n">
+        <v>101.0369656805012</v>
+      </c>
+      <c r="E56" t="n">
+        <v>101.2341079711914</v>
+      </c>
+      <c r="F56" t="n">
+        <v>12609900</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B57" t="n">
+        <v>102.0029806312501</v>
+      </c>
+      <c r="C57" t="n">
+        <v>103.2844205576738</v>
+      </c>
+      <c r="D57" t="n">
+        <v>101.2242558006444</v>
+      </c>
+      <c r="E57" t="n">
+        <v>102.7915573120117</v>
+      </c>
+      <c r="F57" t="n">
+        <v>10785400</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B58" t="n">
+        <v>102.6042684356238</v>
+      </c>
+      <c r="C58" t="n">
+        <v>102.85070006221</v>
+      </c>
+      <c r="D58" t="n">
+        <v>100.4356731298631</v>
+      </c>
+      <c r="E58" t="n">
+        <v>100.4849624633789</v>
+      </c>
+      <c r="F58" t="n">
+        <v>15024800</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101.0271004353643</v>
+      </c>
+      <c r="C59" t="n">
+        <v>102.4366895412752</v>
+      </c>
+      <c r="D59" t="n">
+        <v>100.5440965869111</v>
+      </c>
+      <c r="E59" t="n">
+        <v>101.8353958129883</v>
+      </c>
+      <c r="F59" t="n">
+        <v>10574500</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101.8452666826232</v>
+      </c>
+      <c r="C60" t="n">
+        <v>102.7619926734798</v>
+      </c>
+      <c r="D60" t="n">
+        <v>101.4115445947565</v>
+      </c>
+      <c r="E60" t="n">
+        <v>101.9536972045898</v>
+      </c>
+      <c r="F60" t="n">
+        <v>10130200</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101.8255455445372</v>
+      </c>
+      <c r="C61" t="n">
+        <v>103.2449865221035</v>
+      </c>
+      <c r="D61" t="n">
+        <v>101.7663968434539</v>
+      </c>
+      <c r="E61" t="n">
+        <v>102.9788436889648</v>
+      </c>
+      <c r="F61" t="n">
+        <v>6525500</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B62" t="n">
+        <v>103.4224248942611</v>
+      </c>
+      <c r="C62" t="n">
+        <v>105.3051661613186</v>
+      </c>
+      <c r="D62" t="n">
+        <v>102.9788509675128</v>
+      </c>
+      <c r="E62" t="n">
+        <v>105.2460174560547</v>
+      </c>
+      <c r="F62" t="n">
+        <v>12628900</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B63" t="n">
+        <v>105.0094417410337</v>
+      </c>
+      <c r="C63" t="n">
+        <v>105.0488717030799</v>
+      </c>
+      <c r="D63" t="n">
+        <v>103.3238503461612</v>
+      </c>
+      <c r="E63" t="n">
+        <v>103.3337097167969</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8548200</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B64" t="n">
+        <v>103.4027062810859</v>
+      </c>
+      <c r="C64" t="n">
+        <v>104.339143401945</v>
+      </c>
+      <c r="D64" t="n">
+        <v>102.978843606061</v>
+      </c>
+      <c r="E64" t="n">
+        <v>104.230712890625</v>
+      </c>
+      <c r="F64" t="n">
+        <v>10177800</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B65" t="n">
+        <v>104.3292907185565</v>
+      </c>
+      <c r="C65" t="n">
+        <v>104.7038716073053</v>
+      </c>
+      <c r="D65" t="n">
+        <v>103.0182801694252</v>
+      </c>
+      <c r="E65" t="n">
+        <v>103.9645767211914</v>
+      </c>
+      <c r="F65" t="n">
+        <v>11471400</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B66" t="n">
+        <v>103.6787148109135</v>
+      </c>
+      <c r="C66" t="n">
+        <v>104.6545819518468</v>
+      </c>
+      <c r="D66" t="n">
+        <v>103.0675616662248</v>
+      </c>
+      <c r="E66" t="n">
+        <v>103.797004699707</v>
+      </c>
+      <c r="F66" t="n">
+        <v>10680100</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B67" t="n">
+        <v>103.7970053004195</v>
+      </c>
+      <c r="C67" t="n">
+        <v>106.5077532235307</v>
+      </c>
+      <c r="D67" t="n">
+        <v>103.3337126339174</v>
+      </c>
+      <c r="E67" t="n">
+        <v>106.0937423706055</v>
+      </c>
+      <c r="F67" t="n">
+        <v>13727700</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B68" t="n">
+        <v>106.0543107045445</v>
+      </c>
+      <c r="C68" t="n">
+        <v>106.2120305546496</v>
+      </c>
+      <c r="D68" t="n">
+        <v>105.0291617608474</v>
+      </c>
+      <c r="E68" t="n">
+        <v>105.4924468994141</v>
+      </c>
+      <c r="F68" t="n">
+        <v>8549400</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>105.5910275110776</v>
+      </c>
+      <c r="C69" t="n">
+        <v>108.1046256243346</v>
+      </c>
+      <c r="D69" t="n">
+        <v>105.0587342879123</v>
+      </c>
+      <c r="E69" t="n">
+        <v>107.2766189575195</v>
+      </c>
+      <c r="F69" t="n">
+        <v>11237900</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B70" t="n">
+        <v>107.6413280220333</v>
+      </c>
+      <c r="C70" t="n">
+        <v>109.9676431038136</v>
+      </c>
+      <c r="D70" t="n">
+        <v>107.5526162491543</v>
+      </c>
+      <c r="E70" t="n">
+        <v>109.8690719604492</v>
+      </c>
+      <c r="F70" t="n">
+        <v>13281400</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B71" t="n">
+        <v>110.1352293411146</v>
+      </c>
+      <c r="C71" t="n">
+        <v>111.7222421475927</v>
+      </c>
+      <c r="D71" t="n">
+        <v>109.5635061444599</v>
+      </c>
+      <c r="E71" t="n">
+        <v>110.007080078125</v>
+      </c>
+      <c r="F71" t="n">
+        <v>13059100</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B72" t="n">
+        <v>109.8582130022918</v>
+      </c>
+      <c r="C72" t="n">
+        <v>110.7017554968497</v>
+      </c>
+      <c r="D72" t="n">
+        <v>107.7245680705396</v>
+      </c>
+      <c r="E72" t="n">
+        <v>109.6498107910156</v>
+      </c>
+      <c r="F72" t="n">
+        <v>14318000</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B73" t="n">
+        <v>110.3742651303662</v>
+      </c>
+      <c r="C73" t="n">
+        <v>111.991867603266</v>
+      </c>
+      <c r="D73" t="n">
+        <v>110.0170020268064</v>
+      </c>
+      <c r="E73" t="n">
+        <v>110.7712249755859</v>
+      </c>
+      <c r="F73" t="n">
+        <v>15580200</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B74" t="n">
+        <v>110.2154802113721</v>
+      </c>
+      <c r="C74" t="n">
+        <v>111.2773434635197</v>
+      </c>
+      <c r="D74" t="n">
+        <v>109.6200442181698</v>
+      </c>
+      <c r="E74" t="n">
+        <v>109.7887496948242</v>
+      </c>
+      <c r="F74" t="n">
+        <v>12142500</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B75" t="n">
+        <v>109.6895108947102</v>
+      </c>
+      <c r="C75" t="n">
+        <v>111.9422536896534</v>
+      </c>
+      <c r="D75" t="n">
+        <v>109.5803467466885</v>
+      </c>
+      <c r="E75" t="n">
+        <v>111.0193252563477</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12913900</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B76" t="n">
+        <v>111.4659009625997</v>
+      </c>
+      <c r="C76" t="n">
+        <v>112.6170837765976</v>
+      </c>
+      <c r="D76" t="n">
+        <v>110.076545265884</v>
+      </c>
+      <c r="E76" t="n">
+        <v>110.3941116333008</v>
+      </c>
+      <c r="F76" t="n">
+        <v>21138400</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B77" t="n">
+        <v>110.5628188428948</v>
+      </c>
+      <c r="C77" t="n">
+        <v>111.9422483883379</v>
+      </c>
+      <c r="D77" t="n">
+        <v>110.3047938169375</v>
+      </c>
+      <c r="E77" t="n">
+        <v>111.5254364013672</v>
+      </c>
+      <c r="F77" t="n">
+        <v>8803300</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B78" t="n">
+        <v>111.4361261613625</v>
+      </c>
+      <c r="C78" t="n">
+        <v>112.4483665538656</v>
+      </c>
+      <c r="D78" t="n">
+        <v>111.1880272094238</v>
+      </c>
+      <c r="E78" t="n">
+        <v>112.3590545654297</v>
+      </c>
+      <c r="F78" t="n">
+        <v>7634500</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B79" t="n">
+        <v>112.0811837460467</v>
+      </c>
+      <c r="C79" t="n">
+        <v>113.6590894291559</v>
+      </c>
+      <c r="D79" t="n">
+        <v>111.9422489401646</v>
+      </c>
+      <c r="E79" t="n">
+        <v>113.6094741821289</v>
+      </c>
+      <c r="F79" t="n">
+        <v>4606700</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B80" t="n">
+        <v>113.2819819972415</v>
+      </c>
+      <c r="C80" t="n">
+        <v>113.8674918845297</v>
+      </c>
+      <c r="D80" t="n">
+        <v>112.4086688482299</v>
+      </c>
+      <c r="E80" t="n">
+        <v>112.6964645385742</v>
+      </c>
+      <c r="F80" t="n">
+        <v>5428900</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B81" t="n">
+        <v>112.4582910949776</v>
+      </c>
+      <c r="C81" t="n">
+        <v>113.6193923570513</v>
+      </c>
+      <c r="D81" t="n">
+        <v>112.4483650170496</v>
+      </c>
+      <c r="E81" t="n">
+        <v>113.3216781616211</v>
+      </c>
+      <c r="F81" t="n">
+        <v>7966000</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B82" t="n">
+        <v>113.2323587361736</v>
+      </c>
+      <c r="C82" t="n">
+        <v>114.4033860775522</v>
+      </c>
+      <c r="D82" t="n">
+        <v>113.2323587361736</v>
+      </c>
+      <c r="E82" t="n">
+        <v>113.9171142578125</v>
+      </c>
+      <c r="F82" t="n">
+        <v>6883900</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B83" t="n">
+        <v>113.8972648993226</v>
+      </c>
+      <c r="C83" t="n">
+        <v>114.0163551233871</v>
+      </c>
+      <c r="D83" t="n">
+        <v>112.6865483592072</v>
+      </c>
+      <c r="E83" t="n">
+        <v>112.9048690795898</v>
+      </c>
+      <c r="F83" t="n">
+        <v>6608000</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B84" t="n">
+        <v>112.5773868999257</v>
+      </c>
+      <c r="C84" t="n">
+        <v>112.5773868999257</v>
+      </c>
+      <c r="D84" t="n">
+        <v>110.7712267677642</v>
+      </c>
+      <c r="E84" t="n">
+        <v>110.9994735717773</v>
+      </c>
+      <c r="F84" t="n">
+        <v>8906200</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B85" t="n">
+        <v>110.5727405037633</v>
+      </c>
+      <c r="C85" t="n">
+        <v>115.1476858420111</v>
+      </c>
+      <c r="D85" t="n">
+        <v>110.5330437623775</v>
+      </c>
+      <c r="E85" t="n">
+        <v>113.2025909423828</v>
+      </c>
+      <c r="F85" t="n">
+        <v>12029000</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B86" t="n">
+        <v>112.9247239572814</v>
+      </c>
+      <c r="C86" t="n">
+        <v>113.8873491370408</v>
+      </c>
+      <c r="D86" t="n">
+        <v>112.2498944807456</v>
+      </c>
+      <c r="E86" t="n">
+        <v>113.6987915039062</v>
+      </c>
+      <c r="F86" t="n">
+        <v>7388300</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B87" t="n">
+        <v>113.58962345171</v>
+      </c>
+      <c r="C87" t="n">
+        <v>114.0957474345631</v>
+      </c>
+      <c r="D87" t="n">
+        <v>111.6544546516531</v>
+      </c>
+      <c r="E87" t="n">
+        <v>112.0514144897461</v>
+      </c>
+      <c r="F87" t="n">
+        <v>8296300</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B88" t="n">
+        <v>111.6941501294552</v>
+      </c>
+      <c r="C88" t="n">
+        <v>114.1155907288179</v>
+      </c>
+      <c r="D88" t="n">
+        <v>111.6941501294552</v>
+      </c>
+      <c r="E88" t="n">
+        <v>113.3018264770508</v>
+      </c>
+      <c r="F88" t="n">
+        <v>9778200</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B89" t="n">
+        <v>113.4407639362947</v>
+      </c>
+      <c r="C89" t="n">
+        <v>115.0980707124986</v>
+      </c>
+      <c r="D89" t="n">
+        <v>113.0338855865844</v>
+      </c>
+      <c r="E89" t="n">
+        <v>114.9988250732422</v>
+      </c>
+      <c r="F89" t="n">
+        <v>8935200</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B90" t="n">
+        <v>113.7583311963079</v>
+      </c>
+      <c r="C90" t="n">
+        <v>114.0659790519541</v>
+      </c>
+      <c r="D90" t="n">
+        <v>111.6941536254426</v>
+      </c>
+      <c r="E90" t="n">
+        <v>111.9620971679688</v>
+      </c>
+      <c r="F90" t="n">
+        <v>10833800</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B91" t="n">
+        <v>111.9819377501375</v>
+      </c>
+      <c r="C91" t="n">
+        <v>112.3590529975045</v>
+      </c>
+      <c r="D91" t="n">
+        <v>110.7612951636049</v>
+      </c>
+      <c r="E91" t="n">
+        <v>112.1208801269531</v>
+      </c>
+      <c r="F91" t="n">
+        <v>8945700</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B92" t="n">
+        <v>111.9521684493894</v>
+      </c>
+      <c r="C92" t="n">
+        <v>112.7262359666306</v>
+      </c>
+      <c r="D92" t="n">
+        <v>111.4063552989297</v>
+      </c>
+      <c r="E92" t="n">
+        <v>112.6666946411133</v>
+      </c>
+      <c r="F92" t="n">
+        <v>8950900</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B93" t="n">
+        <v>112.8453292583326</v>
+      </c>
+      <c r="C93" t="n">
+        <v>113.242289105796</v>
+      </c>
+      <c r="D93" t="n">
+        <v>111.3170387669949</v>
+      </c>
+      <c r="E93" t="n">
+        <v>112.5476150512695</v>
+      </c>
+      <c r="F93" t="n">
+        <v>7958500</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B94" t="n">
+        <v>112.339199834173</v>
+      </c>
+      <c r="C94" t="n">
+        <v>112.9842586087029</v>
+      </c>
+      <c r="D94" t="n">
+        <v>110.2750223556077</v>
+      </c>
+      <c r="E94" t="n">
+        <v>110.3544082641602</v>
+      </c>
+      <c r="F94" t="n">
+        <v>12049600</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B95" t="n">
+        <v>108.8261317696502</v>
+      </c>
+      <c r="C95" t="n">
+        <v>110.2452505565117</v>
+      </c>
+      <c r="D95" t="n">
+        <v>107.9726707390225</v>
+      </c>
+      <c r="E95" t="n">
+        <v>109.5009536743164</v>
+      </c>
+      <c r="F95" t="n">
+        <v>9818200</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B96" t="n">
+        <v>109.7292049082389</v>
+      </c>
+      <c r="C96" t="n">
+        <v>112.3888259939984</v>
+      </c>
+      <c r="D96" t="n">
+        <v>109.6597375040779</v>
+      </c>
+      <c r="E96" t="n">
+        <v>112.3292846679688</v>
+      </c>
+      <c r="F96" t="n">
+        <v>10041400</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B97" t="n">
+        <v>112.3094319821855</v>
+      </c>
+      <c r="C97" t="n">
+        <v>113.4209180149001</v>
+      </c>
+      <c r="D97" t="n">
+        <v>111.317036172348</v>
+      </c>
+      <c r="E97" t="n">
+        <v>112.3491287231445</v>
+      </c>
+      <c r="F97" t="n">
+        <v>12437700</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B98" t="n">
+        <v>111.8330891095483</v>
+      </c>
+      <c r="C98" t="n">
+        <v>112.0911065753488</v>
+      </c>
+      <c r="D98" t="n">
+        <v>109.7093626275885</v>
+      </c>
+      <c r="E98" t="n">
+        <v>110.1360931396484</v>
+      </c>
+      <c r="F98" t="n">
+        <v>10819800</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B99" t="n">
+        <v>110.8307664528259</v>
+      </c>
+      <c r="C99" t="n">
+        <v>111.5552187391887</v>
+      </c>
+      <c r="D99" t="n">
+        <v>110.2849457184854</v>
+      </c>
+      <c r="E99" t="n">
+        <v>110.4635772705078</v>
+      </c>
+      <c r="F99" t="n">
+        <v>8859800</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B100" t="n">
+        <v>110.6521373409646</v>
+      </c>
+      <c r="C100" t="n">
+        <v>110.9498591246939</v>
+      </c>
+      <c r="D100" t="n">
+        <v>109.1933142291742</v>
+      </c>
+      <c r="E100" t="n">
+        <v>109.7689056396484</v>
+      </c>
+      <c r="F100" t="n">
+        <v>8956900</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B101" t="n">
+        <v>109.4414091319104</v>
+      </c>
+      <c r="C101" t="n">
+        <v>110.5826658320299</v>
+      </c>
+      <c r="D101" t="n">
+        <v>108.1711437016965</v>
+      </c>
+      <c r="E101" t="n">
+        <v>108.7268829345703</v>
+      </c>
+      <c r="F101" t="n">
+        <v>9016600</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B102" t="n">
+        <v>108.7963528121511</v>
+      </c>
+      <c r="C102" t="n">
+        <v>110.8208412268483</v>
+      </c>
+      <c r="D102" t="n">
+        <v>107.932973280219</v>
+      </c>
+      <c r="E102" t="n">
+        <v>110.7315292358398</v>
+      </c>
+      <c r="F102" t="n">
+        <v>11079000</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B103" t="n">
+        <v>110.5132006888762</v>
+      </c>
+      <c r="C103" t="n">
+        <v>112.0911064308015</v>
+      </c>
+      <c r="D103" t="n">
+        <v>110.1460115045699</v>
+      </c>
+      <c r="E103" t="n">
+        <v>111.942253112793</v>
+      </c>
+      <c r="F103" t="n">
+        <v>17895200</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B104" t="n">
+        <v>103.219089824791</v>
+      </c>
+      <c r="C104" t="n">
+        <v>107.7841090146985</v>
+      </c>
+      <c r="D104" t="n">
+        <v>102.961064795438</v>
+      </c>
+      <c r="E104" t="n">
+        <v>103.6557388305664</v>
+      </c>
+      <c r="F104" t="n">
+        <v>37778500</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B105" t="n">
+        <v>103.9832294528008</v>
+      </c>
+      <c r="C105" t="n">
+        <v>104.1916316597105</v>
+      </c>
+      <c r="D105" t="n">
+        <v>101.5617813072958</v>
+      </c>
+      <c r="E105" t="n">
+        <v>103.427490234375</v>
+      </c>
+      <c r="F105" t="n">
+        <v>24827100</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B106" t="n">
+        <v>103.4076429857971</v>
+      </c>
+      <c r="C106" t="n">
+        <v>107.7741861743833</v>
+      </c>
+      <c r="D106" t="n">
+        <v>102.841977662662</v>
+      </c>
+      <c r="E106" t="n">
+        <v>106.2359771728516</v>
+      </c>
+      <c r="F106" t="n">
+        <v>19070400</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B107" t="n">
+        <v>106.2359762120697</v>
+      </c>
+      <c r="C107" t="n">
+        <v>107.5062416580512</v>
+      </c>
+      <c r="D107" t="n">
+        <v>104.0130041102228</v>
+      </c>
+      <c r="E107" t="n">
+        <v>104.1717910766602</v>
+      </c>
+      <c r="F107" t="n">
+        <v>11859500</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B108" t="n">
+        <v>105.3229638054753</v>
+      </c>
+      <c r="C108" t="n">
+        <v>108.1314457439972</v>
+      </c>
+      <c r="D108" t="n">
+        <v>104.5687484468834</v>
+      </c>
+      <c r="E108" t="n">
+        <v>107.873420715332</v>
+      </c>
+      <c r="F108" t="n">
+        <v>12105600</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B109" t="n">
+        <v>107.8635036441641</v>
+      </c>
+      <c r="C109" t="n">
+        <v>108.09175044183</v>
+      </c>
+      <c r="D109" t="n">
+        <v>105.9580979235442</v>
+      </c>
+      <c r="E109" t="n">
+        <v>106.3153610229492</v>
+      </c>
+      <c r="F109" t="n">
+        <v>10515400</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B110" t="n">
+        <v>106.7817856582252</v>
+      </c>
+      <c r="C110" t="n">
+        <v>110.265097006608</v>
+      </c>
+      <c r="D110" t="n">
+        <v>106.7817856582252</v>
+      </c>
+      <c r="E110" t="n">
+        <v>109.1238403320312</v>
+      </c>
+      <c r="F110" t="n">
+        <v>9815500</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B111" t="n">
+        <v>108.1016744764874</v>
+      </c>
+      <c r="C111" t="n">
+        <v>109.0345289485641</v>
+      </c>
+      <c r="D111" t="n">
+        <v>106.9802699515072</v>
+      </c>
+      <c r="E111" t="n">
+        <v>107.2978363037109</v>
+      </c>
+      <c r="F111" t="n">
+        <v>9374900</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B112" t="n">
+        <v>107.1092782571758</v>
+      </c>
+      <c r="C112" t="n">
+        <v>107.3375326210063</v>
+      </c>
+      <c r="D112" t="n">
+        <v>100.2518196922704</v>
+      </c>
+      <c r="E112" t="n">
+        <v>101.6014785766602</v>
+      </c>
+      <c r="F112" t="n">
+        <v>25319600</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B113" t="n">
+        <v>100.6289339445357</v>
+      </c>
+      <c r="C113" t="n">
+        <v>104.7175997261971</v>
+      </c>
+      <c r="D113" t="n">
+        <v>100.4304502450412</v>
+      </c>
+      <c r="E113" t="n">
+        <v>104.6481323242188</v>
+      </c>
+      <c r="F113" t="n">
+        <v>12845300</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B114" t="n">
+        <v>105.7596186239472</v>
+      </c>
+      <c r="C114" t="n">
+        <v>106.4642187235269</v>
+      </c>
+      <c r="D114" t="n">
+        <v>103.576350923035</v>
+      </c>
+      <c r="E114" t="n">
+        <v>104.6382141113281</v>
+      </c>
+      <c r="F114" t="n">
+        <v>10467400</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B115" t="n">
+        <v>105.1542604930163</v>
+      </c>
+      <c r="C115" t="n">
+        <v>106.9108053396402</v>
+      </c>
+      <c r="D115" t="n">
+        <v>105.0053996052954</v>
+      </c>
+      <c r="E115" t="n">
+        <v>106.2855911254883</v>
+      </c>
+      <c r="F115" t="n">
+        <v>8791600</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B116" t="n">
+        <v>106.2955144080048</v>
+      </c>
+      <c r="C116" t="n">
+        <v>106.9504916968191</v>
+      </c>
+      <c r="D116" t="n">
+        <v>104.6481337509456</v>
+      </c>
+      <c r="E116" t="n">
+        <v>105.1939544677734</v>
+      </c>
+      <c r="F116" t="n">
+        <v>7492900</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B117" t="n">
+        <v>104.8069236784645</v>
+      </c>
+      <c r="C117" t="n">
+        <v>105.3924335809217</v>
+      </c>
+      <c r="D117" t="n">
+        <v>103.8542245950799</v>
+      </c>
+      <c r="E117" t="n">
+        <v>104.7771530151367</v>
+      </c>
+      <c r="F117" t="n">
+        <v>9043600</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B118" t="n">
+        <v>104.1817160321379</v>
+      </c>
+      <c r="C118" t="n">
+        <v>104.3901182448065</v>
+      </c>
+      <c r="D118" t="n">
+        <v>102.1770722450568</v>
+      </c>
+      <c r="E118" t="n">
+        <v>103.6160507202148</v>
+      </c>
+      <c r="F118" t="n">
+        <v>10626500</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B119" t="n">
+        <v>103.6557367363695</v>
+      </c>
+      <c r="C119" t="n">
+        <v>106.4146033792047</v>
+      </c>
+      <c r="D119" t="n">
+        <v>103.1893170772804</v>
+      </c>
+      <c r="E119" t="n">
+        <v>105.2435760498047</v>
+      </c>
+      <c r="F119" t="n">
+        <v>13594800</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B120" t="n">
+        <v>105.193955544271</v>
+      </c>
+      <c r="C120" t="n">
+        <v>105.9084817367471</v>
+      </c>
+      <c r="D120" t="n">
+        <v>103.7152879117953</v>
+      </c>
+      <c r="E120" t="n">
+        <v>104.2511825561523</v>
+      </c>
+      <c r="F120" t="n">
+        <v>8556500</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B121" t="n">
+        <v>104.6679896339684</v>
+      </c>
+      <c r="C121" t="n">
+        <v>105.9580996730059</v>
+      </c>
+      <c r="D121" t="n">
+        <v>104.519128744862</v>
+      </c>
+      <c r="E121" t="n">
+        <v>104.7473831176758</v>
+      </c>
+      <c r="F121" t="n">
+        <v>9578500</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B122" t="n">
+        <v>103.9832293953731</v>
+      </c>
+      <c r="C122" t="n">
+        <v>105.5313644009208</v>
+      </c>
+      <c r="D122" t="n">
+        <v>103.1396944903344</v>
+      </c>
+      <c r="E122" t="n">
+        <v>105.2336502075195</v>
+      </c>
+      <c r="F122" t="n">
+        <v>13954000</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B123" t="n">
+        <v>103.8145288629893</v>
+      </c>
+      <c r="C123" t="n">
+        <v>103.8145288629893</v>
+      </c>
+      <c r="D123" t="n">
+        <v>102.0778361524432</v>
+      </c>
+      <c r="E123" t="n">
+        <v>103.5366592407227</v>
+      </c>
+      <c r="F123" t="n">
+        <v>14178600</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B124" t="n">
+        <v>102.0579794936243</v>
+      </c>
+      <c r="C124" t="n">
+        <v>103.5168025175497</v>
+      </c>
+      <c r="D124" t="n">
+        <v>101.3732315464965</v>
+      </c>
+      <c r="E124" t="n">
+        <v>102.5144882202148</v>
+      </c>
+      <c r="F124" t="n">
+        <v>13608400</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B125" t="n">
+        <v>102.3854784619134</v>
+      </c>
+      <c r="C125" t="n">
+        <v>103.0503818671043</v>
+      </c>
+      <c r="D125" t="n">
+        <v>101.8595098706018</v>
+      </c>
+      <c r="E125" t="n">
+        <v>102.2564697265625</v>
+      </c>
+      <c r="F125" t="n">
+        <v>9672300</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B126" t="n">
+        <v>102.3160040474863</v>
+      </c>
+      <c r="C126" t="n">
+        <v>103.7549824803676</v>
+      </c>
+      <c r="D126" t="n">
+        <v>100.8174842902717</v>
+      </c>
+      <c r="E126" t="n">
+        <v>101.6312561035156</v>
+      </c>
+      <c r="F126" t="n">
+        <v>11751500</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B127" t="n">
+        <v>100.6190147793836</v>
+      </c>
+      <c r="C127" t="n">
+        <v>101.0358192198888</v>
+      </c>
+      <c r="D127" t="n">
+        <v>99.18996233036073</v>
+      </c>
+      <c r="E127" t="n">
+        <v>100.7678756713867</v>
+      </c>
+      <c r="F127" t="n">
+        <v>10448600</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B128" t="n">
+        <v>99.78540292258373</v>
+      </c>
+      <c r="C128" t="n">
+        <v>101.0953651046626</v>
+      </c>
+      <c r="D128" t="n">
+        <v>97.70136563944882</v>
+      </c>
+      <c r="E128" t="n">
+        <v>100.886962890625</v>
+      </c>
+      <c r="F128" t="n">
+        <v>11715100</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B129" t="n">
+        <v>100.9762757982457</v>
+      </c>
+      <c r="C129" t="n">
+        <v>101.4625476354206</v>
+      </c>
+      <c r="D129" t="n">
+        <v>99.47775597353863</v>
+      </c>
+      <c r="E129" t="n">
+        <v>100.5495452880859</v>
+      </c>
+      <c r="F129" t="n">
+        <v>7833100</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B130" t="n">
+        <v>100.6289343352219</v>
+      </c>
+      <c r="C130" t="n">
+        <v>101.1152061509584</v>
+      </c>
+      <c r="D130" t="n">
+        <v>99.63653854803313</v>
+      </c>
+      <c r="E130" t="n">
+        <v>100.1228103637695</v>
+      </c>
+      <c r="F130" t="n">
+        <v>8152800</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B131" t="n">
+        <v>99.33882308016651</v>
+      </c>
+      <c r="C131" t="n">
+        <v>100.1128906318194</v>
+      </c>
+      <c r="D131" t="n">
+        <v>98.61437834957015</v>
+      </c>
+      <c r="E131" t="n">
+        <v>98.67391967773438</v>
+      </c>
+      <c r="F131" t="n">
+        <v>10309400</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B132" t="n">
+        <v>99.07087541929553</v>
+      </c>
+      <c r="C132" t="n">
+        <v>100.0037223311207</v>
+      </c>
+      <c r="D132" t="n">
+        <v>98.4059720444657</v>
+      </c>
+      <c r="E132" t="n">
+        <v>98.53498077392578</v>
+      </c>
+      <c r="F132" t="n">
+        <v>9551500</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B133" t="n">
+        <v>98.71361296789499</v>
+      </c>
+      <c r="C133" t="n">
+        <v>98.93194125870065</v>
+      </c>
+      <c r="D133" t="n">
+        <v>97.71129107436866</v>
+      </c>
+      <c r="E133" t="n">
+        <v>97.90977478027344</v>
+      </c>
+      <c r="F133" t="n">
+        <v>11578500</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B134" t="n">
+        <v>98.41588802886785</v>
+      </c>
+      <c r="C134" t="n">
+        <v>99.94417844396594</v>
+      </c>
+      <c r="D134" t="n">
+        <v>98.26702714707265</v>
+      </c>
+      <c r="E134" t="n">
+        <v>99.53730010986328</v>
+      </c>
+      <c r="F134" t="n">
+        <v>11785600</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B135" t="n">
+        <v>99.08079827635559</v>
+      </c>
+      <c r="C135" t="n">
+        <v>100.2518256851255</v>
+      </c>
+      <c r="D135" t="n">
+        <v>98.24718939454284</v>
+      </c>
+      <c r="E135" t="n">
+        <v>98.66399383544922</v>
+      </c>
+      <c r="F135" t="n">
+        <v>12615100</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B136" t="n">
+        <v>98.2769579779315</v>
+      </c>
+      <c r="C136" t="n">
+        <v>100.0136506829842</v>
+      </c>
+      <c r="D136" t="n">
+        <v>97.69144807163296</v>
+      </c>
+      <c r="E136" t="n">
+        <v>98.44566345214844</v>
+      </c>
+      <c r="F136" t="n">
+        <v>14793800</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B137" t="n">
+        <v>98.25711324225701</v>
+      </c>
+      <c r="C137" t="n">
+        <v>99.269353657388</v>
+      </c>
+      <c r="D137" t="n">
+        <v>97.64182510199821</v>
+      </c>
+      <c r="E137" t="n">
+        <v>98.75331115722656</v>
+      </c>
+      <c r="F137" t="n">
+        <v>27544200</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B138" t="n">
+        <v>99.45791247863863</v>
+      </c>
+      <c r="C138" t="n">
+        <v>99.83502017283372</v>
+      </c>
+      <c r="D138" t="n">
+        <v>97.11585768623267</v>
+      </c>
+      <c r="E138" t="n">
+        <v>97.20516967773438</v>
+      </c>
+      <c r="F138" t="n">
+        <v>11373000</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B139" t="n">
+        <v>96.99676871718921</v>
+      </c>
+      <c r="C139" t="n">
+        <v>97.30441658068045</v>
+      </c>
+      <c r="D139" t="n">
+        <v>95.5181010136908</v>
+      </c>
+      <c r="E139" t="n">
+        <v>95.65703582763672</v>
+      </c>
+      <c r="F139" t="n">
+        <v>9155700</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B140" t="n">
+        <v>96.08376214252051</v>
+      </c>
+      <c r="C140" t="n">
+        <v>96.44102524028141</v>
+      </c>
+      <c r="D140" t="n">
+        <v>94.33714339473161</v>
+      </c>
+      <c r="E140" t="n">
+        <v>95.22037506103516</v>
+      </c>
+      <c r="F140" t="n">
+        <v>8467500</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B141" t="n">
+        <v>94.3966920435457</v>
+      </c>
+      <c r="C141" t="n">
+        <v>95.66695746718439</v>
+      </c>
+      <c r="D141" t="n">
+        <v>93.87071590500793</v>
+      </c>
+      <c r="E141" t="n">
+        <v>94.02950286865234</v>
+      </c>
+      <c r="F141" t="n">
+        <v>8548800</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B142" t="n">
+        <v>93.47376126842354</v>
+      </c>
+      <c r="C142" t="n">
+        <v>93.47376126842354</v>
+      </c>
+      <c r="D142" t="n">
+        <v>91.48896970147202</v>
+      </c>
+      <c r="E142" t="n">
+        <v>91.71721649169922</v>
+      </c>
+      <c r="F142" t="n">
+        <v>12475900</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B143" t="n">
+        <v>92.18364921591858</v>
+      </c>
+      <c r="C143" t="n">
+        <v>94.46616268251262</v>
+      </c>
+      <c r="D143" t="n">
+        <v>92.18364921591858</v>
+      </c>
+      <c r="E143" t="n">
+        <v>93.60277557373047</v>
+      </c>
+      <c r="F143" t="n">
+        <v>10592600</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B144" t="n">
+        <v>94.61501738536155</v>
+      </c>
+      <c r="C144" t="n">
+        <v>96.15323399247868</v>
+      </c>
+      <c r="D144" t="n">
+        <v>93.47376820675542</v>
+      </c>
+      <c r="E144" t="n">
+        <v>95.64710998535156</v>
+      </c>
+      <c r="F144" t="n">
+        <v>11180200</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B145" t="n">
+        <v>96.52041860940267</v>
+      </c>
+      <c r="C145" t="n">
+        <v>97.61205248622655</v>
+      </c>
+      <c r="D145" t="n">
+        <v>95.75626959566054</v>
+      </c>
+      <c r="E145" t="n">
+        <v>95.82573699951172</v>
+      </c>
+      <c r="F145" t="n">
+        <v>8518600</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B146" t="n">
+        <v>95.26999653948798</v>
+      </c>
+      <c r="C146" t="n">
+        <v>96.43109780518201</v>
+      </c>
+      <c r="D146" t="n">
+        <v>94.36691272969546</v>
+      </c>
+      <c r="E146" t="n">
+        <v>95.87535858154297</v>
+      </c>
+      <c r="F146" t="n">
+        <v>6379100</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B147" t="n">
+        <v>95.76619510964362</v>
+      </c>
+      <c r="C147" t="n">
+        <v>96.4211799747073</v>
+      </c>
+      <c r="D147" t="n">
+        <v>95.389087429727</v>
+      </c>
+      <c r="E147" t="n">
+        <v>95.54786682128906</v>
+      </c>
+      <c r="F147" t="n">
+        <v>5882200</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B148" t="n">
+        <v>95.07152604625539</v>
+      </c>
+      <c r="C148" t="n">
+        <v>96.05399582384246</v>
+      </c>
+      <c r="D148" t="n">
+        <v>94.60509878245135</v>
+      </c>
+      <c r="E148" t="n">
+        <v>95.05167388916016</v>
+      </c>
+      <c r="F148" t="n">
+        <v>7913000</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B149" t="n">
+        <v>97.3540300760944</v>
+      </c>
+      <c r="C149" t="n">
+        <v>98.43574547532691</v>
+      </c>
+      <c r="D149" t="n">
+        <v>96.94715172012246</v>
+      </c>
+      <c r="E149" t="n">
+        <v>98.42581939697266</v>
+      </c>
+      <c r="F149" t="n">
+        <v>10821000</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B150" t="n">
+        <v>97.9097767670043</v>
+      </c>
+      <c r="C150" t="n">
+        <v>99.46783792592092</v>
+      </c>
+      <c r="D150" t="n">
+        <v>96.93722551678441</v>
+      </c>
+      <c r="E150" t="n">
+        <v>99.03118133544922</v>
+      </c>
+      <c r="F150" t="n">
+        <v>8918300</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B151" t="n">
+        <v>99.08079694980933</v>
+      </c>
+      <c r="C151" t="n">
+        <v>99.39837088687223</v>
+      </c>
+      <c r="D151" t="n">
+        <v>98.06855652524918</v>
+      </c>
+      <c r="E151" t="n">
+        <v>98.4158935546875</v>
+      </c>
+      <c r="F151" t="n">
+        <v>6359600</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B152" t="n">
+        <v>97.78075602521236</v>
+      </c>
+      <c r="C152" t="n">
+        <v>100.4999183711592</v>
+      </c>
+      <c r="D152" t="n">
+        <v>97.78075602521236</v>
+      </c>
+      <c r="E152" t="n">
+        <v>100.4106063842773</v>
+      </c>
+      <c r="F152" t="n">
+        <v>6790300</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B153" t="n">
+        <v>100.5693883478159</v>
+      </c>
+      <c r="C153" t="n">
+        <v>102.3160071037648</v>
+      </c>
+      <c r="D153" t="n">
+        <v>100.1327393373631</v>
+      </c>
+      <c r="E153" t="n">
+        <v>101.8098831176758</v>
+      </c>
+      <c r="F153" t="n">
+        <v>9997400</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B154" t="n">
+        <v>101.8198131278678</v>
+      </c>
+      <c r="C154" t="n">
+        <v>102.5938806827324</v>
+      </c>
+      <c r="D154" t="n">
+        <v>101.0159749087976</v>
+      </c>
+      <c r="E154" t="n">
+        <v>102.2564697265625</v>
+      </c>
+      <c r="F154" t="n">
+        <v>7035300</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B155" t="n">
+        <v>102.832054706031</v>
+      </c>
+      <c r="C155" t="n">
+        <v>103.7351309397506</v>
+      </c>
+      <c r="D155" t="n">
+        <v>101.9984383035261</v>
+      </c>
+      <c r="E155" t="n">
+        <v>103.1099243164062</v>
+      </c>
+      <c r="F155" t="n">
+        <v>8145900</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B156" t="n">
+        <v>103.8939187225915</v>
+      </c>
+      <c r="C156" t="n">
+        <v>105.5214472288459</v>
+      </c>
+      <c r="D156" t="n">
+        <v>103.8939187225915</v>
+      </c>
+      <c r="E156" t="n">
+        <v>105.4817504882812</v>
+      </c>
+      <c r="F156" t="n">
+        <v>10506200</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B157" t="n">
+        <v>105.1046425751499</v>
+      </c>
+      <c r="C157" t="n">
+        <v>106.2955145039117</v>
+      </c>
+      <c r="D157" t="n">
+        <v>105.1046425751499</v>
+      </c>
+      <c r="E157" t="n">
+        <v>105.4916763305664</v>
+      </c>
+      <c r="F157" t="n">
+        <v>6423400</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B158" t="n">
+        <v>105.3825171192469</v>
+      </c>
+      <c r="C158" t="n">
+        <v>106.0672651032121</v>
+      </c>
+      <c r="D158" t="n">
+        <v>103.1793971336853</v>
+      </c>
+      <c r="E158" t="n">
+        <v>103.4969635009766</v>
+      </c>
+      <c r="F158" t="n">
+        <v>7784500</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B159" t="n">
+        <v>104.2313285377519</v>
+      </c>
+      <c r="C159" t="n">
+        <v>105.4718232743649</v>
+      </c>
+      <c r="D159" t="n">
+        <v>103.437416449147</v>
+      </c>
+      <c r="E159" t="n">
+        <v>104.0229263305664</v>
+      </c>
+      <c r="F159" t="n">
+        <v>6886600</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B160" t="n">
+        <v>104.1420232238167</v>
+      </c>
+      <c r="C160" t="n">
+        <v>104.4000406941716</v>
+      </c>
+      <c r="D160" t="n">
+        <v>101.7701977411496</v>
+      </c>
+      <c r="E160" t="n">
+        <v>102.8618316650391</v>
+      </c>
+      <c r="F160" t="n">
+        <v>6147000</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B161" t="n">
+        <v>102.81220477355</v>
+      </c>
+      <c r="C161" t="n">
+        <v>102.851901514659</v>
+      </c>
+      <c r="D161" t="n">
+        <v>101.1946023230963</v>
+      </c>
+      <c r="E161" t="n">
+        <v>101.8198089599609</v>
+      </c>
+      <c r="F161" t="n">
+        <v>5974500</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B162" t="n">
+        <v>101.839659785339</v>
+      </c>
+      <c r="C162" t="n">
+        <v>103.0206056395392</v>
+      </c>
+      <c r="D162" t="n">
+        <v>101.2839129884539</v>
+      </c>
+      <c r="E162" t="n">
+        <v>101.5717086791992</v>
+      </c>
+      <c r="F162" t="n">
+        <v>6524300</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B163" t="n">
+        <v>101.8793558222072</v>
+      </c>
+      <c r="C163" t="n">
+        <v>102.5045624465828</v>
+      </c>
+      <c r="D163" t="n">
+        <v>99.84494141643668</v>
+      </c>
+      <c r="E163" t="n">
+        <v>100.6984024047852</v>
+      </c>
+      <c r="F163" t="n">
+        <v>6409300</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B164" t="n">
+        <v>100.1724381261774</v>
+      </c>
+      <c r="C164" t="n">
+        <v>100.7083327862765</v>
+      </c>
+      <c r="D164" t="n">
+        <v>99.83501960476121</v>
+      </c>
+      <c r="E164" t="n">
+        <v>100.5297012329102</v>
+      </c>
+      <c r="F164" t="n">
+        <v>5533700</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B165" t="n">
+        <v>100.1426666812253</v>
+      </c>
+      <c r="C165" t="n">
+        <v>103.328256381923</v>
+      </c>
+      <c r="D165" t="n">
+        <v>99.65638727390106</v>
+      </c>
+      <c r="E165" t="n">
+        <v>102.961067199707</v>
+      </c>
+      <c r="F165" t="n">
+        <v>9203500</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B166" t="n">
+        <v>103.6061276781693</v>
+      </c>
+      <c r="C166" t="n">
+        <v>104.0328581941516</v>
+      </c>
+      <c r="D166" t="n">
+        <v>102.1870013177053</v>
+      </c>
+      <c r="E166" t="n">
+        <v>102.2961654663086</v>
+      </c>
+      <c r="F166" t="n">
+        <v>5956900</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B167" t="n">
+        <v>101.9587457902329</v>
+      </c>
+      <c r="C167" t="n">
+        <v>102.2663936470847</v>
+      </c>
+      <c r="D167" t="n">
+        <v>100.4999227039044</v>
+      </c>
+      <c r="E167" t="n">
+        <v>100.5396194458008</v>
+      </c>
+      <c r="F167" t="n">
+        <v>8400100</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B168" t="n">
+        <v>100.7579458156174</v>
+      </c>
+      <c r="C168" t="n">
+        <v>100.9564295213072</v>
+      </c>
+      <c r="D168" t="n">
+        <v>99.29912275715898</v>
+      </c>
+      <c r="E168" t="n">
+        <v>99.71593475341797</v>
+      </c>
+      <c r="F168" t="n">
+        <v>14314700</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B169" t="n">
+        <v>105.7099984223796</v>
+      </c>
+      <c r="C169" t="n">
+        <v>108.3100781720615</v>
+      </c>
+      <c r="D169" t="n">
+        <v>104.5092004000206</v>
+      </c>
+      <c r="E169" t="n">
+        <v>107.2382888793945</v>
+      </c>
+      <c r="F169" t="n">
+        <v>23219500</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B170" t="n">
+        <v>108.2207663660894</v>
+      </c>
+      <c r="C170" t="n">
+        <v>109.6398926806152</v>
+      </c>
+      <c r="D170" t="n">
+        <v>106.2756639110559</v>
+      </c>
+      <c r="E170" t="n">
+        <v>107.8337326049805</v>
+      </c>
+      <c r="F170" t="n">
+        <v>14309200</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B171" t="n">
+        <v>108.2009150377847</v>
+      </c>
+      <c r="C171" t="n">
+        <v>108.3795465882309</v>
+      </c>
+      <c r="D171" t="n">
+        <v>106.7222473860446</v>
+      </c>
+      <c r="E171" t="n">
+        <v>107.1985931396484</v>
+      </c>
+      <c r="F171" t="n">
+        <v>8370000</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B172" t="n">
+        <v>107.1787478525936</v>
+      </c>
+      <c r="C172" t="n">
+        <v>107.5657816141287</v>
+      </c>
+      <c r="D172" t="n">
+        <v>103.5862722822083</v>
+      </c>
+      <c r="E172" t="n">
+        <v>103.9236907958984</v>
+      </c>
+      <c r="F172" t="n">
+        <v>10562300</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B173" t="n">
+        <v>104.1916361796018</v>
+      </c>
+      <c r="C173" t="n">
+        <v>105.4619016318964</v>
+      </c>
+      <c r="D173" t="n">
+        <v>103.4274947211174</v>
+      </c>
+      <c r="E173" t="n">
+        <v>105.3527450561523</v>
+      </c>
+      <c r="F173" t="n">
+        <v>8178500</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B174" t="n">
+        <v>104.5489005402277</v>
+      </c>
+      <c r="C174" t="n">
+        <v>105.0748691255691</v>
+      </c>
+      <c r="D174" t="n">
+        <v>103.0702328542224</v>
+      </c>
+      <c r="E174" t="n">
+        <v>104.1023254394531</v>
+      </c>
+      <c r="F174" t="n">
+        <v>7605900</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B175" t="n">
+        <v>104.7374526473249</v>
+      </c>
+      <c r="C175" t="n">
+        <v>105.4817494902667</v>
+      </c>
+      <c r="D175" t="n">
+        <v>104.0526971289773</v>
+      </c>
+      <c r="E175" t="n">
+        <v>104.6183624267578</v>
+      </c>
+      <c r="F175" t="n">
+        <v>6144600</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B176" t="n">
+        <v>104.2313280181917</v>
+      </c>
+      <c r="C176" t="n">
+        <v>104.6183617683755</v>
+      </c>
+      <c r="D176" t="n">
+        <v>101.5220917669058</v>
+      </c>
+      <c r="E176" t="n">
+        <v>101.9388961791992</v>
+      </c>
+      <c r="F176" t="n">
+        <v>9258600</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B177" t="n">
+        <v>101.9091260836407</v>
+      </c>
+      <c r="C177" t="n">
+        <v>103.9038361698679</v>
+      </c>
+      <c r="D177" t="n">
+        <v>101.7701912787705</v>
+      </c>
+      <c r="E177" t="n">
+        <v>103.1198501586914</v>
+      </c>
+      <c r="F177" t="n">
+        <v>9037200</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B178" t="n">
+        <v>102.9213691252704</v>
+      </c>
+      <c r="C178" t="n">
+        <v>103.1396974161188</v>
+      </c>
+      <c r="D178" t="n">
+        <v>101.1946025261468</v>
+      </c>
+      <c r="E178" t="n">
+        <v>101.5121688842773</v>
+      </c>
+      <c r="F178" t="n">
+        <v>7032600</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B179" t="n">
+        <v>102.1274576654748</v>
+      </c>
+      <c r="C179" t="n">
+        <v>104.0626264896183</v>
+      </c>
+      <c r="D179" t="n">
+        <v>100.8274139902545</v>
+      </c>
+      <c r="E179" t="n">
+        <v>103.2885589599609</v>
+      </c>
+      <c r="F179" t="n">
+        <v>7941400</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B180" t="n">
+        <v>102.822129060906</v>
+      </c>
+      <c r="C180" t="n">
+        <v>103.8244509351605</v>
+      </c>
+      <c r="D180" t="n">
+        <v>101.8098811087023</v>
+      </c>
+      <c r="E180" t="n">
+        <v>102.7923583984375</v>
+      </c>
+      <c r="F180" t="n">
+        <v>8611200</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B181" t="n">
+        <v>103.2488588874603</v>
+      </c>
+      <c r="C181" t="n">
+        <v>103.7053600422387</v>
+      </c>
+      <c r="D181" t="n">
+        <v>102.1969217730311</v>
+      </c>
+      <c r="E181" t="n">
+        <v>102.2167663574219</v>
+      </c>
+      <c r="F181" t="n">
+        <v>5693300</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B182" t="n">
+        <v>102.3160049896206</v>
+      </c>
+      <c r="C182" t="n">
+        <v>103.0106865892155</v>
+      </c>
+      <c r="D182" t="n">
+        <v>101.571708143084</v>
+      </c>
+      <c r="E182" t="n">
+        <v>102.4946365356445</v>
+      </c>
+      <c r="F182" t="n">
+        <v>6714400</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B183" t="n">
+        <v>102.5144889184559</v>
+      </c>
+      <c r="C183" t="n">
+        <v>104.4496576951832</v>
+      </c>
+      <c r="D183" t="n">
+        <v>102.4747921779873</v>
+      </c>
+      <c r="E183" t="n">
+        <v>103.3877944946289</v>
+      </c>
+      <c r="F183" t="n">
+        <v>7360100</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B184" t="n">
+        <v>103.0206090569662</v>
+      </c>
+      <c r="C184" t="n">
+        <v>103.6160526141937</v>
+      </c>
+      <c r="D184" t="n">
+        <v>102.3160089237181</v>
+      </c>
+      <c r="E184" t="n">
+        <v>102.9412231445312</v>
+      </c>
+      <c r="F184" t="n">
+        <v>6511100</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B185" t="n">
+        <v>102.8419796873618</v>
+      </c>
+      <c r="C185" t="n">
+        <v>102.9709959941437</v>
+      </c>
+      <c r="D185" t="n">
+        <v>101.0556716918945</v>
+      </c>
+      <c r="E185" t="n">
+        <v>101.0556716918945</v>
+      </c>
+      <c r="F185" t="n">
+        <v>13340300</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B186" t="n">
+        <v>100.8869633557317</v>
+      </c>
+      <c r="C186" t="n">
+        <v>102.2266962072239</v>
+      </c>
+      <c r="D186" t="n">
+        <v>99.53730442598828</v>
+      </c>
+      <c r="E186" t="n">
+        <v>102.0679092407227</v>
+      </c>
+      <c r="F186" t="n">
+        <v>8219000</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B187" t="n">
+        <v>101.5717095216456</v>
+      </c>
+      <c r="C187" t="n">
+        <v>101.7106443291744</v>
+      </c>
+      <c r="D187" t="n">
+        <v>99.32889287365569</v>
+      </c>
+      <c r="E187" t="n">
+        <v>100.6388626098633</v>
+      </c>
+      <c r="F187" t="n">
+        <v>8397400</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B188" t="n">
+        <v>99.67623490973834</v>
+      </c>
+      <c r="C188" t="n">
+        <v>100.4999176557305</v>
+      </c>
+      <c r="D188" t="n">
+        <v>98.495281504625</v>
+      </c>
+      <c r="E188" t="n">
+        <v>98.63421630859375</v>
+      </c>
+      <c r="F188" t="n">
+        <v>7471600</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B189" t="n">
+        <v>99.77547422442305</v>
+      </c>
+      <c r="C189" t="n">
+        <v>100.6984026174289</v>
+      </c>
+      <c r="D189" t="n">
+        <v>98.25710986817649</v>
+      </c>
+      <c r="E189" t="n">
+        <v>98.5845947265625</v>
+      </c>
+      <c r="F189" t="n">
+        <v>9568000</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B190" t="n">
+        <v>98.92201919170897</v>
+      </c>
+      <c r="C190" t="n">
+        <v>99.43806170522778</v>
+      </c>
+      <c r="D190" t="n">
+        <v>98.33650169977196</v>
+      </c>
+      <c r="E190" t="n">
+        <v>98.95178985595703</v>
+      </c>
+      <c r="F190" t="n">
+        <v>9501600</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B191" t="n">
+        <v>98.76323055949389</v>
+      </c>
+      <c r="C191" t="n">
+        <v>99.08079692509821</v>
+      </c>
+      <c r="D191" t="n">
+        <v>97.66167814394407</v>
+      </c>
+      <c r="E191" t="n">
+        <v>98.11817932128906</v>
+      </c>
+      <c r="F191" t="n">
+        <v>7559200</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B192" t="n">
+        <v>98.29680690142362</v>
+      </c>
+      <c r="C192" t="n">
+        <v>99.32889186938023</v>
+      </c>
+      <c r="D192" t="n">
+        <v>97.7609122614967</v>
+      </c>
+      <c r="E192" t="n">
+        <v>98.57467651367188</v>
+      </c>
+      <c r="F192" t="n">
+        <v>8616300</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B193" t="n">
+        <v>98.7334588011272</v>
+      </c>
+      <c r="C193" t="n">
+        <v>99.00140991464168</v>
+      </c>
+      <c r="D193" t="n">
+        <v>97.20516831754395</v>
+      </c>
+      <c r="E193" t="n">
+        <v>97.86015319824219</v>
+      </c>
+      <c r="F193" t="n">
+        <v>7041400</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B194" t="n">
+        <v>98.07848356908464</v>
+      </c>
+      <c r="C194" t="n">
+        <v>99.97395570346617</v>
+      </c>
+      <c r="D194" t="n">
+        <v>97.35403126794252</v>
+      </c>
+      <c r="E194" t="n">
+        <v>99.57699584960938</v>
+      </c>
+      <c r="F194" t="n">
+        <v>9264400</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B195" t="n">
+        <v>100.2915220505157</v>
+      </c>
+      <c r="C195" t="n">
+        <v>100.9961221945534</v>
+      </c>
+      <c r="D195" t="n">
+        <v>98.78308369184245</v>
+      </c>
+      <c r="E195" t="n">
+        <v>99.27928161621094</v>
+      </c>
+      <c r="F195" t="n">
+        <v>8257200</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B196" t="n">
+        <v>100.1128870298928</v>
+      </c>
+      <c r="C196" t="n">
+        <v>101.6213329077368</v>
+      </c>
+      <c r="D196" t="n">
+        <v>99.82509133515438</v>
+      </c>
+      <c r="E196" t="n">
+        <v>100.9167327880859</v>
+      </c>
+      <c r="F196" t="n">
+        <v>10265100</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B197" t="n">
+        <v>100.658710438741</v>
+      </c>
+      <c r="C197" t="n">
+        <v>101.1549083591584</v>
+      </c>
+      <c r="D197" t="n">
+        <v>99.28920690408536</v>
+      </c>
+      <c r="E197" t="n">
+        <v>100.5098495483398</v>
+      </c>
+      <c r="F197" t="n">
+        <v>10694600</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B198" t="n">
+        <v>99.90448284246082</v>
+      </c>
+      <c r="C198" t="n">
+        <v>101.581634158465</v>
+      </c>
+      <c r="D198" t="n">
+        <v>99.67623604963576</v>
+      </c>
+      <c r="E198" t="n">
+        <v>100.0930404663086</v>
+      </c>
+      <c r="F198" t="n">
+        <v>11168700</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B199" t="n">
+        <v>101.0258948980948</v>
+      </c>
+      <c r="C199" t="n">
+        <v>103.4274909034028</v>
+      </c>
+      <c r="D199" t="n">
+        <v>100.0334991036985</v>
+      </c>
+      <c r="E199" t="n">
+        <v>103.0999984741211</v>
+      </c>
+      <c r="F199" t="n">
+        <v>22943600</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B200" t="n">
+        <v>102.623658522444</v>
+      </c>
+      <c r="C200" t="n">
+        <v>103.5168087306858</v>
+      </c>
+      <c r="D200" t="n">
+        <v>100.7381048924391</v>
+      </c>
+      <c r="E200" t="n">
+        <v>101.6709518432617</v>
+      </c>
+      <c r="F200" t="n">
+        <v>17396300</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B201" t="n">
+        <v>101.2442170259669</v>
+      </c>
+      <c r="C201" t="n">
+        <v>103.2488607985985</v>
+      </c>
+      <c r="D201" t="n">
+        <v>101.025896308111</v>
+      </c>
+      <c r="E201" t="n">
+        <v>102.7427368164062</v>
+      </c>
+      <c r="F201" t="n">
+        <v>14457400</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B202" t="n">
+        <v>102.3160060444983</v>
+      </c>
+      <c r="C202" t="n">
+        <v>103.7351323493811</v>
+      </c>
+      <c r="D202" t="n">
+        <v>100.2716731077754</v>
+      </c>
+      <c r="E202" t="n">
+        <v>100.3510665893555</v>
+      </c>
+      <c r="F202" t="n">
+        <v>12215500</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B203" t="n">
+        <v>100.3411416176147</v>
+      </c>
+      <c r="C203" t="n">
+        <v>100.8075688628163</v>
+      </c>
+      <c r="D203" t="n">
+        <v>97.24486394426569</v>
+      </c>
+      <c r="E203" t="n">
+        <v>97.30441284179688</v>
+      </c>
+      <c r="F203" t="n">
+        <v>12054400</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B204" t="n">
+        <v>97.30440945370802</v>
+      </c>
+      <c r="C204" t="n">
+        <v>98.69375749140566</v>
+      </c>
+      <c r="D204" t="n">
+        <v>97.15554857213215</v>
+      </c>
+      <c r="E204" t="n">
+        <v>98.03878021240234</v>
+      </c>
+      <c r="F204" t="n">
+        <v>13921400</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B205" t="n">
+        <v>98.95178655891404</v>
+      </c>
+      <c r="C205" t="n">
+        <v>99.27927899748993</v>
+      </c>
+      <c r="D205" t="n">
+        <v>97.75098852218167</v>
+      </c>
+      <c r="E205" t="n">
+        <v>97.87999725341797</v>
+      </c>
+      <c r="F205" t="n">
+        <v>10418100</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B206" t="n">
+        <v>97.41000366210938</v>
+      </c>
+      <c r="C206" t="n">
+        <v>97.59999847412109</v>
+      </c>
+      <c r="D206" t="n">
+        <v>95.98999786376953</v>
+      </c>
+      <c r="E206" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="F206" t="n">
+        <v>12717800</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B207" t="n">
+        <v>96.55000305175781</v>
+      </c>
+      <c r="C207" t="n">
+        <v>97.76000213623047</v>
+      </c>
+      <c r="D207" t="n">
+        <v>95.65000152587891</v>
+      </c>
+      <c r="E207" t="n">
+        <v>95.70999908447266</v>
+      </c>
+      <c r="F207" t="n">
+        <v>11590400</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B208" t="n">
+        <v>96.40000152587891</v>
+      </c>
+      <c r="C208" t="n">
+        <v>99.51999664306641</v>
+      </c>
+      <c r="D208" t="n">
+        <v>95.76999664306641</v>
+      </c>
+      <c r="E208" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F208" t="n">
+        <v>11297800</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B209" t="n">
+        <v>98.84999847412109</v>
+      </c>
+      <c r="C209" t="n">
+        <v>99.44000244140625</v>
+      </c>
+      <c r="D209" t="n">
+        <v>97.01999664306641</v>
+      </c>
+      <c r="E209" t="n">
+        <v>97.41000366210938</v>
+      </c>
+      <c r="F209" t="n">
+        <v>10171900</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B210" t="n">
+        <v>98.13999938964844</v>
+      </c>
+      <c r="C210" t="n">
+        <v>99.04000091552734</v>
+      </c>
+      <c r="D210" t="n">
+        <v>96.91999816894531</v>
+      </c>
+      <c r="E210" t="n">
+        <v>97.48000335693359</v>
+      </c>
+      <c r="F210" t="n">
+        <v>9936400</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B211" t="n">
+        <v>97.30000305175781</v>
+      </c>
+      <c r="C211" t="n">
+        <v>97.66000366210938</v>
+      </c>
+      <c r="D211" t="n">
+        <v>96.63999938964844</v>
+      </c>
+      <c r="E211" t="n">
+        <v>96.69999694824219</v>
+      </c>
+      <c r="F211" t="n">
+        <v>8720800</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B212" t="n">
+        <v>96.33999633789062</v>
+      </c>
+      <c r="C212" t="n">
+        <v>96.55000305175781</v>
+      </c>
+      <c r="D212" t="n">
+        <v>94.77999877929688</v>
+      </c>
+      <c r="E212" t="n">
+        <v>96.16999816894531</v>
+      </c>
+      <c r="F212" t="n">
+        <v>11448100</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B213" t="n">
+        <v>96.88999938964844</v>
+      </c>
+      <c r="C213" t="n">
+        <v>97.05000305175781</v>
+      </c>
+      <c r="D213" t="n">
+        <v>95.51999664306641</v>
+      </c>
+      <c r="E213" t="n">
+        <v>95.62000274658203</v>
+      </c>
+      <c r="F213" t="n">
+        <v>10678900</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B214" t="n">
+        <v>96.09999847412109</v>
+      </c>
+      <c r="C214" t="n">
+        <v>97.54000091552734</v>
+      </c>
+      <c r="D214" t="n">
+        <v>95.83000183105469</v>
+      </c>
+      <c r="E214" t="n">
+        <v>96</v>
+      </c>
+      <c r="F214" t="n">
+        <v>9304200</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B215" t="n">
+        <v>95.51000213623047</v>
+      </c>
+      <c r="C215" t="n">
+        <v>96.69000244140625</v>
+      </c>
+      <c r="D215" t="n">
+        <v>95.12999725341797</v>
+      </c>
+      <c r="E215" t="n">
+        <v>95.87000274658203</v>
+      </c>
+      <c r="F215" t="n">
+        <v>7651600</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B216" t="n">
+        <v>96.09999847412109</v>
+      </c>
+      <c r="C216" t="n">
+        <v>97.90000152587891</v>
+      </c>
+      <c r="D216" t="n">
+        <v>96.09999847412109</v>
+      </c>
+      <c r="E216" t="n">
+        <v>97.15000152587891</v>
+      </c>
+      <c r="F216" t="n">
+        <v>10219200</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B217" t="n">
+        <v>97.27999877929688</v>
+      </c>
+      <c r="C217" t="n">
+        <v>99.84999847412109</v>
+      </c>
+      <c r="D217" t="n">
+        <v>97.27999877929688</v>
+      </c>
+      <c r="E217" t="n">
+        <v>99.70999908447266</v>
+      </c>
+      <c r="F217" t="n">
+        <v>7480000</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B218" t="n">
+        <v>99.01000213623047</v>
+      </c>
+      <c r="C218" t="n">
+        <v>99.79000091552734</v>
+      </c>
+      <c r="D218" t="n">
+        <v>97.05000305175781</v>
+      </c>
+      <c r="E218" t="n">
+        <v>97.66999816894531</v>
+      </c>
+      <c r="F218" t="n">
+        <v>10496500</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B219" t="n">
+        <v>97.84999847412109</v>
+      </c>
+      <c r="C219" t="n">
+        <v>98.38999938964844</v>
+      </c>
+      <c r="D219" t="n">
+        <v>96</v>
+      </c>
+      <c r="E219" t="n">
+        <v>96.41000366210938</v>
+      </c>
+      <c r="F219" t="n">
+        <v>9861700</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B220" t="n">
+        <v>96</v>
+      </c>
+      <c r="C220" t="n">
+        <v>96.88999938964844</v>
+      </c>
+      <c r="D220" t="n">
+        <v>95.83999633789062</v>
+      </c>
+      <c r="E220" t="n">
+        <v>96.13999938964844</v>
+      </c>
+      <c r="F220" t="n">
+        <v>9745400</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B221" t="n">
+        <v>97.12000274658203</v>
+      </c>
+      <c r="C221" t="n">
+        <v>97.30000305175781</v>
+      </c>
+      <c r="D221" t="n">
+        <v>95.65000152587891</v>
+      </c>
+      <c r="E221" t="n">
+        <v>95.87000274658203</v>
+      </c>
+      <c r="F221" t="n">
+        <v>9119200</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B222" t="n">
+        <v>94.80999755859375</v>
+      </c>
+      <c r="C222" t="n">
+        <v>94.81999969482422</v>
+      </c>
+      <c r="D222" t="n">
+        <v>92.48999786376953</v>
+      </c>
+      <c r="E222" t="n">
+        <v>92.83000183105469</v>
+      </c>
+      <c r="F222" t="n">
+        <v>13562500</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B223" t="n">
+        <v>93.26000213623047</v>
+      </c>
+      <c r="C223" t="n">
+        <v>96.29000091552734</v>
+      </c>
+      <c r="D223" t="n">
+        <v>93</v>
+      </c>
+      <c r="E223" t="n">
+        <v>94.84999847412109</v>
+      </c>
+      <c r="F223" t="n">
+        <v>12153100</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B224" t="n">
+        <v>95.51000213623047</v>
+      </c>
+      <c r="C224" t="n">
+        <v>97.19000244140625</v>
+      </c>
+      <c r="D224" t="n">
+        <v>95.51000213623047</v>
+      </c>
+      <c r="E224" t="n">
+        <v>96.65000152587891</v>
+      </c>
+      <c r="F224" t="n">
+        <v>10593900</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B225" t="n">
+        <v>97</v>
+      </c>
+      <c r="C225" t="n">
+        <v>99.23000335693359</v>
+      </c>
+      <c r="D225" t="n">
+        <v>96.97000122070312</v>
+      </c>
+      <c r="E225" t="n">
+        <v>98.88999938964844</v>
+      </c>
+      <c r="F225" t="n">
+        <v>11389300</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B226" t="n">
+        <v>98.33999633789062</v>
+      </c>
+      <c r="C226" t="n">
+        <v>99.41000366210938</v>
+      </c>
+      <c r="D226" t="n">
+        <v>97.98999786376953</v>
+      </c>
+      <c r="E226" t="n">
+        <v>98.48000335693359</v>
+      </c>
+      <c r="F226" t="n">
+        <v>11070100</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B227" t="n">
+        <v>97.41000366210938</v>
+      </c>
+      <c r="C227" t="n">
+        <v>97.48000335693359</v>
+      </c>
+      <c r="D227" t="n">
+        <v>94.45999908447266</v>
+      </c>
+      <c r="E227" t="n">
+        <v>96.16000366210938</v>
+      </c>
+      <c r="F227" t="n">
+        <v>21112400</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B228" t="n">
+        <v>96.08000183105469</v>
+      </c>
+      <c r="C228" t="n">
+        <v>96.58999633789062</v>
+      </c>
+      <c r="D228" t="n">
+        <v>95.59999847412109</v>
+      </c>
+      <c r="E228" t="n">
+        <v>96.19000244140625</v>
+      </c>
+      <c r="F228" t="n">
+        <v>11193000</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B229" t="n">
+        <v>97.62000274658203</v>
+      </c>
+      <c r="C229" t="n">
+        <v>99.05000305175781</v>
+      </c>
+      <c r="D229" t="n">
+        <v>97.20999908447266</v>
+      </c>
+      <c r="E229" t="n">
+        <v>98.13999938964844</v>
+      </c>
+      <c r="F229" t="n">
+        <v>11480300</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B230" t="n">
+        <v>97.87000274658203</v>
+      </c>
+      <c r="C230" t="n">
+        <v>98.56999969482422</v>
+      </c>
+      <c r="D230" t="n">
+        <v>97.37999725341797</v>
+      </c>
+      <c r="E230" t="n">
+        <v>98.18000030517578</v>
+      </c>
+      <c r="F230" t="n">
+        <v>16796800</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B231" t="n">
+        <v>101.9899978637695</v>
+      </c>
+      <c r="C231" t="n">
+        <v>103.2099990844727</v>
+      </c>
+      <c r="D231" t="n">
+        <v>99.69000244140625</v>
+      </c>
+      <c r="E231" t="n">
+        <v>101.7600021362305</v>
+      </c>
+      <c r="F231" t="n">
+        <v>20809000</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B232" t="n">
+        <v>102.5400009155273</v>
+      </c>
+      <c r="C232" t="n">
+        <v>104.7300033569336</v>
+      </c>
+      <c r="D232" t="n">
+        <v>102.5199966430664</v>
+      </c>
+      <c r="E232" t="n">
+        <v>104.6800003051758</v>
+      </c>
+      <c r="F232" t="n">
+        <v>14047200</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B233" t="n">
+        <v>104.4199981689453</v>
+      </c>
+      <c r="C233" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="D233" t="n">
+        <v>103.6999969482422</v>
+      </c>
+      <c r="E233" t="n">
+        <v>104.9100036621094</v>
+      </c>
+      <c r="F233" t="n">
+        <v>10929700</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B234" t="n">
+        <v>104.6100006103516</v>
+      </c>
+      <c r="C234" t="n">
+        <v>104.8000030517578</v>
+      </c>
+      <c r="D234" t="n">
+        <v>102.8000030517578</v>
+      </c>
+      <c r="E234" t="n">
+        <v>103.1800003051758</v>
+      </c>
+      <c r="F234" t="n">
+        <v>8631900</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B235" t="n">
+        <v>102.9499969482422</v>
+      </c>
+      <c r="C235" t="n">
+        <v>104.0899963378906</v>
+      </c>
+      <c r="D235" t="n">
+        <v>102.7900009155273</v>
+      </c>
+      <c r="E235" t="n">
+        <v>103.5299987792969</v>
+      </c>
+      <c r="F235" t="n">
+        <v>6781600</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B236" t="n">
+        <v>103.2900009155273</v>
+      </c>
+      <c r="C236" t="n">
+        <v>103.6800003051758</v>
+      </c>
+      <c r="D236" t="n">
+        <v>102.0299987792969</v>
+      </c>
+      <c r="E236" t="n">
+        <v>103.2200012207031</v>
+      </c>
+      <c r="F236" t="n">
+        <v>6717500</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B237" t="n">
+        <v>103.8000030517578</v>
+      </c>
+      <c r="C237" t="n">
+        <v>104.9400024414062</v>
+      </c>
+      <c r="D237" t="n">
+        <v>103.4599990844727</v>
+      </c>
+      <c r="E237" t="n">
+        <v>104.8000030517578</v>
+      </c>
+      <c r="F237" t="n">
+        <v>7100000</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B238" t="n">
+        <v>104.9899978637695</v>
+      </c>
+      <c r="C238" t="n">
+        <v>107.1100006103516</v>
+      </c>
+      <c r="D238" t="n">
+        <v>104.9100036621094</v>
+      </c>
+      <c r="E238" t="n">
+        <v>106.8499984741211</v>
+      </c>
+      <c r="F238" t="n">
+        <v>8176900</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B239" t="n">
+        <v>106.3300018310547</v>
+      </c>
+      <c r="C239" t="n">
+        <v>106.6399993896484</v>
+      </c>
+      <c r="D239" t="n">
+        <v>103.4599990844727</v>
+      </c>
+      <c r="E239" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="F239" t="n">
+        <v>7635000</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B240" t="n">
+        <v>104.1900024414062</v>
+      </c>
+      <c r="C240" t="n">
+        <v>105.2099990844727</v>
+      </c>
+      <c r="D240" t="n">
+        <v>103.629997253418</v>
+      </c>
+      <c r="E240" t="n">
+        <v>103.9499969482422</v>
+      </c>
+      <c r="F240" t="n">
+        <v>6149900</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B241" t="n">
+        <v>104.0599975585938</v>
+      </c>
+      <c r="C241" t="n">
+        <v>107.0599975585938</v>
+      </c>
+      <c r="D241" t="n">
+        <v>103.9599990844727</v>
+      </c>
+      <c r="E241" t="n">
+        <v>106.9300003051758</v>
+      </c>
+      <c r="F241" t="n">
+        <v>8046100</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B242" t="n">
+        <v>106.879997253418</v>
+      </c>
+      <c r="C242" t="n">
+        <v>108.6900024414062</v>
+      </c>
+      <c r="D242" t="n">
+        <v>106.4199981689453</v>
+      </c>
+      <c r="E242" t="n">
+        <v>107.3199996948242</v>
+      </c>
+      <c r="F242" t="n">
+        <v>7971500</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B243" t="n">
+        <v>107.5699996948242</v>
+      </c>
+      <c r="C243" t="n">
+        <v>108.4100036621094</v>
+      </c>
+      <c r="D243" t="n">
+        <v>106.9700012207031</v>
+      </c>
+      <c r="E243" t="n">
+        <v>107.7799987792969</v>
+      </c>
+      <c r="F243" t="n">
+        <v>6840800</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B244" t="n">
+        <v>108.3899993896484</v>
+      </c>
+      <c r="C244" t="n">
+        <v>111.870002746582</v>
+      </c>
+      <c r="D244" t="n">
+        <v>108.0800018310547</v>
+      </c>
+      <c r="E244" t="n">
+        <v>110.6100006103516</v>
+      </c>
+      <c r="F244" t="n">
+        <v>12658400</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B245" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="C245" t="n">
+        <v>111.5999984741211</v>
+      </c>
+      <c r="D245" t="n">
+        <v>109.7600021362305</v>
+      </c>
+      <c r="E245" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="F245" t="n">
+        <v>6747100</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B246" t="n">
+        <v>111.3000030517578</v>
+      </c>
+      <c r="C246" t="n">
+        <v>111.5199966430664</v>
+      </c>
+      <c r="D246" t="n">
+        <v>109.4499969482422</v>
+      </c>
+      <c r="E246" t="n">
+        <v>109.629997253418</v>
+      </c>
+      <c r="F246" t="n">
+        <v>8524600</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B247" t="n">
+        <v>108.7799987792969</v>
+      </c>
+      <c r="C247" t="n">
+        <v>108.870002746582</v>
+      </c>
+      <c r="D247" t="n">
+        <v>106.7399978637695</v>
+      </c>
+      <c r="E247" t="n">
+        <v>106.8199996948242</v>
+      </c>
+      <c r="F247" t="n">
+        <v>8699500</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B248" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="C248" t="n">
+        <v>108.1999969482422</v>
+      </c>
+      <c r="D248" t="n">
+        <v>107.0299987792969</v>
+      </c>
+      <c r="E248" t="n">
+        <v>108.0999984741211</v>
+      </c>
+      <c r="F248" t="n">
+        <v>5465900</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B249" t="n">
+        <v>107.7799987792969</v>
+      </c>
+      <c r="C249" t="n">
+        <v>108.0899963378906</v>
+      </c>
+      <c r="D249" t="n">
+        <v>106.9700012207031</v>
+      </c>
+      <c r="E249" t="n">
+        <v>107.5500030517578</v>
+      </c>
+      <c r="F249" t="n">
+        <v>8728700</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B250" t="n">
+        <v>107.2399978637695</v>
+      </c>
+      <c r="C250" t="n">
+        <v>108.9499969482422</v>
+      </c>
+      <c r="D250" t="n">
+        <v>106.1399993896484</v>
+      </c>
+      <c r="E250" t="n">
+        <v>106.2200012207031</v>
+      </c>
+      <c r="F250" t="n">
+        <v>7033700</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B251" t="n">
+        <v>106.7099990844727</v>
+      </c>
+      <c r="C251" t="n">
+        <v>108.9899978637695</v>
+      </c>
+      <c r="D251" t="n">
+        <v>106.3300018310547</v>
+      </c>
+      <c r="E251" t="n">
+        <v>107.9800033569336</v>
+      </c>
+      <c r="F251" t="n">
+        <v>7555300</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B252" t="n">
+        <v>108.620002746582</v>
+      </c>
+      <c r="C252" t="n">
+        <v>109.1999969482422</v>
+      </c>
+      <c r="D252" t="n">
+        <v>106.9000015258789</v>
+      </c>
+      <c r="E252" t="n">
+        <v>107.1600036621094</v>
+      </c>
+      <c r="F252" t="n">
+        <v>6241300</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B253" t="n">
         <v>106.4899978637695</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C253" t="n">
         <v>106.879997253418</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D253" t="n">
         <v>105.1699981689453</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E253" t="n">
         <v>105.3099975585938</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F253" t="n">
         <v>6103700</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5305,7 +11259,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:59:56</t>
+          <t>2026-09-07 03:08:48</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -472,16 +472,16 @@
         <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>117.2127468064064</v>
+        <v>117.2127391123067</v>
       </c>
       <c r="C2" t="n">
-        <v>118.0703240854676</v>
+        <v>118.0703163350746</v>
       </c>
       <c r="D2" t="n">
-        <v>116.0200110716605</v>
+        <v>116.0200034558545</v>
       </c>
       <c r="E2" t="n">
-        <v>116.2270202636719</v>
+        <v>116.2270126342773</v>
       </c>
       <c r="F2" t="n">
         <v>6669100</v>
@@ -550,16 +550,16 @@
         <v>45910</v>
       </c>
       <c r="B5" t="n">
-        <v>115.1821434099858</v>
+        <v>115.1821357107481</v>
       </c>
       <c r="C5" t="n">
-        <v>115.8327265289666</v>
+        <v>115.8327187862414</v>
       </c>
       <c r="D5" t="n">
-        <v>112.8656875709264</v>
+        <v>112.8656800265299</v>
       </c>
       <c r="E5" t="n">
-        <v>114.1372756958008</v>
+        <v>114.1372680664062</v>
       </c>
       <c r="F5" t="n">
         <v>7484900</v>
@@ -602,16 +602,16 @@
         <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>114.6005610358709</v>
+        <v>114.6005686850037</v>
       </c>
       <c r="C7" t="n">
-        <v>115.3398558853256</v>
+        <v>115.3398635838033</v>
       </c>
       <c r="D7" t="n">
-        <v>113.4571147255429</v>
+        <v>113.4571222983551</v>
       </c>
       <c r="E7" t="n">
-        <v>114.3048400878906</v>
+        <v>114.3048477172852</v>
       </c>
       <c r="F7" t="n">
         <v>7640900</v>
@@ -628,16 +628,16 @@
         <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>114.45269990472</v>
+        <v>114.452707566448</v>
       </c>
       <c r="C8" t="n">
-        <v>115.0835642376594</v>
+        <v>115.0835719416188</v>
       </c>
       <c r="D8" t="n">
-        <v>113.3585429321699</v>
+        <v>113.3585505206524</v>
       </c>
       <c r="E8" t="n">
-        <v>113.9696960449219</v>
+        <v>113.9697036743164</v>
       </c>
       <c r="F8" t="n">
         <v>7150900</v>
@@ -654,16 +654,16 @@
         <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>113.8021196226455</v>
+        <v>113.8021272666058</v>
       </c>
       <c r="C9" t="n">
-        <v>114.1964117205285</v>
+        <v>114.196419390973</v>
       </c>
       <c r="D9" t="n">
-        <v>113.0726841298844</v>
+        <v>113.0726917248494</v>
       </c>
       <c r="E9" t="n">
-        <v>113.5852661132812</v>
+        <v>113.5852737426758</v>
       </c>
       <c r="F9" t="n">
         <v>6844900</v>
@@ -680,16 +680,16 @@
         <v>45917</v>
       </c>
       <c r="B10" t="n">
-        <v>113.5951227912625</v>
+        <v>113.595115218382</v>
       </c>
       <c r="C10" t="n">
-        <v>114.9948601742622</v>
+        <v>114.9948525080674</v>
       </c>
       <c r="D10" t="n">
-        <v>113.5754115697539</v>
+        <v>113.5754039981875</v>
       </c>
       <c r="E10" t="n">
-        <v>114.4428482055664</v>
+        <v>114.4428405761719</v>
       </c>
       <c r="F10" t="n">
         <v>7333900</v>
@@ -706,16 +706,16 @@
         <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>113.6838432123518</v>
+        <v>113.6838355517382</v>
       </c>
       <c r="C11" t="n">
-        <v>114.1274171453944</v>
+        <v>114.1274094548904</v>
       </c>
       <c r="D11" t="n">
-        <v>112.4221144494342</v>
+        <v>112.4221068738425</v>
       </c>
       <c r="E11" t="n">
-        <v>113.2205505371094</v>
+        <v>113.2205429077148</v>
       </c>
       <c r="F11" t="n">
         <v>9460500</v>
@@ -784,16 +784,16 @@
         <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>111.111089276602</v>
+        <v>111.1110969379416</v>
       </c>
       <c r="C14" t="n">
-        <v>111.9982446066948</v>
+        <v>111.9982523292055</v>
       </c>
       <c r="D14" t="n">
-        <v>110.0070729190981</v>
+        <v>110.0070805043135</v>
       </c>
       <c r="E14" t="n">
-        <v>110.6477966308594</v>
+        <v>110.6478042602539</v>
       </c>
       <c r="F14" t="n">
         <v>13145000</v>
@@ -966,16 +966,16 @@
         <v>45932</v>
       </c>
       <c r="B21" t="n">
-        <v>111.3673895222522</v>
+        <v>111.3673818357084</v>
       </c>
       <c r="C21" t="n">
-        <v>111.5546724538137</v>
+        <v>111.5546647543437</v>
       </c>
       <c r="D21" t="n">
-        <v>109.1987865883829</v>
+        <v>109.1987790515154</v>
       </c>
       <c r="E21" t="n">
-        <v>110.5393753051758</v>
+        <v>110.5393676757812</v>
       </c>
       <c r="F21" t="n">
         <v>8695100</v>
@@ -1096,16 +1096,16 @@
         <v>45939</v>
       </c>
       <c r="B26" t="n">
-        <v>110.2239394253812</v>
+        <v>110.2239317389327</v>
       </c>
       <c r="C26" t="n">
-        <v>111.3870970225426</v>
+        <v>111.3870892549816</v>
       </c>
       <c r="D26" t="n">
-        <v>109.2973540878383</v>
+        <v>109.2973464660052</v>
       </c>
       <c r="E26" t="n">
-        <v>109.4057846069336</v>
+        <v>109.4057769775391</v>
       </c>
       <c r="F26" t="n">
         <v>6502400</v>
@@ -1148,16 +1148,16 @@
         <v>45943</v>
       </c>
       <c r="B28" t="n">
-        <v>108.8143424328862</v>
+        <v>108.8143500705835</v>
       </c>
       <c r="C28" t="n">
-        <v>109.3762062096973</v>
+        <v>109.3762138868319</v>
       </c>
       <c r="D28" t="n">
-        <v>107.8187566106434</v>
+        <v>107.8187641784603</v>
       </c>
       <c r="E28" t="n">
-        <v>108.6960525512695</v>
+        <v>108.6960601806641</v>
       </c>
       <c r="F28" t="n">
         <v>7435100</v>
@@ -1252,16 +1252,16 @@
         <v>45947</v>
       </c>
       <c r="B32" t="n">
-        <v>108.1736289318545</v>
+        <v>108.1736213665725</v>
       </c>
       <c r="C32" t="n">
-        <v>109.8690797923661</v>
+        <v>109.8690721085103</v>
       </c>
       <c r="D32" t="n">
-        <v>107.8779154806818</v>
+        <v>107.877907936081</v>
       </c>
       <c r="E32" t="n">
-        <v>109.0903549194336</v>
+        <v>109.0903472900391</v>
       </c>
       <c r="F32" t="n">
         <v>10090500</v>
@@ -1330,16 +1330,16 @@
         <v>45952</v>
       </c>
       <c r="B35" t="n">
-        <v>112.3728242428528</v>
+        <v>112.3728165513869</v>
       </c>
       <c r="C35" t="n">
-        <v>112.6488264675382</v>
+        <v>112.6488187571811</v>
       </c>
       <c r="D35" t="n">
-        <v>111.3673864928563</v>
+        <v>111.3673788702085</v>
       </c>
       <c r="E35" t="n">
-        <v>111.4659576416016</v>
+        <v>111.465950012207</v>
       </c>
       <c r="F35" t="n">
         <v>7569200</v>
@@ -1356,16 +1356,16 @@
         <v>45953</v>
       </c>
       <c r="B36" t="n">
-        <v>111.5546728695406</v>
+        <v>111.5546652306962</v>
       </c>
       <c r="C36" t="n">
-        <v>112.2052560082749</v>
+        <v>112.2052483248811</v>
       </c>
       <c r="D36" t="n">
-        <v>110.3028034487141</v>
+        <v>110.3027958955931</v>
       </c>
       <c r="E36" t="n">
-        <v>111.4166717529297</v>
+        <v>111.4166641235352</v>
       </c>
       <c r="F36" t="n">
         <v>6945400</v>
@@ -1460,16 +1460,16 @@
         <v>45959</v>
       </c>
       <c r="B40" t="n">
-        <v>109.59306628145</v>
+        <v>109.5930739758994</v>
       </c>
       <c r="C40" t="n">
-        <v>109.9380690325516</v>
+        <v>109.9380767512234</v>
       </c>
       <c r="D40" t="n">
-        <v>108.4397681475551</v>
+        <v>108.4397757610322</v>
       </c>
       <c r="E40" t="n">
-        <v>108.6664810180664</v>
+        <v>108.6664886474609</v>
       </c>
       <c r="F40" t="n">
         <v>7097100</v>
@@ -1512,16 +1512,16 @@
         <v>45961</v>
       </c>
       <c r="B42" t="n">
-        <v>109.98736338598</v>
+        <v>109.9873709449201</v>
       </c>
       <c r="C42" t="n">
-        <v>111.485664339403</v>
+        <v>111.4856720013147</v>
       </c>
       <c r="D42" t="n">
-        <v>108.9523475649108</v>
+        <v>108.9523550527189</v>
       </c>
       <c r="E42" t="n">
-        <v>111.0125198364258</v>
+        <v>111.0125274658203</v>
       </c>
       <c r="F42" t="n">
         <v>8700600</v>
@@ -1564,16 +1564,16 @@
         <v>45965</v>
       </c>
       <c r="B44" t="n">
-        <v>109.3860659107013</v>
+        <v>109.3860735058741</v>
       </c>
       <c r="C44" t="n">
-        <v>110.1943613029524</v>
+        <v>110.1943689542488</v>
       </c>
       <c r="D44" t="n">
-        <v>109.0607743756439</v>
+        <v>109.0607819482302</v>
       </c>
       <c r="E44" t="n">
-        <v>109.8789291381836</v>
+        <v>109.8789367675781</v>
       </c>
       <c r="F44" t="n">
         <v>7950100</v>
@@ -1642,16 +1642,16 @@
         <v>45968</v>
       </c>
       <c r="B47" t="n">
-        <v>108.6862030385313</v>
+        <v>108.6862106348567</v>
       </c>
       <c r="C47" t="n">
-        <v>109.8395012072324</v>
+        <v>109.8395088841645</v>
       </c>
       <c r="D47" t="n">
-        <v>108.4693420111524</v>
+        <v>108.4693495923209</v>
       </c>
       <c r="E47" t="n">
-        <v>109.1593475341797</v>
+        <v>109.1593551635742</v>
       </c>
       <c r="F47" t="n">
         <v>8782100</v>
@@ -1694,16 +1694,16 @@
         <v>45972</v>
       </c>
       <c r="B49" t="n">
-        <v>111.0420979461576</v>
+        <v>111.0420904629071</v>
       </c>
       <c r="C49" t="n">
-        <v>113.3289832533765</v>
+        <v>113.3289756160103</v>
       </c>
       <c r="D49" t="n">
-        <v>110.8153775294455</v>
+        <v>110.815370061474</v>
       </c>
       <c r="E49" t="n">
-        <v>113.210693359375</v>
+        <v>113.2106857299805</v>
       </c>
       <c r="F49" t="n">
         <v>9713300</v>
@@ -1720,16 +1720,16 @@
         <v>45973</v>
       </c>
       <c r="B50" t="n">
-        <v>112.9346801407027</v>
+        <v>112.9346876340564</v>
       </c>
       <c r="C50" t="n">
-        <v>115.4187075091099</v>
+        <v>115.4187151672819</v>
       </c>
       <c r="D50" t="n">
-        <v>112.7572490772096</v>
+        <v>112.7572565587906</v>
       </c>
       <c r="E50" t="n">
-        <v>114.984992980957</v>
+        <v>114.9850006103516</v>
       </c>
       <c r="F50" t="n">
         <v>15248700</v>
@@ -1746,16 +1746,16 @@
         <v>45974</v>
       </c>
       <c r="B51" t="n">
-        <v>107.3357644371155</v>
+        <v>107.3357567169709</v>
       </c>
       <c r="C51" t="n">
-        <v>107.7990571232513</v>
+        <v>107.7990493697842</v>
       </c>
       <c r="D51" t="n">
-        <v>103.4125769427048</v>
+        <v>103.4125695047362</v>
       </c>
       <c r="E51" t="n">
-        <v>106.0740356445312</v>
+        <v>106.0740280151367</v>
       </c>
       <c r="F51" t="n">
         <v>44045400</v>
@@ -1772,16 +1772,16 @@
         <v>45975</v>
       </c>
       <c r="B52" t="n">
-        <v>105.9853145518839</v>
+        <v>105.9853067984581</v>
       </c>
       <c r="C52" t="n">
-        <v>107.1780502864732</v>
+        <v>107.178042445792</v>
       </c>
       <c r="D52" t="n">
-        <v>103.7970079445177</v>
+        <v>103.797000351179</v>
       </c>
       <c r="E52" t="n">
-        <v>104.2898712158203</v>
+        <v>104.2898635864258</v>
       </c>
       <c r="F52" t="n">
         <v>16691400</v>
@@ -1850,16 +1850,16 @@
         <v>45980</v>
       </c>
       <c r="B55" t="n">
-        <v>104.5658729007312</v>
+        <v>104.5658651685615</v>
       </c>
       <c r="C55" t="n">
-        <v>106.0543145575675</v>
+        <v>106.0543067153343</v>
       </c>
       <c r="D55" t="n">
-        <v>102.5944198257724</v>
+        <v>102.5944122393827</v>
       </c>
       <c r="E55" t="n">
-        <v>103.1759948730469</v>
+        <v>103.1759872436523</v>
       </c>
       <c r="F55" t="n">
         <v>12790000</v>
@@ -2006,16 +2006,16 @@
         <v>45989</v>
       </c>
       <c r="B61" t="n">
-        <v>101.8255455445372</v>
+        <v>101.8255530884873</v>
       </c>
       <c r="C61" t="n">
-        <v>103.2449865221035</v>
+        <v>103.2449941712158</v>
       </c>
       <c r="D61" t="n">
-        <v>101.7663968434539</v>
+        <v>101.7664043830219</v>
       </c>
       <c r="E61" t="n">
-        <v>102.9788436889648</v>
+        <v>102.9788513183594</v>
       </c>
       <c r="F61" t="n">
         <v>6525500</v>
@@ -2058,16 +2058,16 @@
         <v>45993</v>
       </c>
       <c r="B63" t="n">
-        <v>105.0094417410337</v>
+        <v>105.0094494941518</v>
       </c>
       <c r="C63" t="n">
-        <v>105.0488717030799</v>
+        <v>105.0488794591093</v>
       </c>
       <c r="D63" t="n">
-        <v>103.3238503461612</v>
+        <v>103.3238579748278</v>
       </c>
       <c r="E63" t="n">
-        <v>103.3337097167969</v>
+        <v>103.3337173461914</v>
       </c>
       <c r="F63" t="n">
         <v>8548200</v>
@@ -2084,16 +2084,16 @@
         <v>45994</v>
       </c>
       <c r="B64" t="n">
-        <v>103.4027062810859</v>
+        <v>103.4027138498727</v>
       </c>
       <c r="C64" t="n">
-        <v>104.339143401945</v>
+        <v>104.3391510392764</v>
       </c>
       <c r="D64" t="n">
-        <v>102.978843606061</v>
+        <v>102.9788511438223</v>
       </c>
       <c r="E64" t="n">
-        <v>104.230712890625</v>
+        <v>104.2307205200195</v>
       </c>
       <c r="F64" t="n">
         <v>10177800</v>
@@ -2266,16 +2266,16 @@
         <v>46003</v>
       </c>
       <c r="B71" t="n">
-        <v>110.1352293411146</v>
+        <v>110.1352217028325</v>
       </c>
       <c r="C71" t="n">
-        <v>111.7222421475927</v>
+        <v>111.7222343992454</v>
       </c>
       <c r="D71" t="n">
-        <v>109.5635061444599</v>
+        <v>109.5634985458288</v>
       </c>
       <c r="E71" t="n">
-        <v>110.007080078125</v>
+        <v>110.0070724487305</v>
       </c>
       <c r="F71" t="n">
         <v>13059100</v>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-07 03:08:48</t>
+          <t>2026-09-08 08:52:39</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45905</v>
+        <v>45909</v>
       </c>
       <c r="B2" t="n">
-        <v>117.2127391123067</v>
+        <v>116.8381638958523</v>
       </c>
       <c r="C2" t="n">
-        <v>118.0703163350746</v>
+        <v>117.3507459007291</v>
       </c>
       <c r="D2" t="n">
-        <v>116.0200034558545</v>
+        <v>115.5468645536568</v>
       </c>
       <c r="E2" t="n">
-        <v>116.2270126342773</v>
+        <v>115.6947250366211</v>
       </c>
       <c r="F2" t="n">
-        <v>6669100</v>
+        <v>5444300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="B3" t="n">
-        <v>116.2763011496704</v>
+        <v>115.1821434099858</v>
       </c>
       <c r="C3" t="n">
-        <v>117.1831677568228</v>
+        <v>115.8327265289666</v>
       </c>
       <c r="D3" t="n">
-        <v>115.0737135738613</v>
+        <v>112.8656875709264</v>
       </c>
       <c r="E3" t="n">
-        <v>117.1437377929688</v>
+        <v>114.1372756958008</v>
       </c>
       <c r="F3" t="n">
-        <v>6450700</v>
+        <v>7484900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="B4" t="n">
-        <v>116.8381638958523</v>
+        <v>113.8021202611286</v>
       </c>
       <c r="C4" t="n">
-        <v>117.3507459007291</v>
+        <v>115.4975710271905</v>
       </c>
       <c r="D4" t="n">
-        <v>115.5468645536568</v>
+        <v>112.9938248401568</v>
       </c>
       <c r="E4" t="n">
-        <v>115.6947250366211</v>
+        <v>115.4088592529297</v>
       </c>
       <c r="F4" t="n">
-        <v>5444300</v>
+        <v>8399100</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="B5" t="n">
-        <v>115.1821357107481</v>
+        <v>114.6005610358709</v>
       </c>
       <c r="C5" t="n">
-        <v>115.8327187862414</v>
+        <v>115.3398558853256</v>
       </c>
       <c r="D5" t="n">
-        <v>112.8656800265299</v>
+        <v>113.4571147255429</v>
       </c>
       <c r="E5" t="n">
-        <v>114.1372680664062</v>
+        <v>114.3048400878906</v>
       </c>
       <c r="F5" t="n">
-        <v>7484900</v>
+        <v>7640900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="B6" t="n">
-        <v>113.8021202611286</v>
+        <v>114.45269990472</v>
       </c>
       <c r="C6" t="n">
-        <v>115.4975710271905</v>
+        <v>115.0835642376594</v>
       </c>
       <c r="D6" t="n">
-        <v>112.9938248401568</v>
+        <v>113.3585429321699</v>
       </c>
       <c r="E6" t="n">
-        <v>115.4088592529297</v>
+        <v>113.9696960449219</v>
       </c>
       <c r="F6" t="n">
-        <v>8399100</v>
+        <v>7150900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="B7" t="n">
-        <v>114.6005686850037</v>
+        <v>113.8021196226455</v>
       </c>
       <c r="C7" t="n">
-        <v>115.3398635838033</v>
+        <v>114.1964117205285</v>
       </c>
       <c r="D7" t="n">
-        <v>113.4571222983551</v>
+        <v>113.0726841298844</v>
       </c>
       <c r="E7" t="n">
-        <v>114.3048477172852</v>
+        <v>113.5852661132812</v>
       </c>
       <c r="F7" t="n">
-        <v>7640900</v>
+        <v>6844900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B8" t="n">
-        <v>114.452707566448</v>
+        <v>113.5951227912625</v>
       </c>
       <c r="C8" t="n">
-        <v>115.0835719416188</v>
+        <v>114.9948601742622</v>
       </c>
       <c r="D8" t="n">
-        <v>113.3585505206524</v>
+        <v>113.5754115697539</v>
       </c>
       <c r="E8" t="n">
-        <v>113.9697036743164</v>
+        <v>114.4428482055664</v>
       </c>
       <c r="F8" t="n">
-        <v>7150900</v>
+        <v>7333900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B9" t="n">
-        <v>113.8021272666058</v>
+        <v>113.6838432123518</v>
       </c>
       <c r="C9" t="n">
-        <v>114.196419390973</v>
+        <v>114.1274171453944</v>
       </c>
       <c r="D9" t="n">
-        <v>113.0726917248494</v>
+        <v>112.4221144494342</v>
       </c>
       <c r="E9" t="n">
-        <v>113.5852737426758</v>
+        <v>113.2205505371094</v>
       </c>
       <c r="F9" t="n">
-        <v>6844900</v>
+        <v>9460500</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B10" t="n">
-        <v>113.595115218382</v>
+        <v>112.9642523554146</v>
       </c>
       <c r="C10" t="n">
-        <v>114.9948525080674</v>
+        <v>112.9642523554146</v>
       </c>
       <c r="D10" t="n">
-        <v>113.5754039981875</v>
+        <v>110.3323644761722</v>
       </c>
       <c r="E10" t="n">
-        <v>114.4428405761719</v>
+        <v>112.1362457275391</v>
       </c>
       <c r="F10" t="n">
-        <v>7333900</v>
+        <v>23398400</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B11" t="n">
-        <v>113.6838355517382</v>
+        <v>110.1647924763258</v>
       </c>
       <c r="C11" t="n">
-        <v>114.1274094548904</v>
+        <v>112.0080961635035</v>
       </c>
       <c r="D11" t="n">
-        <v>112.4221068738425</v>
+        <v>109.9282127085895</v>
       </c>
       <c r="E11" t="n">
-        <v>113.2205429077148</v>
+        <v>110.953369140625</v>
       </c>
       <c r="F11" t="n">
-        <v>9460500</v>
+        <v>15479800</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B12" t="n">
-        <v>112.9642523554146</v>
+        <v>111.111089276602</v>
       </c>
       <c r="C12" t="n">
-        <v>112.9642523554146</v>
+        <v>111.9982446066948</v>
       </c>
       <c r="D12" t="n">
-        <v>110.3323644761722</v>
+        <v>110.0070729190981</v>
       </c>
       <c r="E12" t="n">
-        <v>112.1362457275391</v>
+        <v>110.6477966308594</v>
       </c>
       <c r="F12" t="n">
-        <v>23398400</v>
+        <v>13145000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B13" t="n">
-        <v>110.1647924763258</v>
+        <v>110.8055211263376</v>
       </c>
       <c r="C13" t="n">
-        <v>112.0080961635035</v>
+        <v>112.5206831561622</v>
       </c>
       <c r="D13" t="n">
-        <v>109.9282127085895</v>
+        <v>110.5985119402154</v>
       </c>
       <c r="E13" t="n">
-        <v>110.953369140625</v>
+        <v>111.8109588623047</v>
       </c>
       <c r="F13" t="n">
-        <v>15479800</v>
+        <v>8755200</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B14" t="n">
-        <v>111.1110969379416</v>
+        <v>111.1012331951749</v>
       </c>
       <c r="C14" t="n">
-        <v>111.9982523292055</v>
+        <v>112.4221106191933</v>
       </c>
       <c r="D14" t="n">
-        <v>110.0070805043135</v>
+        <v>111.0420920115833</v>
       </c>
       <c r="E14" t="n">
-        <v>110.6478042602539</v>
+        <v>111.3772354125977</v>
       </c>
       <c r="F14" t="n">
-        <v>13145000</v>
+        <v>6365500</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B15" t="n">
-        <v>110.8055211263376</v>
+        <v>111.5152366513407</v>
       </c>
       <c r="C15" t="n">
-        <v>112.5206831561622</v>
+        <v>111.9489587195086</v>
       </c>
       <c r="D15" t="n">
-        <v>110.5985119402154</v>
+        <v>111.1505226581053</v>
       </c>
       <c r="E15" t="n">
-        <v>111.8109588623047</v>
+        <v>111.8503875732422</v>
       </c>
       <c r="F15" t="n">
-        <v>8755200</v>
+        <v>6145700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B16" t="n">
-        <v>111.1012331951749</v>
+        <v>111.8503861885936</v>
       </c>
       <c r="C16" t="n">
-        <v>112.4221106191933</v>
+        <v>113.3684058878927</v>
       </c>
       <c r="D16" t="n">
-        <v>111.0420920115833</v>
+        <v>111.7123850814297</v>
       </c>
       <c r="E16" t="n">
-        <v>111.3772354125977</v>
+        <v>113.1416854858398</v>
       </c>
       <c r="F16" t="n">
-        <v>6365500</v>
+        <v>9304100</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B17" t="n">
-        <v>111.5152366513407</v>
+        <v>112.8952551010659</v>
       </c>
       <c r="C17" t="n">
-        <v>111.9489587195086</v>
+        <v>113.2402578727591</v>
       </c>
       <c r="D17" t="n">
-        <v>111.1505226581053</v>
+        <v>111.7222381568123</v>
       </c>
       <c r="E17" t="n">
-        <v>111.8503875732422</v>
+        <v>112.8656845092773</v>
       </c>
       <c r="F17" t="n">
-        <v>6145700</v>
+        <v>9303700</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B18" t="n">
-        <v>111.8503861885936</v>
+        <v>112.4516824751333</v>
       </c>
       <c r="C18" t="n">
-        <v>113.3684058878927</v>
+        <v>114.4034167605612</v>
       </c>
       <c r="D18" t="n">
-        <v>111.7123850814297</v>
+        <v>111.1800943701441</v>
       </c>
       <c r="E18" t="n">
-        <v>113.1416854858398</v>
+        <v>111.3378067016602</v>
       </c>
       <c r="F18" t="n">
-        <v>9304100</v>
+        <v>9736300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B19" t="n">
-        <v>112.8952551010659</v>
+        <v>111.3673895222522</v>
       </c>
       <c r="C19" t="n">
-        <v>113.2402578727591</v>
+        <v>111.5546724538137</v>
       </c>
       <c r="D19" t="n">
-        <v>111.7222381568123</v>
+        <v>109.1987865883829</v>
       </c>
       <c r="E19" t="n">
-        <v>112.8656845092773</v>
+        <v>110.5393753051758</v>
       </c>
       <c r="F19" t="n">
-        <v>9303700</v>
+        <v>8695100</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B20" t="n">
-        <v>112.4516824751333</v>
+        <v>110.4407994688091</v>
       </c>
       <c r="C20" t="n">
-        <v>114.4034167605612</v>
+        <v>111.9489598311001</v>
       </c>
       <c r="D20" t="n">
-        <v>111.1800943701441</v>
+        <v>109.9676474333371</v>
       </c>
       <c r="E20" t="n">
-        <v>111.3378067016602</v>
+        <v>110.8646621704102</v>
       </c>
       <c r="F20" t="n">
-        <v>9736300</v>
+        <v>7148400</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B21" t="n">
-        <v>111.3673818357084</v>
+        <v>111.0815219633868</v>
       </c>
       <c r="C21" t="n">
-        <v>111.5546647543437</v>
+        <v>111.4955252894808</v>
       </c>
       <c r="D21" t="n">
-        <v>109.1987790515154</v>
+        <v>109.8592156856383</v>
       </c>
       <c r="E21" t="n">
-        <v>110.5393676757812</v>
+        <v>111.1406631469727</v>
       </c>
       <c r="F21" t="n">
-        <v>8695100</v>
+        <v>6141200</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B22" t="n">
-        <v>110.4407994688091</v>
+        <v>111.0223763857341</v>
       </c>
       <c r="C22" t="n">
-        <v>111.9489598311001</v>
+        <v>111.7813900254436</v>
       </c>
       <c r="D22" t="n">
-        <v>109.9676474333371</v>
+        <v>110.20422908127</v>
       </c>
       <c r="E22" t="n">
-        <v>110.8646621704102</v>
+        <v>110.9238052368164</v>
       </c>
       <c r="F22" t="n">
-        <v>7148400</v>
+        <v>5409800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B23" t="n">
-        <v>111.0815219633868</v>
+        <v>111.1998048136618</v>
       </c>
       <c r="C23" t="n">
-        <v>111.4955252894808</v>
+        <v>111.584237549633</v>
       </c>
       <c r="D23" t="n">
-        <v>109.8592156856383</v>
+        <v>110.0563659765542</v>
       </c>
       <c r="E23" t="n">
-        <v>111.1406631469727</v>
+        <v>110.2929382324219</v>
       </c>
       <c r="F23" t="n">
-        <v>6141200</v>
+        <v>7074400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B24" t="n">
-        <v>111.0223763857341</v>
+        <v>110.2239394253812</v>
       </c>
       <c r="C24" t="n">
-        <v>111.7813900254436</v>
+        <v>111.3870970225426</v>
       </c>
       <c r="D24" t="n">
-        <v>110.20422908127</v>
+        <v>109.2973540878383</v>
       </c>
       <c r="E24" t="n">
-        <v>110.9238052368164</v>
+        <v>109.4057846069336</v>
       </c>
       <c r="F24" t="n">
-        <v>5409800</v>
+        <v>6502400</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B25" t="n">
-        <v>111.1998048136618</v>
+        <v>109.9380737221385</v>
       </c>
       <c r="C25" t="n">
-        <v>111.584237549633</v>
+        <v>111.0716606845381</v>
       </c>
       <c r="D25" t="n">
-        <v>110.0563659765542</v>
+        <v>107.5526174321997</v>
       </c>
       <c r="E25" t="n">
-        <v>110.2929382324219</v>
+        <v>107.631477355957</v>
       </c>
       <c r="F25" t="n">
-        <v>7074400</v>
+        <v>9635200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B26" t="n">
-        <v>110.2239317389327</v>
+        <v>108.8143424328862</v>
       </c>
       <c r="C26" t="n">
-        <v>111.3870892549816</v>
+        <v>109.3762062096973</v>
       </c>
       <c r="D26" t="n">
-        <v>109.2973464660052</v>
+        <v>107.8187566106434</v>
       </c>
       <c r="E26" t="n">
-        <v>109.4057769775391</v>
+        <v>108.6960525512695</v>
       </c>
       <c r="F26" t="n">
-        <v>6502400</v>
+        <v>7435100</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B27" t="n">
-        <v>109.9380737221385</v>
+        <v>108.0849128268841</v>
       </c>
       <c r="C27" t="n">
-        <v>111.0716606845381</v>
+        <v>110.2436487598859</v>
       </c>
       <c r="D27" t="n">
-        <v>107.5526174321997</v>
+        <v>107.641331387133</v>
       </c>
       <c r="E27" t="n">
-        <v>107.631477355957</v>
+        <v>109.5832138061523</v>
       </c>
       <c r="F27" t="n">
-        <v>9635200</v>
+        <v>7898000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B28" t="n">
-        <v>108.8143500705835</v>
+        <v>109.8789291603083</v>
       </c>
       <c r="C28" t="n">
-        <v>109.3762138868319</v>
+        <v>111.0716572685961</v>
       </c>
       <c r="D28" t="n">
-        <v>107.8187641784603</v>
+        <v>109.5536376251855</v>
       </c>
       <c r="E28" t="n">
-        <v>108.6960601806641</v>
+        <v>110.1155014038086</v>
       </c>
       <c r="F28" t="n">
-        <v>7435100</v>
+        <v>7012600</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B29" t="n">
-        <v>108.0849128268841</v>
+        <v>110.1943638011324</v>
       </c>
       <c r="C29" t="n">
-        <v>110.2436487598859</v>
+        <v>110.4900772320282</v>
       </c>
       <c r="D29" t="n">
-        <v>107.641331387133</v>
+        <v>106.9611821588295</v>
       </c>
       <c r="E29" t="n">
-        <v>109.5832138061523</v>
+        <v>108.3116226196289</v>
       </c>
       <c r="F29" t="n">
-        <v>7898000</v>
+        <v>7531200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B30" t="n">
-        <v>109.8789291603083</v>
+        <v>108.1736289318545</v>
       </c>
       <c r="C30" t="n">
-        <v>111.0716572685961</v>
+        <v>109.8690797923661</v>
       </c>
       <c r="D30" t="n">
-        <v>109.5536376251855</v>
+        <v>107.8779154806818</v>
       </c>
       <c r="E30" t="n">
-        <v>110.1155014038086</v>
+        <v>109.0903549194336</v>
       </c>
       <c r="F30" t="n">
-        <v>7012600</v>
+        <v>10090500</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B31" t="n">
-        <v>110.1943638011324</v>
+        <v>109.4452125270959</v>
       </c>
       <c r="C31" t="n">
-        <v>110.4900772320282</v>
+        <v>110.6478000651592</v>
       </c>
       <c r="D31" t="n">
-        <v>106.9611821588295</v>
+        <v>109.0213498295899</v>
       </c>
       <c r="E31" t="n">
-        <v>108.3116226196289</v>
+        <v>110.3619384765625</v>
       </c>
       <c r="F31" t="n">
-        <v>7531200</v>
+        <v>8047500</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B32" t="n">
-        <v>108.1736213665725</v>
+        <v>110.6477986393913</v>
       </c>
       <c r="C32" t="n">
-        <v>109.8690721085103</v>
+        <v>112.9051132067436</v>
       </c>
       <c r="D32" t="n">
-        <v>107.877907936081</v>
+        <v>110.4407969786948</v>
       </c>
       <c r="E32" t="n">
-        <v>109.0903472900391</v>
+        <v>112.6685409545898</v>
       </c>
       <c r="F32" t="n">
-        <v>10090500</v>
+        <v>8163200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B33" t="n">
-        <v>109.4452125270959</v>
+        <v>112.3728242428528</v>
       </c>
       <c r="C33" t="n">
-        <v>110.6478000651592</v>
+        <v>112.6488264675382</v>
       </c>
       <c r="D33" t="n">
-        <v>109.0213498295899</v>
+        <v>111.3673864928563</v>
       </c>
       <c r="E33" t="n">
-        <v>110.3619384765625</v>
+        <v>111.4659576416016</v>
       </c>
       <c r="F33" t="n">
-        <v>8047500</v>
+        <v>7569200</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B34" t="n">
-        <v>110.6477986393913</v>
+        <v>111.5546728695406</v>
       </c>
       <c r="C34" t="n">
-        <v>112.9051132067436</v>
+        <v>112.2052560082749</v>
       </c>
       <c r="D34" t="n">
-        <v>110.4407969786948</v>
+        <v>110.3028034487141</v>
       </c>
       <c r="E34" t="n">
-        <v>112.6685409545898</v>
+        <v>111.4166717529297</v>
       </c>
       <c r="F34" t="n">
-        <v>8163200</v>
+        <v>6945400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B35" t="n">
-        <v>112.3728165513869</v>
+        <v>111.6138166065038</v>
       </c>
       <c r="C35" t="n">
-        <v>112.6488187571811</v>
+        <v>112.0278199378997</v>
       </c>
       <c r="D35" t="n">
-        <v>111.3673788702085</v>
+        <v>109.9972182029886</v>
       </c>
       <c r="E35" t="n">
-        <v>111.465950012207</v>
+        <v>110.0859375</v>
       </c>
       <c r="F35" t="n">
-        <v>7569200</v>
+        <v>6235200</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B36" t="n">
-        <v>111.5546652306962</v>
+        <v>110.34222664747</v>
       </c>
       <c r="C36" t="n">
-        <v>112.2052483248811</v>
+        <v>110.992802225815</v>
       </c>
       <c r="D36" t="n">
-        <v>110.3027958955931</v>
+        <v>109.721214140304</v>
       </c>
       <c r="E36" t="n">
-        <v>111.4166641235352</v>
+        <v>110.7365112304688</v>
       </c>
       <c r="F36" t="n">
-        <v>6945400</v>
+        <v>6029600</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B37" t="n">
-        <v>111.6138166065038</v>
+        <v>110.3126569642538</v>
       </c>
       <c r="C37" t="n">
-        <v>112.0278199378997</v>
+        <v>110.8745207722</v>
       </c>
       <c r="D37" t="n">
-        <v>109.9972182029886</v>
+        <v>109.8690755239826</v>
       </c>
       <c r="E37" t="n">
-        <v>110.0859375</v>
+        <v>110.0563659667969</v>
       </c>
       <c r="F37" t="n">
-        <v>6235200</v>
+        <v>6839400</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B38" t="n">
-        <v>110.34222664747</v>
+        <v>109.59306628145</v>
       </c>
       <c r="C38" t="n">
-        <v>110.992802225815</v>
+        <v>109.9380690325516</v>
       </c>
       <c r="D38" t="n">
-        <v>109.721214140304</v>
+        <v>108.4397681475551</v>
       </c>
       <c r="E38" t="n">
-        <v>110.7365112304688</v>
+        <v>108.6664810180664</v>
       </c>
       <c r="F38" t="n">
-        <v>6029600</v>
+        <v>7097100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B39" t="n">
-        <v>110.3126569642538</v>
+        <v>108.5580608670909</v>
       </c>
       <c r="C39" t="n">
-        <v>110.8745207722</v>
+        <v>111.9588219337512</v>
       </c>
       <c r="D39" t="n">
-        <v>109.8690755239826</v>
+        <v>107.9863451909205</v>
       </c>
       <c r="E39" t="n">
-        <v>110.0563659667969</v>
+        <v>110.24365234375</v>
       </c>
       <c r="F39" t="n">
-        <v>6839400</v>
+        <v>8311300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B40" t="n">
-        <v>109.5930739758994</v>
+        <v>109.98736338598</v>
       </c>
       <c r="C40" t="n">
-        <v>109.9380767512234</v>
+        <v>111.485664339403</v>
       </c>
       <c r="D40" t="n">
-        <v>108.4397757610322</v>
+        <v>108.9523475649108</v>
       </c>
       <c r="E40" t="n">
-        <v>108.6664886474609</v>
+        <v>111.0125198364258</v>
       </c>
       <c r="F40" t="n">
-        <v>7097100</v>
+        <v>8700600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B41" t="n">
-        <v>108.5580608670909</v>
+        <v>110.9435236572715</v>
       </c>
       <c r="C41" t="n">
-        <v>111.9588219337512</v>
+        <v>111.1998071396153</v>
       </c>
       <c r="D41" t="n">
-        <v>107.9863451909205</v>
+        <v>109.4452151242777</v>
       </c>
       <c r="E41" t="n">
-        <v>110.24365234375</v>
+        <v>110.519660949707</v>
       </c>
       <c r="F41" t="n">
-        <v>8311300</v>
+        <v>8542300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B42" t="n">
-        <v>109.9873709449201</v>
+        <v>109.3860659107013</v>
       </c>
       <c r="C42" t="n">
-        <v>111.4856720013147</v>
+        <v>110.1943613029524</v>
       </c>
       <c r="D42" t="n">
-        <v>108.9523550527189</v>
+        <v>109.0607743756439</v>
       </c>
       <c r="E42" t="n">
-        <v>111.0125274658203</v>
+        <v>109.8789291381836</v>
       </c>
       <c r="F42" t="n">
-        <v>8700600</v>
+        <v>7950100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B43" t="n">
-        <v>110.9435236572715</v>
+        <v>109.7606408126771</v>
       </c>
       <c r="C43" t="n">
-        <v>111.1998071396153</v>
+        <v>110.3717939308002</v>
       </c>
       <c r="D43" t="n">
-        <v>109.4452151242777</v>
+        <v>109.0213459609701</v>
       </c>
       <c r="E43" t="n">
-        <v>110.519660949707</v>
+        <v>109.7705001831055</v>
       </c>
       <c r="F43" t="n">
-        <v>8542300</v>
+        <v>5746000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B44" t="n">
-        <v>109.3860735058741</v>
+        <v>109.5832124067878</v>
       </c>
       <c r="C44" t="n">
-        <v>110.1943689542488</v>
+        <v>110.115505615394</v>
       </c>
       <c r="D44" t="n">
-        <v>109.0607819482302</v>
+        <v>107.6216187917271</v>
       </c>
       <c r="E44" t="n">
-        <v>109.8789367675781</v>
+        <v>108.9129180908203</v>
       </c>
       <c r="F44" t="n">
-        <v>7950100</v>
+        <v>10291800</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B45" t="n">
-        <v>109.7606408126771</v>
+        <v>108.6862030385313</v>
       </c>
       <c r="C45" t="n">
-        <v>110.3717939308002</v>
+        <v>109.8395012072324</v>
       </c>
       <c r="D45" t="n">
-        <v>109.0213459609701</v>
+        <v>108.4693420111524</v>
       </c>
       <c r="E45" t="n">
-        <v>109.7705001831055</v>
+        <v>109.1593475341797</v>
       </c>
       <c r="F45" t="n">
-        <v>5746000</v>
+        <v>8782100</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B46" t="n">
-        <v>109.5832124067878</v>
+        <v>109.5635011857433</v>
       </c>
       <c r="C46" t="n">
-        <v>110.115505615394</v>
+        <v>111.1800920323978</v>
       </c>
       <c r="D46" t="n">
-        <v>107.6216187917271</v>
+        <v>109.4452112992212</v>
       </c>
       <c r="E46" t="n">
-        <v>108.9129180908203</v>
+        <v>110.637939453125</v>
       </c>
       <c r="F46" t="n">
-        <v>10291800</v>
+        <v>9158700</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B47" t="n">
-        <v>108.6862106348567</v>
+        <v>111.0420979461576</v>
       </c>
       <c r="C47" t="n">
-        <v>109.8395088841645</v>
+        <v>113.3289832533765</v>
       </c>
       <c r="D47" t="n">
-        <v>108.4693495923209</v>
+        <v>110.8153775294455</v>
       </c>
       <c r="E47" t="n">
-        <v>109.1593551635742</v>
+        <v>113.210693359375</v>
       </c>
       <c r="F47" t="n">
-        <v>8782100</v>
+        <v>9713300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B48" t="n">
-        <v>109.5635011857433</v>
+        <v>112.9346801407027</v>
       </c>
       <c r="C48" t="n">
-        <v>111.1800920323978</v>
+        <v>115.4187075091099</v>
       </c>
       <c r="D48" t="n">
-        <v>109.4452112992212</v>
+        <v>112.7572490772096</v>
       </c>
       <c r="E48" t="n">
-        <v>110.637939453125</v>
+        <v>114.984992980957</v>
       </c>
       <c r="F48" t="n">
-        <v>9158700</v>
+        <v>15248700</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B49" t="n">
-        <v>111.0420904629071</v>
+        <v>107.3357644371155</v>
       </c>
       <c r="C49" t="n">
-        <v>113.3289756160103</v>
+        <v>107.7990571232513</v>
       </c>
       <c r="D49" t="n">
-        <v>110.815370061474</v>
+        <v>103.4125769427048</v>
       </c>
       <c r="E49" t="n">
-        <v>113.2106857299805</v>
+        <v>106.0740356445312</v>
       </c>
       <c r="F49" t="n">
-        <v>9713300</v>
+        <v>44045400</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B50" t="n">
-        <v>112.9346876340564</v>
+        <v>105.9853145518839</v>
       </c>
       <c r="C50" t="n">
-        <v>115.4187151672819</v>
+        <v>107.1780502864732</v>
       </c>
       <c r="D50" t="n">
-        <v>112.7572565587906</v>
+        <v>103.7970079445177</v>
       </c>
       <c r="E50" t="n">
-        <v>114.9850006103516</v>
+        <v>104.2898712158203</v>
       </c>
       <c r="F50" t="n">
-        <v>15248700</v>
+        <v>16691400</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B51" t="n">
-        <v>107.3357567169709</v>
+        <v>104.2405758139031</v>
       </c>
       <c r="C51" t="n">
-        <v>107.7990493697842</v>
+        <v>106.1331688606407</v>
       </c>
       <c r="D51" t="n">
-        <v>103.4125695047362</v>
+        <v>103.6195708355819</v>
       </c>
       <c r="E51" t="n">
-        <v>106.0740280151367</v>
+        <v>104.1814346313477</v>
       </c>
       <c r="F51" t="n">
-        <v>44045400</v>
+        <v>12296400</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B52" t="n">
-        <v>105.9853067984581</v>
+        <v>103.5998505812639</v>
       </c>
       <c r="C52" t="n">
-        <v>107.178042445792</v>
+        <v>105.5515923025468</v>
       </c>
       <c r="D52" t="n">
-        <v>103.797000351179</v>
+        <v>103.501279438279</v>
       </c>
       <c r="E52" t="n">
-        <v>104.2898635864258</v>
+        <v>104.7630081176758</v>
       </c>
       <c r="F52" t="n">
-        <v>16691400</v>
+        <v>11796200</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B53" t="n">
-        <v>104.2405758139031</v>
+        <v>104.5658729007312</v>
       </c>
       <c r="C53" t="n">
-        <v>106.1331688606407</v>
+        <v>106.0543145575675</v>
       </c>
       <c r="D53" t="n">
-        <v>103.6195708355819</v>
+        <v>102.5944198257724</v>
       </c>
       <c r="E53" t="n">
-        <v>104.1814346313477</v>
+        <v>103.1759948730469</v>
       </c>
       <c r="F53" t="n">
-        <v>12296400</v>
+        <v>12790000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B54" t="n">
-        <v>103.5998505812639</v>
+        <v>103.8660034269339</v>
       </c>
       <c r="C54" t="n">
-        <v>105.5515923025468</v>
+        <v>104.2898661203646</v>
       </c>
       <c r="D54" t="n">
-        <v>103.501279438279</v>
+        <v>101.0369656805012</v>
       </c>
       <c r="E54" t="n">
-        <v>104.7630081176758</v>
+        <v>101.2341079711914</v>
       </c>
       <c r="F54" t="n">
-        <v>11796200</v>
+        <v>12609900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B55" t="n">
-        <v>104.5658651685615</v>
+        <v>102.0029806312501</v>
       </c>
       <c r="C55" t="n">
-        <v>106.0543067153343</v>
+        <v>103.2844205576738</v>
       </c>
       <c r="D55" t="n">
-        <v>102.5944122393827</v>
+        <v>101.2242558006444</v>
       </c>
       <c r="E55" t="n">
-        <v>103.1759872436523</v>
+        <v>102.7915573120117</v>
       </c>
       <c r="F55" t="n">
-        <v>12790000</v>
+        <v>10785400</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B56" t="n">
-        <v>103.8660034269339</v>
+        <v>102.6042684356238</v>
       </c>
       <c r="C56" t="n">
-        <v>104.2898661203646</v>
+        <v>102.85070006221</v>
       </c>
       <c r="D56" t="n">
-        <v>101.0369656805012</v>
+        <v>100.4356731298631</v>
       </c>
       <c r="E56" t="n">
-        <v>101.2341079711914</v>
+        <v>100.4849624633789</v>
       </c>
       <c r="F56" t="n">
-        <v>12609900</v>
+        <v>15024800</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B57" t="n">
-        <v>102.0029806312501</v>
+        <v>101.0271004353643</v>
       </c>
       <c r="C57" t="n">
-        <v>103.2844205576738</v>
+        <v>102.4366895412752</v>
       </c>
       <c r="D57" t="n">
-        <v>101.2242558006444</v>
+        <v>100.5440965869111</v>
       </c>
       <c r="E57" t="n">
-        <v>102.7915573120117</v>
+        <v>101.8353958129883</v>
       </c>
       <c r="F57" t="n">
-        <v>10785400</v>
+        <v>10574500</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B58" t="n">
-        <v>102.6042684356238</v>
+        <v>101.8452666826232</v>
       </c>
       <c r="C58" t="n">
-        <v>102.85070006221</v>
+        <v>102.7619926734798</v>
       </c>
       <c r="D58" t="n">
-        <v>100.4356731298631</v>
+        <v>101.4115445947565</v>
       </c>
       <c r="E58" t="n">
-        <v>100.4849624633789</v>
+        <v>101.9536972045898</v>
       </c>
       <c r="F58" t="n">
-        <v>15024800</v>
+        <v>10130200</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B59" t="n">
-        <v>101.0271004353643</v>
+        <v>101.8255455445372</v>
       </c>
       <c r="C59" t="n">
-        <v>102.4366895412752</v>
+        <v>103.2449865221035</v>
       </c>
       <c r="D59" t="n">
-        <v>100.5440965869111</v>
+        <v>101.7663968434539</v>
       </c>
       <c r="E59" t="n">
-        <v>101.8353958129883</v>
+        <v>102.9788436889648</v>
       </c>
       <c r="F59" t="n">
-        <v>10574500</v>
+        <v>6525500</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B60" t="n">
-        <v>101.8452666826232</v>
+        <v>103.4224248942611</v>
       </c>
       <c r="C60" t="n">
-        <v>102.7619926734798</v>
+        <v>105.3051661613186</v>
       </c>
       <c r="D60" t="n">
-        <v>101.4115445947565</v>
+        <v>102.9788509675128</v>
       </c>
       <c r="E60" t="n">
-        <v>101.9536972045898</v>
+        <v>105.2460174560547</v>
       </c>
       <c r="F60" t="n">
-        <v>10130200</v>
+        <v>12628900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B61" t="n">
-        <v>101.8255530884873</v>
+        <v>105.0094417410337</v>
       </c>
       <c r="C61" t="n">
-        <v>103.2449941712158</v>
+        <v>105.0488717030799</v>
       </c>
       <c r="D61" t="n">
-        <v>101.7664043830219</v>
+        <v>103.3238503461612</v>
       </c>
       <c r="E61" t="n">
-        <v>102.9788513183594</v>
+        <v>103.3337097167969</v>
       </c>
       <c r="F61" t="n">
-        <v>6525500</v>
+        <v>8548200</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B62" t="n">
-        <v>103.4224248942611</v>
+        <v>103.4027062810859</v>
       </c>
       <c r="C62" t="n">
-        <v>105.3051661613186</v>
+        <v>104.339143401945</v>
       </c>
       <c r="D62" t="n">
-        <v>102.9788509675128</v>
+        <v>102.978843606061</v>
       </c>
       <c r="E62" t="n">
-        <v>105.2460174560547</v>
+        <v>104.230712890625</v>
       </c>
       <c r="F62" t="n">
-        <v>12628900</v>
+        <v>10177800</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B63" t="n">
-        <v>105.0094494941518</v>
+        <v>104.3292907185565</v>
       </c>
       <c r="C63" t="n">
-        <v>105.0488794591093</v>
+        <v>104.7038716073053</v>
       </c>
       <c r="D63" t="n">
-        <v>103.3238579748278</v>
+        <v>103.0182801694252</v>
       </c>
       <c r="E63" t="n">
-        <v>103.3337173461914</v>
+        <v>103.9645767211914</v>
       </c>
       <c r="F63" t="n">
-        <v>8548200</v>
+        <v>11471400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B64" t="n">
-        <v>103.4027138498727</v>
+        <v>103.6787148109135</v>
       </c>
       <c r="C64" t="n">
-        <v>104.3391510392764</v>
+        <v>104.6545819518468</v>
       </c>
       <c r="D64" t="n">
-        <v>102.9788511438223</v>
+        <v>103.0675616662248</v>
       </c>
       <c r="E64" t="n">
-        <v>104.2307205200195</v>
+        <v>103.797004699707</v>
       </c>
       <c r="F64" t="n">
-        <v>10177800</v>
+        <v>10680100</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B65" t="n">
-        <v>104.3292907185565</v>
+        <v>103.7970053004195</v>
       </c>
       <c r="C65" t="n">
-        <v>104.7038716073053</v>
+        <v>106.5077532235307</v>
       </c>
       <c r="D65" t="n">
-        <v>103.0182801694252</v>
+        <v>103.3337126339174</v>
       </c>
       <c r="E65" t="n">
-        <v>103.9645767211914</v>
+        <v>106.0937423706055</v>
       </c>
       <c r="F65" t="n">
-        <v>11471400</v>
+        <v>13727700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B66" t="n">
-        <v>103.6787148109135</v>
+        <v>106.0543107045445</v>
       </c>
       <c r="C66" t="n">
-        <v>104.6545819518468</v>
+        <v>106.2120305546496</v>
       </c>
       <c r="D66" t="n">
-        <v>103.0675616662248</v>
+        <v>105.0291617608474</v>
       </c>
       <c r="E66" t="n">
-        <v>103.797004699707</v>
+        <v>105.4924468994141</v>
       </c>
       <c r="F66" t="n">
-        <v>10680100</v>
+        <v>8549400</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B67" t="n">
-        <v>103.7970053004195</v>
+        <v>105.5910275110776</v>
       </c>
       <c r="C67" t="n">
-        <v>106.5077532235307</v>
+        <v>108.1046256243346</v>
       </c>
       <c r="D67" t="n">
-        <v>103.3337126339174</v>
+        <v>105.0587342879123</v>
       </c>
       <c r="E67" t="n">
-        <v>106.0937423706055</v>
+        <v>107.2766189575195</v>
       </c>
       <c r="F67" t="n">
-        <v>13727700</v>
+        <v>11237900</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B68" t="n">
-        <v>106.0543107045445</v>
+        <v>107.6413280220333</v>
       </c>
       <c r="C68" t="n">
-        <v>106.2120305546496</v>
+        <v>109.9676431038136</v>
       </c>
       <c r="D68" t="n">
-        <v>105.0291617608474</v>
+        <v>107.5526162491543</v>
       </c>
       <c r="E68" t="n">
-        <v>105.4924468994141</v>
+        <v>109.8690719604492</v>
       </c>
       <c r="F68" t="n">
-        <v>8549400</v>
+        <v>13281400</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B69" t="n">
-        <v>105.5910275110776</v>
+        <v>110.1352293411146</v>
       </c>
       <c r="C69" t="n">
-        <v>108.1046256243346</v>
+        <v>111.7222421475927</v>
       </c>
       <c r="D69" t="n">
-        <v>105.0587342879123</v>
+        <v>109.5635061444599</v>
       </c>
       <c r="E69" t="n">
-        <v>107.2766189575195</v>
+        <v>110.007080078125</v>
       </c>
       <c r="F69" t="n">
-        <v>11237900</v>
+        <v>13059100</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,25 +2237,25 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B70" t="n">
-        <v>107.6413280220333</v>
+        <v>109.8582130022918</v>
       </c>
       <c r="C70" t="n">
-        <v>109.9676431038136</v>
+        <v>110.7017554968497</v>
       </c>
       <c r="D70" t="n">
-        <v>107.5526162491543</v>
+        <v>107.7245680705396</v>
       </c>
       <c r="E70" t="n">
-        <v>109.8690719604492</v>
+        <v>109.6498107910156</v>
       </c>
       <c r="F70" t="n">
-        <v>13281400</v>
+        <v>14318000</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B71" t="n">
-        <v>110.1352217028325</v>
+        <v>110.3742651303662</v>
       </c>
       <c r="C71" t="n">
-        <v>111.7222343992454</v>
+        <v>111.991867603266</v>
       </c>
       <c r="D71" t="n">
-        <v>109.5634985458288</v>
+        <v>110.0170020268064</v>
       </c>
       <c r="E71" t="n">
-        <v>110.0070724487305</v>
+        <v>110.7712249755859</v>
       </c>
       <c r="F71" t="n">
-        <v>13059100</v>
+        <v>15580200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,25 +2289,25 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B72" t="n">
-        <v>109.8582130022918</v>
+        <v>110.2154802113721</v>
       </c>
       <c r="C72" t="n">
-        <v>110.7017554968497</v>
+        <v>111.2773434635197</v>
       </c>
       <c r="D72" t="n">
-        <v>107.7245680705396</v>
+        <v>109.6200442181698</v>
       </c>
       <c r="E72" t="n">
-        <v>109.6498107910156</v>
+        <v>109.7887496948242</v>
       </c>
       <c r="F72" t="n">
-        <v>14318000</v>
+        <v>12142500</v>
       </c>
       <c r="G72" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B73" t="n">
-        <v>110.3742651303662</v>
+        <v>109.6895108947102</v>
       </c>
       <c r="C73" t="n">
-        <v>111.991867603266</v>
+        <v>111.9422536896534</v>
       </c>
       <c r="D73" t="n">
-        <v>110.0170020268064</v>
+        <v>109.5803467466885</v>
       </c>
       <c r="E73" t="n">
-        <v>110.7712249755859</v>
+        <v>111.0193252563477</v>
       </c>
       <c r="F73" t="n">
-        <v>15580200</v>
+        <v>12913900</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B74" t="n">
-        <v>110.2154802113721</v>
+        <v>111.4659009625997</v>
       </c>
       <c r="C74" t="n">
-        <v>111.2773434635197</v>
+        <v>112.6170837765976</v>
       </c>
       <c r="D74" t="n">
-        <v>109.6200442181698</v>
+        <v>110.076545265884</v>
       </c>
       <c r="E74" t="n">
-        <v>109.7887496948242</v>
+        <v>110.3941116333008</v>
       </c>
       <c r="F74" t="n">
-        <v>12142500</v>
+        <v>21138400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B75" t="n">
-        <v>109.6895108947102</v>
+        <v>110.5628188428948</v>
       </c>
       <c r="C75" t="n">
-        <v>111.9422536896534</v>
+        <v>111.9422483883379</v>
       </c>
       <c r="D75" t="n">
-        <v>109.5803467466885</v>
+        <v>110.3047938169375</v>
       </c>
       <c r="E75" t="n">
-        <v>111.0193252563477</v>
+        <v>111.5254364013672</v>
       </c>
       <c r="F75" t="n">
-        <v>12913900</v>
+        <v>8803300</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B76" t="n">
-        <v>111.4659009625997</v>
+        <v>111.4361261613625</v>
       </c>
       <c r="C76" t="n">
-        <v>112.6170837765976</v>
+        <v>112.4483665538656</v>
       </c>
       <c r="D76" t="n">
-        <v>110.076545265884</v>
+        <v>111.1880272094238</v>
       </c>
       <c r="E76" t="n">
-        <v>110.3941116333008</v>
+        <v>112.3590545654297</v>
       </c>
       <c r="F76" t="n">
-        <v>21138400</v>
+        <v>7634500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B77" t="n">
-        <v>110.5628188428948</v>
+        <v>112.0811837460467</v>
       </c>
       <c r="C77" t="n">
-        <v>111.9422483883379</v>
+        <v>113.6590894291559</v>
       </c>
       <c r="D77" t="n">
-        <v>110.3047938169375</v>
+        <v>111.9422489401646</v>
       </c>
       <c r="E77" t="n">
-        <v>111.5254364013672</v>
+        <v>113.6094741821289</v>
       </c>
       <c r="F77" t="n">
-        <v>8803300</v>
+        <v>4606700</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B78" t="n">
-        <v>111.4361261613625</v>
+        <v>113.2819819972415</v>
       </c>
       <c r="C78" t="n">
-        <v>112.4483665538656</v>
+        <v>113.8674918845297</v>
       </c>
       <c r="D78" t="n">
-        <v>111.1880272094238</v>
+        <v>112.4086688482299</v>
       </c>
       <c r="E78" t="n">
-        <v>112.3590545654297</v>
+        <v>112.6964645385742</v>
       </c>
       <c r="F78" t="n">
-        <v>7634500</v>
+        <v>5428900</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B79" t="n">
-        <v>112.0811837460467</v>
+        <v>112.4582910949776</v>
       </c>
       <c r="C79" t="n">
-        <v>113.6590894291559</v>
+        <v>113.6193923570513</v>
       </c>
       <c r="D79" t="n">
-        <v>111.9422489401646</v>
+        <v>112.4483650170496</v>
       </c>
       <c r="E79" t="n">
-        <v>113.6094741821289</v>
+        <v>113.3216781616211</v>
       </c>
       <c r="F79" t="n">
-        <v>4606700</v>
+        <v>7966000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B80" t="n">
-        <v>113.2819819972415</v>
+        <v>113.2323587361736</v>
       </c>
       <c r="C80" t="n">
-        <v>113.8674918845297</v>
+        <v>114.4033860775522</v>
       </c>
       <c r="D80" t="n">
-        <v>112.4086688482299</v>
+        <v>113.2323587361736</v>
       </c>
       <c r="E80" t="n">
-        <v>112.6964645385742</v>
+        <v>113.9171142578125</v>
       </c>
       <c r="F80" t="n">
-        <v>5428900</v>
+        <v>6883900</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B81" t="n">
-        <v>112.4582910949776</v>
+        <v>113.8972648993226</v>
       </c>
       <c r="C81" t="n">
-        <v>113.6193923570513</v>
+        <v>114.0163551233871</v>
       </c>
       <c r="D81" t="n">
-        <v>112.4483650170496</v>
+        <v>112.6865483592072</v>
       </c>
       <c r="E81" t="n">
-        <v>113.3216781616211</v>
+        <v>112.9048690795898</v>
       </c>
       <c r="F81" t="n">
-        <v>7966000</v>
+        <v>6608000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B82" t="n">
-        <v>113.2323587361736</v>
+        <v>112.5773868999257</v>
       </c>
       <c r="C82" t="n">
-        <v>114.4033860775522</v>
+        <v>112.5773868999257</v>
       </c>
       <c r="D82" t="n">
-        <v>113.2323587361736</v>
+        <v>110.7712267677642</v>
       </c>
       <c r="E82" t="n">
-        <v>113.9171142578125</v>
+        <v>110.9994735717773</v>
       </c>
       <c r="F82" t="n">
-        <v>6883900</v>
+        <v>8906200</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B83" t="n">
-        <v>113.8972648993226</v>
+        <v>110.5727405037633</v>
       </c>
       <c r="C83" t="n">
-        <v>114.0163551233871</v>
+        <v>115.1476858420111</v>
       </c>
       <c r="D83" t="n">
-        <v>112.6865483592072</v>
+        <v>110.5330437623775</v>
       </c>
       <c r="E83" t="n">
-        <v>112.9048690795898</v>
+        <v>113.2025909423828</v>
       </c>
       <c r="F83" t="n">
-        <v>6608000</v>
+        <v>12029000</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B84" t="n">
-        <v>112.5773868999257</v>
+        <v>112.9247239572814</v>
       </c>
       <c r="C84" t="n">
-        <v>112.5773868999257</v>
+        <v>113.8873491370408</v>
       </c>
       <c r="D84" t="n">
-        <v>110.7712267677642</v>
+        <v>112.2498944807456</v>
       </c>
       <c r="E84" t="n">
-        <v>110.9994735717773</v>
+        <v>113.6987915039062</v>
       </c>
       <c r="F84" t="n">
-        <v>8906200</v>
+        <v>7388300</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B85" t="n">
-        <v>110.5727405037633</v>
+        <v>113.58962345171</v>
       </c>
       <c r="C85" t="n">
-        <v>115.1476858420111</v>
+        <v>114.0957474345631</v>
       </c>
       <c r="D85" t="n">
-        <v>110.5330437623775</v>
+        <v>111.6544546516531</v>
       </c>
       <c r="E85" t="n">
-        <v>113.2025909423828</v>
+        <v>112.0514144897461</v>
       </c>
       <c r="F85" t="n">
-        <v>12029000</v>
+        <v>8296300</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B86" t="n">
-        <v>112.9247239572814</v>
+        <v>111.6941501294552</v>
       </c>
       <c r="C86" t="n">
-        <v>113.8873491370408</v>
+        <v>114.1155907288179</v>
       </c>
       <c r="D86" t="n">
-        <v>112.2498944807456</v>
+        <v>111.6941501294552</v>
       </c>
       <c r="E86" t="n">
-        <v>113.6987915039062</v>
+        <v>113.3018264770508</v>
       </c>
       <c r="F86" t="n">
-        <v>7388300</v>
+        <v>9778200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B87" t="n">
-        <v>113.58962345171</v>
+        <v>113.4407639362947</v>
       </c>
       <c r="C87" t="n">
-        <v>114.0957474345631</v>
+        <v>115.0980707124986</v>
       </c>
       <c r="D87" t="n">
-        <v>111.6544546516531</v>
+        <v>113.0338855865844</v>
       </c>
       <c r="E87" t="n">
-        <v>112.0514144897461</v>
+        <v>114.9988250732422</v>
       </c>
       <c r="F87" t="n">
-        <v>8296300</v>
+        <v>8935200</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B88" t="n">
-        <v>111.6941501294552</v>
+        <v>113.7583311963079</v>
       </c>
       <c r="C88" t="n">
-        <v>114.1155907288179</v>
+        <v>114.0659790519541</v>
       </c>
       <c r="D88" t="n">
-        <v>111.6941501294552</v>
+        <v>111.6941536254426</v>
       </c>
       <c r="E88" t="n">
-        <v>113.3018264770508</v>
+        <v>111.9620971679688</v>
       </c>
       <c r="F88" t="n">
-        <v>9778200</v>
+        <v>10833800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B89" t="n">
-        <v>113.4407639362947</v>
+        <v>111.9819377501375</v>
       </c>
       <c r="C89" t="n">
-        <v>115.0980707124986</v>
+        <v>112.3590529975045</v>
       </c>
       <c r="D89" t="n">
-        <v>113.0338855865844</v>
+        <v>110.7612951636049</v>
       </c>
       <c r="E89" t="n">
-        <v>114.9988250732422</v>
+        <v>112.1208801269531</v>
       </c>
       <c r="F89" t="n">
-        <v>8935200</v>
+        <v>8945700</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B90" t="n">
-        <v>113.7583311963079</v>
+        <v>111.9521684493894</v>
       </c>
       <c r="C90" t="n">
-        <v>114.0659790519541</v>
+        <v>112.7262359666306</v>
       </c>
       <c r="D90" t="n">
-        <v>111.6941536254426</v>
+        <v>111.4063552989297</v>
       </c>
       <c r="E90" t="n">
-        <v>111.9620971679688</v>
+        <v>112.6666946411133</v>
       </c>
       <c r="F90" t="n">
-        <v>10833800</v>
+        <v>8950900</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B91" t="n">
-        <v>111.9819377501375</v>
+        <v>112.8453292583326</v>
       </c>
       <c r="C91" t="n">
-        <v>112.3590529975045</v>
+        <v>113.242289105796</v>
       </c>
       <c r="D91" t="n">
-        <v>110.7612951636049</v>
+        <v>111.3170387669949</v>
       </c>
       <c r="E91" t="n">
-        <v>112.1208801269531</v>
+        <v>112.5476150512695</v>
       </c>
       <c r="F91" t="n">
-        <v>8945700</v>
+        <v>7958500</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B92" t="n">
-        <v>111.9521684493894</v>
+        <v>112.339199834173</v>
       </c>
       <c r="C92" t="n">
-        <v>112.7262359666306</v>
+        <v>112.9842586087029</v>
       </c>
       <c r="D92" t="n">
-        <v>111.4063552989297</v>
+        <v>110.2750223556077</v>
       </c>
       <c r="E92" t="n">
-        <v>112.6666946411133</v>
+        <v>110.3544082641602</v>
       </c>
       <c r="F92" t="n">
-        <v>8950900</v>
+        <v>12049600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B93" t="n">
-        <v>112.8453292583326</v>
+        <v>108.8261317696502</v>
       </c>
       <c r="C93" t="n">
-        <v>113.242289105796</v>
+        <v>110.2452505565117</v>
       </c>
       <c r="D93" t="n">
-        <v>111.3170387669949</v>
+        <v>107.9726707390225</v>
       </c>
       <c r="E93" t="n">
-        <v>112.5476150512695</v>
+        <v>109.5009536743164</v>
       </c>
       <c r="F93" t="n">
-        <v>7958500</v>
+        <v>9818200</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B94" t="n">
-        <v>112.339199834173</v>
+        <v>109.7292049082389</v>
       </c>
       <c r="C94" t="n">
-        <v>112.9842586087029</v>
+        <v>112.3888259939984</v>
       </c>
       <c r="D94" t="n">
-        <v>110.2750223556077</v>
+        <v>109.6597375040779</v>
       </c>
       <c r="E94" t="n">
-        <v>110.3544082641602</v>
+        <v>112.3292846679688</v>
       </c>
       <c r="F94" t="n">
-        <v>12049600</v>
+        <v>10041400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B95" t="n">
-        <v>108.8261317696502</v>
+        <v>112.3094319821855</v>
       </c>
       <c r="C95" t="n">
-        <v>110.2452505565117</v>
+        <v>113.4209180149001</v>
       </c>
       <c r="D95" t="n">
-        <v>107.9726707390225</v>
+        <v>111.317036172348</v>
       </c>
       <c r="E95" t="n">
-        <v>109.5009536743164</v>
+        <v>112.3491287231445</v>
       </c>
       <c r="F95" t="n">
-        <v>9818200</v>
+        <v>12437700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B96" t="n">
-        <v>109.7292049082389</v>
+        <v>111.8330891095483</v>
       </c>
       <c r="C96" t="n">
-        <v>112.3888259939984</v>
+        <v>112.0911065753488</v>
       </c>
       <c r="D96" t="n">
-        <v>109.6597375040779</v>
+        <v>109.7093626275885</v>
       </c>
       <c r="E96" t="n">
-        <v>112.3292846679688</v>
+        <v>110.1360931396484</v>
       </c>
       <c r="F96" t="n">
-        <v>10041400</v>
+        <v>10819800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B97" t="n">
-        <v>112.3094319821855</v>
+        <v>110.8307664528259</v>
       </c>
       <c r="C97" t="n">
-        <v>113.4209180149001</v>
+        <v>111.5552187391887</v>
       </c>
       <c r="D97" t="n">
-        <v>111.317036172348</v>
+        <v>110.2849457184854</v>
       </c>
       <c r="E97" t="n">
-        <v>112.3491287231445</v>
+        <v>110.4635772705078</v>
       </c>
       <c r="F97" t="n">
-        <v>12437700</v>
+        <v>8859800</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B98" t="n">
-        <v>111.8330891095483</v>
+        <v>110.6521373409646</v>
       </c>
       <c r="C98" t="n">
-        <v>112.0911065753488</v>
+        <v>110.9498591246939</v>
       </c>
       <c r="D98" t="n">
-        <v>109.7093626275885</v>
+        <v>109.1933142291742</v>
       </c>
       <c r="E98" t="n">
-        <v>110.1360931396484</v>
+        <v>109.7689056396484</v>
       </c>
       <c r="F98" t="n">
-        <v>10819800</v>
+        <v>8956900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B99" t="n">
-        <v>110.8307664528259</v>
+        <v>109.4414091319104</v>
       </c>
       <c r="C99" t="n">
-        <v>111.5552187391887</v>
+        <v>110.5826658320299</v>
       </c>
       <c r="D99" t="n">
-        <v>110.2849457184854</v>
+        <v>108.1711437016965</v>
       </c>
       <c r="E99" t="n">
-        <v>110.4635772705078</v>
+        <v>108.7268829345703</v>
       </c>
       <c r="F99" t="n">
-        <v>8859800</v>
+        <v>9016600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B100" t="n">
-        <v>110.6521373409646</v>
+        <v>108.7963528121511</v>
       </c>
       <c r="C100" t="n">
-        <v>110.9498591246939</v>
+        <v>110.8208412268483</v>
       </c>
       <c r="D100" t="n">
-        <v>109.1933142291742</v>
+        <v>107.932973280219</v>
       </c>
       <c r="E100" t="n">
-        <v>109.7689056396484</v>
+        <v>110.7315292358398</v>
       </c>
       <c r="F100" t="n">
-        <v>8956900</v>
+        <v>11079000</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B101" t="n">
-        <v>109.4414091319104</v>
+        <v>110.5132006888762</v>
       </c>
       <c r="C101" t="n">
-        <v>110.5826658320299</v>
+        <v>112.0911064308015</v>
       </c>
       <c r="D101" t="n">
-        <v>108.1711437016965</v>
+        <v>110.1460115045699</v>
       </c>
       <c r="E101" t="n">
-        <v>108.7268829345703</v>
+        <v>111.942253112793</v>
       </c>
       <c r="F101" t="n">
-        <v>9016600</v>
+        <v>17895200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B102" t="n">
-        <v>108.7963528121511</v>
+        <v>103.219089824791</v>
       </c>
       <c r="C102" t="n">
-        <v>110.8208412268483</v>
+        <v>107.7841090146985</v>
       </c>
       <c r="D102" t="n">
-        <v>107.932973280219</v>
+        <v>102.961064795438</v>
       </c>
       <c r="E102" t="n">
-        <v>110.7315292358398</v>
+        <v>103.6557388305664</v>
       </c>
       <c r="F102" t="n">
-        <v>11079000</v>
+        <v>37778500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B103" t="n">
-        <v>110.5132006888762</v>
+        <v>103.9832294528008</v>
       </c>
       <c r="C103" t="n">
-        <v>112.0911064308015</v>
+        <v>104.1916316597105</v>
       </c>
       <c r="D103" t="n">
-        <v>110.1460115045699</v>
+        <v>101.5617813072958</v>
       </c>
       <c r="E103" t="n">
-        <v>111.942253112793</v>
+        <v>103.427490234375</v>
       </c>
       <c r="F103" t="n">
-        <v>17895200</v>
+        <v>24827100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B104" t="n">
-        <v>103.219089824791</v>
+        <v>103.4076429857971</v>
       </c>
       <c r="C104" t="n">
-        <v>107.7841090146985</v>
+        <v>107.7741861743833</v>
       </c>
       <c r="D104" t="n">
-        <v>102.961064795438</v>
+        <v>102.841977662662</v>
       </c>
       <c r="E104" t="n">
-        <v>103.6557388305664</v>
+        <v>106.2359771728516</v>
       </c>
       <c r="F104" t="n">
-        <v>37778500</v>
+        <v>19070400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B105" t="n">
-        <v>103.9832294528008</v>
+        <v>106.2359762120697</v>
       </c>
       <c r="C105" t="n">
-        <v>104.1916316597105</v>
+        <v>107.5062416580512</v>
       </c>
       <c r="D105" t="n">
-        <v>101.5617813072958</v>
+        <v>104.0130041102228</v>
       </c>
       <c r="E105" t="n">
-        <v>103.427490234375</v>
+        <v>104.1717910766602</v>
       </c>
       <c r="F105" t="n">
-        <v>24827100</v>
+        <v>11859500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B106" t="n">
-        <v>103.4076429857971</v>
+        <v>105.3229638054753</v>
       </c>
       <c r="C106" t="n">
-        <v>107.7741861743833</v>
+        <v>108.1314457439972</v>
       </c>
       <c r="D106" t="n">
-        <v>102.841977662662</v>
+        <v>104.5687484468834</v>
       </c>
       <c r="E106" t="n">
-        <v>106.2359771728516</v>
+        <v>107.873420715332</v>
       </c>
       <c r="F106" t="n">
-        <v>19070400</v>
+        <v>12105600</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B107" t="n">
-        <v>106.2359762120697</v>
+        <v>107.8635036441641</v>
       </c>
       <c r="C107" t="n">
-        <v>107.5062416580512</v>
+        <v>108.09175044183</v>
       </c>
       <c r="D107" t="n">
-        <v>104.0130041102228</v>
+        <v>105.9580979235442</v>
       </c>
       <c r="E107" t="n">
-        <v>104.1717910766602</v>
+        <v>106.3153610229492</v>
       </c>
       <c r="F107" t="n">
-        <v>11859500</v>
+        <v>10515400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B108" t="n">
-        <v>105.3229638054753</v>
+        <v>106.7817856582252</v>
       </c>
       <c r="C108" t="n">
-        <v>108.1314457439972</v>
+        <v>110.265097006608</v>
       </c>
       <c r="D108" t="n">
-        <v>104.5687484468834</v>
+        <v>106.7817856582252</v>
       </c>
       <c r="E108" t="n">
-        <v>107.873420715332</v>
+        <v>109.1238403320312</v>
       </c>
       <c r="F108" t="n">
-        <v>12105600</v>
+        <v>9815500</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B109" t="n">
-        <v>107.8635036441641</v>
+        <v>108.1016744764874</v>
       </c>
       <c r="C109" t="n">
-        <v>108.09175044183</v>
+        <v>109.0345289485641</v>
       </c>
       <c r="D109" t="n">
-        <v>105.9580979235442</v>
+        <v>106.9802699515072</v>
       </c>
       <c r="E109" t="n">
-        <v>106.3153610229492</v>
+        <v>107.2978363037109</v>
       </c>
       <c r="F109" t="n">
-        <v>10515400</v>
+        <v>9374900</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B110" t="n">
-        <v>106.7817856582252</v>
+        <v>107.1092782571758</v>
       </c>
       <c r="C110" t="n">
-        <v>110.265097006608</v>
+        <v>107.3375326210063</v>
       </c>
       <c r="D110" t="n">
-        <v>106.7817856582252</v>
+        <v>100.2518196922704</v>
       </c>
       <c r="E110" t="n">
-        <v>109.1238403320312</v>
+        <v>101.6014785766602</v>
       </c>
       <c r="F110" t="n">
-        <v>9815500</v>
+        <v>25319600</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B111" t="n">
-        <v>108.1016744764874</v>
+        <v>100.6289339445357</v>
       </c>
       <c r="C111" t="n">
-        <v>109.0345289485641</v>
+        <v>104.7175997261971</v>
       </c>
       <c r="D111" t="n">
-        <v>106.9802699515072</v>
+        <v>100.4304502450412</v>
       </c>
       <c r="E111" t="n">
-        <v>107.2978363037109</v>
+        <v>104.6481323242188</v>
       </c>
       <c r="F111" t="n">
-        <v>9374900</v>
+        <v>12845300</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B112" t="n">
-        <v>107.1092782571758</v>
+        <v>105.7596186239472</v>
       </c>
       <c r="C112" t="n">
-        <v>107.3375326210063</v>
+        <v>106.4642187235269</v>
       </c>
       <c r="D112" t="n">
-        <v>100.2518196922704</v>
+        <v>103.576350923035</v>
       </c>
       <c r="E112" t="n">
-        <v>101.6014785766602</v>
+        <v>104.6382141113281</v>
       </c>
       <c r="F112" t="n">
-        <v>25319600</v>
+        <v>10467400</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B113" t="n">
-        <v>100.6289339445357</v>
+        <v>105.1542604930163</v>
       </c>
       <c r="C113" t="n">
-        <v>104.7175997261971</v>
+        <v>106.9108053396402</v>
       </c>
       <c r="D113" t="n">
-        <v>100.4304502450412</v>
+        <v>105.0053996052954</v>
       </c>
       <c r="E113" t="n">
-        <v>104.6481323242188</v>
+        <v>106.2855911254883</v>
       </c>
       <c r="F113" t="n">
-        <v>12845300</v>
+        <v>8791600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B114" t="n">
-        <v>105.7596186239472</v>
+        <v>106.2955144080048</v>
       </c>
       <c r="C114" t="n">
-        <v>106.4642187235269</v>
+        <v>106.9504916968191</v>
       </c>
       <c r="D114" t="n">
-        <v>103.576350923035</v>
+        <v>104.6481337509456</v>
       </c>
       <c r="E114" t="n">
-        <v>104.6382141113281</v>
+        <v>105.1939544677734</v>
       </c>
       <c r="F114" t="n">
-        <v>10467400</v>
+        <v>7492900</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B115" t="n">
-        <v>105.1542604930163</v>
+        <v>104.8069236784645</v>
       </c>
       <c r="C115" t="n">
-        <v>106.9108053396402</v>
+        <v>105.3924335809217</v>
       </c>
       <c r="D115" t="n">
-        <v>105.0053996052954</v>
+        <v>103.8542245950799</v>
       </c>
       <c r="E115" t="n">
-        <v>106.2855911254883</v>
+        <v>104.7771530151367</v>
       </c>
       <c r="F115" t="n">
-        <v>8791600</v>
+        <v>9043600</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B116" t="n">
-        <v>106.2955144080048</v>
+        <v>104.1817160321379</v>
       </c>
       <c r="C116" t="n">
-        <v>106.9504916968191</v>
+        <v>104.3901182448065</v>
       </c>
       <c r="D116" t="n">
-        <v>104.6481337509456</v>
+        <v>102.1770722450568</v>
       </c>
       <c r="E116" t="n">
-        <v>105.1939544677734</v>
+        <v>103.6160507202148</v>
       </c>
       <c r="F116" t="n">
-        <v>7492900</v>
+        <v>10626500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B117" t="n">
-        <v>104.8069236784645</v>
+        <v>103.6557367363695</v>
       </c>
       <c r="C117" t="n">
-        <v>105.3924335809217</v>
+        <v>106.4146033792047</v>
       </c>
       <c r="D117" t="n">
-        <v>103.8542245950799</v>
+        <v>103.1893170772804</v>
       </c>
       <c r="E117" t="n">
-        <v>104.7771530151367</v>
+        <v>105.2435760498047</v>
       </c>
       <c r="F117" t="n">
-        <v>9043600</v>
+        <v>13594800</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B118" t="n">
-        <v>104.1817160321379</v>
+        <v>105.193955544271</v>
       </c>
       <c r="C118" t="n">
-        <v>104.3901182448065</v>
+        <v>105.9084817367471</v>
       </c>
       <c r="D118" t="n">
-        <v>102.1770722450568</v>
+        <v>103.7152879117953</v>
       </c>
       <c r="E118" t="n">
-        <v>103.6160507202148</v>
+        <v>104.2511825561523</v>
       </c>
       <c r="F118" t="n">
-        <v>10626500</v>
+        <v>8556500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B119" t="n">
-        <v>103.6557367363695</v>
+        <v>104.6679896339684</v>
       </c>
       <c r="C119" t="n">
-        <v>106.4146033792047</v>
+        <v>105.9580996730059</v>
       </c>
       <c r="D119" t="n">
-        <v>103.1893170772804</v>
+        <v>104.519128744862</v>
       </c>
       <c r="E119" t="n">
-        <v>105.2435760498047</v>
+        <v>104.7473831176758</v>
       </c>
       <c r="F119" t="n">
-        <v>13594800</v>
+        <v>9578500</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B120" t="n">
-        <v>105.193955544271</v>
+        <v>103.9832293953731</v>
       </c>
       <c r="C120" t="n">
-        <v>105.9084817367471</v>
+        <v>105.5313644009208</v>
       </c>
       <c r="D120" t="n">
-        <v>103.7152879117953</v>
+        <v>103.1396944903344</v>
       </c>
       <c r="E120" t="n">
-        <v>104.2511825561523</v>
+        <v>105.2336502075195</v>
       </c>
       <c r="F120" t="n">
-        <v>8556500</v>
+        <v>13954000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B121" t="n">
-        <v>104.6679896339684</v>
+        <v>103.8145288629893</v>
       </c>
       <c r="C121" t="n">
-        <v>105.9580996730059</v>
+        <v>103.8145288629893</v>
       </c>
       <c r="D121" t="n">
-        <v>104.519128744862</v>
+        <v>102.0778361524432</v>
       </c>
       <c r="E121" t="n">
-        <v>104.7473831176758</v>
+        <v>103.5366592407227</v>
       </c>
       <c r="F121" t="n">
-        <v>9578500</v>
+        <v>14178600</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B122" t="n">
-        <v>103.9832293953731</v>
+        <v>102.0579794936243</v>
       </c>
       <c r="C122" t="n">
-        <v>105.5313644009208</v>
+        <v>103.5168025175497</v>
       </c>
       <c r="D122" t="n">
-        <v>103.1396944903344</v>
+        <v>101.3732315464965</v>
       </c>
       <c r="E122" t="n">
-        <v>105.2336502075195</v>
+        <v>102.5144882202148</v>
       </c>
       <c r="F122" t="n">
-        <v>13954000</v>
+        <v>13608400</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B123" t="n">
-        <v>103.8145288629893</v>
+        <v>102.3854784619134</v>
       </c>
       <c r="C123" t="n">
-        <v>103.8145288629893</v>
+        <v>103.0503818671043</v>
       </c>
       <c r="D123" t="n">
-        <v>102.0778361524432</v>
+        <v>101.8595098706018</v>
       </c>
       <c r="E123" t="n">
-        <v>103.5366592407227</v>
+        <v>102.2564697265625</v>
       </c>
       <c r="F123" t="n">
-        <v>14178600</v>
+        <v>9672300</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B124" t="n">
-        <v>102.0579794936243</v>
+        <v>102.3160040474863</v>
       </c>
       <c r="C124" t="n">
-        <v>103.5168025175497</v>
+        <v>103.7549824803676</v>
       </c>
       <c r="D124" t="n">
-        <v>101.3732315464965</v>
+        <v>100.8174842902717</v>
       </c>
       <c r="E124" t="n">
-        <v>102.5144882202148</v>
+        <v>101.6312561035156</v>
       </c>
       <c r="F124" t="n">
-        <v>13608400</v>
+        <v>11751500</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B125" t="n">
-        <v>102.3854784619134</v>
+        <v>100.6190147793836</v>
       </c>
       <c r="C125" t="n">
-        <v>103.0503818671043</v>
+        <v>101.0358192198888</v>
       </c>
       <c r="D125" t="n">
-        <v>101.8595098706018</v>
+        <v>99.18996233036073</v>
       </c>
       <c r="E125" t="n">
-        <v>102.2564697265625</v>
+        <v>100.7678756713867</v>
       </c>
       <c r="F125" t="n">
-        <v>9672300</v>
+        <v>10448600</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B126" t="n">
-        <v>102.3160040474863</v>
+        <v>99.78540292258373</v>
       </c>
       <c r="C126" t="n">
-        <v>103.7549824803676</v>
+        <v>101.0953651046626</v>
       </c>
       <c r="D126" t="n">
-        <v>100.8174842902717</v>
+        <v>97.70136563944882</v>
       </c>
       <c r="E126" t="n">
-        <v>101.6312561035156</v>
+        <v>100.886962890625</v>
       </c>
       <c r="F126" t="n">
-        <v>11751500</v>
+        <v>11715100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B127" t="n">
-        <v>100.6190147793836</v>
+        <v>100.9762757982457</v>
       </c>
       <c r="C127" t="n">
-        <v>101.0358192198888</v>
+        <v>101.4625476354206</v>
       </c>
       <c r="D127" t="n">
-        <v>99.18996233036073</v>
+        <v>99.47775597353863</v>
       </c>
       <c r="E127" t="n">
-        <v>100.7678756713867</v>
+        <v>100.5495452880859</v>
       </c>
       <c r="F127" t="n">
-        <v>10448600</v>
+        <v>7833100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B128" t="n">
-        <v>99.78540292258373</v>
+        <v>100.6289343352219</v>
       </c>
       <c r="C128" t="n">
-        <v>101.0953651046626</v>
+        <v>101.1152061509584</v>
       </c>
       <c r="D128" t="n">
-        <v>97.70136563944882</v>
+        <v>99.63653854803313</v>
       </c>
       <c r="E128" t="n">
-        <v>100.886962890625</v>
+        <v>100.1228103637695</v>
       </c>
       <c r="F128" t="n">
-        <v>11715100</v>
+        <v>8152800</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B129" t="n">
-        <v>100.9762757982457</v>
+        <v>99.33882308016651</v>
       </c>
       <c r="C129" t="n">
-        <v>101.4625476354206</v>
+        <v>100.1128906318194</v>
       </c>
       <c r="D129" t="n">
-        <v>99.47775597353863</v>
+        <v>98.61437834957015</v>
       </c>
       <c r="E129" t="n">
-        <v>100.5495452880859</v>
+        <v>98.67391967773438</v>
       </c>
       <c r="F129" t="n">
-        <v>7833100</v>
+        <v>10309400</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B130" t="n">
-        <v>100.6289343352219</v>
+        <v>99.07087541929553</v>
       </c>
       <c r="C130" t="n">
-        <v>101.1152061509584</v>
+        <v>100.0037223311207</v>
       </c>
       <c r="D130" t="n">
-        <v>99.63653854803313</v>
+        <v>98.4059720444657</v>
       </c>
       <c r="E130" t="n">
-        <v>100.1228103637695</v>
+        <v>98.53498077392578</v>
       </c>
       <c r="F130" t="n">
-        <v>8152800</v>
+        <v>9551500</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B131" t="n">
-        <v>99.33882308016651</v>
+        <v>98.71361296789499</v>
       </c>
       <c r="C131" t="n">
-        <v>100.1128906318194</v>
+        <v>98.93194125870065</v>
       </c>
       <c r="D131" t="n">
-        <v>98.61437834957015</v>
+        <v>97.71129107436866</v>
       </c>
       <c r="E131" t="n">
-        <v>98.67391967773438</v>
+        <v>97.90977478027344</v>
       </c>
       <c r="F131" t="n">
-        <v>10309400</v>
+        <v>11578500</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B132" t="n">
-        <v>99.07087541929553</v>
+        <v>98.41588802886785</v>
       </c>
       <c r="C132" t="n">
-        <v>100.0037223311207</v>
+        <v>99.94417844396594</v>
       </c>
       <c r="D132" t="n">
-        <v>98.4059720444657</v>
+        <v>98.26702714707265</v>
       </c>
       <c r="E132" t="n">
-        <v>98.53498077392578</v>
+        <v>99.53730010986328</v>
       </c>
       <c r="F132" t="n">
-        <v>9551500</v>
+        <v>11785600</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B133" t="n">
-        <v>98.71361296789499</v>
+        <v>99.08079827635559</v>
       </c>
       <c r="C133" t="n">
-        <v>98.93194125870065</v>
+        <v>100.2518256851255</v>
       </c>
       <c r="D133" t="n">
-        <v>97.71129107436866</v>
+        <v>98.24718939454284</v>
       </c>
       <c r="E133" t="n">
-        <v>97.90977478027344</v>
+        <v>98.66399383544922</v>
       </c>
       <c r="F133" t="n">
-        <v>11578500</v>
+        <v>12615100</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B134" t="n">
-        <v>98.41588802886785</v>
+        <v>98.2769579779315</v>
       </c>
       <c r="C134" t="n">
-        <v>99.94417844396594</v>
+        <v>100.0136506829842</v>
       </c>
       <c r="D134" t="n">
-        <v>98.26702714707265</v>
+        <v>97.69144807163296</v>
       </c>
       <c r="E134" t="n">
-        <v>99.53730010986328</v>
+        <v>98.44566345214844</v>
       </c>
       <c r="F134" t="n">
-        <v>11785600</v>
+        <v>14793800</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B135" t="n">
-        <v>99.08079827635559</v>
+        <v>98.25711324225701</v>
       </c>
       <c r="C135" t="n">
-        <v>100.2518256851255</v>
+        <v>99.269353657388</v>
       </c>
       <c r="D135" t="n">
-        <v>98.24718939454284</v>
+        <v>97.64182510199821</v>
       </c>
       <c r="E135" t="n">
-        <v>98.66399383544922</v>
+        <v>98.75331115722656</v>
       </c>
       <c r="F135" t="n">
-        <v>12615100</v>
+        <v>27544200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B136" t="n">
-        <v>98.2769579779315</v>
+        <v>99.45791247863863</v>
       </c>
       <c r="C136" t="n">
-        <v>100.0136506829842</v>
+        <v>99.83502017283372</v>
       </c>
       <c r="D136" t="n">
-        <v>97.69144807163296</v>
+        <v>97.11585768623267</v>
       </c>
       <c r="E136" t="n">
-        <v>98.44566345214844</v>
+        <v>97.20516967773438</v>
       </c>
       <c r="F136" t="n">
-        <v>14793800</v>
+        <v>11373000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B137" t="n">
-        <v>98.25711324225701</v>
+        <v>96.99676871718921</v>
       </c>
       <c r="C137" t="n">
-        <v>99.269353657388</v>
+        <v>97.30441658068045</v>
       </c>
       <c r="D137" t="n">
-        <v>97.64182510199821</v>
+        <v>95.5181010136908</v>
       </c>
       <c r="E137" t="n">
-        <v>98.75331115722656</v>
+        <v>95.65703582763672</v>
       </c>
       <c r="F137" t="n">
-        <v>27544200</v>
+        <v>9155700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B138" t="n">
-        <v>99.45791247863863</v>
+        <v>96.08376214252051</v>
       </c>
       <c r="C138" t="n">
-        <v>99.83502017283372</v>
+        <v>96.44102524028141</v>
       </c>
       <c r="D138" t="n">
-        <v>97.11585768623267</v>
+        <v>94.33714339473161</v>
       </c>
       <c r="E138" t="n">
-        <v>97.20516967773438</v>
+        <v>95.22037506103516</v>
       </c>
       <c r="F138" t="n">
-        <v>11373000</v>
+        <v>8467500</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B139" t="n">
-        <v>96.99676871718921</v>
+        <v>94.3966920435457</v>
       </c>
       <c r="C139" t="n">
-        <v>97.30441658068045</v>
+        <v>95.66695746718439</v>
       </c>
       <c r="D139" t="n">
-        <v>95.5181010136908</v>
+        <v>93.87071590500793</v>
       </c>
       <c r="E139" t="n">
-        <v>95.65703582763672</v>
+        <v>94.02950286865234</v>
       </c>
       <c r="F139" t="n">
-        <v>9155700</v>
+        <v>8548800</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B140" t="n">
-        <v>96.08376214252051</v>
+        <v>93.47376126842354</v>
       </c>
       <c r="C140" t="n">
-        <v>96.44102524028141</v>
+        <v>93.47376126842354</v>
       </c>
       <c r="D140" t="n">
-        <v>94.33714339473161</v>
+        <v>91.48896970147202</v>
       </c>
       <c r="E140" t="n">
-        <v>95.22037506103516</v>
+        <v>91.71721649169922</v>
       </c>
       <c r="F140" t="n">
-        <v>8467500</v>
+        <v>12475900</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B141" t="n">
-        <v>94.3966920435457</v>
+        <v>92.18364921591858</v>
       </c>
       <c r="C141" t="n">
-        <v>95.66695746718439</v>
+        <v>94.46616268251262</v>
       </c>
       <c r="D141" t="n">
-        <v>93.87071590500793</v>
+        <v>92.18364921591858</v>
       </c>
       <c r="E141" t="n">
-        <v>94.02950286865234</v>
+        <v>93.60277557373047</v>
       </c>
       <c r="F141" t="n">
-        <v>8548800</v>
+        <v>10592600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B142" t="n">
-        <v>93.47376126842354</v>
+        <v>94.61501738536155</v>
       </c>
       <c r="C142" t="n">
-        <v>93.47376126842354</v>
+        <v>96.15323399247868</v>
       </c>
       <c r="D142" t="n">
-        <v>91.48896970147202</v>
+        <v>93.47376820675542</v>
       </c>
       <c r="E142" t="n">
-        <v>91.71721649169922</v>
+        <v>95.64710998535156</v>
       </c>
       <c r="F142" t="n">
-        <v>12475900</v>
+        <v>11180200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B143" t="n">
-        <v>92.18364921591858</v>
+        <v>96.52041860940267</v>
       </c>
       <c r="C143" t="n">
-        <v>94.46616268251262</v>
+        <v>97.61205248622655</v>
       </c>
       <c r="D143" t="n">
-        <v>92.18364921591858</v>
+        <v>95.75626959566054</v>
       </c>
       <c r="E143" t="n">
-        <v>93.60277557373047</v>
+        <v>95.82573699951172</v>
       </c>
       <c r="F143" t="n">
-        <v>10592600</v>
+        <v>8518600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B144" t="n">
-        <v>94.61501738536155</v>
+        <v>95.26999653948798</v>
       </c>
       <c r="C144" t="n">
-        <v>96.15323399247868</v>
+        <v>96.43109780518201</v>
       </c>
       <c r="D144" t="n">
-        <v>93.47376820675542</v>
+        <v>94.36691272969546</v>
       </c>
       <c r="E144" t="n">
-        <v>95.64710998535156</v>
+        <v>95.87535858154297</v>
       </c>
       <c r="F144" t="n">
-        <v>11180200</v>
+        <v>6379100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B145" t="n">
-        <v>96.52041860940267</v>
+        <v>95.76619510964362</v>
       </c>
       <c r="C145" t="n">
-        <v>97.61205248622655</v>
+        <v>96.4211799747073</v>
       </c>
       <c r="D145" t="n">
-        <v>95.75626959566054</v>
+        <v>95.389087429727</v>
       </c>
       <c r="E145" t="n">
-        <v>95.82573699951172</v>
+        <v>95.54786682128906</v>
       </c>
       <c r="F145" t="n">
-        <v>8518600</v>
+        <v>5882200</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B146" t="n">
-        <v>95.26999653948798</v>
+        <v>95.07152604625539</v>
       </c>
       <c r="C146" t="n">
-        <v>96.43109780518201</v>
+        <v>96.05399582384246</v>
       </c>
       <c r="D146" t="n">
-        <v>94.36691272969546</v>
+        <v>94.60509878245135</v>
       </c>
       <c r="E146" t="n">
-        <v>95.87535858154297</v>
+        <v>95.05167388916016</v>
       </c>
       <c r="F146" t="n">
-        <v>6379100</v>
+        <v>7913000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B147" t="n">
-        <v>95.76619510964362</v>
+        <v>97.3540300760944</v>
       </c>
       <c r="C147" t="n">
-        <v>96.4211799747073</v>
+        <v>98.43574547532691</v>
       </c>
       <c r="D147" t="n">
-        <v>95.389087429727</v>
+        <v>96.94715172012246</v>
       </c>
       <c r="E147" t="n">
-        <v>95.54786682128906</v>
+        <v>98.42581939697266</v>
       </c>
       <c r="F147" t="n">
-        <v>5882200</v>
+        <v>10821000</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B148" t="n">
-        <v>95.07152604625539</v>
+        <v>97.9097767670043</v>
       </c>
       <c r="C148" t="n">
-        <v>96.05399582384246</v>
+        <v>99.46783792592092</v>
       </c>
       <c r="D148" t="n">
-        <v>94.60509878245135</v>
+        <v>96.93722551678441</v>
       </c>
       <c r="E148" t="n">
-        <v>95.05167388916016</v>
+        <v>99.03118133544922</v>
       </c>
       <c r="F148" t="n">
-        <v>7913000</v>
+        <v>8918300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B149" t="n">
-        <v>97.3540300760944</v>
+        <v>99.08079694980933</v>
       </c>
       <c r="C149" t="n">
-        <v>98.43574547532691</v>
+        <v>99.39837088687223</v>
       </c>
       <c r="D149" t="n">
-        <v>96.94715172012246</v>
+        <v>98.06855652524918</v>
       </c>
       <c r="E149" t="n">
-        <v>98.42581939697266</v>
+        <v>98.4158935546875</v>
       </c>
       <c r="F149" t="n">
-        <v>10821000</v>
+        <v>6359600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B150" t="n">
-        <v>97.9097767670043</v>
+        <v>97.78075602521236</v>
       </c>
       <c r="C150" t="n">
-        <v>99.46783792592092</v>
+        <v>100.4999183711592</v>
       </c>
       <c r="D150" t="n">
-        <v>96.93722551678441</v>
+        <v>97.78075602521236</v>
       </c>
       <c r="E150" t="n">
-        <v>99.03118133544922</v>
+        <v>100.4106063842773</v>
       </c>
       <c r="F150" t="n">
-        <v>8918300</v>
+        <v>6790300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B151" t="n">
-        <v>99.08079694980933</v>
+        <v>100.5693883478159</v>
       </c>
       <c r="C151" t="n">
-        <v>99.39837088687223</v>
+        <v>102.3160071037648</v>
       </c>
       <c r="D151" t="n">
-        <v>98.06855652524918</v>
+        <v>100.1327393373631</v>
       </c>
       <c r="E151" t="n">
-        <v>98.4158935546875</v>
+        <v>101.8098831176758</v>
       </c>
       <c r="F151" t="n">
-        <v>6359600</v>
+        <v>9997400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B152" t="n">
-        <v>97.78075602521236</v>
+        <v>101.8198131278678</v>
       </c>
       <c r="C152" t="n">
-        <v>100.4999183711592</v>
+        <v>102.5938806827324</v>
       </c>
       <c r="D152" t="n">
-        <v>97.78075602521236</v>
+        <v>101.0159749087976</v>
       </c>
       <c r="E152" t="n">
-        <v>100.4106063842773</v>
+        <v>102.2564697265625</v>
       </c>
       <c r="F152" t="n">
-        <v>6790300</v>
+        <v>7035300</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B153" t="n">
-        <v>100.5693883478159</v>
+        <v>102.832054706031</v>
       </c>
       <c r="C153" t="n">
-        <v>102.3160071037648</v>
+        <v>103.7351309397506</v>
       </c>
       <c r="D153" t="n">
-        <v>100.1327393373631</v>
+        <v>101.9984383035261</v>
       </c>
       <c r="E153" t="n">
-        <v>101.8098831176758</v>
+        <v>103.1099243164062</v>
       </c>
       <c r="F153" t="n">
-        <v>9997400</v>
+        <v>8145900</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B154" t="n">
-        <v>101.8198131278678</v>
+        <v>103.8939187225915</v>
       </c>
       <c r="C154" t="n">
-        <v>102.5938806827324</v>
+        <v>105.5214472288459</v>
       </c>
       <c r="D154" t="n">
-        <v>101.0159749087976</v>
+        <v>103.8939187225915</v>
       </c>
       <c r="E154" t="n">
-        <v>102.2564697265625</v>
+        <v>105.4817504882812</v>
       </c>
       <c r="F154" t="n">
-        <v>7035300</v>
+        <v>10506200</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B155" t="n">
-        <v>102.832054706031</v>
+        <v>105.1046425751499</v>
       </c>
       <c r="C155" t="n">
-        <v>103.7351309397506</v>
+        <v>106.2955145039117</v>
       </c>
       <c r="D155" t="n">
-        <v>101.9984383035261</v>
+        <v>105.1046425751499</v>
       </c>
       <c r="E155" t="n">
-        <v>103.1099243164062</v>
+        <v>105.4916763305664</v>
       </c>
       <c r="F155" t="n">
-        <v>8145900</v>
+        <v>6423400</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B156" t="n">
-        <v>103.8939187225915</v>
+        <v>105.3825171192469</v>
       </c>
       <c r="C156" t="n">
-        <v>105.5214472288459</v>
+        <v>106.0672651032121</v>
       </c>
       <c r="D156" t="n">
-        <v>103.8939187225915</v>
+        <v>103.1793971336853</v>
       </c>
       <c r="E156" t="n">
-        <v>105.4817504882812</v>
+        <v>103.4969635009766</v>
       </c>
       <c r="F156" t="n">
-        <v>10506200</v>
+        <v>7784500</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B157" t="n">
-        <v>105.1046425751499</v>
+        <v>104.2313285377519</v>
       </c>
       <c r="C157" t="n">
-        <v>106.2955145039117</v>
+        <v>105.4718232743649</v>
       </c>
       <c r="D157" t="n">
-        <v>105.1046425751499</v>
+        <v>103.437416449147</v>
       </c>
       <c r="E157" t="n">
-        <v>105.4916763305664</v>
+        <v>104.0229263305664</v>
       </c>
       <c r="F157" t="n">
-        <v>6423400</v>
+        <v>6886600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B158" t="n">
-        <v>105.3825171192469</v>
+        <v>104.1420232238167</v>
       </c>
       <c r="C158" t="n">
-        <v>106.0672651032121</v>
+        <v>104.4000406941716</v>
       </c>
       <c r="D158" t="n">
-        <v>103.1793971336853</v>
+        <v>101.7701977411496</v>
       </c>
       <c r="E158" t="n">
-        <v>103.4969635009766</v>
+        <v>102.8618316650391</v>
       </c>
       <c r="F158" t="n">
-        <v>7784500</v>
+        <v>6147000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B159" t="n">
-        <v>104.2313285377519</v>
+        <v>102.81220477355</v>
       </c>
       <c r="C159" t="n">
-        <v>105.4718232743649</v>
+        <v>102.851901514659</v>
       </c>
       <c r="D159" t="n">
-        <v>103.437416449147</v>
+        <v>101.1946023230963</v>
       </c>
       <c r="E159" t="n">
-        <v>104.0229263305664</v>
+        <v>101.8198089599609</v>
       </c>
       <c r="F159" t="n">
-        <v>6886600</v>
+        <v>5974500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B160" t="n">
-        <v>104.1420232238167</v>
+        <v>101.839659785339</v>
       </c>
       <c r="C160" t="n">
-        <v>104.4000406941716</v>
+        <v>103.0206056395392</v>
       </c>
       <c r="D160" t="n">
-        <v>101.7701977411496</v>
+        <v>101.2839129884539</v>
       </c>
       <c r="E160" t="n">
-        <v>102.8618316650391</v>
+        <v>101.5717086791992</v>
       </c>
       <c r="F160" t="n">
-        <v>6147000</v>
+        <v>6524300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B161" t="n">
-        <v>102.81220477355</v>
+        <v>101.8793558222072</v>
       </c>
       <c r="C161" t="n">
-        <v>102.851901514659</v>
+        <v>102.5045624465828</v>
       </c>
       <c r="D161" t="n">
-        <v>101.1946023230963</v>
+        <v>99.84494141643668</v>
       </c>
       <c r="E161" t="n">
-        <v>101.8198089599609</v>
+        <v>100.6984024047852</v>
       </c>
       <c r="F161" t="n">
-        <v>5974500</v>
+        <v>6409300</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B162" t="n">
-        <v>101.839659785339</v>
+        <v>100.1724381261774</v>
       </c>
       <c r="C162" t="n">
-        <v>103.0206056395392</v>
+        <v>100.7083327862765</v>
       </c>
       <c r="D162" t="n">
-        <v>101.2839129884539</v>
+        <v>99.83501960476121</v>
       </c>
       <c r="E162" t="n">
-        <v>101.5717086791992</v>
+        <v>100.5297012329102</v>
       </c>
       <c r="F162" t="n">
-        <v>6524300</v>
+        <v>5533700</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B163" t="n">
-        <v>101.8793558222072</v>
+        <v>100.1426666812253</v>
       </c>
       <c r="C163" t="n">
-        <v>102.5045624465828</v>
+        <v>103.328256381923</v>
       </c>
       <c r="D163" t="n">
-        <v>99.84494141643668</v>
+        <v>99.65638727390106</v>
       </c>
       <c r="E163" t="n">
-        <v>100.6984024047852</v>
+        <v>102.961067199707</v>
       </c>
       <c r="F163" t="n">
-        <v>6409300</v>
+        <v>9203500</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B164" t="n">
-        <v>100.1724381261774</v>
+        <v>103.6061276781693</v>
       </c>
       <c r="C164" t="n">
-        <v>100.7083327862765</v>
+        <v>104.0328581941516</v>
       </c>
       <c r="D164" t="n">
-        <v>99.83501960476121</v>
+        <v>102.1870013177053</v>
       </c>
       <c r="E164" t="n">
-        <v>100.5297012329102</v>
+        <v>102.2961654663086</v>
       </c>
       <c r="F164" t="n">
-        <v>5533700</v>
+        <v>5956900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B165" t="n">
-        <v>100.1426666812253</v>
+        <v>101.9587457902329</v>
       </c>
       <c r="C165" t="n">
-        <v>103.328256381923</v>
+        <v>102.2663936470847</v>
       </c>
       <c r="D165" t="n">
-        <v>99.65638727390106</v>
+        <v>100.4999227039044</v>
       </c>
       <c r="E165" t="n">
-        <v>102.961067199707</v>
+        <v>100.5396194458008</v>
       </c>
       <c r="F165" t="n">
-        <v>9203500</v>
+        <v>8400100</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B166" t="n">
-        <v>103.6061276781693</v>
+        <v>100.7579458156174</v>
       </c>
       <c r="C166" t="n">
-        <v>104.0328581941516</v>
+        <v>100.9564295213072</v>
       </c>
       <c r="D166" t="n">
-        <v>102.1870013177053</v>
+        <v>99.29912275715898</v>
       </c>
       <c r="E166" t="n">
-        <v>102.2961654663086</v>
+        <v>99.71593475341797</v>
       </c>
       <c r="F166" t="n">
-        <v>5956900</v>
+        <v>14314700</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B167" t="n">
-        <v>101.9587457902329</v>
+        <v>105.7099984223796</v>
       </c>
       <c r="C167" t="n">
-        <v>102.2663936470847</v>
+        <v>108.3100781720615</v>
       </c>
       <c r="D167" t="n">
-        <v>100.4999227039044</v>
+        <v>104.5092004000206</v>
       </c>
       <c r="E167" t="n">
-        <v>100.5396194458008</v>
+        <v>107.2382888793945</v>
       </c>
       <c r="F167" t="n">
-        <v>8400100</v>
+        <v>23219500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B168" t="n">
-        <v>100.7579458156174</v>
+        <v>108.2207663660894</v>
       </c>
       <c r="C168" t="n">
-        <v>100.9564295213072</v>
+        <v>109.6398926806152</v>
       </c>
       <c r="D168" t="n">
-        <v>99.29912275715898</v>
+        <v>106.2756639110559</v>
       </c>
       <c r="E168" t="n">
-        <v>99.71593475341797</v>
+        <v>107.8337326049805</v>
       </c>
       <c r="F168" t="n">
-        <v>14314700</v>
+        <v>14309200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B169" t="n">
-        <v>105.7099984223796</v>
+        <v>108.2009150377847</v>
       </c>
       <c r="C169" t="n">
-        <v>108.3100781720615</v>
+        <v>108.3795465882309</v>
       </c>
       <c r="D169" t="n">
-        <v>104.5092004000206</v>
+        <v>106.7222473860446</v>
       </c>
       <c r="E169" t="n">
-        <v>107.2382888793945</v>
+        <v>107.1985931396484</v>
       </c>
       <c r="F169" t="n">
-        <v>23219500</v>
+        <v>8370000</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B170" t="n">
-        <v>108.2207663660894</v>
+        <v>107.1787478525936</v>
       </c>
       <c r="C170" t="n">
-        <v>109.6398926806152</v>
+        <v>107.5657816141287</v>
       </c>
       <c r="D170" t="n">
-        <v>106.2756639110559</v>
+        <v>103.5862722822083</v>
       </c>
       <c r="E170" t="n">
-        <v>107.8337326049805</v>
+        <v>103.9236907958984</v>
       </c>
       <c r="F170" t="n">
-        <v>14309200</v>
+        <v>10562300</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B171" t="n">
-        <v>108.2009150377847</v>
+        <v>104.1916361796018</v>
       </c>
       <c r="C171" t="n">
-        <v>108.3795465882309</v>
+        <v>105.4619016318964</v>
       </c>
       <c r="D171" t="n">
-        <v>106.7222473860446</v>
+        <v>103.4274947211174</v>
       </c>
       <c r="E171" t="n">
-        <v>107.1985931396484</v>
+        <v>105.3527450561523</v>
       </c>
       <c r="F171" t="n">
-        <v>8370000</v>
+        <v>8178500</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B172" t="n">
-        <v>107.1787478525936</v>
+        <v>104.5489005402277</v>
       </c>
       <c r="C172" t="n">
-        <v>107.5657816141287</v>
+        <v>105.0748691255691</v>
       </c>
       <c r="D172" t="n">
-        <v>103.5862722822083</v>
+        <v>103.0702328542224</v>
       </c>
       <c r="E172" t="n">
-        <v>103.9236907958984</v>
+        <v>104.1023254394531</v>
       </c>
       <c r="F172" t="n">
-        <v>10562300</v>
+        <v>7605900</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B173" t="n">
-        <v>104.1916361796018</v>
+        <v>104.7374526473249</v>
       </c>
       <c r="C173" t="n">
-        <v>105.4619016318964</v>
+        <v>105.4817494902667</v>
       </c>
       <c r="D173" t="n">
-        <v>103.4274947211174</v>
+        <v>104.0526971289773</v>
       </c>
       <c r="E173" t="n">
-        <v>105.3527450561523</v>
+        <v>104.6183624267578</v>
       </c>
       <c r="F173" t="n">
-        <v>8178500</v>
+        <v>6144600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B174" t="n">
-        <v>104.5489005402277</v>
+        <v>104.2313280181917</v>
       </c>
       <c r="C174" t="n">
-        <v>105.0748691255691</v>
+        <v>104.6183617683755</v>
       </c>
       <c r="D174" t="n">
-        <v>103.0702328542224</v>
+        <v>101.5220917669058</v>
       </c>
       <c r="E174" t="n">
-        <v>104.1023254394531</v>
+        <v>101.9388961791992</v>
       </c>
       <c r="F174" t="n">
-        <v>7605900</v>
+        <v>9258600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B175" t="n">
-        <v>104.7374526473249</v>
+        <v>101.9091260836407</v>
       </c>
       <c r="C175" t="n">
-        <v>105.4817494902667</v>
+        <v>103.9038361698679</v>
       </c>
       <c r="D175" t="n">
-        <v>104.0526971289773</v>
+        <v>101.7701912787705</v>
       </c>
       <c r="E175" t="n">
-        <v>104.6183624267578</v>
+        <v>103.1198501586914</v>
       </c>
       <c r="F175" t="n">
-        <v>6144600</v>
+        <v>9037200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B176" t="n">
-        <v>104.2313280181917</v>
+        <v>102.9213691252704</v>
       </c>
       <c r="C176" t="n">
-        <v>104.6183617683755</v>
+        <v>103.1396974161188</v>
       </c>
       <c r="D176" t="n">
-        <v>101.5220917669058</v>
+        <v>101.1946025261468</v>
       </c>
       <c r="E176" t="n">
-        <v>101.9388961791992</v>
+        <v>101.5121688842773</v>
       </c>
       <c r="F176" t="n">
-        <v>9258600</v>
+        <v>7032600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B177" t="n">
-        <v>101.9091260836407</v>
+        <v>102.1274576654748</v>
       </c>
       <c r="C177" t="n">
-        <v>103.9038361698679</v>
+        <v>104.0626264896183</v>
       </c>
       <c r="D177" t="n">
-        <v>101.7701912787705</v>
+        <v>100.8274139902545</v>
       </c>
       <c r="E177" t="n">
-        <v>103.1198501586914</v>
+        <v>103.2885589599609</v>
       </c>
       <c r="F177" t="n">
-        <v>9037200</v>
+        <v>7941400</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B178" t="n">
-        <v>102.9213691252704</v>
+        <v>102.822129060906</v>
       </c>
       <c r="C178" t="n">
-        <v>103.1396974161188</v>
+        <v>103.8244509351605</v>
       </c>
       <c r="D178" t="n">
-        <v>101.1946025261468</v>
+        <v>101.8098811087023</v>
       </c>
       <c r="E178" t="n">
-        <v>101.5121688842773</v>
+        <v>102.7923583984375</v>
       </c>
       <c r="F178" t="n">
-        <v>7032600</v>
+        <v>8611200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B179" t="n">
-        <v>102.1274576654748</v>
+        <v>103.2488588874603</v>
       </c>
       <c r="C179" t="n">
-        <v>104.0626264896183</v>
+        <v>103.7053600422387</v>
       </c>
       <c r="D179" t="n">
-        <v>100.8274139902545</v>
+        <v>102.1969217730311</v>
       </c>
       <c r="E179" t="n">
-        <v>103.2885589599609</v>
+        <v>102.2167663574219</v>
       </c>
       <c r="F179" t="n">
-        <v>7941400</v>
+        <v>5693300</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B180" t="n">
-        <v>102.822129060906</v>
+        <v>102.3160049896206</v>
       </c>
       <c r="C180" t="n">
-        <v>103.8244509351605</v>
+        <v>103.0106865892155</v>
       </c>
       <c r="D180" t="n">
-        <v>101.8098811087023</v>
+        <v>101.571708143084</v>
       </c>
       <c r="E180" t="n">
-        <v>102.7923583984375</v>
+        <v>102.4946365356445</v>
       </c>
       <c r="F180" t="n">
-        <v>8611200</v>
+        <v>6714400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B181" t="n">
-        <v>103.2488588874603</v>
+        <v>102.5144889184559</v>
       </c>
       <c r="C181" t="n">
-        <v>103.7053600422387</v>
+        <v>104.4496576951832</v>
       </c>
       <c r="D181" t="n">
-        <v>102.1969217730311</v>
+        <v>102.4747921779873</v>
       </c>
       <c r="E181" t="n">
-        <v>102.2167663574219</v>
+        <v>103.3877944946289</v>
       </c>
       <c r="F181" t="n">
-        <v>5693300</v>
+        <v>7360100</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B182" t="n">
-        <v>102.3160049896206</v>
+        <v>103.0206090569662</v>
       </c>
       <c r="C182" t="n">
-        <v>103.0106865892155</v>
+        <v>103.6160526141937</v>
       </c>
       <c r="D182" t="n">
-        <v>101.571708143084</v>
+        <v>102.3160089237181</v>
       </c>
       <c r="E182" t="n">
-        <v>102.4946365356445</v>
+        <v>102.9412231445312</v>
       </c>
       <c r="F182" t="n">
-        <v>6714400</v>
+        <v>6511100</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B183" t="n">
-        <v>102.5144889184559</v>
+        <v>102.8419796873618</v>
       </c>
       <c r="C183" t="n">
-        <v>104.4496576951832</v>
+        <v>102.9709959941437</v>
       </c>
       <c r="D183" t="n">
-        <v>102.4747921779873</v>
+        <v>101.0556716918945</v>
       </c>
       <c r="E183" t="n">
-        <v>103.3877944946289</v>
+        <v>101.0556716918945</v>
       </c>
       <c r="F183" t="n">
-        <v>7360100</v>
+        <v>13340300</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B184" t="n">
-        <v>103.0206090569662</v>
+        <v>100.8869633557317</v>
       </c>
       <c r="C184" t="n">
-        <v>103.6160526141937</v>
+        <v>102.2266962072239</v>
       </c>
       <c r="D184" t="n">
-        <v>102.3160089237181</v>
+        <v>99.53730442598828</v>
       </c>
       <c r="E184" t="n">
-        <v>102.9412231445312</v>
+        <v>102.0679092407227</v>
       </c>
       <c r="F184" t="n">
-        <v>6511100</v>
+        <v>8219000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B185" t="n">
-        <v>102.8419796873618</v>
+        <v>101.5717095216456</v>
       </c>
       <c r="C185" t="n">
-        <v>102.9709959941437</v>
+        <v>101.7106443291744</v>
       </c>
       <c r="D185" t="n">
-        <v>101.0556716918945</v>
+        <v>99.32889287365569</v>
       </c>
       <c r="E185" t="n">
-        <v>101.0556716918945</v>
+        <v>100.6388626098633</v>
       </c>
       <c r="F185" t="n">
-        <v>13340300</v>
+        <v>8397400</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B186" t="n">
-        <v>100.8869633557317</v>
+        <v>99.67623490973834</v>
       </c>
       <c r="C186" t="n">
-        <v>102.2266962072239</v>
+        <v>100.4999176557305</v>
       </c>
       <c r="D186" t="n">
-        <v>99.53730442598828</v>
+        <v>98.495281504625</v>
       </c>
       <c r="E186" t="n">
-        <v>102.0679092407227</v>
+        <v>98.63421630859375</v>
       </c>
       <c r="F186" t="n">
-        <v>8219000</v>
+        <v>7471600</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B187" t="n">
-        <v>101.5717095216456</v>
+        <v>99.77547422442305</v>
       </c>
       <c r="C187" t="n">
-        <v>101.7106443291744</v>
+        <v>100.6984026174289</v>
       </c>
       <c r="D187" t="n">
-        <v>99.32889287365569</v>
+        <v>98.25710986817649</v>
       </c>
       <c r="E187" t="n">
-        <v>100.6388626098633</v>
+        <v>98.5845947265625</v>
       </c>
       <c r="F187" t="n">
-        <v>8397400</v>
+        <v>9568000</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B188" t="n">
-        <v>99.67623490973834</v>
+        <v>98.92201919170897</v>
       </c>
       <c r="C188" t="n">
-        <v>100.4999176557305</v>
+        <v>99.43806170522778</v>
       </c>
       <c r="D188" t="n">
-        <v>98.495281504625</v>
+        <v>98.33650169977196</v>
       </c>
       <c r="E188" t="n">
-        <v>98.63421630859375</v>
+        <v>98.95178985595703</v>
       </c>
       <c r="F188" t="n">
-        <v>7471600</v>
+        <v>9501600</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B189" t="n">
-        <v>99.77547422442305</v>
+        <v>98.76323055949389</v>
       </c>
       <c r="C189" t="n">
-        <v>100.6984026174289</v>
+        <v>99.08079692509821</v>
       </c>
       <c r="D189" t="n">
-        <v>98.25710986817649</v>
+        <v>97.66167814394407</v>
       </c>
       <c r="E189" t="n">
-        <v>98.5845947265625</v>
+        <v>98.11817932128906</v>
       </c>
       <c r="F189" t="n">
-        <v>9568000</v>
+        <v>7559200</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B190" t="n">
-        <v>98.92201919170897</v>
+        <v>98.29680690142362</v>
       </c>
       <c r="C190" t="n">
-        <v>99.43806170522778</v>
+        <v>99.32889186938023</v>
       </c>
       <c r="D190" t="n">
-        <v>98.33650169977196</v>
+        <v>97.7609122614967</v>
       </c>
       <c r="E190" t="n">
-        <v>98.95178985595703</v>
+        <v>98.57467651367188</v>
       </c>
       <c r="F190" t="n">
-        <v>9501600</v>
+        <v>8616300</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B191" t="n">
-        <v>98.76323055949389</v>
+        <v>98.7334588011272</v>
       </c>
       <c r="C191" t="n">
-        <v>99.08079692509821</v>
+        <v>99.00140991464168</v>
       </c>
       <c r="D191" t="n">
-        <v>97.66167814394407</v>
+        <v>97.20516831754395</v>
       </c>
       <c r="E191" t="n">
-        <v>98.11817932128906</v>
+        <v>97.86015319824219</v>
       </c>
       <c r="F191" t="n">
-        <v>7559200</v>
+        <v>7041400</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B192" t="n">
-        <v>98.29680690142362</v>
+        <v>98.07848356908464</v>
       </c>
       <c r="C192" t="n">
-        <v>99.32889186938023</v>
+        <v>99.97395570346617</v>
       </c>
       <c r="D192" t="n">
-        <v>97.7609122614967</v>
+        <v>97.35403126794252</v>
       </c>
       <c r="E192" t="n">
-        <v>98.57467651367188</v>
+        <v>99.57699584960938</v>
       </c>
       <c r="F192" t="n">
-        <v>8616300</v>
+        <v>9264400</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B193" t="n">
-        <v>98.7334588011272</v>
+        <v>100.2915220505157</v>
       </c>
       <c r="C193" t="n">
-        <v>99.00140991464168</v>
+        <v>100.9961221945534</v>
       </c>
       <c r="D193" t="n">
-        <v>97.20516831754395</v>
+        <v>98.78308369184245</v>
       </c>
       <c r="E193" t="n">
-        <v>97.86015319824219</v>
+        <v>99.27928161621094</v>
       </c>
       <c r="F193" t="n">
-        <v>7041400</v>
+        <v>8257200</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B194" t="n">
-        <v>98.07848356908464</v>
+        <v>100.1128870298928</v>
       </c>
       <c r="C194" t="n">
-        <v>99.97395570346617</v>
+        <v>101.6213329077368</v>
       </c>
       <c r="D194" t="n">
-        <v>97.35403126794252</v>
+        <v>99.82509133515438</v>
       </c>
       <c r="E194" t="n">
-        <v>99.57699584960938</v>
+        <v>100.9167327880859</v>
       </c>
       <c r="F194" t="n">
-        <v>9264400</v>
+        <v>10265100</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B195" t="n">
-        <v>100.2915220505157</v>
+        <v>100.658710438741</v>
       </c>
       <c r="C195" t="n">
-        <v>100.9961221945534</v>
+        <v>101.1549083591584</v>
       </c>
       <c r="D195" t="n">
-        <v>98.78308369184245</v>
+        <v>99.28920690408536</v>
       </c>
       <c r="E195" t="n">
-        <v>99.27928161621094</v>
+        <v>100.5098495483398</v>
       </c>
       <c r="F195" t="n">
-        <v>8257200</v>
+        <v>10694600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B196" t="n">
-        <v>100.1128870298928</v>
+        <v>99.90448284246082</v>
       </c>
       <c r="C196" t="n">
-        <v>101.6213329077368</v>
+        <v>101.581634158465</v>
       </c>
       <c r="D196" t="n">
-        <v>99.82509133515438</v>
+        <v>99.67623604963576</v>
       </c>
       <c r="E196" t="n">
-        <v>100.9167327880859</v>
+        <v>100.0930404663086</v>
       </c>
       <c r="F196" t="n">
-        <v>10265100</v>
+        <v>11168700</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B197" t="n">
-        <v>100.658710438741</v>
+        <v>101.0258948980948</v>
       </c>
       <c r="C197" t="n">
-        <v>101.1549083591584</v>
+        <v>103.4274909034028</v>
       </c>
       <c r="D197" t="n">
-        <v>99.28920690408536</v>
+        <v>100.0334991036985</v>
       </c>
       <c r="E197" t="n">
-        <v>100.5098495483398</v>
+        <v>103.0999984741211</v>
       </c>
       <c r="F197" t="n">
-        <v>10694600</v>
+        <v>22943600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B198" t="n">
-        <v>99.90448284246082</v>
+        <v>102.623658522444</v>
       </c>
       <c r="C198" t="n">
-        <v>101.581634158465</v>
+        <v>103.5168087306858</v>
       </c>
       <c r="D198" t="n">
-        <v>99.67623604963576</v>
+        <v>100.7381048924391</v>
       </c>
       <c r="E198" t="n">
-        <v>100.0930404663086</v>
+        <v>101.6709518432617</v>
       </c>
       <c r="F198" t="n">
-        <v>11168700</v>
+        <v>17396300</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B199" t="n">
-        <v>101.0258948980948</v>
+        <v>101.2442170259669</v>
       </c>
       <c r="C199" t="n">
-        <v>103.4274909034028</v>
+        <v>103.2488607985985</v>
       </c>
       <c r="D199" t="n">
-        <v>100.0334991036985</v>
+        <v>101.025896308111</v>
       </c>
       <c r="E199" t="n">
-        <v>103.0999984741211</v>
+        <v>102.7427368164062</v>
       </c>
       <c r="F199" t="n">
-        <v>22943600</v>
+        <v>14457400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B200" t="n">
-        <v>102.623658522444</v>
+        <v>102.3160060444983</v>
       </c>
       <c r="C200" t="n">
-        <v>103.5168087306858</v>
+        <v>103.7351323493811</v>
       </c>
       <c r="D200" t="n">
-        <v>100.7381048924391</v>
+        <v>100.2716731077754</v>
       </c>
       <c r="E200" t="n">
-        <v>101.6709518432617</v>
+        <v>100.3510665893555</v>
       </c>
       <c r="F200" t="n">
-        <v>17396300</v>
+        <v>12215500</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B201" t="n">
-        <v>101.2442170259669</v>
+        <v>100.3411416176147</v>
       </c>
       <c r="C201" t="n">
-        <v>103.2488607985985</v>
+        <v>100.8075688628163</v>
       </c>
       <c r="D201" t="n">
-        <v>101.025896308111</v>
+        <v>97.24486394426569</v>
       </c>
       <c r="E201" t="n">
-        <v>102.7427368164062</v>
+        <v>97.30441284179688</v>
       </c>
       <c r="F201" t="n">
-        <v>14457400</v>
+        <v>12054400</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B202" t="n">
-        <v>102.3160060444983</v>
+        <v>97.30440945370802</v>
       </c>
       <c r="C202" t="n">
-        <v>103.7351323493811</v>
+        <v>98.69375749140566</v>
       </c>
       <c r="D202" t="n">
-        <v>100.2716731077754</v>
+        <v>97.15554857213215</v>
       </c>
       <c r="E202" t="n">
-        <v>100.3510665893555</v>
+        <v>98.03878021240234</v>
       </c>
       <c r="F202" t="n">
-        <v>12215500</v>
+        <v>13921400</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B203" t="n">
-        <v>100.3411416176147</v>
+        <v>98.95178655891404</v>
       </c>
       <c r="C203" t="n">
-        <v>100.8075688628163</v>
+        <v>99.27927899748993</v>
       </c>
       <c r="D203" t="n">
-        <v>97.24486394426569</v>
+        <v>97.75098852218167</v>
       </c>
       <c r="E203" t="n">
-        <v>97.30441284179688</v>
+        <v>97.87999725341797</v>
       </c>
       <c r="F203" t="n">
-        <v>12054400</v>
+        <v>10418100</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,25 +5721,25 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B204" t="n">
-        <v>97.30440945370802</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C204" t="n">
-        <v>98.69375749140566</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D204" t="n">
-        <v>97.15554857213215</v>
+        <v>95.98999786376953</v>
       </c>
       <c r="E204" t="n">
-        <v>98.03878021240234</v>
+        <v>96.25</v>
       </c>
       <c r="F204" t="n">
-        <v>13921400</v>
+        <v>12717800</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B205" t="n">
-        <v>98.95178655891404</v>
+        <v>96.55000305175781</v>
       </c>
       <c r="C205" t="n">
-        <v>99.27927899748993</v>
+        <v>97.76000213623047</v>
       </c>
       <c r="D205" t="n">
-        <v>97.75098852218167</v>
+        <v>95.65000152587891</v>
       </c>
       <c r="E205" t="n">
-        <v>97.87999725341797</v>
+        <v>95.70999908447266</v>
       </c>
       <c r="F205" t="n">
-        <v>10418100</v>
+        <v>11590400</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,25 +5773,25 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B206" t="n">
-        <v>97.41000366210938</v>
+        <v>96.40000152587891</v>
       </c>
       <c r="C206" t="n">
-        <v>97.59999847412109</v>
+        <v>99.51999664306641</v>
       </c>
       <c r="D206" t="n">
-        <v>95.98999786376953</v>
+        <v>95.76999664306641</v>
       </c>
       <c r="E206" t="n">
-        <v>96.25</v>
+        <v>99.5</v>
       </c>
       <c r="F206" t="n">
-        <v>12717800</v>
+        <v>11297800</v>
       </c>
       <c r="G206" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B207" t="n">
-        <v>96.55000305175781</v>
+        <v>98.84999847412109</v>
       </c>
       <c r="C207" t="n">
-        <v>97.76000213623047</v>
+        <v>99.44000244140625</v>
       </c>
       <c r="D207" t="n">
-        <v>95.65000152587891</v>
+        <v>97.01999664306641</v>
       </c>
       <c r="E207" t="n">
-        <v>95.70999908447266</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="F207" t="n">
-        <v>11590400</v>
+        <v>10171900</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B208" t="n">
-        <v>96.40000152587891</v>
+        <v>98.13999938964844</v>
       </c>
       <c r="C208" t="n">
-        <v>99.51999664306641</v>
+        <v>99.04000091552734</v>
       </c>
       <c r="D208" t="n">
-        <v>95.76999664306641</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="E208" t="n">
-        <v>99.5</v>
+        <v>97.48000335693359</v>
       </c>
       <c r="F208" t="n">
-        <v>11297800</v>
+        <v>9936400</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B209" t="n">
-        <v>98.84999847412109</v>
+        <v>97.30000305175781</v>
       </c>
       <c r="C209" t="n">
-        <v>99.44000244140625</v>
+        <v>97.66000366210938</v>
       </c>
       <c r="D209" t="n">
-        <v>97.01999664306641</v>
+        <v>96.63999938964844</v>
       </c>
       <c r="E209" t="n">
-        <v>97.41000366210938</v>
+        <v>96.69999694824219</v>
       </c>
       <c r="F209" t="n">
-        <v>10171900</v>
+        <v>8720800</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B210" t="n">
-        <v>98.13999938964844</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="C210" t="n">
-        <v>99.04000091552734</v>
+        <v>96.55000305175781</v>
       </c>
       <c r="D210" t="n">
-        <v>96.91999816894531</v>
+        <v>94.77999877929688</v>
       </c>
       <c r="E210" t="n">
-        <v>97.48000335693359</v>
+        <v>96.16999816894531</v>
       </c>
       <c r="F210" t="n">
-        <v>9936400</v>
+        <v>11448100</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B211" t="n">
-        <v>97.30000305175781</v>
+        <v>96.88999938964844</v>
       </c>
       <c r="C211" t="n">
-        <v>97.66000366210938</v>
+        <v>97.05000305175781</v>
       </c>
       <c r="D211" t="n">
-        <v>96.63999938964844</v>
+        <v>95.51999664306641</v>
       </c>
       <c r="E211" t="n">
-        <v>96.69999694824219</v>
+        <v>95.62000274658203</v>
       </c>
       <c r="F211" t="n">
-        <v>8720800</v>
+        <v>10678900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B212" t="n">
-        <v>96.33999633789062</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="C212" t="n">
-        <v>96.55000305175781</v>
+        <v>97.54000091552734</v>
       </c>
       <c r="D212" t="n">
-        <v>94.77999877929688</v>
+        <v>95.83000183105469</v>
       </c>
       <c r="E212" t="n">
-        <v>96.16999816894531</v>
+        <v>96</v>
       </c>
       <c r="F212" t="n">
-        <v>11448100</v>
+        <v>9304200</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>96.88999938964844</v>
+        <v>95.51000213623047</v>
       </c>
       <c r="C213" t="n">
-        <v>97.05000305175781</v>
+        <v>96.69000244140625</v>
       </c>
       <c r="D213" t="n">
-        <v>95.51999664306641</v>
+        <v>95.12999725341797</v>
       </c>
       <c r="E213" t="n">
-        <v>95.62000274658203</v>
+        <v>95.87000274658203</v>
       </c>
       <c r="F213" t="n">
-        <v>10678900</v>
+        <v>7651600</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B214" t="n">
         <v>96.09999847412109</v>
       </c>
       <c r="C214" t="n">
-        <v>97.54000091552734</v>
+        <v>97.90000152587891</v>
       </c>
       <c r="D214" t="n">
-        <v>95.83000183105469</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="E214" t="n">
-        <v>96</v>
+        <v>97.15000152587891</v>
       </c>
       <c r="F214" t="n">
-        <v>9304200</v>
+        <v>10219200</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B215" t="n">
-        <v>95.51000213623047</v>
+        <v>97.27999877929688</v>
       </c>
       <c r="C215" t="n">
-        <v>96.69000244140625</v>
+        <v>99.84999847412109</v>
       </c>
       <c r="D215" t="n">
-        <v>95.12999725341797</v>
+        <v>97.27999877929688</v>
       </c>
       <c r="E215" t="n">
-        <v>95.87000274658203</v>
+        <v>99.70999908447266</v>
       </c>
       <c r="F215" t="n">
-        <v>7651600</v>
+        <v>7480000</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B216" t="n">
-        <v>96.09999847412109</v>
+        <v>99.01000213623047</v>
       </c>
       <c r="C216" t="n">
-        <v>97.90000152587891</v>
+        <v>99.79000091552734</v>
       </c>
       <c r="D216" t="n">
-        <v>96.09999847412109</v>
+        <v>97.05000305175781</v>
       </c>
       <c r="E216" t="n">
-        <v>97.15000152587891</v>
+        <v>97.66999816894531</v>
       </c>
       <c r="F216" t="n">
-        <v>10219200</v>
+        <v>10496500</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B217" t="n">
-        <v>97.27999877929688</v>
+        <v>97.84999847412109</v>
       </c>
       <c r="C217" t="n">
-        <v>99.84999847412109</v>
+        <v>98.38999938964844</v>
       </c>
       <c r="D217" t="n">
-        <v>97.27999877929688</v>
+        <v>96</v>
       </c>
       <c r="E217" t="n">
-        <v>99.70999908447266</v>
+        <v>96.41000366210938</v>
       </c>
       <c r="F217" t="n">
-        <v>7480000</v>
+        <v>9861700</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B218" t="n">
-        <v>99.01000213623047</v>
+        <v>96</v>
       </c>
       <c r="C218" t="n">
-        <v>99.79000091552734</v>
+        <v>96.88999938964844</v>
       </c>
       <c r="D218" t="n">
-        <v>97.05000305175781</v>
+        <v>95.83999633789062</v>
       </c>
       <c r="E218" t="n">
-        <v>97.66999816894531</v>
+        <v>96.13999938964844</v>
       </c>
       <c r="F218" t="n">
-        <v>10496500</v>
+        <v>9745400</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B219" t="n">
-        <v>97.84999847412109</v>
+        <v>97.12000274658203</v>
       </c>
       <c r="C219" t="n">
-        <v>98.38999938964844</v>
+        <v>97.30000305175781</v>
       </c>
       <c r="D219" t="n">
-        <v>96</v>
+        <v>95.65000152587891</v>
       </c>
       <c r="E219" t="n">
-        <v>96.41000366210938</v>
+        <v>95.87000274658203</v>
       </c>
       <c r="F219" t="n">
-        <v>9861700</v>
+        <v>9119200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B220" t="n">
-        <v>96</v>
+        <v>94.80999755859375</v>
       </c>
       <c r="C220" t="n">
-        <v>96.88999938964844</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D220" t="n">
-        <v>95.83999633789062</v>
+        <v>92.48999786376953</v>
       </c>
       <c r="E220" t="n">
-        <v>96.13999938964844</v>
+        <v>92.83000183105469</v>
       </c>
       <c r="F220" t="n">
-        <v>9745400</v>
+        <v>13562500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B221" t="n">
-        <v>97.12000274658203</v>
+        <v>93.26000213623047</v>
       </c>
       <c r="C221" t="n">
-        <v>97.30000305175781</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="D221" t="n">
-        <v>95.65000152587891</v>
+        <v>93</v>
       </c>
       <c r="E221" t="n">
-        <v>95.87000274658203</v>
+        <v>94.84999847412109</v>
       </c>
       <c r="F221" t="n">
-        <v>9119200</v>
+        <v>12153100</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B222" t="n">
-        <v>94.80999755859375</v>
+        <v>95.51000213623047</v>
       </c>
       <c r="C222" t="n">
-        <v>94.81999969482422</v>
+        <v>97.19000244140625</v>
       </c>
       <c r="D222" t="n">
-        <v>92.48999786376953</v>
+        <v>95.51000213623047</v>
       </c>
       <c r="E222" t="n">
-        <v>92.83000183105469</v>
+        <v>96.65000152587891</v>
       </c>
       <c r="F222" t="n">
-        <v>13562500</v>
+        <v>10593900</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B223" t="n">
-        <v>93.26000213623047</v>
+        <v>97</v>
       </c>
       <c r="C223" t="n">
-        <v>96.29000091552734</v>
+        <v>99.23000335693359</v>
       </c>
       <c r="D223" t="n">
-        <v>93</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="E223" t="n">
-        <v>94.84999847412109</v>
+        <v>98.88999938964844</v>
       </c>
       <c r="F223" t="n">
-        <v>12153100</v>
+        <v>11389300</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B224" t="n">
-        <v>95.51000213623047</v>
+        <v>98.33999633789062</v>
       </c>
       <c r="C224" t="n">
-        <v>97.19000244140625</v>
+        <v>99.41000366210938</v>
       </c>
       <c r="D224" t="n">
-        <v>95.51000213623047</v>
+        <v>97.98999786376953</v>
       </c>
       <c r="E224" t="n">
-        <v>96.65000152587891</v>
+        <v>98.48000335693359</v>
       </c>
       <c r="F224" t="n">
-        <v>10593900</v>
+        <v>11070100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B225" t="n">
-        <v>97</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C225" t="n">
-        <v>99.23000335693359</v>
+        <v>97.48000335693359</v>
       </c>
       <c r="D225" t="n">
-        <v>96.97000122070312</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E225" t="n">
-        <v>98.88999938964844</v>
+        <v>96.16000366210938</v>
       </c>
       <c r="F225" t="n">
-        <v>11389300</v>
+        <v>21112400</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B226" t="n">
-        <v>98.33999633789062</v>
+        <v>96.08000183105469</v>
       </c>
       <c r="C226" t="n">
-        <v>99.41000366210938</v>
+        <v>96.58999633789062</v>
       </c>
       <c r="D226" t="n">
-        <v>97.98999786376953</v>
+        <v>95.59999847412109</v>
       </c>
       <c r="E226" t="n">
-        <v>98.48000335693359</v>
+        <v>96.19000244140625</v>
       </c>
       <c r="F226" t="n">
-        <v>11070100</v>
+        <v>11193000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B227" t="n">
-        <v>97.41000366210938</v>
+        <v>97.62000274658203</v>
       </c>
       <c r="C227" t="n">
-        <v>97.48000335693359</v>
+        <v>99.05000305175781</v>
       </c>
       <c r="D227" t="n">
-        <v>94.45999908447266</v>
+        <v>97.20999908447266</v>
       </c>
       <c r="E227" t="n">
-        <v>96.16000366210938</v>
+        <v>98.13999938964844</v>
       </c>
       <c r="F227" t="n">
-        <v>21112400</v>
+        <v>11480300</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B228" t="n">
-        <v>96.08000183105469</v>
+        <v>97.87000274658203</v>
       </c>
       <c r="C228" t="n">
-        <v>96.58999633789062</v>
+        <v>98.56999969482422</v>
       </c>
       <c r="D228" t="n">
-        <v>95.59999847412109</v>
+        <v>97.37999725341797</v>
       </c>
       <c r="E228" t="n">
-        <v>96.19000244140625</v>
+        <v>98.18000030517578</v>
       </c>
       <c r="F228" t="n">
-        <v>11193000</v>
+        <v>16796800</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B229" t="n">
-        <v>97.62000274658203</v>
+        <v>101.9899978637695</v>
       </c>
       <c r="C229" t="n">
-        <v>99.05000305175781</v>
+        <v>103.2099990844727</v>
       </c>
       <c r="D229" t="n">
-        <v>97.20999908447266</v>
+        <v>99.69000244140625</v>
       </c>
       <c r="E229" t="n">
-        <v>98.13999938964844</v>
+        <v>101.7600021362305</v>
       </c>
       <c r="F229" t="n">
-        <v>11480300</v>
+        <v>20809000</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B230" t="n">
-        <v>97.87000274658203</v>
+        <v>102.5400009155273</v>
       </c>
       <c r="C230" t="n">
-        <v>98.56999969482422</v>
+        <v>104.7300033569336</v>
       </c>
       <c r="D230" t="n">
-        <v>97.37999725341797</v>
+        <v>102.5199966430664</v>
       </c>
       <c r="E230" t="n">
-        <v>98.18000030517578</v>
+        <v>104.6800003051758</v>
       </c>
       <c r="F230" t="n">
-        <v>16796800</v>
+        <v>14047200</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B231" t="n">
-        <v>101.9899978637695</v>
+        <v>104.4199981689453</v>
       </c>
       <c r="C231" t="n">
-        <v>103.2099990844727</v>
+        <v>105.25</v>
       </c>
       <c r="D231" t="n">
-        <v>99.69000244140625</v>
+        <v>103.6999969482422</v>
       </c>
       <c r="E231" t="n">
-        <v>101.7600021362305</v>
+        <v>104.9100036621094</v>
       </c>
       <c r="F231" t="n">
-        <v>20809000</v>
+        <v>10929700</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B232" t="n">
-        <v>102.5400009155273</v>
+        <v>104.6100006103516</v>
       </c>
       <c r="C232" t="n">
-        <v>104.7300033569336</v>
+        <v>104.8000030517578</v>
       </c>
       <c r="D232" t="n">
-        <v>102.5199966430664</v>
+        <v>102.8000030517578</v>
       </c>
       <c r="E232" t="n">
-        <v>104.6800003051758</v>
+        <v>103.1800003051758</v>
       </c>
       <c r="F232" t="n">
-        <v>14047200</v>
+        <v>8631900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B233" t="n">
-        <v>104.4199981689453</v>
+        <v>102.9499969482422</v>
       </c>
       <c r="C233" t="n">
-        <v>105.25</v>
+        <v>104.0899963378906</v>
       </c>
       <c r="D233" t="n">
-        <v>103.6999969482422</v>
+        <v>102.7900009155273</v>
       </c>
       <c r="E233" t="n">
-        <v>104.9100036621094</v>
+        <v>103.5299987792969</v>
       </c>
       <c r="F233" t="n">
-        <v>10929700</v>
+        <v>6781600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B234" t="n">
-        <v>104.6100006103516</v>
+        <v>103.2900009155273</v>
       </c>
       <c r="C234" t="n">
-        <v>104.8000030517578</v>
+        <v>103.6800003051758</v>
       </c>
       <c r="D234" t="n">
-        <v>102.8000030517578</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E234" t="n">
-        <v>103.1800003051758</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F234" t="n">
-        <v>8631900</v>
+        <v>6717500</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B235" t="n">
-        <v>102.9499969482422</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="C235" t="n">
-        <v>104.0899963378906</v>
+        <v>104.9400024414062</v>
       </c>
       <c r="D235" t="n">
-        <v>102.7900009155273</v>
+        <v>103.4599990844727</v>
       </c>
       <c r="E235" t="n">
-        <v>103.5299987792969</v>
+        <v>104.8000030517578</v>
       </c>
       <c r="F235" t="n">
-        <v>6781600</v>
+        <v>7100000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B236" t="n">
-        <v>103.2900009155273</v>
+        <v>104.9899978637695</v>
       </c>
       <c r="C236" t="n">
-        <v>103.6800003051758</v>
+        <v>107.1100006103516</v>
       </c>
       <c r="D236" t="n">
-        <v>102.0299987792969</v>
+        <v>104.9100036621094</v>
       </c>
       <c r="E236" t="n">
-        <v>103.2200012207031</v>
+        <v>106.8499984741211</v>
       </c>
       <c r="F236" t="n">
-        <v>6717500</v>
+        <v>8176900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B237" t="n">
-        <v>103.8000030517578</v>
+        <v>106.3300018310547</v>
       </c>
       <c r="C237" t="n">
-        <v>104.9400024414062</v>
+        <v>106.6399993896484</v>
       </c>
       <c r="D237" t="n">
         <v>103.4599990844727</v>
       </c>
       <c r="E237" t="n">
-        <v>104.8000030517578</v>
+        <v>103.5</v>
       </c>
       <c r="F237" t="n">
-        <v>7100000</v>
+        <v>7635000</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B238" t="n">
-        <v>104.9899978637695</v>
+        <v>104.1900024414062</v>
       </c>
       <c r="C238" t="n">
-        <v>107.1100006103516</v>
+        <v>105.2099990844727</v>
       </c>
       <c r="D238" t="n">
-        <v>104.9100036621094</v>
+        <v>103.629997253418</v>
       </c>
       <c r="E238" t="n">
-        <v>106.8499984741211</v>
+        <v>103.9499969482422</v>
       </c>
       <c r="F238" t="n">
-        <v>8176900</v>
+        <v>6149900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B239" t="n">
-        <v>106.3300018310547</v>
+        <v>104.0599975585938</v>
       </c>
       <c r="C239" t="n">
-        <v>106.6399993896484</v>
+        <v>107.0599975585938</v>
       </c>
       <c r="D239" t="n">
-        <v>103.4599990844727</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="E239" t="n">
-        <v>103.5</v>
+        <v>106.9300003051758</v>
       </c>
       <c r="F239" t="n">
-        <v>7635000</v>
+        <v>8046100</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B240" t="n">
-        <v>104.1900024414062</v>
+        <v>106.879997253418</v>
       </c>
       <c r="C240" t="n">
-        <v>105.2099990844727</v>
+        <v>108.6900024414062</v>
       </c>
       <c r="D240" t="n">
-        <v>103.629997253418</v>
+        <v>106.4199981689453</v>
       </c>
       <c r="E240" t="n">
-        <v>103.9499969482422</v>
+        <v>107.3199996948242</v>
       </c>
       <c r="F240" t="n">
-        <v>6149900</v>
+        <v>7971500</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B241" t="n">
-        <v>104.0599975585938</v>
+        <v>107.5699996948242</v>
       </c>
       <c r="C241" t="n">
-        <v>107.0599975585938</v>
+        <v>108.4100036621094</v>
       </c>
       <c r="D241" t="n">
-        <v>103.9599990844727</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="E241" t="n">
-        <v>106.9300003051758</v>
+        <v>107.7799987792969</v>
       </c>
       <c r="F241" t="n">
-        <v>8046100</v>
+        <v>6840800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B242" t="n">
-        <v>106.879997253418</v>
+        <v>108.3899993896484</v>
       </c>
       <c r="C242" t="n">
-        <v>108.6900024414062</v>
+        <v>111.870002746582</v>
       </c>
       <c r="D242" t="n">
-        <v>106.4199981689453</v>
+        <v>108.0800018310547</v>
       </c>
       <c r="E242" t="n">
-        <v>107.3199996948242</v>
+        <v>110.6100006103516</v>
       </c>
       <c r="F242" t="n">
-        <v>7971500</v>
+        <v>12658400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B243" t="n">
-        <v>107.5699996948242</v>
+        <v>110.5</v>
       </c>
       <c r="C243" t="n">
-        <v>108.4100036621094</v>
+        <v>111.5999984741211</v>
       </c>
       <c r="D243" t="n">
-        <v>106.9700012207031</v>
+        <v>109.7600021362305</v>
       </c>
       <c r="E243" t="n">
-        <v>107.7799987792969</v>
+        <v>111.25</v>
       </c>
       <c r="F243" t="n">
-        <v>6840800</v>
+        <v>6747100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B244" t="n">
-        <v>108.3899993896484</v>
+        <v>111.3000030517578</v>
       </c>
       <c r="C244" t="n">
-        <v>111.870002746582</v>
+        <v>111.5199966430664</v>
       </c>
       <c r="D244" t="n">
-        <v>108.0800018310547</v>
+        <v>109.4499969482422</v>
       </c>
       <c r="E244" t="n">
-        <v>110.6100006103516</v>
+        <v>109.629997253418</v>
       </c>
       <c r="F244" t="n">
-        <v>12658400</v>
+        <v>8524600</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B245" t="n">
-        <v>110.5</v>
+        <v>108.7799987792969</v>
       </c>
       <c r="C245" t="n">
-        <v>111.5999984741211</v>
+        <v>108.870002746582</v>
       </c>
       <c r="D245" t="n">
-        <v>109.7600021362305</v>
+        <v>106.7399978637695</v>
       </c>
       <c r="E245" t="n">
-        <v>111.25</v>
+        <v>106.8199996948242</v>
       </c>
       <c r="F245" t="n">
-        <v>6747100</v>
+        <v>8699500</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B246" t="n">
-        <v>111.3000030517578</v>
+        <v>107.25</v>
       </c>
       <c r="C246" t="n">
-        <v>111.5199966430664</v>
+        <v>108.1999969482422</v>
       </c>
       <c r="D246" t="n">
-        <v>109.4499969482422</v>
+        <v>107.0299987792969</v>
       </c>
       <c r="E246" t="n">
-        <v>109.629997253418</v>
+        <v>108.0999984741211</v>
       </c>
       <c r="F246" t="n">
-        <v>8524600</v>
+        <v>5465900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B247" t="n">
-        <v>108.7799987792969</v>
+        <v>107.7799987792969</v>
       </c>
       <c r="C247" t="n">
-        <v>108.870002746582</v>
+        <v>108.0899963378906</v>
       </c>
       <c r="D247" t="n">
-        <v>106.7399978637695</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="E247" t="n">
-        <v>106.8199996948242</v>
+        <v>107.5500030517578</v>
       </c>
       <c r="F247" t="n">
-        <v>8699500</v>
+        <v>8728700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B248" t="n">
-        <v>107.25</v>
+        <v>107.2399978637695</v>
       </c>
       <c r="C248" t="n">
-        <v>108.1999969482422</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D248" t="n">
-        <v>107.0299987792969</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="E248" t="n">
-        <v>108.0999984741211</v>
+        <v>106.2200012207031</v>
       </c>
       <c r="F248" t="n">
-        <v>5465900</v>
+        <v>7033700</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B249" t="n">
-        <v>107.7799987792969</v>
+        <v>106.7099990844727</v>
       </c>
       <c r="C249" t="n">
-        <v>108.0899963378906</v>
+        <v>108.9899978637695</v>
       </c>
       <c r="D249" t="n">
-        <v>106.9700012207031</v>
+        <v>106.3300018310547</v>
       </c>
       <c r="E249" t="n">
-        <v>107.5500030517578</v>
+        <v>107.9800033569336</v>
       </c>
       <c r="F249" t="n">
-        <v>8728700</v>
+        <v>7555300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B250" t="n">
-        <v>107.2399978637695</v>
+        <v>108.620002746582</v>
       </c>
       <c r="C250" t="n">
-        <v>108.9499969482422</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="D250" t="n">
-        <v>106.1399993896484</v>
+        <v>106.9000015258789</v>
       </c>
       <c r="E250" t="n">
-        <v>106.2200012207031</v>
+        <v>107.1600036621094</v>
       </c>
       <c r="F250" t="n">
-        <v>7033700</v>
+        <v>6241300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B251" t="n">
-        <v>106.7099990844727</v>
+        <v>106.4899978637695</v>
       </c>
       <c r="C251" t="n">
-        <v>108.9899978637695</v>
+        <v>106.879997253418</v>
       </c>
       <c r="D251" t="n">
-        <v>106.3300018310547</v>
+        <v>105.1699981689453</v>
       </c>
       <c r="E251" t="n">
-        <v>107.9800033569336</v>
+        <v>105.3099975585938</v>
       </c>
       <c r="F251" t="n">
-        <v>7555300</v>
+        <v>6103700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,53 +6969,19 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B252" t="n">
-        <v>108.620002746582</v>
-      </c>
-      <c r="C252" t="n">
-        <v>109.1999969482422</v>
-      </c>
-      <c r="D252" t="n">
-        <v>106.9000015258789</v>
-      </c>
-      <c r="E252" t="n">
-        <v>107.1600036621094</v>
-      </c>
+        <v>46273</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>6241300</v>
+        <v>7332699</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B253" t="n">
-        <v>106.4899978637695</v>
-      </c>
-      <c r="C253" t="n">
-        <v>106.879997253418</v>
-      </c>
-      <c r="D253" t="n">
-        <v>105.1699981689453</v>
-      </c>
-      <c r="E253" t="n">
-        <v>105.3099975585938</v>
-      </c>
-      <c r="F253" t="n">
-        <v>6103700</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11154,34 +11120,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>105.06</v>
+      </c>
+      <c r="D2" t="n">
         <v>105.31</v>
       </c>
-      <c r="D2" t="n">
-        <v>107.16</v>
-      </c>
       <c r="E2" t="n">
-        <v>106.49</v>
+        <v>104.68</v>
       </c>
       <c r="F2" t="n">
-        <v>106.88</v>
+        <v>105.1</v>
       </c>
       <c r="G2" t="n">
-        <v>105.17</v>
+        <v>103.71</v>
       </c>
       <c r="H2" t="n">
-        <v>5945953</v>
+        <v>7332699</v>
       </c>
       <c r="I2" t="n">
-        <v>10375558</v>
+        <v>10420983</v>
       </c>
       <c r="J2" t="n">
-        <v>181837381632</v>
+        <v>181405712384</v>
       </c>
       <c r="K2" t="n">
-        <v>21.713402</v>
+        <v>21.661856</v>
       </c>
       <c r="L2" t="n">
-        <v>14.0888405</v>
+        <v>14.055394</v>
       </c>
       <c r="M2" t="n">
         <v>4.85</v>
@@ -11220,7 +11186,7 @@
         <v>63.602</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.6557654</v>
+        <v>1.6518347</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.483</v>
@@ -11232,7 +11198,7 @@
         <v>98860998656</v>
       </c>
       <c r="AC2" t="n">
-        <v>229503401984</v>
+        <v>229071732736</v>
       </c>
       <c r="AD2" t="n">
         <v>20963000320</v>
@@ -11259,7 +11225,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-08 08:52:39</t>
+          <t>2026-09-09 09:15:36</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B2" t="n">
-        <v>116.8381638958523</v>
+        <v>115.1821357107481</v>
       </c>
       <c r="C2" t="n">
-        <v>117.3507459007291</v>
+        <v>115.8327187862414</v>
       </c>
       <c r="D2" t="n">
-        <v>115.5468645536568</v>
+        <v>112.8656800265299</v>
       </c>
       <c r="E2" t="n">
-        <v>115.6947250366211</v>
+        <v>114.1372680664062</v>
       </c>
       <c r="F2" t="n">
-        <v>5444300</v>
+        <v>7484900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>115.1821434099858</v>
+        <v>113.8021202611286</v>
       </c>
       <c r="C3" t="n">
-        <v>115.8327265289666</v>
+        <v>115.4975710271905</v>
       </c>
       <c r="D3" t="n">
-        <v>112.8656875709264</v>
+        <v>112.9938248401568</v>
       </c>
       <c r="E3" t="n">
-        <v>114.1372756958008</v>
+        <v>115.4088592529297</v>
       </c>
       <c r="F3" t="n">
-        <v>7484900</v>
+        <v>8399100</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B4" t="n">
-        <v>113.8021202611286</v>
+        <v>114.6005686850037</v>
       </c>
       <c r="C4" t="n">
-        <v>115.4975710271905</v>
+        <v>115.3398635838033</v>
       </c>
       <c r="D4" t="n">
-        <v>112.9938248401568</v>
+        <v>113.4571222983551</v>
       </c>
       <c r="E4" t="n">
-        <v>115.4088592529297</v>
+        <v>114.3048477172852</v>
       </c>
       <c r="F4" t="n">
-        <v>8399100</v>
+        <v>7640900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B5" t="n">
-        <v>114.6005610358709</v>
+        <v>114.452707566448</v>
       </c>
       <c r="C5" t="n">
-        <v>115.3398558853256</v>
+        <v>115.0835719416188</v>
       </c>
       <c r="D5" t="n">
-        <v>113.4571147255429</v>
+        <v>113.3585505206524</v>
       </c>
       <c r="E5" t="n">
-        <v>114.3048400878906</v>
+        <v>113.9697036743164</v>
       </c>
       <c r="F5" t="n">
-        <v>7640900</v>
+        <v>7150900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B6" t="n">
-        <v>114.45269990472</v>
+        <v>113.8021272666058</v>
       </c>
       <c r="C6" t="n">
-        <v>115.0835642376594</v>
+        <v>114.196419390973</v>
       </c>
       <c r="D6" t="n">
-        <v>113.3585429321699</v>
+        <v>113.0726917248494</v>
       </c>
       <c r="E6" t="n">
-        <v>113.9696960449219</v>
+        <v>113.5852737426758</v>
       </c>
       <c r="F6" t="n">
-        <v>7150900</v>
+        <v>6844900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B7" t="n">
-        <v>113.8021196226455</v>
+        <v>113.595115218382</v>
       </c>
       <c r="C7" t="n">
-        <v>114.1964117205285</v>
+        <v>114.9948525080674</v>
       </c>
       <c r="D7" t="n">
-        <v>113.0726841298844</v>
+        <v>113.5754039981875</v>
       </c>
       <c r="E7" t="n">
-        <v>113.5852661132812</v>
+        <v>114.4428405761719</v>
       </c>
       <c r="F7" t="n">
-        <v>6844900</v>
+        <v>7333900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B8" t="n">
-        <v>113.5951227912625</v>
+        <v>113.6838355517382</v>
       </c>
       <c r="C8" t="n">
-        <v>114.9948601742622</v>
+        <v>114.1274094548904</v>
       </c>
       <c r="D8" t="n">
-        <v>113.5754115697539</v>
+        <v>112.4221068738425</v>
       </c>
       <c r="E8" t="n">
-        <v>114.4428482055664</v>
+        <v>113.2205429077148</v>
       </c>
       <c r="F8" t="n">
-        <v>7333900</v>
+        <v>9460500</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B9" t="n">
-        <v>113.6838432123518</v>
+        <v>112.9642523554146</v>
       </c>
       <c r="C9" t="n">
-        <v>114.1274171453944</v>
+        <v>112.9642523554146</v>
       </c>
       <c r="D9" t="n">
-        <v>112.4221144494342</v>
+        <v>110.3323644761722</v>
       </c>
       <c r="E9" t="n">
-        <v>113.2205505371094</v>
+        <v>112.1362457275391</v>
       </c>
       <c r="F9" t="n">
-        <v>9460500</v>
+        <v>23398400</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B10" t="n">
-        <v>112.9642523554146</v>
+        <v>110.1647924763258</v>
       </c>
       <c r="C10" t="n">
-        <v>112.9642523554146</v>
+        <v>112.0080961635035</v>
       </c>
       <c r="D10" t="n">
-        <v>110.3323644761722</v>
+        <v>109.9282127085895</v>
       </c>
       <c r="E10" t="n">
-        <v>112.1362457275391</v>
+        <v>110.953369140625</v>
       </c>
       <c r="F10" t="n">
-        <v>23398400</v>
+        <v>15479800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B11" t="n">
-        <v>110.1647924763258</v>
+        <v>111.1110969379416</v>
       </c>
       <c r="C11" t="n">
-        <v>112.0080961635035</v>
+        <v>111.9982523292055</v>
       </c>
       <c r="D11" t="n">
-        <v>109.9282127085895</v>
+        <v>110.0070805043135</v>
       </c>
       <c r="E11" t="n">
-        <v>110.953369140625</v>
+        <v>110.6478042602539</v>
       </c>
       <c r="F11" t="n">
-        <v>15479800</v>
+        <v>13145000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B12" t="n">
-        <v>111.111089276602</v>
+        <v>110.8055211263376</v>
       </c>
       <c r="C12" t="n">
-        <v>111.9982446066948</v>
+        <v>112.5206831561622</v>
       </c>
       <c r="D12" t="n">
-        <v>110.0070729190981</v>
+        <v>110.5985119402154</v>
       </c>
       <c r="E12" t="n">
-        <v>110.6477966308594</v>
+        <v>111.8109588623047</v>
       </c>
       <c r="F12" t="n">
-        <v>13145000</v>
+        <v>8755200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B13" t="n">
-        <v>110.8055211263376</v>
+        <v>111.1012331951749</v>
       </c>
       <c r="C13" t="n">
-        <v>112.5206831561622</v>
+        <v>112.4221106191933</v>
       </c>
       <c r="D13" t="n">
-        <v>110.5985119402154</v>
+        <v>111.0420920115833</v>
       </c>
       <c r="E13" t="n">
-        <v>111.8109588623047</v>
+        <v>111.3772354125977</v>
       </c>
       <c r="F13" t="n">
-        <v>8755200</v>
+        <v>6365500</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B14" t="n">
-        <v>111.1012331951749</v>
+        <v>111.5152366513407</v>
       </c>
       <c r="C14" t="n">
-        <v>112.4221106191933</v>
+        <v>111.9489587195086</v>
       </c>
       <c r="D14" t="n">
-        <v>111.0420920115833</v>
+        <v>111.1505226581053</v>
       </c>
       <c r="E14" t="n">
-        <v>111.3772354125977</v>
+        <v>111.8503875732422</v>
       </c>
       <c r="F14" t="n">
-        <v>6365500</v>
+        <v>6145700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B15" t="n">
-        <v>111.5152366513407</v>
+        <v>111.8503861885936</v>
       </c>
       <c r="C15" t="n">
-        <v>111.9489587195086</v>
+        <v>113.3684058878927</v>
       </c>
       <c r="D15" t="n">
-        <v>111.1505226581053</v>
+        <v>111.7123850814297</v>
       </c>
       <c r="E15" t="n">
-        <v>111.8503875732422</v>
+        <v>113.1416854858398</v>
       </c>
       <c r="F15" t="n">
-        <v>6145700</v>
+        <v>9304100</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B16" t="n">
-        <v>111.8503861885936</v>
+        <v>112.8952551010659</v>
       </c>
       <c r="C16" t="n">
-        <v>113.3684058878927</v>
+        <v>113.2402578727591</v>
       </c>
       <c r="D16" t="n">
-        <v>111.7123850814297</v>
+        <v>111.7222381568123</v>
       </c>
       <c r="E16" t="n">
-        <v>113.1416854858398</v>
+        <v>112.8656845092773</v>
       </c>
       <c r="F16" t="n">
-        <v>9304100</v>
+        <v>9303700</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
-        <v>112.8952551010659</v>
+        <v>112.4516824751333</v>
       </c>
       <c r="C17" t="n">
-        <v>113.2402578727591</v>
+        <v>114.4034167605612</v>
       </c>
       <c r="D17" t="n">
-        <v>111.7222381568123</v>
+        <v>111.1800943701441</v>
       </c>
       <c r="E17" t="n">
-        <v>112.8656845092773</v>
+        <v>111.3378067016602</v>
       </c>
       <c r="F17" t="n">
-        <v>9303700</v>
+        <v>9736300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B18" t="n">
-        <v>112.4516824751333</v>
+        <v>111.3673818357084</v>
       </c>
       <c r="C18" t="n">
-        <v>114.4034167605612</v>
+        <v>111.5546647543437</v>
       </c>
       <c r="D18" t="n">
-        <v>111.1800943701441</v>
+        <v>109.1987790515154</v>
       </c>
       <c r="E18" t="n">
-        <v>111.3378067016602</v>
+        <v>110.5393676757812</v>
       </c>
       <c r="F18" t="n">
-        <v>9736300</v>
+        <v>8695100</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B19" t="n">
-        <v>111.3673895222522</v>
+        <v>110.4407994688091</v>
       </c>
       <c r="C19" t="n">
-        <v>111.5546724538137</v>
+        <v>111.9489598311001</v>
       </c>
       <c r="D19" t="n">
-        <v>109.1987865883829</v>
+        <v>109.9676474333371</v>
       </c>
       <c r="E19" t="n">
-        <v>110.5393753051758</v>
+        <v>110.8646621704102</v>
       </c>
       <c r="F19" t="n">
-        <v>8695100</v>
+        <v>7148400</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B20" t="n">
-        <v>110.4407994688091</v>
+        <v>111.0815219633868</v>
       </c>
       <c r="C20" t="n">
-        <v>111.9489598311001</v>
+        <v>111.4955252894808</v>
       </c>
       <c r="D20" t="n">
-        <v>109.9676474333371</v>
+        <v>109.8592156856383</v>
       </c>
       <c r="E20" t="n">
-        <v>110.8646621704102</v>
+        <v>111.1406631469727</v>
       </c>
       <c r="F20" t="n">
-        <v>7148400</v>
+        <v>6141200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B21" t="n">
-        <v>111.0815219633868</v>
+        <v>111.0223763857341</v>
       </c>
       <c r="C21" t="n">
-        <v>111.4955252894808</v>
+        <v>111.7813900254436</v>
       </c>
       <c r="D21" t="n">
-        <v>109.8592156856383</v>
+        <v>110.20422908127</v>
       </c>
       <c r="E21" t="n">
-        <v>111.1406631469727</v>
+        <v>110.9238052368164</v>
       </c>
       <c r="F21" t="n">
-        <v>6141200</v>
+        <v>5409800</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B22" t="n">
-        <v>111.0223763857341</v>
+        <v>111.1998048136618</v>
       </c>
       <c r="C22" t="n">
-        <v>111.7813900254436</v>
+        <v>111.584237549633</v>
       </c>
       <c r="D22" t="n">
-        <v>110.20422908127</v>
+        <v>110.0563659765542</v>
       </c>
       <c r="E22" t="n">
-        <v>110.9238052368164</v>
+        <v>110.2929382324219</v>
       </c>
       <c r="F22" t="n">
-        <v>5409800</v>
+        <v>7074400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B23" t="n">
-        <v>111.1998048136618</v>
+        <v>110.2239317389327</v>
       </c>
       <c r="C23" t="n">
-        <v>111.584237549633</v>
+        <v>111.3870892549816</v>
       </c>
       <c r="D23" t="n">
-        <v>110.0563659765542</v>
+        <v>109.2973464660052</v>
       </c>
       <c r="E23" t="n">
-        <v>110.2929382324219</v>
+        <v>109.4057769775391</v>
       </c>
       <c r="F23" t="n">
-        <v>7074400</v>
+        <v>6502400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B24" t="n">
-        <v>110.2239394253812</v>
+        <v>109.9380737221385</v>
       </c>
       <c r="C24" t="n">
-        <v>111.3870970225426</v>
+        <v>111.0716606845381</v>
       </c>
       <c r="D24" t="n">
-        <v>109.2973540878383</v>
+        <v>107.5526174321997</v>
       </c>
       <c r="E24" t="n">
-        <v>109.4057846069336</v>
+        <v>107.631477355957</v>
       </c>
       <c r="F24" t="n">
-        <v>6502400</v>
+        <v>9635200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B25" t="n">
-        <v>109.9380737221385</v>
+        <v>108.8143500705835</v>
       </c>
       <c r="C25" t="n">
-        <v>111.0716606845381</v>
+        <v>109.3762138868319</v>
       </c>
       <c r="D25" t="n">
-        <v>107.5526174321997</v>
+        <v>107.8187641784603</v>
       </c>
       <c r="E25" t="n">
-        <v>107.631477355957</v>
+        <v>108.6960601806641</v>
       </c>
       <c r="F25" t="n">
-        <v>9635200</v>
+        <v>7435100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B26" t="n">
-        <v>108.8143424328862</v>
+        <v>108.0849128268841</v>
       </c>
       <c r="C26" t="n">
-        <v>109.3762062096973</v>
+        <v>110.2436487598859</v>
       </c>
       <c r="D26" t="n">
-        <v>107.8187566106434</v>
+        <v>107.641331387133</v>
       </c>
       <c r="E26" t="n">
-        <v>108.6960525512695</v>
+        <v>109.5832138061523</v>
       </c>
       <c r="F26" t="n">
-        <v>7435100</v>
+        <v>7898000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B27" t="n">
-        <v>108.0849128268841</v>
+        <v>109.8789291603083</v>
       </c>
       <c r="C27" t="n">
-        <v>110.2436487598859</v>
+        <v>111.0716572685961</v>
       </c>
       <c r="D27" t="n">
-        <v>107.641331387133</v>
+        <v>109.5536376251855</v>
       </c>
       <c r="E27" t="n">
-        <v>109.5832138061523</v>
+        <v>110.1155014038086</v>
       </c>
       <c r="F27" t="n">
-        <v>7898000</v>
+        <v>7012600</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B28" t="n">
-        <v>109.8789291603083</v>
+        <v>110.1943638011324</v>
       </c>
       <c r="C28" t="n">
-        <v>111.0716572685961</v>
+        <v>110.4900772320282</v>
       </c>
       <c r="D28" t="n">
-        <v>109.5536376251855</v>
+        <v>106.9611821588295</v>
       </c>
       <c r="E28" t="n">
-        <v>110.1155014038086</v>
+        <v>108.3116226196289</v>
       </c>
       <c r="F28" t="n">
-        <v>7012600</v>
+        <v>7531200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B29" t="n">
-        <v>110.1943638011324</v>
+        <v>108.1736213665725</v>
       </c>
       <c r="C29" t="n">
-        <v>110.4900772320282</v>
+        <v>109.8690721085103</v>
       </c>
       <c r="D29" t="n">
-        <v>106.9611821588295</v>
+        <v>107.877907936081</v>
       </c>
       <c r="E29" t="n">
-        <v>108.3116226196289</v>
+        <v>109.0903472900391</v>
       </c>
       <c r="F29" t="n">
-        <v>7531200</v>
+        <v>10090500</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B30" t="n">
-        <v>108.1736289318545</v>
+        <v>109.4452125270959</v>
       </c>
       <c r="C30" t="n">
-        <v>109.8690797923661</v>
+        <v>110.6478000651592</v>
       </c>
       <c r="D30" t="n">
-        <v>107.8779154806818</v>
+        <v>109.0213498295899</v>
       </c>
       <c r="E30" t="n">
-        <v>109.0903549194336</v>
+        <v>110.3619384765625</v>
       </c>
       <c r="F30" t="n">
-        <v>10090500</v>
+        <v>8047500</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B31" t="n">
-        <v>109.4452125270959</v>
+        <v>110.6477986393913</v>
       </c>
       <c r="C31" t="n">
-        <v>110.6478000651592</v>
+        <v>112.9051132067436</v>
       </c>
       <c r="D31" t="n">
-        <v>109.0213498295899</v>
+        <v>110.4407969786948</v>
       </c>
       <c r="E31" t="n">
-        <v>110.3619384765625</v>
+        <v>112.6685409545898</v>
       </c>
       <c r="F31" t="n">
-        <v>8047500</v>
+        <v>8163200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B32" t="n">
-        <v>110.6477986393913</v>
+        <v>112.3728165513869</v>
       </c>
       <c r="C32" t="n">
-        <v>112.9051132067436</v>
+        <v>112.6488187571811</v>
       </c>
       <c r="D32" t="n">
-        <v>110.4407969786948</v>
+        <v>111.3673788702085</v>
       </c>
       <c r="E32" t="n">
-        <v>112.6685409545898</v>
+        <v>111.465950012207</v>
       </c>
       <c r="F32" t="n">
-        <v>8163200</v>
+        <v>7569200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B33" t="n">
-        <v>112.3728242428528</v>
+        <v>111.5546652306962</v>
       </c>
       <c r="C33" t="n">
-        <v>112.6488264675382</v>
+        <v>112.2052483248811</v>
       </c>
       <c r="D33" t="n">
-        <v>111.3673864928563</v>
+        <v>110.3027958955931</v>
       </c>
       <c r="E33" t="n">
-        <v>111.4659576416016</v>
+        <v>111.4166641235352</v>
       </c>
       <c r="F33" t="n">
-        <v>7569200</v>
+        <v>6945400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B34" t="n">
-        <v>111.5546728695406</v>
+        <v>111.6138166065038</v>
       </c>
       <c r="C34" t="n">
-        <v>112.2052560082749</v>
+        <v>112.0278199378997</v>
       </c>
       <c r="D34" t="n">
-        <v>110.3028034487141</v>
+        <v>109.9972182029886</v>
       </c>
       <c r="E34" t="n">
-        <v>111.4166717529297</v>
+        <v>110.0859375</v>
       </c>
       <c r="F34" t="n">
-        <v>6945400</v>
+        <v>6235200</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B35" t="n">
-        <v>111.6138166065038</v>
+        <v>110.34222664747</v>
       </c>
       <c r="C35" t="n">
-        <v>112.0278199378997</v>
+        <v>110.992802225815</v>
       </c>
       <c r="D35" t="n">
-        <v>109.9972182029886</v>
+        <v>109.721214140304</v>
       </c>
       <c r="E35" t="n">
-        <v>110.0859375</v>
+        <v>110.7365112304688</v>
       </c>
       <c r="F35" t="n">
-        <v>6235200</v>
+        <v>6029600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B36" t="n">
-        <v>110.34222664747</v>
+        <v>110.3126569642538</v>
       </c>
       <c r="C36" t="n">
-        <v>110.992802225815</v>
+        <v>110.8745207722</v>
       </c>
       <c r="D36" t="n">
-        <v>109.721214140304</v>
+        <v>109.8690755239826</v>
       </c>
       <c r="E36" t="n">
-        <v>110.7365112304688</v>
+        <v>110.0563659667969</v>
       </c>
       <c r="F36" t="n">
-        <v>6029600</v>
+        <v>6839400</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B37" t="n">
-        <v>110.3126569642538</v>
+        <v>109.5930739758994</v>
       </c>
       <c r="C37" t="n">
-        <v>110.8745207722</v>
+        <v>109.9380767512234</v>
       </c>
       <c r="D37" t="n">
-        <v>109.8690755239826</v>
+        <v>108.4397757610322</v>
       </c>
       <c r="E37" t="n">
-        <v>110.0563659667969</v>
+        <v>108.6664886474609</v>
       </c>
       <c r="F37" t="n">
-        <v>6839400</v>
+        <v>7097100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B38" t="n">
-        <v>109.59306628145</v>
+        <v>108.5580608670909</v>
       </c>
       <c r="C38" t="n">
-        <v>109.9380690325516</v>
+        <v>111.9588219337512</v>
       </c>
       <c r="D38" t="n">
-        <v>108.4397681475551</v>
+        <v>107.9863451909205</v>
       </c>
       <c r="E38" t="n">
-        <v>108.6664810180664</v>
+        <v>110.24365234375</v>
       </c>
       <c r="F38" t="n">
-        <v>7097100</v>
+        <v>8311300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B39" t="n">
-        <v>108.5580608670909</v>
+        <v>109.9873709449201</v>
       </c>
       <c r="C39" t="n">
-        <v>111.9588219337512</v>
+        <v>111.4856720013147</v>
       </c>
       <c r="D39" t="n">
-        <v>107.9863451909205</v>
+        <v>108.9523550527189</v>
       </c>
       <c r="E39" t="n">
-        <v>110.24365234375</v>
+        <v>111.0125274658203</v>
       </c>
       <c r="F39" t="n">
-        <v>8311300</v>
+        <v>8700600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B40" t="n">
-        <v>109.98736338598</v>
+        <v>110.9435236572715</v>
       </c>
       <c r="C40" t="n">
-        <v>111.485664339403</v>
+        <v>111.1998071396153</v>
       </c>
       <c r="D40" t="n">
-        <v>108.9523475649108</v>
+        <v>109.4452151242777</v>
       </c>
       <c r="E40" t="n">
-        <v>111.0125198364258</v>
+        <v>110.519660949707</v>
       </c>
       <c r="F40" t="n">
-        <v>8700600</v>
+        <v>8542300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B41" t="n">
-        <v>110.9435236572715</v>
+        <v>109.3860735058741</v>
       </c>
       <c r="C41" t="n">
-        <v>111.1998071396153</v>
+        <v>110.1943689542488</v>
       </c>
       <c r="D41" t="n">
-        <v>109.4452151242777</v>
+        <v>109.0607819482302</v>
       </c>
       <c r="E41" t="n">
-        <v>110.519660949707</v>
+        <v>109.8789367675781</v>
       </c>
       <c r="F41" t="n">
-        <v>8542300</v>
+        <v>7950100</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B42" t="n">
-        <v>109.3860659107013</v>
+        <v>109.7606408126771</v>
       </c>
       <c r="C42" t="n">
-        <v>110.1943613029524</v>
+        <v>110.3717939308002</v>
       </c>
       <c r="D42" t="n">
-        <v>109.0607743756439</v>
+        <v>109.0213459609701</v>
       </c>
       <c r="E42" t="n">
-        <v>109.8789291381836</v>
+        <v>109.7705001831055</v>
       </c>
       <c r="F42" t="n">
-        <v>7950100</v>
+        <v>5746000</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B43" t="n">
-        <v>109.7606408126771</v>
+        <v>109.5832124067878</v>
       </c>
       <c r="C43" t="n">
-        <v>110.3717939308002</v>
+        <v>110.115505615394</v>
       </c>
       <c r="D43" t="n">
-        <v>109.0213459609701</v>
+        <v>107.6216187917271</v>
       </c>
       <c r="E43" t="n">
-        <v>109.7705001831055</v>
+        <v>108.9129180908203</v>
       </c>
       <c r="F43" t="n">
-        <v>5746000</v>
+        <v>10291800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B44" t="n">
-        <v>109.5832124067878</v>
+        <v>108.6862106348567</v>
       </c>
       <c r="C44" t="n">
-        <v>110.115505615394</v>
+        <v>109.8395088841645</v>
       </c>
       <c r="D44" t="n">
-        <v>107.6216187917271</v>
+        <v>108.4693495923209</v>
       </c>
       <c r="E44" t="n">
-        <v>108.9129180908203</v>
+        <v>109.1593551635742</v>
       </c>
       <c r="F44" t="n">
-        <v>10291800</v>
+        <v>8782100</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B45" t="n">
-        <v>108.6862030385313</v>
+        <v>109.5635011857433</v>
       </c>
       <c r="C45" t="n">
-        <v>109.8395012072324</v>
+        <v>111.1800920323978</v>
       </c>
       <c r="D45" t="n">
-        <v>108.4693420111524</v>
+        <v>109.4452112992212</v>
       </c>
       <c r="E45" t="n">
-        <v>109.1593475341797</v>
+        <v>110.637939453125</v>
       </c>
       <c r="F45" t="n">
-        <v>8782100</v>
+        <v>9158700</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B46" t="n">
-        <v>109.5635011857433</v>
+        <v>111.0420904629071</v>
       </c>
       <c r="C46" t="n">
-        <v>111.1800920323978</v>
+        <v>113.3289756160103</v>
       </c>
       <c r="D46" t="n">
-        <v>109.4452112992212</v>
+        <v>110.815370061474</v>
       </c>
       <c r="E46" t="n">
-        <v>110.637939453125</v>
+        <v>113.2106857299805</v>
       </c>
       <c r="F46" t="n">
-        <v>9158700</v>
+        <v>9713300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B47" t="n">
-        <v>111.0420979461576</v>
+        <v>112.9346876340564</v>
       </c>
       <c r="C47" t="n">
-        <v>113.3289832533765</v>
+        <v>115.4187151672819</v>
       </c>
       <c r="D47" t="n">
-        <v>110.8153775294455</v>
+        <v>112.7572565587906</v>
       </c>
       <c r="E47" t="n">
-        <v>113.210693359375</v>
+        <v>114.9850006103516</v>
       </c>
       <c r="F47" t="n">
-        <v>9713300</v>
+        <v>15248700</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B48" t="n">
-        <v>112.9346801407027</v>
+        <v>107.3357567169709</v>
       </c>
       <c r="C48" t="n">
-        <v>115.4187075091099</v>
+        <v>107.7990493697842</v>
       </c>
       <c r="D48" t="n">
-        <v>112.7572490772096</v>
+        <v>103.4125695047362</v>
       </c>
       <c r="E48" t="n">
-        <v>114.984992980957</v>
+        <v>106.0740280151367</v>
       </c>
       <c r="F48" t="n">
-        <v>15248700</v>
+        <v>44045400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B49" t="n">
-        <v>107.3357644371155</v>
+        <v>105.9853067984581</v>
       </c>
       <c r="C49" t="n">
-        <v>107.7990571232513</v>
+        <v>107.178042445792</v>
       </c>
       <c r="D49" t="n">
-        <v>103.4125769427048</v>
+        <v>103.797000351179</v>
       </c>
       <c r="E49" t="n">
-        <v>106.0740356445312</v>
+        <v>104.2898635864258</v>
       </c>
       <c r="F49" t="n">
-        <v>44045400</v>
+        <v>16691400</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B50" t="n">
-        <v>105.9853145518839</v>
+        <v>104.2405758139031</v>
       </c>
       <c r="C50" t="n">
-        <v>107.1780502864732</v>
+        <v>106.1331688606407</v>
       </c>
       <c r="D50" t="n">
-        <v>103.7970079445177</v>
+        <v>103.6195708355819</v>
       </c>
       <c r="E50" t="n">
-        <v>104.2898712158203</v>
+        <v>104.1814346313477</v>
       </c>
       <c r="F50" t="n">
-        <v>16691400</v>
+        <v>12296400</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B51" t="n">
-        <v>104.2405758139031</v>
+        <v>103.5998505812639</v>
       </c>
       <c r="C51" t="n">
-        <v>106.1331688606407</v>
+        <v>105.5515923025468</v>
       </c>
       <c r="D51" t="n">
-        <v>103.6195708355819</v>
+        <v>103.501279438279</v>
       </c>
       <c r="E51" t="n">
-        <v>104.1814346313477</v>
+        <v>104.7630081176758</v>
       </c>
       <c r="F51" t="n">
-        <v>12296400</v>
+        <v>11796200</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B52" t="n">
-        <v>103.5998505812639</v>
+        <v>104.5658651685615</v>
       </c>
       <c r="C52" t="n">
-        <v>105.5515923025468</v>
+        <v>106.0543067153343</v>
       </c>
       <c r="D52" t="n">
-        <v>103.501279438279</v>
+        <v>102.5944122393827</v>
       </c>
       <c r="E52" t="n">
-        <v>104.7630081176758</v>
+        <v>103.1759872436523</v>
       </c>
       <c r="F52" t="n">
-        <v>11796200</v>
+        <v>12790000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B53" t="n">
-        <v>104.5658729007312</v>
+        <v>103.8660034269339</v>
       </c>
       <c r="C53" t="n">
-        <v>106.0543145575675</v>
+        <v>104.2898661203646</v>
       </c>
       <c r="D53" t="n">
-        <v>102.5944198257724</v>
+        <v>101.0369656805012</v>
       </c>
       <c r="E53" t="n">
-        <v>103.1759948730469</v>
+        <v>101.2341079711914</v>
       </c>
       <c r="F53" t="n">
-        <v>12790000</v>
+        <v>12609900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B54" t="n">
-        <v>103.8660034269339</v>
+        <v>102.0029806312501</v>
       </c>
       <c r="C54" t="n">
-        <v>104.2898661203646</v>
+        <v>103.2844205576738</v>
       </c>
       <c r="D54" t="n">
-        <v>101.0369656805012</v>
+        <v>101.2242558006444</v>
       </c>
       <c r="E54" t="n">
-        <v>101.2341079711914</v>
+        <v>102.7915573120117</v>
       </c>
       <c r="F54" t="n">
-        <v>12609900</v>
+        <v>10785400</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B55" t="n">
-        <v>102.0029806312501</v>
+        <v>102.6042684356238</v>
       </c>
       <c r="C55" t="n">
-        <v>103.2844205576738</v>
+        <v>102.85070006221</v>
       </c>
       <c r="D55" t="n">
-        <v>101.2242558006444</v>
+        <v>100.4356731298631</v>
       </c>
       <c r="E55" t="n">
-        <v>102.7915573120117</v>
+        <v>100.4849624633789</v>
       </c>
       <c r="F55" t="n">
-        <v>10785400</v>
+        <v>15024800</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B56" t="n">
-        <v>102.6042684356238</v>
+        <v>101.0271004353643</v>
       </c>
       <c r="C56" t="n">
-        <v>102.85070006221</v>
+        <v>102.4366895412752</v>
       </c>
       <c r="D56" t="n">
-        <v>100.4356731298631</v>
+        <v>100.5440965869111</v>
       </c>
       <c r="E56" t="n">
-        <v>100.4849624633789</v>
+        <v>101.8353958129883</v>
       </c>
       <c r="F56" t="n">
-        <v>15024800</v>
+        <v>10574500</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B57" t="n">
-        <v>101.0271004353643</v>
+        <v>101.8452666826232</v>
       </c>
       <c r="C57" t="n">
-        <v>102.4366895412752</v>
+        <v>102.7619926734798</v>
       </c>
       <c r="D57" t="n">
-        <v>100.5440965869111</v>
+        <v>101.4115445947565</v>
       </c>
       <c r="E57" t="n">
-        <v>101.8353958129883</v>
+        <v>101.9536972045898</v>
       </c>
       <c r="F57" t="n">
-        <v>10574500</v>
+        <v>10130200</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B58" t="n">
-        <v>101.8452666826232</v>
+        <v>101.8255530884873</v>
       </c>
       <c r="C58" t="n">
-        <v>102.7619926734798</v>
+        <v>103.2449941712158</v>
       </c>
       <c r="D58" t="n">
-        <v>101.4115445947565</v>
+        <v>101.7664043830219</v>
       </c>
       <c r="E58" t="n">
-        <v>101.9536972045898</v>
+        <v>102.9788513183594</v>
       </c>
       <c r="F58" t="n">
-        <v>10130200</v>
+        <v>6525500</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B59" t="n">
-        <v>101.8255455445372</v>
+        <v>103.4224248942611</v>
       </c>
       <c r="C59" t="n">
-        <v>103.2449865221035</v>
+        <v>105.3051661613186</v>
       </c>
       <c r="D59" t="n">
-        <v>101.7663968434539</v>
+        <v>102.9788509675128</v>
       </c>
       <c r="E59" t="n">
-        <v>102.9788436889648</v>
+        <v>105.2460174560547</v>
       </c>
       <c r="F59" t="n">
-        <v>6525500</v>
+        <v>12628900</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B60" t="n">
-        <v>103.4224248942611</v>
+        <v>105.0094494941518</v>
       </c>
       <c r="C60" t="n">
-        <v>105.3051661613186</v>
+        <v>105.0488794591093</v>
       </c>
       <c r="D60" t="n">
-        <v>102.9788509675128</v>
+        <v>103.3238579748278</v>
       </c>
       <c r="E60" t="n">
-        <v>105.2460174560547</v>
+        <v>103.3337173461914</v>
       </c>
       <c r="F60" t="n">
-        <v>12628900</v>
+        <v>8548200</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B61" t="n">
-        <v>105.0094417410337</v>
+        <v>103.4027138498727</v>
       </c>
       <c r="C61" t="n">
-        <v>105.0488717030799</v>
+        <v>104.3391510392764</v>
       </c>
       <c r="D61" t="n">
-        <v>103.3238503461612</v>
+        <v>102.9788511438223</v>
       </c>
       <c r="E61" t="n">
-        <v>103.3337097167969</v>
+        <v>104.2307205200195</v>
       </c>
       <c r="F61" t="n">
-        <v>8548200</v>
+        <v>10177800</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B62" t="n">
-        <v>103.4027062810859</v>
+        <v>104.3292907185565</v>
       </c>
       <c r="C62" t="n">
-        <v>104.339143401945</v>
+        <v>104.7038716073053</v>
       </c>
       <c r="D62" t="n">
-        <v>102.978843606061</v>
+        <v>103.0182801694252</v>
       </c>
       <c r="E62" t="n">
-        <v>104.230712890625</v>
+        <v>103.9645767211914</v>
       </c>
       <c r="F62" t="n">
-        <v>10177800</v>
+        <v>11471400</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B63" t="n">
-        <v>104.3292907185565</v>
+        <v>103.6787148109135</v>
       </c>
       <c r="C63" t="n">
-        <v>104.7038716073053</v>
+        <v>104.6545819518468</v>
       </c>
       <c r="D63" t="n">
-        <v>103.0182801694252</v>
+        <v>103.0675616662248</v>
       </c>
       <c r="E63" t="n">
-        <v>103.9645767211914</v>
+        <v>103.797004699707</v>
       </c>
       <c r="F63" t="n">
-        <v>11471400</v>
+        <v>10680100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B64" t="n">
-        <v>103.6787148109135</v>
+        <v>103.7970053004195</v>
       </c>
       <c r="C64" t="n">
-        <v>104.6545819518468</v>
+        <v>106.5077532235307</v>
       </c>
       <c r="D64" t="n">
-        <v>103.0675616662248</v>
+        <v>103.3337126339174</v>
       </c>
       <c r="E64" t="n">
-        <v>103.797004699707</v>
+        <v>106.0937423706055</v>
       </c>
       <c r="F64" t="n">
-        <v>10680100</v>
+        <v>13727700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B65" t="n">
-        <v>103.7970053004195</v>
+        <v>106.0543107045445</v>
       </c>
       <c r="C65" t="n">
-        <v>106.5077532235307</v>
+        <v>106.2120305546496</v>
       </c>
       <c r="D65" t="n">
-        <v>103.3337126339174</v>
+        <v>105.0291617608474</v>
       </c>
       <c r="E65" t="n">
-        <v>106.0937423706055</v>
+        <v>105.4924468994141</v>
       </c>
       <c r="F65" t="n">
-        <v>13727700</v>
+        <v>8549400</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B66" t="n">
-        <v>106.0543107045445</v>
+        <v>105.5910275110776</v>
       </c>
       <c r="C66" t="n">
-        <v>106.2120305546496</v>
+        <v>108.1046256243346</v>
       </c>
       <c r="D66" t="n">
-        <v>105.0291617608474</v>
+        <v>105.0587342879123</v>
       </c>
       <c r="E66" t="n">
-        <v>105.4924468994141</v>
+        <v>107.2766189575195</v>
       </c>
       <c r="F66" t="n">
-        <v>8549400</v>
+        <v>11237900</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B67" t="n">
-        <v>105.5910275110776</v>
+        <v>107.6413280220333</v>
       </c>
       <c r="C67" t="n">
-        <v>108.1046256243346</v>
+        <v>109.9676431038136</v>
       </c>
       <c r="D67" t="n">
-        <v>105.0587342879123</v>
+        <v>107.5526162491543</v>
       </c>
       <c r="E67" t="n">
-        <v>107.2766189575195</v>
+        <v>109.8690719604492</v>
       </c>
       <c r="F67" t="n">
-        <v>11237900</v>
+        <v>13281400</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B68" t="n">
-        <v>107.6413280220333</v>
+        <v>110.1352217028325</v>
       </c>
       <c r="C68" t="n">
-        <v>109.9676431038136</v>
+        <v>111.7222343992454</v>
       </c>
       <c r="D68" t="n">
-        <v>107.5526162491543</v>
+        <v>109.5634985458288</v>
       </c>
       <c r="E68" t="n">
-        <v>109.8690719604492</v>
+        <v>110.0070724487305</v>
       </c>
       <c r="F68" t="n">
-        <v>13281400</v>
+        <v>13059100</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,25 +2211,25 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B69" t="n">
-        <v>110.1352293411146</v>
+        <v>109.8582130022918</v>
       </c>
       <c r="C69" t="n">
-        <v>111.7222421475927</v>
+        <v>110.7017554968497</v>
       </c>
       <c r="D69" t="n">
-        <v>109.5635061444599</v>
+        <v>107.7245680705396</v>
       </c>
       <c r="E69" t="n">
-        <v>110.007080078125</v>
+        <v>109.6498107910156</v>
       </c>
       <c r="F69" t="n">
-        <v>13059100</v>
+        <v>14318000</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2237,25 +2237,25 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B70" t="n">
-        <v>109.8582130022918</v>
+        <v>110.3742651303662</v>
       </c>
       <c r="C70" t="n">
-        <v>110.7017554968497</v>
+        <v>111.991867603266</v>
       </c>
       <c r="D70" t="n">
-        <v>107.7245680705396</v>
+        <v>110.0170020268064</v>
       </c>
       <c r="E70" t="n">
-        <v>109.6498107910156</v>
+        <v>110.7712249755859</v>
       </c>
       <c r="F70" t="n">
-        <v>14318000</v>
+        <v>15580200</v>
       </c>
       <c r="G70" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B71" t="n">
-        <v>110.3742651303662</v>
+        <v>110.2154802113721</v>
       </c>
       <c r="C71" t="n">
-        <v>111.991867603266</v>
+        <v>111.2773434635197</v>
       </c>
       <c r="D71" t="n">
-        <v>110.0170020268064</v>
+        <v>109.6200442181698</v>
       </c>
       <c r="E71" t="n">
-        <v>110.7712249755859</v>
+        <v>109.7887496948242</v>
       </c>
       <c r="F71" t="n">
-        <v>15580200</v>
+        <v>12142500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B72" t="n">
-        <v>110.2154802113721</v>
+        <v>109.6895108947102</v>
       </c>
       <c r="C72" t="n">
-        <v>111.2773434635197</v>
+        <v>111.9422536896534</v>
       </c>
       <c r="D72" t="n">
-        <v>109.6200442181698</v>
+        <v>109.5803467466885</v>
       </c>
       <c r="E72" t="n">
-        <v>109.7887496948242</v>
+        <v>111.0193252563477</v>
       </c>
       <c r="F72" t="n">
-        <v>12142500</v>
+        <v>12913900</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B73" t="n">
-        <v>109.6895108947102</v>
+        <v>111.4659009625997</v>
       </c>
       <c r="C73" t="n">
-        <v>111.9422536896534</v>
+        <v>112.6170837765976</v>
       </c>
       <c r="D73" t="n">
-        <v>109.5803467466885</v>
+        <v>110.076545265884</v>
       </c>
       <c r="E73" t="n">
-        <v>111.0193252563477</v>
+        <v>110.3941116333008</v>
       </c>
       <c r="F73" t="n">
-        <v>12913900</v>
+        <v>21138400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B74" t="n">
-        <v>111.4659009625997</v>
+        <v>110.5628188428948</v>
       </c>
       <c r="C74" t="n">
-        <v>112.6170837765976</v>
+        <v>111.9422483883379</v>
       </c>
       <c r="D74" t="n">
-        <v>110.076545265884</v>
+        <v>110.3047938169375</v>
       </c>
       <c r="E74" t="n">
-        <v>110.3941116333008</v>
+        <v>111.5254364013672</v>
       </c>
       <c r="F74" t="n">
-        <v>21138400</v>
+        <v>8803300</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B75" t="n">
-        <v>110.5628188428948</v>
+        <v>111.4361261613625</v>
       </c>
       <c r="C75" t="n">
-        <v>111.9422483883379</v>
+        <v>112.4483665538656</v>
       </c>
       <c r="D75" t="n">
-        <v>110.3047938169375</v>
+        <v>111.1880272094238</v>
       </c>
       <c r="E75" t="n">
-        <v>111.5254364013672</v>
+        <v>112.3590545654297</v>
       </c>
       <c r="F75" t="n">
-        <v>8803300</v>
+        <v>7634500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B76" t="n">
-        <v>111.4361261613625</v>
+        <v>112.0811837460467</v>
       </c>
       <c r="C76" t="n">
-        <v>112.4483665538656</v>
+        <v>113.6590894291559</v>
       </c>
       <c r="D76" t="n">
-        <v>111.1880272094238</v>
+        <v>111.9422489401646</v>
       </c>
       <c r="E76" t="n">
-        <v>112.3590545654297</v>
+        <v>113.6094741821289</v>
       </c>
       <c r="F76" t="n">
-        <v>7634500</v>
+        <v>4606700</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B77" t="n">
-        <v>112.0811837460467</v>
+        <v>113.2819819972415</v>
       </c>
       <c r="C77" t="n">
-        <v>113.6590894291559</v>
+        <v>113.8674918845297</v>
       </c>
       <c r="D77" t="n">
-        <v>111.9422489401646</v>
+        <v>112.4086688482299</v>
       </c>
       <c r="E77" t="n">
-        <v>113.6094741821289</v>
+        <v>112.6964645385742</v>
       </c>
       <c r="F77" t="n">
-        <v>4606700</v>
+        <v>5428900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B78" t="n">
-        <v>113.2819819972415</v>
+        <v>112.4582910949776</v>
       </c>
       <c r="C78" t="n">
-        <v>113.8674918845297</v>
+        <v>113.6193923570513</v>
       </c>
       <c r="D78" t="n">
-        <v>112.4086688482299</v>
+        <v>112.4483650170496</v>
       </c>
       <c r="E78" t="n">
-        <v>112.6964645385742</v>
+        <v>113.3216781616211</v>
       </c>
       <c r="F78" t="n">
-        <v>5428900</v>
+        <v>7966000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B79" t="n">
-        <v>112.4582910949776</v>
+        <v>113.2323587361736</v>
       </c>
       <c r="C79" t="n">
-        <v>113.6193923570513</v>
+        <v>114.4033860775522</v>
       </c>
       <c r="D79" t="n">
-        <v>112.4483650170496</v>
+        <v>113.2323587361736</v>
       </c>
       <c r="E79" t="n">
-        <v>113.3216781616211</v>
+        <v>113.9171142578125</v>
       </c>
       <c r="F79" t="n">
-        <v>7966000</v>
+        <v>6883900</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B80" t="n">
-        <v>113.2323587361736</v>
+        <v>113.8972648993226</v>
       </c>
       <c r="C80" t="n">
-        <v>114.4033860775522</v>
+        <v>114.0163551233871</v>
       </c>
       <c r="D80" t="n">
-        <v>113.2323587361736</v>
+        <v>112.6865483592072</v>
       </c>
       <c r="E80" t="n">
-        <v>113.9171142578125</v>
+        <v>112.9048690795898</v>
       </c>
       <c r="F80" t="n">
-        <v>6883900</v>
+        <v>6608000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B81" t="n">
-        <v>113.8972648993226</v>
+        <v>112.5773868999257</v>
       </c>
       <c r="C81" t="n">
-        <v>114.0163551233871</v>
+        <v>112.5773868999257</v>
       </c>
       <c r="D81" t="n">
-        <v>112.6865483592072</v>
+        <v>110.7712267677642</v>
       </c>
       <c r="E81" t="n">
-        <v>112.9048690795898</v>
+        <v>110.9994735717773</v>
       </c>
       <c r="F81" t="n">
-        <v>6608000</v>
+        <v>8906200</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B82" t="n">
-        <v>112.5773868999257</v>
+        <v>110.5727405037633</v>
       </c>
       <c r="C82" t="n">
-        <v>112.5773868999257</v>
+        <v>115.1476858420111</v>
       </c>
       <c r="D82" t="n">
-        <v>110.7712267677642</v>
+        <v>110.5330437623775</v>
       </c>
       <c r="E82" t="n">
-        <v>110.9994735717773</v>
+        <v>113.2025909423828</v>
       </c>
       <c r="F82" t="n">
-        <v>8906200</v>
+        <v>12029000</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B83" t="n">
-        <v>110.5727405037633</v>
+        <v>112.9247239572814</v>
       </c>
       <c r="C83" t="n">
-        <v>115.1476858420111</v>
+        <v>113.8873491370408</v>
       </c>
       <c r="D83" t="n">
-        <v>110.5330437623775</v>
+        <v>112.2498944807456</v>
       </c>
       <c r="E83" t="n">
-        <v>113.2025909423828</v>
+        <v>113.6987915039062</v>
       </c>
       <c r="F83" t="n">
-        <v>12029000</v>
+        <v>7388300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B84" t="n">
-        <v>112.9247239572814</v>
+        <v>113.58962345171</v>
       </c>
       <c r="C84" t="n">
-        <v>113.8873491370408</v>
+        <v>114.0957474345631</v>
       </c>
       <c r="D84" t="n">
-        <v>112.2498944807456</v>
+        <v>111.6544546516531</v>
       </c>
       <c r="E84" t="n">
-        <v>113.6987915039062</v>
+        <v>112.0514144897461</v>
       </c>
       <c r="F84" t="n">
-        <v>7388300</v>
+        <v>8296300</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B85" t="n">
-        <v>113.58962345171</v>
+        <v>111.6941501294552</v>
       </c>
       <c r="C85" t="n">
-        <v>114.0957474345631</v>
+        <v>114.1155907288179</v>
       </c>
       <c r="D85" t="n">
-        <v>111.6544546516531</v>
+        <v>111.6941501294552</v>
       </c>
       <c r="E85" t="n">
-        <v>112.0514144897461</v>
+        <v>113.3018264770508</v>
       </c>
       <c r="F85" t="n">
-        <v>8296300</v>
+        <v>9778200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B86" t="n">
-        <v>111.6941501294552</v>
+        <v>113.4407639362947</v>
       </c>
       <c r="C86" t="n">
-        <v>114.1155907288179</v>
+        <v>115.0980707124986</v>
       </c>
       <c r="D86" t="n">
-        <v>111.6941501294552</v>
+        <v>113.0338855865844</v>
       </c>
       <c r="E86" t="n">
-        <v>113.3018264770508</v>
+        <v>114.9988250732422</v>
       </c>
       <c r="F86" t="n">
-        <v>9778200</v>
+        <v>8935200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B87" t="n">
-        <v>113.4407639362947</v>
+        <v>113.7583311963079</v>
       </c>
       <c r="C87" t="n">
-        <v>115.0980707124986</v>
+        <v>114.0659790519541</v>
       </c>
       <c r="D87" t="n">
-        <v>113.0338855865844</v>
+        <v>111.6941536254426</v>
       </c>
       <c r="E87" t="n">
-        <v>114.9988250732422</v>
+        <v>111.9620971679688</v>
       </c>
       <c r="F87" t="n">
-        <v>8935200</v>
+        <v>10833800</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B88" t="n">
-        <v>113.7583311963079</v>
+        <v>111.9819377501375</v>
       </c>
       <c r="C88" t="n">
-        <v>114.0659790519541</v>
+        <v>112.3590529975045</v>
       </c>
       <c r="D88" t="n">
-        <v>111.6941536254426</v>
+        <v>110.7612951636049</v>
       </c>
       <c r="E88" t="n">
-        <v>111.9620971679688</v>
+        <v>112.1208801269531</v>
       </c>
       <c r="F88" t="n">
-        <v>10833800</v>
+        <v>8945700</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B89" t="n">
-        <v>111.9819377501375</v>
+        <v>111.9521684493894</v>
       </c>
       <c r="C89" t="n">
-        <v>112.3590529975045</v>
+        <v>112.7262359666306</v>
       </c>
       <c r="D89" t="n">
-        <v>110.7612951636049</v>
+        <v>111.4063552989297</v>
       </c>
       <c r="E89" t="n">
-        <v>112.1208801269531</v>
+        <v>112.6666946411133</v>
       </c>
       <c r="F89" t="n">
-        <v>8945700</v>
+        <v>8950900</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B90" t="n">
-        <v>111.9521684493894</v>
+        <v>112.8453292583326</v>
       </c>
       <c r="C90" t="n">
-        <v>112.7262359666306</v>
+        <v>113.242289105796</v>
       </c>
       <c r="D90" t="n">
-        <v>111.4063552989297</v>
+        <v>111.3170387669949</v>
       </c>
       <c r="E90" t="n">
-        <v>112.6666946411133</v>
+        <v>112.5476150512695</v>
       </c>
       <c r="F90" t="n">
-        <v>8950900</v>
+        <v>7958500</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B91" t="n">
-        <v>112.8453292583326</v>
+        <v>112.339199834173</v>
       </c>
       <c r="C91" t="n">
-        <v>113.242289105796</v>
+        <v>112.9842586087029</v>
       </c>
       <c r="D91" t="n">
-        <v>111.3170387669949</v>
+        <v>110.2750223556077</v>
       </c>
       <c r="E91" t="n">
-        <v>112.5476150512695</v>
+        <v>110.3544082641602</v>
       </c>
       <c r="F91" t="n">
-        <v>7958500</v>
+        <v>12049600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>112.339199834173</v>
+        <v>108.8261317696502</v>
       </c>
       <c r="C92" t="n">
-        <v>112.9842586087029</v>
+        <v>110.2452505565117</v>
       </c>
       <c r="D92" t="n">
-        <v>110.2750223556077</v>
+        <v>107.9726707390225</v>
       </c>
       <c r="E92" t="n">
-        <v>110.3544082641602</v>
+        <v>109.5009536743164</v>
       </c>
       <c r="F92" t="n">
-        <v>12049600</v>
+        <v>9818200</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>108.8261317696502</v>
+        <v>109.7292049082389</v>
       </c>
       <c r="C93" t="n">
-        <v>110.2452505565117</v>
+        <v>112.3888259939984</v>
       </c>
       <c r="D93" t="n">
-        <v>107.9726707390225</v>
+        <v>109.6597375040779</v>
       </c>
       <c r="E93" t="n">
-        <v>109.5009536743164</v>
+        <v>112.3292846679688</v>
       </c>
       <c r="F93" t="n">
-        <v>9818200</v>
+        <v>10041400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>109.7292049082389</v>
+        <v>112.3094319821855</v>
       </c>
       <c r="C94" t="n">
-        <v>112.3888259939984</v>
+        <v>113.4209180149001</v>
       </c>
       <c r="D94" t="n">
-        <v>109.6597375040779</v>
+        <v>111.317036172348</v>
       </c>
       <c r="E94" t="n">
-        <v>112.3292846679688</v>
+        <v>112.3491287231445</v>
       </c>
       <c r="F94" t="n">
-        <v>10041400</v>
+        <v>12437700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B95" t="n">
-        <v>112.3094319821855</v>
+        <v>111.8330891095483</v>
       </c>
       <c r="C95" t="n">
-        <v>113.4209180149001</v>
+        <v>112.0911065753488</v>
       </c>
       <c r="D95" t="n">
-        <v>111.317036172348</v>
+        <v>109.7093626275885</v>
       </c>
       <c r="E95" t="n">
-        <v>112.3491287231445</v>
+        <v>110.1360931396484</v>
       </c>
       <c r="F95" t="n">
-        <v>12437700</v>
+        <v>10819800</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>111.8330891095483</v>
+        <v>110.8307664528259</v>
       </c>
       <c r="C96" t="n">
-        <v>112.0911065753488</v>
+        <v>111.5552187391887</v>
       </c>
       <c r="D96" t="n">
-        <v>109.7093626275885</v>
+        <v>110.2849457184854</v>
       </c>
       <c r="E96" t="n">
-        <v>110.1360931396484</v>
+        <v>110.4635772705078</v>
       </c>
       <c r="F96" t="n">
-        <v>10819800</v>
+        <v>8859800</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>110.8307664528259</v>
+        <v>110.6521373409646</v>
       </c>
       <c r="C97" t="n">
-        <v>111.5552187391887</v>
+        <v>110.9498591246939</v>
       </c>
       <c r="D97" t="n">
-        <v>110.2849457184854</v>
+        <v>109.1933142291742</v>
       </c>
       <c r="E97" t="n">
-        <v>110.4635772705078</v>
+        <v>109.7689056396484</v>
       </c>
       <c r="F97" t="n">
-        <v>8859800</v>
+        <v>8956900</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>110.6521373409646</v>
+        <v>109.4414091319104</v>
       </c>
       <c r="C98" t="n">
-        <v>110.9498591246939</v>
+        <v>110.5826658320299</v>
       </c>
       <c r="D98" t="n">
-        <v>109.1933142291742</v>
+        <v>108.1711437016965</v>
       </c>
       <c r="E98" t="n">
-        <v>109.7689056396484</v>
+        <v>108.7268829345703</v>
       </c>
       <c r="F98" t="n">
-        <v>8956900</v>
+        <v>9016600</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>109.4414091319104</v>
+        <v>108.7963528121511</v>
       </c>
       <c r="C99" t="n">
-        <v>110.5826658320299</v>
+        <v>110.8208412268483</v>
       </c>
       <c r="D99" t="n">
-        <v>108.1711437016965</v>
+        <v>107.932973280219</v>
       </c>
       <c r="E99" t="n">
-        <v>108.7268829345703</v>
+        <v>110.7315292358398</v>
       </c>
       <c r="F99" t="n">
-        <v>9016600</v>
+        <v>11079000</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B100" t="n">
-        <v>108.7963528121511</v>
+        <v>110.5132006888762</v>
       </c>
       <c r="C100" t="n">
-        <v>110.8208412268483</v>
+        <v>112.0911064308015</v>
       </c>
       <c r="D100" t="n">
-        <v>107.932973280219</v>
+        <v>110.1460115045699</v>
       </c>
       <c r="E100" t="n">
-        <v>110.7315292358398</v>
+        <v>111.942253112793</v>
       </c>
       <c r="F100" t="n">
-        <v>11079000</v>
+        <v>17895200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>110.5132006888762</v>
+        <v>103.219089824791</v>
       </c>
       <c r="C101" t="n">
-        <v>112.0911064308015</v>
+        <v>107.7841090146985</v>
       </c>
       <c r="D101" t="n">
-        <v>110.1460115045699</v>
+        <v>102.961064795438</v>
       </c>
       <c r="E101" t="n">
-        <v>111.942253112793</v>
+        <v>103.6557388305664</v>
       </c>
       <c r="F101" t="n">
-        <v>17895200</v>
+        <v>37778500</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>103.219089824791</v>
+        <v>103.9832294528008</v>
       </c>
       <c r="C102" t="n">
-        <v>107.7841090146985</v>
+        <v>104.1916316597105</v>
       </c>
       <c r="D102" t="n">
-        <v>102.961064795438</v>
+        <v>101.5617813072958</v>
       </c>
       <c r="E102" t="n">
-        <v>103.6557388305664</v>
+        <v>103.427490234375</v>
       </c>
       <c r="F102" t="n">
-        <v>37778500</v>
+        <v>24827100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>103.9832294528008</v>
+        <v>103.4076429857971</v>
       </c>
       <c r="C103" t="n">
-        <v>104.1916316597105</v>
+        <v>107.7741861743833</v>
       </c>
       <c r="D103" t="n">
-        <v>101.5617813072958</v>
+        <v>102.841977662662</v>
       </c>
       <c r="E103" t="n">
-        <v>103.427490234375</v>
+        <v>106.2359771728516</v>
       </c>
       <c r="F103" t="n">
-        <v>24827100</v>
+        <v>19070400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>103.4076429857971</v>
+        <v>106.2359762120697</v>
       </c>
       <c r="C104" t="n">
-        <v>107.7741861743833</v>
+        <v>107.5062416580512</v>
       </c>
       <c r="D104" t="n">
-        <v>102.841977662662</v>
+        <v>104.0130041102228</v>
       </c>
       <c r="E104" t="n">
-        <v>106.2359771728516</v>
+        <v>104.1717910766602</v>
       </c>
       <c r="F104" t="n">
-        <v>19070400</v>
+        <v>11859500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B105" t="n">
-        <v>106.2359762120697</v>
+        <v>105.3229638054753</v>
       </c>
       <c r="C105" t="n">
-        <v>107.5062416580512</v>
+        <v>108.1314457439972</v>
       </c>
       <c r="D105" t="n">
-        <v>104.0130041102228</v>
+        <v>104.5687484468834</v>
       </c>
       <c r="E105" t="n">
-        <v>104.1717910766602</v>
+        <v>107.873420715332</v>
       </c>
       <c r="F105" t="n">
-        <v>11859500</v>
+        <v>12105600</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>105.3229638054753</v>
+        <v>107.8635036441641</v>
       </c>
       <c r="C106" t="n">
-        <v>108.1314457439972</v>
+        <v>108.09175044183</v>
       </c>
       <c r="D106" t="n">
-        <v>104.5687484468834</v>
+        <v>105.9580979235442</v>
       </c>
       <c r="E106" t="n">
-        <v>107.873420715332</v>
+        <v>106.3153610229492</v>
       </c>
       <c r="F106" t="n">
-        <v>12105600</v>
+        <v>10515400</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>107.8635036441641</v>
+        <v>106.7817856582252</v>
       </c>
       <c r="C107" t="n">
-        <v>108.09175044183</v>
+        <v>110.265097006608</v>
       </c>
       <c r="D107" t="n">
-        <v>105.9580979235442</v>
+        <v>106.7817856582252</v>
       </c>
       <c r="E107" t="n">
-        <v>106.3153610229492</v>
+        <v>109.1238403320312</v>
       </c>
       <c r="F107" t="n">
-        <v>10515400</v>
+        <v>9815500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>106.7817856582252</v>
+        <v>108.1016744764874</v>
       </c>
       <c r="C108" t="n">
-        <v>110.265097006608</v>
+        <v>109.0345289485641</v>
       </c>
       <c r="D108" t="n">
-        <v>106.7817856582252</v>
+        <v>106.9802699515072</v>
       </c>
       <c r="E108" t="n">
-        <v>109.1238403320312</v>
+        <v>107.2978363037109</v>
       </c>
       <c r="F108" t="n">
-        <v>9815500</v>
+        <v>9374900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>108.1016744764874</v>
+        <v>107.1092782571758</v>
       </c>
       <c r="C109" t="n">
-        <v>109.0345289485641</v>
+        <v>107.3375326210063</v>
       </c>
       <c r="D109" t="n">
-        <v>106.9802699515072</v>
+        <v>100.2518196922704</v>
       </c>
       <c r="E109" t="n">
-        <v>107.2978363037109</v>
+        <v>101.6014785766602</v>
       </c>
       <c r="F109" t="n">
-        <v>9374900</v>
+        <v>25319600</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B110" t="n">
-        <v>107.1092782571758</v>
+        <v>100.6289339445357</v>
       </c>
       <c r="C110" t="n">
-        <v>107.3375326210063</v>
+        <v>104.7175997261971</v>
       </c>
       <c r="D110" t="n">
-        <v>100.2518196922704</v>
+        <v>100.4304502450412</v>
       </c>
       <c r="E110" t="n">
-        <v>101.6014785766602</v>
+        <v>104.6481323242188</v>
       </c>
       <c r="F110" t="n">
-        <v>25319600</v>
+        <v>12845300</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B111" t="n">
-        <v>100.6289339445357</v>
+        <v>105.7596186239472</v>
       </c>
       <c r="C111" t="n">
-        <v>104.7175997261971</v>
+        <v>106.4642187235269</v>
       </c>
       <c r="D111" t="n">
-        <v>100.4304502450412</v>
+        <v>103.576350923035</v>
       </c>
       <c r="E111" t="n">
-        <v>104.6481323242188</v>
+        <v>104.6382141113281</v>
       </c>
       <c r="F111" t="n">
-        <v>12845300</v>
+        <v>10467400</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B112" t="n">
-        <v>105.7596186239472</v>
+        <v>105.1542604930163</v>
       </c>
       <c r="C112" t="n">
-        <v>106.4642187235269</v>
+        <v>106.9108053396402</v>
       </c>
       <c r="D112" t="n">
-        <v>103.576350923035</v>
+        <v>105.0053996052954</v>
       </c>
       <c r="E112" t="n">
-        <v>104.6382141113281</v>
+        <v>106.2855911254883</v>
       </c>
       <c r="F112" t="n">
-        <v>10467400</v>
+        <v>8791600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B113" t="n">
-        <v>105.1542604930163</v>
+        <v>106.2955144080048</v>
       </c>
       <c r="C113" t="n">
-        <v>106.9108053396402</v>
+        <v>106.9504916968191</v>
       </c>
       <c r="D113" t="n">
-        <v>105.0053996052954</v>
+        <v>104.6481337509456</v>
       </c>
       <c r="E113" t="n">
-        <v>106.2855911254883</v>
+        <v>105.1939544677734</v>
       </c>
       <c r="F113" t="n">
-        <v>8791600</v>
+        <v>7492900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B114" t="n">
-        <v>106.2955144080048</v>
+        <v>104.8069236784645</v>
       </c>
       <c r="C114" t="n">
-        <v>106.9504916968191</v>
+        <v>105.3924335809217</v>
       </c>
       <c r="D114" t="n">
-        <v>104.6481337509456</v>
+        <v>103.8542245950799</v>
       </c>
       <c r="E114" t="n">
-        <v>105.1939544677734</v>
+        <v>104.7771530151367</v>
       </c>
       <c r="F114" t="n">
-        <v>7492900</v>
+        <v>9043600</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>104.8069236784645</v>
+        <v>104.1817160321379</v>
       </c>
       <c r="C115" t="n">
-        <v>105.3924335809217</v>
+        <v>104.3901182448065</v>
       </c>
       <c r="D115" t="n">
-        <v>103.8542245950799</v>
+        <v>102.1770722450568</v>
       </c>
       <c r="E115" t="n">
-        <v>104.7771530151367</v>
+        <v>103.6160507202148</v>
       </c>
       <c r="F115" t="n">
-        <v>9043600</v>
+        <v>10626500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>104.1817160321379</v>
+        <v>103.6557367363695</v>
       </c>
       <c r="C116" t="n">
-        <v>104.3901182448065</v>
+        <v>106.4146033792047</v>
       </c>
       <c r="D116" t="n">
-        <v>102.1770722450568</v>
+        <v>103.1893170772804</v>
       </c>
       <c r="E116" t="n">
-        <v>103.6160507202148</v>
+        <v>105.2435760498047</v>
       </c>
       <c r="F116" t="n">
-        <v>10626500</v>
+        <v>13594800</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>103.6557367363695</v>
+        <v>105.193955544271</v>
       </c>
       <c r="C117" t="n">
-        <v>106.4146033792047</v>
+        <v>105.9084817367471</v>
       </c>
       <c r="D117" t="n">
-        <v>103.1893170772804</v>
+        <v>103.7152879117953</v>
       </c>
       <c r="E117" t="n">
-        <v>105.2435760498047</v>
+        <v>104.2511825561523</v>
       </c>
       <c r="F117" t="n">
-        <v>13594800</v>
+        <v>8556500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>105.193955544271</v>
+        <v>104.6679896339684</v>
       </c>
       <c r="C118" t="n">
-        <v>105.9084817367471</v>
+        <v>105.9580996730059</v>
       </c>
       <c r="D118" t="n">
-        <v>103.7152879117953</v>
+        <v>104.519128744862</v>
       </c>
       <c r="E118" t="n">
-        <v>104.2511825561523</v>
+        <v>104.7473831176758</v>
       </c>
       <c r="F118" t="n">
-        <v>8556500</v>
+        <v>9578500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B119" t="n">
-        <v>104.6679896339684</v>
+        <v>103.9832293953731</v>
       </c>
       <c r="C119" t="n">
-        <v>105.9580996730059</v>
+        <v>105.5313644009208</v>
       </c>
       <c r="D119" t="n">
-        <v>104.519128744862</v>
+        <v>103.1396944903344</v>
       </c>
       <c r="E119" t="n">
-        <v>104.7473831176758</v>
+        <v>105.2336502075195</v>
       </c>
       <c r="F119" t="n">
-        <v>9578500</v>
+        <v>13954000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>103.9832293953731</v>
+        <v>103.8145288629893</v>
       </c>
       <c r="C120" t="n">
-        <v>105.5313644009208</v>
+        <v>103.8145288629893</v>
       </c>
       <c r="D120" t="n">
-        <v>103.1396944903344</v>
+        <v>102.0778361524432</v>
       </c>
       <c r="E120" t="n">
-        <v>105.2336502075195</v>
+        <v>103.5366592407227</v>
       </c>
       <c r="F120" t="n">
-        <v>13954000</v>
+        <v>14178600</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>103.8145288629893</v>
+        <v>102.0579794936243</v>
       </c>
       <c r="C121" t="n">
-        <v>103.8145288629893</v>
+        <v>103.5168025175497</v>
       </c>
       <c r="D121" t="n">
-        <v>102.0778361524432</v>
+        <v>101.3732315464965</v>
       </c>
       <c r="E121" t="n">
-        <v>103.5366592407227</v>
+        <v>102.5144882202148</v>
       </c>
       <c r="F121" t="n">
-        <v>14178600</v>
+        <v>13608400</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>102.0579794936243</v>
+        <v>102.3854784619134</v>
       </c>
       <c r="C122" t="n">
-        <v>103.5168025175497</v>
+        <v>103.0503818671043</v>
       </c>
       <c r="D122" t="n">
-        <v>101.3732315464965</v>
+        <v>101.8595098706018</v>
       </c>
       <c r="E122" t="n">
-        <v>102.5144882202148</v>
+        <v>102.2564697265625</v>
       </c>
       <c r="F122" t="n">
-        <v>13608400</v>
+        <v>9672300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>102.3854784619134</v>
+        <v>102.3160040474863</v>
       </c>
       <c r="C123" t="n">
-        <v>103.0503818671043</v>
+        <v>103.7549824803676</v>
       </c>
       <c r="D123" t="n">
-        <v>101.8595098706018</v>
+        <v>100.8174842902717</v>
       </c>
       <c r="E123" t="n">
-        <v>102.2564697265625</v>
+        <v>101.6312561035156</v>
       </c>
       <c r="F123" t="n">
-        <v>9672300</v>
+        <v>11751500</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B124" t="n">
-        <v>102.3160040474863</v>
+        <v>100.6190147793836</v>
       </c>
       <c r="C124" t="n">
-        <v>103.7549824803676</v>
+        <v>101.0358192198888</v>
       </c>
       <c r="D124" t="n">
-        <v>100.8174842902717</v>
+        <v>99.18996233036073</v>
       </c>
       <c r="E124" t="n">
-        <v>101.6312561035156</v>
+        <v>100.7678756713867</v>
       </c>
       <c r="F124" t="n">
-        <v>11751500</v>
+        <v>10448600</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>100.6190147793836</v>
+        <v>99.78540292258373</v>
       </c>
       <c r="C125" t="n">
-        <v>101.0358192198888</v>
+        <v>101.0953651046626</v>
       </c>
       <c r="D125" t="n">
-        <v>99.18996233036073</v>
+        <v>97.70136563944882</v>
       </c>
       <c r="E125" t="n">
-        <v>100.7678756713867</v>
+        <v>100.886962890625</v>
       </c>
       <c r="F125" t="n">
-        <v>10448600</v>
+        <v>11715100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>99.78540292258373</v>
+        <v>100.9762757982457</v>
       </c>
       <c r="C126" t="n">
-        <v>101.0953651046626</v>
+        <v>101.4625476354206</v>
       </c>
       <c r="D126" t="n">
-        <v>97.70136563944882</v>
+        <v>99.47775597353863</v>
       </c>
       <c r="E126" t="n">
-        <v>100.886962890625</v>
+        <v>100.5495452880859</v>
       </c>
       <c r="F126" t="n">
-        <v>11715100</v>
+        <v>7833100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>100.9762757982457</v>
+        <v>100.6289343352219</v>
       </c>
       <c r="C127" t="n">
-        <v>101.4625476354206</v>
+        <v>101.1152061509584</v>
       </c>
       <c r="D127" t="n">
-        <v>99.47775597353863</v>
+        <v>99.63653854803313</v>
       </c>
       <c r="E127" t="n">
-        <v>100.5495452880859</v>
+        <v>100.1228103637695</v>
       </c>
       <c r="F127" t="n">
-        <v>7833100</v>
+        <v>8152800</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>100.6289343352219</v>
+        <v>99.33882308016651</v>
       </c>
       <c r="C128" t="n">
-        <v>101.1152061509584</v>
+        <v>100.1128906318194</v>
       </c>
       <c r="D128" t="n">
-        <v>99.63653854803313</v>
+        <v>98.61437834957015</v>
       </c>
       <c r="E128" t="n">
-        <v>100.1228103637695</v>
+        <v>98.67391967773438</v>
       </c>
       <c r="F128" t="n">
-        <v>8152800</v>
+        <v>10309400</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B129" t="n">
-        <v>99.33882308016651</v>
+        <v>99.07087541929553</v>
       </c>
       <c r="C129" t="n">
-        <v>100.1128906318194</v>
+        <v>100.0037223311207</v>
       </c>
       <c r="D129" t="n">
-        <v>98.61437834957015</v>
+        <v>98.4059720444657</v>
       </c>
       <c r="E129" t="n">
-        <v>98.67391967773438</v>
+        <v>98.53498077392578</v>
       </c>
       <c r="F129" t="n">
-        <v>10309400</v>
+        <v>9551500</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>99.07087541929553</v>
+        <v>98.71361296789499</v>
       </c>
       <c r="C130" t="n">
-        <v>100.0037223311207</v>
+        <v>98.93194125870065</v>
       </c>
       <c r="D130" t="n">
-        <v>98.4059720444657</v>
+        <v>97.71129107436866</v>
       </c>
       <c r="E130" t="n">
-        <v>98.53498077392578</v>
+        <v>97.90977478027344</v>
       </c>
       <c r="F130" t="n">
-        <v>9551500</v>
+        <v>11578500</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>98.71361296789499</v>
+        <v>98.41588802886785</v>
       </c>
       <c r="C131" t="n">
-        <v>98.93194125870065</v>
+        <v>99.94417844396594</v>
       </c>
       <c r="D131" t="n">
-        <v>97.71129107436866</v>
+        <v>98.26702714707265</v>
       </c>
       <c r="E131" t="n">
-        <v>97.90977478027344</v>
+        <v>99.53730010986328</v>
       </c>
       <c r="F131" t="n">
-        <v>11578500</v>
+        <v>11785600</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>98.41588802886785</v>
+        <v>99.08079827635559</v>
       </c>
       <c r="C132" t="n">
-        <v>99.94417844396594</v>
+        <v>100.2518256851255</v>
       </c>
       <c r="D132" t="n">
-        <v>98.26702714707265</v>
+        <v>98.24718939454284</v>
       </c>
       <c r="E132" t="n">
-        <v>99.53730010986328</v>
+        <v>98.66399383544922</v>
       </c>
       <c r="F132" t="n">
-        <v>11785600</v>
+        <v>12615100</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>99.08079827635559</v>
+        <v>98.2769579779315</v>
       </c>
       <c r="C133" t="n">
-        <v>100.2518256851255</v>
+        <v>100.0136506829842</v>
       </c>
       <c r="D133" t="n">
-        <v>98.24718939454284</v>
+        <v>97.69144807163296</v>
       </c>
       <c r="E133" t="n">
-        <v>98.66399383544922</v>
+        <v>98.44566345214844</v>
       </c>
       <c r="F133" t="n">
-        <v>12615100</v>
+        <v>14793800</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B134" t="n">
-        <v>98.2769579779315</v>
+        <v>98.25711324225701</v>
       </c>
       <c r="C134" t="n">
-        <v>100.0136506829842</v>
+        <v>99.269353657388</v>
       </c>
       <c r="D134" t="n">
-        <v>97.69144807163296</v>
+        <v>97.64182510199821</v>
       </c>
       <c r="E134" t="n">
-        <v>98.44566345214844</v>
+        <v>98.75331115722656</v>
       </c>
       <c r="F134" t="n">
-        <v>14793800</v>
+        <v>27544200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B135" t="n">
-        <v>98.25711324225701</v>
+        <v>99.45791247863863</v>
       </c>
       <c r="C135" t="n">
-        <v>99.269353657388</v>
+        <v>99.83502017283372</v>
       </c>
       <c r="D135" t="n">
-        <v>97.64182510199821</v>
+        <v>97.11585768623267</v>
       </c>
       <c r="E135" t="n">
-        <v>98.75331115722656</v>
+        <v>97.20516967773438</v>
       </c>
       <c r="F135" t="n">
-        <v>27544200</v>
+        <v>11373000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B136" t="n">
-        <v>99.45791247863863</v>
+        <v>96.99676871718921</v>
       </c>
       <c r="C136" t="n">
-        <v>99.83502017283372</v>
+        <v>97.30441658068045</v>
       </c>
       <c r="D136" t="n">
-        <v>97.11585768623267</v>
+        <v>95.5181010136908</v>
       </c>
       <c r="E136" t="n">
-        <v>97.20516967773438</v>
+        <v>95.65703582763672</v>
       </c>
       <c r="F136" t="n">
-        <v>11373000</v>
+        <v>9155700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B137" t="n">
-        <v>96.99676871718921</v>
+        <v>96.08376214252051</v>
       </c>
       <c r="C137" t="n">
-        <v>97.30441658068045</v>
+        <v>96.44102524028141</v>
       </c>
       <c r="D137" t="n">
-        <v>95.5181010136908</v>
+        <v>94.33714339473161</v>
       </c>
       <c r="E137" t="n">
-        <v>95.65703582763672</v>
+        <v>95.22037506103516</v>
       </c>
       <c r="F137" t="n">
-        <v>9155700</v>
+        <v>8467500</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B138" t="n">
-        <v>96.08376214252051</v>
+        <v>94.3966920435457</v>
       </c>
       <c r="C138" t="n">
-        <v>96.44102524028141</v>
+        <v>95.66695746718439</v>
       </c>
       <c r="D138" t="n">
-        <v>94.33714339473161</v>
+        <v>93.87071590500793</v>
       </c>
       <c r="E138" t="n">
-        <v>95.22037506103516</v>
+        <v>94.02950286865234</v>
       </c>
       <c r="F138" t="n">
-        <v>8467500</v>
+        <v>8548800</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B139" t="n">
-        <v>94.3966920435457</v>
+        <v>93.47376126842354</v>
       </c>
       <c r="C139" t="n">
-        <v>95.66695746718439</v>
+        <v>93.47376126842354</v>
       </c>
       <c r="D139" t="n">
-        <v>93.87071590500793</v>
+        <v>91.48896970147202</v>
       </c>
       <c r="E139" t="n">
-        <v>94.02950286865234</v>
+        <v>91.71721649169922</v>
       </c>
       <c r="F139" t="n">
-        <v>8548800</v>
+        <v>12475900</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B140" t="n">
-        <v>93.47376126842354</v>
+        <v>92.18364921591858</v>
       </c>
       <c r="C140" t="n">
-        <v>93.47376126842354</v>
+        <v>94.46616268251262</v>
       </c>
       <c r="D140" t="n">
-        <v>91.48896970147202</v>
+        <v>92.18364921591858</v>
       </c>
       <c r="E140" t="n">
-        <v>91.71721649169922</v>
+        <v>93.60277557373047</v>
       </c>
       <c r="F140" t="n">
-        <v>12475900</v>
+        <v>10592600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B141" t="n">
-        <v>92.18364921591858</v>
+        <v>94.61501738536155</v>
       </c>
       <c r="C141" t="n">
-        <v>94.46616268251262</v>
+        <v>96.15323399247868</v>
       </c>
       <c r="D141" t="n">
-        <v>92.18364921591858</v>
+        <v>93.47376820675542</v>
       </c>
       <c r="E141" t="n">
-        <v>93.60277557373047</v>
+        <v>95.64710998535156</v>
       </c>
       <c r="F141" t="n">
-        <v>10592600</v>
+        <v>11180200</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B142" t="n">
-        <v>94.61501738536155</v>
+        <v>96.52041860940267</v>
       </c>
       <c r="C142" t="n">
-        <v>96.15323399247868</v>
+        <v>97.61205248622655</v>
       </c>
       <c r="D142" t="n">
-        <v>93.47376820675542</v>
+        <v>95.75626959566054</v>
       </c>
       <c r="E142" t="n">
-        <v>95.64710998535156</v>
+        <v>95.82573699951172</v>
       </c>
       <c r="F142" t="n">
-        <v>11180200</v>
+        <v>8518600</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B143" t="n">
-        <v>96.52041860940267</v>
+        <v>95.26999653948798</v>
       </c>
       <c r="C143" t="n">
-        <v>97.61205248622655</v>
+        <v>96.43109780518201</v>
       </c>
       <c r="D143" t="n">
-        <v>95.75626959566054</v>
+        <v>94.36691272969546</v>
       </c>
       <c r="E143" t="n">
-        <v>95.82573699951172</v>
+        <v>95.87535858154297</v>
       </c>
       <c r="F143" t="n">
-        <v>8518600</v>
+        <v>6379100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B144" t="n">
-        <v>95.26999653948798</v>
+        <v>95.76619510964362</v>
       </c>
       <c r="C144" t="n">
-        <v>96.43109780518201</v>
+        <v>96.4211799747073</v>
       </c>
       <c r="D144" t="n">
-        <v>94.36691272969546</v>
+        <v>95.389087429727</v>
       </c>
       <c r="E144" t="n">
-        <v>95.87535858154297</v>
+        <v>95.54786682128906</v>
       </c>
       <c r="F144" t="n">
-        <v>6379100</v>
+        <v>5882200</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B145" t="n">
-        <v>95.76619510964362</v>
+        <v>95.07152604625539</v>
       </c>
       <c r="C145" t="n">
-        <v>96.4211799747073</v>
+        <v>96.05399582384246</v>
       </c>
       <c r="D145" t="n">
-        <v>95.389087429727</v>
+        <v>94.60509878245135</v>
       </c>
       <c r="E145" t="n">
-        <v>95.54786682128906</v>
+        <v>95.05167388916016</v>
       </c>
       <c r="F145" t="n">
-        <v>5882200</v>
+        <v>7913000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B146" t="n">
-        <v>95.07152604625539</v>
+        <v>97.3540300760944</v>
       </c>
       <c r="C146" t="n">
-        <v>96.05399582384246</v>
+        <v>98.43574547532691</v>
       </c>
       <c r="D146" t="n">
-        <v>94.60509878245135</v>
+        <v>96.94715172012246</v>
       </c>
       <c r="E146" t="n">
-        <v>95.05167388916016</v>
+        <v>98.42581939697266</v>
       </c>
       <c r="F146" t="n">
-        <v>7913000</v>
+        <v>10821000</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B147" t="n">
-        <v>97.3540300760944</v>
+        <v>97.9097767670043</v>
       </c>
       <c r="C147" t="n">
-        <v>98.43574547532691</v>
+        <v>99.46783792592092</v>
       </c>
       <c r="D147" t="n">
-        <v>96.94715172012246</v>
+        <v>96.93722551678441</v>
       </c>
       <c r="E147" t="n">
-        <v>98.42581939697266</v>
+        <v>99.03118133544922</v>
       </c>
       <c r="F147" t="n">
-        <v>10821000</v>
+        <v>8918300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B148" t="n">
-        <v>97.9097767670043</v>
+        <v>99.08079694980933</v>
       </c>
       <c r="C148" t="n">
-        <v>99.46783792592092</v>
+        <v>99.39837088687223</v>
       </c>
       <c r="D148" t="n">
-        <v>96.93722551678441</v>
+        <v>98.06855652524918</v>
       </c>
       <c r="E148" t="n">
-        <v>99.03118133544922</v>
+        <v>98.4158935546875</v>
       </c>
       <c r="F148" t="n">
-        <v>8918300</v>
+        <v>6359600</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B149" t="n">
-        <v>99.08079694980933</v>
+        <v>97.78075602521236</v>
       </c>
       <c r="C149" t="n">
-        <v>99.39837088687223</v>
+        <v>100.4999183711592</v>
       </c>
       <c r="D149" t="n">
-        <v>98.06855652524918</v>
+        <v>97.78075602521236</v>
       </c>
       <c r="E149" t="n">
-        <v>98.4158935546875</v>
+        <v>100.4106063842773</v>
       </c>
       <c r="F149" t="n">
-        <v>6359600</v>
+        <v>6790300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B150" t="n">
-        <v>97.78075602521236</v>
+        <v>100.5693883478159</v>
       </c>
       <c r="C150" t="n">
-        <v>100.4999183711592</v>
+        <v>102.3160071037648</v>
       </c>
       <c r="D150" t="n">
-        <v>97.78075602521236</v>
+        <v>100.1327393373631</v>
       </c>
       <c r="E150" t="n">
-        <v>100.4106063842773</v>
+        <v>101.8098831176758</v>
       </c>
       <c r="F150" t="n">
-        <v>6790300</v>
+        <v>9997400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B151" t="n">
-        <v>100.5693883478159</v>
+        <v>101.8198131278678</v>
       </c>
       <c r="C151" t="n">
-        <v>102.3160071037648</v>
+        <v>102.5938806827324</v>
       </c>
       <c r="D151" t="n">
-        <v>100.1327393373631</v>
+        <v>101.0159749087976</v>
       </c>
       <c r="E151" t="n">
-        <v>101.8098831176758</v>
+        <v>102.2564697265625</v>
       </c>
       <c r="F151" t="n">
-        <v>9997400</v>
+        <v>7035300</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B152" t="n">
-        <v>101.8198131278678</v>
+        <v>102.832054706031</v>
       </c>
       <c r="C152" t="n">
-        <v>102.5938806827324</v>
+        <v>103.7351309397506</v>
       </c>
       <c r="D152" t="n">
-        <v>101.0159749087976</v>
+        <v>101.9984383035261</v>
       </c>
       <c r="E152" t="n">
-        <v>102.2564697265625</v>
+        <v>103.1099243164062</v>
       </c>
       <c r="F152" t="n">
-        <v>7035300</v>
+        <v>8145900</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B153" t="n">
-        <v>102.832054706031</v>
+        <v>103.8939187225915</v>
       </c>
       <c r="C153" t="n">
-        <v>103.7351309397506</v>
+        <v>105.5214472288459</v>
       </c>
       <c r="D153" t="n">
-        <v>101.9984383035261</v>
+        <v>103.8939187225915</v>
       </c>
       <c r="E153" t="n">
-        <v>103.1099243164062</v>
+        <v>105.4817504882812</v>
       </c>
       <c r="F153" t="n">
-        <v>8145900</v>
+        <v>10506200</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B154" t="n">
-        <v>103.8939187225915</v>
+        <v>105.1046425751499</v>
       </c>
       <c r="C154" t="n">
-        <v>105.5214472288459</v>
+        <v>106.2955145039117</v>
       </c>
       <c r="D154" t="n">
-        <v>103.8939187225915</v>
+        <v>105.1046425751499</v>
       </c>
       <c r="E154" t="n">
-        <v>105.4817504882812</v>
+        <v>105.4916763305664</v>
       </c>
       <c r="F154" t="n">
-        <v>10506200</v>
+        <v>6423400</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B155" t="n">
-        <v>105.1046425751499</v>
+        <v>105.3825171192469</v>
       </c>
       <c r="C155" t="n">
-        <v>106.2955145039117</v>
+        <v>106.0672651032121</v>
       </c>
       <c r="D155" t="n">
-        <v>105.1046425751499</v>
+        <v>103.1793971336853</v>
       </c>
       <c r="E155" t="n">
-        <v>105.4916763305664</v>
+        <v>103.4969635009766</v>
       </c>
       <c r="F155" t="n">
-        <v>6423400</v>
+        <v>7784500</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B156" t="n">
-        <v>105.3825171192469</v>
+        <v>104.2313285377519</v>
       </c>
       <c r="C156" t="n">
-        <v>106.0672651032121</v>
+        <v>105.4718232743649</v>
       </c>
       <c r="D156" t="n">
-        <v>103.1793971336853</v>
+        <v>103.437416449147</v>
       </c>
       <c r="E156" t="n">
-        <v>103.4969635009766</v>
+        <v>104.0229263305664</v>
       </c>
       <c r="F156" t="n">
-        <v>7784500</v>
+        <v>6886600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B157" t="n">
-        <v>104.2313285377519</v>
+        <v>104.1420232238167</v>
       </c>
       <c r="C157" t="n">
-        <v>105.4718232743649</v>
+        <v>104.4000406941716</v>
       </c>
       <c r="D157" t="n">
-        <v>103.437416449147</v>
+        <v>101.7701977411496</v>
       </c>
       <c r="E157" t="n">
-        <v>104.0229263305664</v>
+        <v>102.8618316650391</v>
       </c>
       <c r="F157" t="n">
-        <v>6886600</v>
+        <v>6147000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B158" t="n">
-        <v>104.1420232238167</v>
+        <v>102.81220477355</v>
       </c>
       <c r="C158" t="n">
-        <v>104.4000406941716</v>
+        <v>102.851901514659</v>
       </c>
       <c r="D158" t="n">
-        <v>101.7701977411496</v>
+        <v>101.1946023230963</v>
       </c>
       <c r="E158" t="n">
-        <v>102.8618316650391</v>
+        <v>101.8198089599609</v>
       </c>
       <c r="F158" t="n">
-        <v>6147000</v>
+        <v>5974500</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B159" t="n">
-        <v>102.81220477355</v>
+        <v>101.839659785339</v>
       </c>
       <c r="C159" t="n">
-        <v>102.851901514659</v>
+        <v>103.0206056395392</v>
       </c>
       <c r="D159" t="n">
-        <v>101.1946023230963</v>
+        <v>101.2839129884539</v>
       </c>
       <c r="E159" t="n">
-        <v>101.8198089599609</v>
+        <v>101.5717086791992</v>
       </c>
       <c r="F159" t="n">
-        <v>5974500</v>
+        <v>6524300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B160" t="n">
-        <v>101.839659785339</v>
+        <v>101.8793558222072</v>
       </c>
       <c r="C160" t="n">
-        <v>103.0206056395392</v>
+        <v>102.5045624465828</v>
       </c>
       <c r="D160" t="n">
-        <v>101.2839129884539</v>
+        <v>99.84494141643668</v>
       </c>
       <c r="E160" t="n">
-        <v>101.5717086791992</v>
+        <v>100.6984024047852</v>
       </c>
       <c r="F160" t="n">
-        <v>6524300</v>
+        <v>6409300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B161" t="n">
-        <v>101.8793558222072</v>
+        <v>100.1724381261774</v>
       </c>
       <c r="C161" t="n">
-        <v>102.5045624465828</v>
+        <v>100.7083327862765</v>
       </c>
       <c r="D161" t="n">
-        <v>99.84494141643668</v>
+        <v>99.83501960476121</v>
       </c>
       <c r="E161" t="n">
-        <v>100.6984024047852</v>
+        <v>100.5297012329102</v>
       </c>
       <c r="F161" t="n">
-        <v>6409300</v>
+        <v>5533700</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B162" t="n">
-        <v>100.1724381261774</v>
+        <v>100.1426666812253</v>
       </c>
       <c r="C162" t="n">
-        <v>100.7083327862765</v>
+        <v>103.328256381923</v>
       </c>
       <c r="D162" t="n">
-        <v>99.83501960476121</v>
+        <v>99.65638727390106</v>
       </c>
       <c r="E162" t="n">
-        <v>100.5297012329102</v>
+        <v>102.961067199707</v>
       </c>
       <c r="F162" t="n">
-        <v>5533700</v>
+        <v>9203500</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B163" t="n">
-        <v>100.1426666812253</v>
+        <v>103.6061276781693</v>
       </c>
       <c r="C163" t="n">
-        <v>103.328256381923</v>
+        <v>104.0328581941516</v>
       </c>
       <c r="D163" t="n">
-        <v>99.65638727390106</v>
+        <v>102.1870013177053</v>
       </c>
       <c r="E163" t="n">
-        <v>102.961067199707</v>
+        <v>102.2961654663086</v>
       </c>
       <c r="F163" t="n">
-        <v>9203500</v>
+        <v>5956900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B164" t="n">
-        <v>103.6061276781693</v>
+        <v>101.9587457902329</v>
       </c>
       <c r="C164" t="n">
-        <v>104.0328581941516</v>
+        <v>102.2663936470847</v>
       </c>
       <c r="D164" t="n">
-        <v>102.1870013177053</v>
+        <v>100.4999227039044</v>
       </c>
       <c r="E164" t="n">
-        <v>102.2961654663086</v>
+        <v>100.5396194458008</v>
       </c>
       <c r="F164" t="n">
-        <v>5956900</v>
+        <v>8400100</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B165" t="n">
-        <v>101.9587457902329</v>
+        <v>100.7579458156174</v>
       </c>
       <c r="C165" t="n">
-        <v>102.2663936470847</v>
+        <v>100.9564295213072</v>
       </c>
       <c r="D165" t="n">
-        <v>100.4999227039044</v>
+        <v>99.29912275715898</v>
       </c>
       <c r="E165" t="n">
-        <v>100.5396194458008</v>
+        <v>99.71593475341797</v>
       </c>
       <c r="F165" t="n">
-        <v>8400100</v>
+        <v>14314700</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B166" t="n">
-        <v>100.7579458156174</v>
+        <v>105.7099984223796</v>
       </c>
       <c r="C166" t="n">
-        <v>100.9564295213072</v>
+        <v>108.3100781720615</v>
       </c>
       <c r="D166" t="n">
-        <v>99.29912275715898</v>
+        <v>104.5092004000206</v>
       </c>
       <c r="E166" t="n">
-        <v>99.71593475341797</v>
+        <v>107.2382888793945</v>
       </c>
       <c r="F166" t="n">
-        <v>14314700</v>
+        <v>23219500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B167" t="n">
-        <v>105.7099984223796</v>
+        <v>108.2207663660894</v>
       </c>
       <c r="C167" t="n">
-        <v>108.3100781720615</v>
+        <v>109.6398926806152</v>
       </c>
       <c r="D167" t="n">
-        <v>104.5092004000206</v>
+        <v>106.2756639110559</v>
       </c>
       <c r="E167" t="n">
-        <v>107.2382888793945</v>
+        <v>107.8337326049805</v>
       </c>
       <c r="F167" t="n">
-        <v>23219500</v>
+        <v>14309200</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B168" t="n">
-        <v>108.2207663660894</v>
+        <v>108.2009150377847</v>
       </c>
       <c r="C168" t="n">
-        <v>109.6398926806152</v>
+        <v>108.3795465882309</v>
       </c>
       <c r="D168" t="n">
-        <v>106.2756639110559</v>
+        <v>106.7222473860446</v>
       </c>
       <c r="E168" t="n">
-        <v>107.8337326049805</v>
+        <v>107.1985931396484</v>
       </c>
       <c r="F168" t="n">
-        <v>14309200</v>
+        <v>8370000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B169" t="n">
-        <v>108.2009150377847</v>
+        <v>107.1787478525936</v>
       </c>
       <c r="C169" t="n">
-        <v>108.3795465882309</v>
+        <v>107.5657816141287</v>
       </c>
       <c r="D169" t="n">
-        <v>106.7222473860446</v>
+        <v>103.5862722822083</v>
       </c>
       <c r="E169" t="n">
-        <v>107.1985931396484</v>
+        <v>103.9236907958984</v>
       </c>
       <c r="F169" t="n">
-        <v>8370000</v>
+        <v>10562300</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B170" t="n">
-        <v>107.1787478525936</v>
+        <v>104.1916361796018</v>
       </c>
       <c r="C170" t="n">
-        <v>107.5657816141287</v>
+        <v>105.4619016318964</v>
       </c>
       <c r="D170" t="n">
-        <v>103.5862722822083</v>
+        <v>103.4274947211174</v>
       </c>
       <c r="E170" t="n">
-        <v>103.9236907958984</v>
+        <v>105.3527450561523</v>
       </c>
       <c r="F170" t="n">
-        <v>10562300</v>
+        <v>8178500</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B171" t="n">
-        <v>104.1916361796018</v>
+        <v>104.5489005402277</v>
       </c>
       <c r="C171" t="n">
-        <v>105.4619016318964</v>
+        <v>105.0748691255691</v>
       </c>
       <c r="D171" t="n">
-        <v>103.4274947211174</v>
+        <v>103.0702328542224</v>
       </c>
       <c r="E171" t="n">
-        <v>105.3527450561523</v>
+        <v>104.1023254394531</v>
       </c>
       <c r="F171" t="n">
-        <v>8178500</v>
+        <v>7605900</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B172" t="n">
-        <v>104.5489005402277</v>
+        <v>104.7374526473249</v>
       </c>
       <c r="C172" t="n">
-        <v>105.0748691255691</v>
+        <v>105.4817494902667</v>
       </c>
       <c r="D172" t="n">
-        <v>103.0702328542224</v>
+        <v>104.0526971289773</v>
       </c>
       <c r="E172" t="n">
-        <v>104.1023254394531</v>
+        <v>104.6183624267578</v>
       </c>
       <c r="F172" t="n">
-        <v>7605900</v>
+        <v>6144600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B173" t="n">
-        <v>104.7374526473249</v>
+        <v>104.2313280181917</v>
       </c>
       <c r="C173" t="n">
-        <v>105.4817494902667</v>
+        <v>104.6183617683755</v>
       </c>
       <c r="D173" t="n">
-        <v>104.0526971289773</v>
+        <v>101.5220917669058</v>
       </c>
       <c r="E173" t="n">
-        <v>104.6183624267578</v>
+        <v>101.9388961791992</v>
       </c>
       <c r="F173" t="n">
-        <v>6144600</v>
+        <v>9258600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B174" t="n">
-        <v>104.2313280181917</v>
+        <v>101.9091260836407</v>
       </c>
       <c r="C174" t="n">
-        <v>104.6183617683755</v>
+        <v>103.9038361698679</v>
       </c>
       <c r="D174" t="n">
-        <v>101.5220917669058</v>
+        <v>101.7701912787705</v>
       </c>
       <c r="E174" t="n">
-        <v>101.9388961791992</v>
+        <v>103.1198501586914</v>
       </c>
       <c r="F174" t="n">
-        <v>9258600</v>
+        <v>9037200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B175" t="n">
-        <v>101.9091260836407</v>
+        <v>102.9213691252704</v>
       </c>
       <c r="C175" t="n">
-        <v>103.9038361698679</v>
+        <v>103.1396974161188</v>
       </c>
       <c r="D175" t="n">
-        <v>101.7701912787705</v>
+        <v>101.1946025261468</v>
       </c>
       <c r="E175" t="n">
-        <v>103.1198501586914</v>
+        <v>101.5121688842773</v>
       </c>
       <c r="F175" t="n">
-        <v>9037200</v>
+        <v>7032600</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B176" t="n">
-        <v>102.9213691252704</v>
+        <v>102.1274576654748</v>
       </c>
       <c r="C176" t="n">
-        <v>103.1396974161188</v>
+        <v>104.0626264896183</v>
       </c>
       <c r="D176" t="n">
-        <v>101.1946025261468</v>
+        <v>100.8274139902545</v>
       </c>
       <c r="E176" t="n">
-        <v>101.5121688842773</v>
+        <v>103.2885589599609</v>
       </c>
       <c r="F176" t="n">
-        <v>7032600</v>
+        <v>7941400</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B177" t="n">
-        <v>102.1274576654748</v>
+        <v>102.822129060906</v>
       </c>
       <c r="C177" t="n">
-        <v>104.0626264896183</v>
+        <v>103.8244509351605</v>
       </c>
       <c r="D177" t="n">
-        <v>100.8274139902545</v>
+        <v>101.8098811087023</v>
       </c>
       <c r="E177" t="n">
-        <v>103.2885589599609</v>
+        <v>102.7923583984375</v>
       </c>
       <c r="F177" t="n">
-        <v>7941400</v>
+        <v>8611200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B178" t="n">
-        <v>102.822129060906</v>
+        <v>103.2488588874603</v>
       </c>
       <c r="C178" t="n">
-        <v>103.8244509351605</v>
+        <v>103.7053600422387</v>
       </c>
       <c r="D178" t="n">
-        <v>101.8098811087023</v>
+        <v>102.1969217730311</v>
       </c>
       <c r="E178" t="n">
-        <v>102.7923583984375</v>
+        <v>102.2167663574219</v>
       </c>
       <c r="F178" t="n">
-        <v>8611200</v>
+        <v>5693300</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B179" t="n">
-        <v>103.2488588874603</v>
+        <v>102.3160049896206</v>
       </c>
       <c r="C179" t="n">
-        <v>103.7053600422387</v>
+        <v>103.0106865892155</v>
       </c>
       <c r="D179" t="n">
-        <v>102.1969217730311</v>
+        <v>101.571708143084</v>
       </c>
       <c r="E179" t="n">
-        <v>102.2167663574219</v>
+        <v>102.4946365356445</v>
       </c>
       <c r="F179" t="n">
-        <v>5693300</v>
+        <v>6714400</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B180" t="n">
-        <v>102.3160049896206</v>
+        <v>102.5144889184559</v>
       </c>
       <c r="C180" t="n">
-        <v>103.0106865892155</v>
+        <v>104.4496576951832</v>
       </c>
       <c r="D180" t="n">
-        <v>101.571708143084</v>
+        <v>102.4747921779873</v>
       </c>
       <c r="E180" t="n">
-        <v>102.4946365356445</v>
+        <v>103.3877944946289</v>
       </c>
       <c r="F180" t="n">
-        <v>6714400</v>
+        <v>7360100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B181" t="n">
-        <v>102.5144889184559</v>
+        <v>103.0206090569662</v>
       </c>
       <c r="C181" t="n">
-        <v>104.4496576951832</v>
+        <v>103.6160526141937</v>
       </c>
       <c r="D181" t="n">
-        <v>102.4747921779873</v>
+        <v>102.3160089237181</v>
       </c>
       <c r="E181" t="n">
-        <v>103.3877944946289</v>
+        <v>102.9412231445312</v>
       </c>
       <c r="F181" t="n">
-        <v>7360100</v>
+        <v>6511100</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B182" t="n">
-        <v>103.0206090569662</v>
+        <v>102.8419796873618</v>
       </c>
       <c r="C182" t="n">
-        <v>103.6160526141937</v>
+        <v>102.9709959941437</v>
       </c>
       <c r="D182" t="n">
-        <v>102.3160089237181</v>
+        <v>101.0556716918945</v>
       </c>
       <c r="E182" t="n">
-        <v>102.9412231445312</v>
+        <v>101.0556716918945</v>
       </c>
       <c r="F182" t="n">
-        <v>6511100</v>
+        <v>13340300</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B183" t="n">
-        <v>102.8419796873618</v>
+        <v>100.8869633557317</v>
       </c>
       <c r="C183" t="n">
-        <v>102.9709959941437</v>
+        <v>102.2266962072239</v>
       </c>
       <c r="D183" t="n">
-        <v>101.0556716918945</v>
+        <v>99.53730442598828</v>
       </c>
       <c r="E183" t="n">
-        <v>101.0556716918945</v>
+        <v>102.0679092407227</v>
       </c>
       <c r="F183" t="n">
-        <v>13340300</v>
+        <v>8219000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B184" t="n">
-        <v>100.8869633557317</v>
+        <v>101.5717095216456</v>
       </c>
       <c r="C184" t="n">
-        <v>102.2266962072239</v>
+        <v>101.7106443291744</v>
       </c>
       <c r="D184" t="n">
-        <v>99.53730442598828</v>
+        <v>99.32889287365569</v>
       </c>
       <c r="E184" t="n">
-        <v>102.0679092407227</v>
+        <v>100.6388626098633</v>
       </c>
       <c r="F184" t="n">
-        <v>8219000</v>
+        <v>8397400</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B185" t="n">
-        <v>101.5717095216456</v>
+        <v>99.67623490973834</v>
       </c>
       <c r="C185" t="n">
-        <v>101.7106443291744</v>
+        <v>100.4999176557305</v>
       </c>
       <c r="D185" t="n">
-        <v>99.32889287365569</v>
+        <v>98.495281504625</v>
       </c>
       <c r="E185" t="n">
-        <v>100.6388626098633</v>
+        <v>98.63421630859375</v>
       </c>
       <c r="F185" t="n">
-        <v>8397400</v>
+        <v>7471600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B186" t="n">
-        <v>99.67623490973834</v>
+        <v>99.77547422442305</v>
       </c>
       <c r="C186" t="n">
-        <v>100.4999176557305</v>
+        <v>100.6984026174289</v>
       </c>
       <c r="D186" t="n">
-        <v>98.495281504625</v>
+        <v>98.25710986817649</v>
       </c>
       <c r="E186" t="n">
-        <v>98.63421630859375</v>
+        <v>98.5845947265625</v>
       </c>
       <c r="F186" t="n">
-        <v>7471600</v>
+        <v>9568000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B187" t="n">
-        <v>99.77547422442305</v>
+        <v>98.92201919170897</v>
       </c>
       <c r="C187" t="n">
-        <v>100.6984026174289</v>
+        <v>99.43806170522778</v>
       </c>
       <c r="D187" t="n">
-        <v>98.25710986817649</v>
+        <v>98.33650169977196</v>
       </c>
       <c r="E187" t="n">
-        <v>98.5845947265625</v>
+        <v>98.95178985595703</v>
       </c>
       <c r="F187" t="n">
-        <v>9568000</v>
+        <v>9501600</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B188" t="n">
-        <v>98.92201919170897</v>
+        <v>98.76323055949389</v>
       </c>
       <c r="C188" t="n">
-        <v>99.43806170522778</v>
+        <v>99.08079692509821</v>
       </c>
       <c r="D188" t="n">
-        <v>98.33650169977196</v>
+        <v>97.66167814394407</v>
       </c>
       <c r="E188" t="n">
-        <v>98.95178985595703</v>
+        <v>98.11817932128906</v>
       </c>
       <c r="F188" t="n">
-        <v>9501600</v>
+        <v>7559200</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="n">
-        <v>98.76323055949389</v>
+        <v>98.29680690142362</v>
       </c>
       <c r="C189" t="n">
-        <v>99.08079692509821</v>
+        <v>99.32889186938023</v>
       </c>
       <c r="D189" t="n">
-        <v>97.66167814394407</v>
+        <v>97.7609122614967</v>
       </c>
       <c r="E189" t="n">
-        <v>98.11817932128906</v>
+        <v>98.57467651367188</v>
       </c>
       <c r="F189" t="n">
-        <v>7559200</v>
+        <v>8616300</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B190" t="n">
-        <v>98.29680690142362</v>
+        <v>98.7334588011272</v>
       </c>
       <c r="C190" t="n">
-        <v>99.32889186938023</v>
+        <v>99.00140991464168</v>
       </c>
       <c r="D190" t="n">
-        <v>97.7609122614967</v>
+        <v>97.20516831754395</v>
       </c>
       <c r="E190" t="n">
-        <v>98.57467651367188</v>
+        <v>97.86015319824219</v>
       </c>
       <c r="F190" t="n">
-        <v>8616300</v>
+        <v>7041400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B191" t="n">
-        <v>98.7334588011272</v>
+        <v>98.07848356908464</v>
       </c>
       <c r="C191" t="n">
-        <v>99.00140991464168</v>
+        <v>99.97395570346617</v>
       </c>
       <c r="D191" t="n">
-        <v>97.20516831754395</v>
+        <v>97.35403126794252</v>
       </c>
       <c r="E191" t="n">
-        <v>97.86015319824219</v>
+        <v>99.57699584960938</v>
       </c>
       <c r="F191" t="n">
-        <v>7041400</v>
+        <v>9264400</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B192" t="n">
-        <v>98.07848356908464</v>
+        <v>100.2915220505157</v>
       </c>
       <c r="C192" t="n">
-        <v>99.97395570346617</v>
+        <v>100.9961221945534</v>
       </c>
       <c r="D192" t="n">
-        <v>97.35403126794252</v>
+        <v>98.78308369184245</v>
       </c>
       <c r="E192" t="n">
-        <v>99.57699584960938</v>
+        <v>99.27928161621094</v>
       </c>
       <c r="F192" t="n">
-        <v>9264400</v>
+        <v>8257200</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B193" t="n">
-        <v>100.2915220505157</v>
+        <v>100.1128870298928</v>
       </c>
       <c r="C193" t="n">
-        <v>100.9961221945534</v>
+        <v>101.6213329077368</v>
       </c>
       <c r="D193" t="n">
-        <v>98.78308369184245</v>
+        <v>99.82509133515438</v>
       </c>
       <c r="E193" t="n">
-        <v>99.27928161621094</v>
+        <v>100.9167327880859</v>
       </c>
       <c r="F193" t="n">
-        <v>8257200</v>
+        <v>10265100</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B194" t="n">
-        <v>100.1128870298928</v>
+        <v>100.658710438741</v>
       </c>
       <c r="C194" t="n">
-        <v>101.6213329077368</v>
+        <v>101.1549083591584</v>
       </c>
       <c r="D194" t="n">
-        <v>99.82509133515438</v>
+        <v>99.28920690408536</v>
       </c>
       <c r="E194" t="n">
-        <v>100.9167327880859</v>
+        <v>100.5098495483398</v>
       </c>
       <c r="F194" t="n">
-        <v>10265100</v>
+        <v>10694600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B195" t="n">
-        <v>100.658710438741</v>
+        <v>99.90448284246082</v>
       </c>
       <c r="C195" t="n">
-        <v>101.1549083591584</v>
+        <v>101.581634158465</v>
       </c>
       <c r="D195" t="n">
-        <v>99.28920690408536</v>
+        <v>99.67623604963576</v>
       </c>
       <c r="E195" t="n">
-        <v>100.5098495483398</v>
+        <v>100.0930404663086</v>
       </c>
       <c r="F195" t="n">
-        <v>10694600</v>
+        <v>11168700</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B196" t="n">
-        <v>99.90448284246082</v>
+        <v>101.0258948980948</v>
       </c>
       <c r="C196" t="n">
-        <v>101.581634158465</v>
+        <v>103.4274909034028</v>
       </c>
       <c r="D196" t="n">
-        <v>99.67623604963576</v>
+        <v>100.0334991036985</v>
       </c>
       <c r="E196" t="n">
-        <v>100.0930404663086</v>
+        <v>103.0999984741211</v>
       </c>
       <c r="F196" t="n">
-        <v>11168700</v>
+        <v>22943600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B197" t="n">
-        <v>101.0258948980948</v>
+        <v>102.623658522444</v>
       </c>
       <c r="C197" t="n">
-        <v>103.4274909034028</v>
+        <v>103.5168087306858</v>
       </c>
       <c r="D197" t="n">
-        <v>100.0334991036985</v>
+        <v>100.7381048924391</v>
       </c>
       <c r="E197" t="n">
-        <v>103.0999984741211</v>
+        <v>101.6709518432617</v>
       </c>
       <c r="F197" t="n">
-        <v>22943600</v>
+        <v>17396300</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B198" t="n">
-        <v>102.623658522444</v>
+        <v>101.2442170259669</v>
       </c>
       <c r="C198" t="n">
-        <v>103.5168087306858</v>
+        <v>103.2488607985985</v>
       </c>
       <c r="D198" t="n">
-        <v>100.7381048924391</v>
+        <v>101.025896308111</v>
       </c>
       <c r="E198" t="n">
-        <v>101.6709518432617</v>
+        <v>102.7427368164062</v>
       </c>
       <c r="F198" t="n">
-        <v>17396300</v>
+        <v>14457400</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B199" t="n">
-        <v>101.2442170259669</v>
+        <v>102.3160060444983</v>
       </c>
       <c r="C199" t="n">
-        <v>103.2488607985985</v>
+        <v>103.7351323493811</v>
       </c>
       <c r="D199" t="n">
-        <v>101.025896308111</v>
+        <v>100.2716731077754</v>
       </c>
       <c r="E199" t="n">
-        <v>102.7427368164062</v>
+        <v>100.3510665893555</v>
       </c>
       <c r="F199" t="n">
-        <v>14457400</v>
+        <v>12215500</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B200" t="n">
-        <v>102.3160060444983</v>
+        <v>100.3411416176147</v>
       </c>
       <c r="C200" t="n">
-        <v>103.7351323493811</v>
+        <v>100.8075688628163</v>
       </c>
       <c r="D200" t="n">
-        <v>100.2716731077754</v>
+        <v>97.24486394426569</v>
       </c>
       <c r="E200" t="n">
-        <v>100.3510665893555</v>
+        <v>97.30441284179688</v>
       </c>
       <c r="F200" t="n">
-        <v>12215500</v>
+        <v>12054400</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B201" t="n">
-        <v>100.3411416176147</v>
+        <v>97.30440945370802</v>
       </c>
       <c r="C201" t="n">
-        <v>100.8075688628163</v>
+        <v>98.69375749140566</v>
       </c>
       <c r="D201" t="n">
-        <v>97.24486394426569</v>
+        <v>97.15554857213215</v>
       </c>
       <c r="E201" t="n">
-        <v>97.30441284179688</v>
+        <v>98.03878021240234</v>
       </c>
       <c r="F201" t="n">
-        <v>12054400</v>
+        <v>13921400</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B202" t="n">
-        <v>97.30440945370802</v>
+        <v>98.95178655891404</v>
       </c>
       <c r="C202" t="n">
-        <v>98.69375749140566</v>
+        <v>99.27927899748993</v>
       </c>
       <c r="D202" t="n">
-        <v>97.15554857213215</v>
+        <v>97.75098852218167</v>
       </c>
       <c r="E202" t="n">
-        <v>98.03878021240234</v>
+        <v>97.87999725341797</v>
       </c>
       <c r="F202" t="n">
-        <v>13921400</v>
+        <v>10418100</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,25 +5695,25 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B203" t="n">
-        <v>98.95178655891404</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C203" t="n">
-        <v>99.27927899748993</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D203" t="n">
-        <v>97.75098852218167</v>
+        <v>95.98999786376953</v>
       </c>
       <c r="E203" t="n">
-        <v>97.87999725341797</v>
+        <v>96.25</v>
       </c>
       <c r="F203" t="n">
-        <v>10418100</v>
+        <v>12717800</v>
       </c>
       <c r="G203" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -5721,25 +5721,25 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B204" t="n">
-        <v>97.41000366210938</v>
+        <v>96.55000305175781</v>
       </c>
       <c r="C204" t="n">
-        <v>97.59999847412109</v>
+        <v>97.76000213623047</v>
       </c>
       <c r="D204" t="n">
-        <v>95.98999786376953</v>
+        <v>95.65000152587891</v>
       </c>
       <c r="E204" t="n">
-        <v>96.25</v>
+        <v>95.70999908447266</v>
       </c>
       <c r="F204" t="n">
-        <v>12717800</v>
+        <v>11590400</v>
       </c>
       <c r="G204" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B205" t="n">
-        <v>96.55000305175781</v>
+        <v>96.40000152587891</v>
       </c>
       <c r="C205" t="n">
-        <v>97.76000213623047</v>
+        <v>99.51999664306641</v>
       </c>
       <c r="D205" t="n">
-        <v>95.65000152587891</v>
+        <v>95.76999664306641</v>
       </c>
       <c r="E205" t="n">
-        <v>95.70999908447266</v>
+        <v>99.5</v>
       </c>
       <c r="F205" t="n">
-        <v>11590400</v>
+        <v>11297800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B206" t="n">
-        <v>96.40000152587891</v>
+        <v>98.84999847412109</v>
       </c>
       <c r="C206" t="n">
-        <v>99.51999664306641</v>
+        <v>99.44000244140625</v>
       </c>
       <c r="D206" t="n">
-        <v>95.76999664306641</v>
+        <v>97.01999664306641</v>
       </c>
       <c r="E206" t="n">
-        <v>99.5</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="F206" t="n">
-        <v>11297800</v>
+        <v>10171900</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B207" t="n">
-        <v>98.84999847412109</v>
+        <v>98.13999938964844</v>
       </c>
       <c r="C207" t="n">
-        <v>99.44000244140625</v>
+        <v>99.04000091552734</v>
       </c>
       <c r="D207" t="n">
-        <v>97.01999664306641</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="E207" t="n">
-        <v>97.41000366210938</v>
+        <v>97.48000335693359</v>
       </c>
       <c r="F207" t="n">
-        <v>10171900</v>
+        <v>9936400</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B208" t="n">
-        <v>98.13999938964844</v>
+        <v>97.30000305175781</v>
       </c>
       <c r="C208" t="n">
-        <v>99.04000091552734</v>
+        <v>97.66000366210938</v>
       </c>
       <c r="D208" t="n">
-        <v>96.91999816894531</v>
+        <v>96.63999938964844</v>
       </c>
       <c r="E208" t="n">
-        <v>97.48000335693359</v>
+        <v>96.69999694824219</v>
       </c>
       <c r="F208" t="n">
-        <v>9936400</v>
+        <v>8720800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B209" t="n">
-        <v>97.30000305175781</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="C209" t="n">
-        <v>97.66000366210938</v>
+        <v>96.55000305175781</v>
       </c>
       <c r="D209" t="n">
-        <v>96.63999938964844</v>
+        <v>94.77999877929688</v>
       </c>
       <c r="E209" t="n">
-        <v>96.69999694824219</v>
+        <v>96.16999816894531</v>
       </c>
       <c r="F209" t="n">
-        <v>8720800</v>
+        <v>11448100</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B210" t="n">
-        <v>96.33999633789062</v>
+        <v>96.88999938964844</v>
       </c>
       <c r="C210" t="n">
-        <v>96.55000305175781</v>
+        <v>97.05000305175781</v>
       </c>
       <c r="D210" t="n">
-        <v>94.77999877929688</v>
+        <v>95.51999664306641</v>
       </c>
       <c r="E210" t="n">
-        <v>96.16999816894531</v>
+        <v>95.62000274658203</v>
       </c>
       <c r="F210" t="n">
-        <v>11448100</v>
+        <v>10678900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B211" t="n">
-        <v>96.88999938964844</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="C211" t="n">
-        <v>97.05000305175781</v>
+        <v>97.54000091552734</v>
       </c>
       <c r="D211" t="n">
-        <v>95.51999664306641</v>
+        <v>95.83000183105469</v>
       </c>
       <c r="E211" t="n">
-        <v>95.62000274658203</v>
+        <v>96</v>
       </c>
       <c r="F211" t="n">
-        <v>10678900</v>
+        <v>9304200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>96.09999847412109</v>
+        <v>95.51000213623047</v>
       </c>
       <c r="C212" t="n">
-        <v>97.54000091552734</v>
+        <v>96.69000244140625</v>
       </c>
       <c r="D212" t="n">
-        <v>95.83000183105469</v>
+        <v>95.12999725341797</v>
       </c>
       <c r="E212" t="n">
-        <v>96</v>
+        <v>95.87000274658203</v>
       </c>
       <c r="F212" t="n">
-        <v>9304200</v>
+        <v>7651600</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>95.51000213623047</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="C213" t="n">
-        <v>96.69000244140625</v>
+        <v>97.90000152587891</v>
       </c>
       <c r="D213" t="n">
-        <v>95.12999725341797</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="E213" t="n">
-        <v>95.87000274658203</v>
+        <v>97.15000152587891</v>
       </c>
       <c r="F213" t="n">
-        <v>7651600</v>
+        <v>10219200</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>96.09999847412109</v>
+        <v>97.27999877929688</v>
       </c>
       <c r="C214" t="n">
-        <v>97.90000152587891</v>
+        <v>99.84999847412109</v>
       </c>
       <c r="D214" t="n">
-        <v>96.09999847412109</v>
+        <v>97.27999877929688</v>
       </c>
       <c r="E214" t="n">
-        <v>97.15000152587891</v>
+        <v>99.70999908447266</v>
       </c>
       <c r="F214" t="n">
-        <v>10219200</v>
+        <v>7480000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B215" t="n">
-        <v>97.27999877929688</v>
+        <v>99.01000213623047</v>
       </c>
       <c r="C215" t="n">
-        <v>99.84999847412109</v>
+        <v>99.79000091552734</v>
       </c>
       <c r="D215" t="n">
-        <v>97.27999877929688</v>
+        <v>97.05000305175781</v>
       </c>
       <c r="E215" t="n">
-        <v>99.70999908447266</v>
+        <v>97.66999816894531</v>
       </c>
       <c r="F215" t="n">
-        <v>7480000</v>
+        <v>10496500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B216" t="n">
-        <v>99.01000213623047</v>
+        <v>97.84999847412109</v>
       </c>
       <c r="C216" t="n">
-        <v>99.79000091552734</v>
+        <v>98.38999938964844</v>
       </c>
       <c r="D216" t="n">
-        <v>97.05000305175781</v>
+        <v>96</v>
       </c>
       <c r="E216" t="n">
-        <v>97.66999816894531</v>
+        <v>96.41000366210938</v>
       </c>
       <c r="F216" t="n">
-        <v>10496500</v>
+        <v>9861700</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B217" t="n">
-        <v>97.84999847412109</v>
+        <v>96</v>
       </c>
       <c r="C217" t="n">
-        <v>98.38999938964844</v>
+        <v>96.88999938964844</v>
       </c>
       <c r="D217" t="n">
-        <v>96</v>
+        <v>95.83999633789062</v>
       </c>
       <c r="E217" t="n">
-        <v>96.41000366210938</v>
+        <v>96.13999938964844</v>
       </c>
       <c r="F217" t="n">
-        <v>9861700</v>
+        <v>9745400</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B218" t="n">
-        <v>96</v>
+        <v>97.12000274658203</v>
       </c>
       <c r="C218" t="n">
-        <v>96.88999938964844</v>
+        <v>97.30000305175781</v>
       </c>
       <c r="D218" t="n">
-        <v>95.83999633789062</v>
+        <v>95.65000152587891</v>
       </c>
       <c r="E218" t="n">
-        <v>96.13999938964844</v>
+        <v>95.87000274658203</v>
       </c>
       <c r="F218" t="n">
-        <v>9745400</v>
+        <v>9119200</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B219" t="n">
-        <v>97.12000274658203</v>
+        <v>94.80999755859375</v>
       </c>
       <c r="C219" t="n">
-        <v>97.30000305175781</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D219" t="n">
-        <v>95.65000152587891</v>
+        <v>92.48999786376953</v>
       </c>
       <c r="E219" t="n">
-        <v>95.87000274658203</v>
+        <v>92.83000183105469</v>
       </c>
       <c r="F219" t="n">
-        <v>9119200</v>
+        <v>13562500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B220" t="n">
-        <v>94.80999755859375</v>
+        <v>93.26000213623047</v>
       </c>
       <c r="C220" t="n">
-        <v>94.81999969482422</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="D220" t="n">
-        <v>92.48999786376953</v>
+        <v>93</v>
       </c>
       <c r="E220" t="n">
-        <v>92.83000183105469</v>
+        <v>94.84999847412109</v>
       </c>
       <c r="F220" t="n">
-        <v>13562500</v>
+        <v>12153100</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B221" t="n">
-        <v>93.26000213623047</v>
+        <v>95.51000213623047</v>
       </c>
       <c r="C221" t="n">
-        <v>96.29000091552734</v>
+        <v>97.19000244140625</v>
       </c>
       <c r="D221" t="n">
-        <v>93</v>
+        <v>95.51000213623047</v>
       </c>
       <c r="E221" t="n">
-        <v>94.84999847412109</v>
+        <v>96.65000152587891</v>
       </c>
       <c r="F221" t="n">
-        <v>12153100</v>
+        <v>10593900</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B222" t="n">
-        <v>95.51000213623047</v>
+        <v>97</v>
       </c>
       <c r="C222" t="n">
-        <v>97.19000244140625</v>
+        <v>99.23000335693359</v>
       </c>
       <c r="D222" t="n">
-        <v>95.51000213623047</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="E222" t="n">
-        <v>96.65000152587891</v>
+        <v>98.88999938964844</v>
       </c>
       <c r="F222" t="n">
-        <v>10593900</v>
+        <v>11389300</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B223" t="n">
-        <v>97</v>
+        <v>98.33999633789062</v>
       </c>
       <c r="C223" t="n">
-        <v>99.23000335693359</v>
+        <v>99.41000366210938</v>
       </c>
       <c r="D223" t="n">
-        <v>96.97000122070312</v>
+        <v>97.98999786376953</v>
       </c>
       <c r="E223" t="n">
-        <v>98.88999938964844</v>
+        <v>98.48000335693359</v>
       </c>
       <c r="F223" t="n">
-        <v>11389300</v>
+        <v>11070100</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B224" t="n">
-        <v>98.33999633789062</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C224" t="n">
-        <v>99.41000366210938</v>
+        <v>97.48000335693359</v>
       </c>
       <c r="D224" t="n">
-        <v>97.98999786376953</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E224" t="n">
-        <v>98.48000335693359</v>
+        <v>96.16000366210938</v>
       </c>
       <c r="F224" t="n">
-        <v>11070100</v>
+        <v>21112400</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B225" t="n">
-        <v>97.41000366210938</v>
+        <v>96.08000183105469</v>
       </c>
       <c r="C225" t="n">
-        <v>97.48000335693359</v>
+        <v>96.58999633789062</v>
       </c>
       <c r="D225" t="n">
-        <v>94.45999908447266</v>
+        <v>95.59999847412109</v>
       </c>
       <c r="E225" t="n">
-        <v>96.16000366210938</v>
+        <v>96.19000244140625</v>
       </c>
       <c r="F225" t="n">
-        <v>21112400</v>
+        <v>11193000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B226" t="n">
-        <v>96.08000183105469</v>
+        <v>97.62000274658203</v>
       </c>
       <c r="C226" t="n">
-        <v>96.58999633789062</v>
+        <v>99.05000305175781</v>
       </c>
       <c r="D226" t="n">
-        <v>95.59999847412109</v>
+        <v>97.20999908447266</v>
       </c>
       <c r="E226" t="n">
-        <v>96.19000244140625</v>
+        <v>98.13999938964844</v>
       </c>
       <c r="F226" t="n">
-        <v>11193000</v>
+        <v>11480300</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B227" t="n">
-        <v>97.62000274658203</v>
+        <v>97.87000274658203</v>
       </c>
       <c r="C227" t="n">
-        <v>99.05000305175781</v>
+        <v>98.56999969482422</v>
       </c>
       <c r="D227" t="n">
-        <v>97.20999908447266</v>
+        <v>97.37999725341797</v>
       </c>
       <c r="E227" t="n">
-        <v>98.13999938964844</v>
+        <v>98.18000030517578</v>
       </c>
       <c r="F227" t="n">
-        <v>11480300</v>
+        <v>16796800</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B228" t="n">
-        <v>97.87000274658203</v>
+        <v>101.9899978637695</v>
       </c>
       <c r="C228" t="n">
-        <v>98.56999969482422</v>
+        <v>103.2099990844727</v>
       </c>
       <c r="D228" t="n">
-        <v>97.37999725341797</v>
+        <v>99.69000244140625</v>
       </c>
       <c r="E228" t="n">
-        <v>98.18000030517578</v>
+        <v>101.7600021362305</v>
       </c>
       <c r="F228" t="n">
-        <v>16796800</v>
+        <v>20809000</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B229" t="n">
-        <v>101.9899978637695</v>
+        <v>102.5400009155273</v>
       </c>
       <c r="C229" t="n">
-        <v>103.2099990844727</v>
+        <v>104.7300033569336</v>
       </c>
       <c r="D229" t="n">
-        <v>99.69000244140625</v>
+        <v>102.5199966430664</v>
       </c>
       <c r="E229" t="n">
-        <v>101.7600021362305</v>
+        <v>104.6800003051758</v>
       </c>
       <c r="F229" t="n">
-        <v>20809000</v>
+        <v>14047200</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B230" t="n">
-        <v>102.5400009155273</v>
+        <v>104.4199981689453</v>
       </c>
       <c r="C230" t="n">
-        <v>104.7300033569336</v>
+        <v>105.25</v>
       </c>
       <c r="D230" t="n">
-        <v>102.5199966430664</v>
+        <v>103.6999969482422</v>
       </c>
       <c r="E230" t="n">
-        <v>104.6800003051758</v>
+        <v>104.9100036621094</v>
       </c>
       <c r="F230" t="n">
-        <v>14047200</v>
+        <v>10929700</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B231" t="n">
-        <v>104.4199981689453</v>
+        <v>104.6100006103516</v>
       </c>
       <c r="C231" t="n">
-        <v>105.25</v>
+        <v>104.8000030517578</v>
       </c>
       <c r="D231" t="n">
-        <v>103.6999969482422</v>
+        <v>102.8000030517578</v>
       </c>
       <c r="E231" t="n">
-        <v>104.9100036621094</v>
+        <v>103.1800003051758</v>
       </c>
       <c r="F231" t="n">
-        <v>10929700</v>
+        <v>8631900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B232" t="n">
-        <v>104.6100006103516</v>
+        <v>102.9499969482422</v>
       </c>
       <c r="C232" t="n">
-        <v>104.8000030517578</v>
+        <v>104.0899963378906</v>
       </c>
       <c r="D232" t="n">
-        <v>102.8000030517578</v>
+        <v>102.7900009155273</v>
       </c>
       <c r="E232" t="n">
-        <v>103.1800003051758</v>
+        <v>103.5299987792969</v>
       </c>
       <c r="F232" t="n">
-        <v>8631900</v>
+        <v>6781600</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B233" t="n">
-        <v>102.9499969482422</v>
+        <v>103.2900009155273</v>
       </c>
       <c r="C233" t="n">
-        <v>104.0899963378906</v>
+        <v>103.6800003051758</v>
       </c>
       <c r="D233" t="n">
-        <v>102.7900009155273</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E233" t="n">
-        <v>103.5299987792969</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F233" t="n">
-        <v>6781600</v>
+        <v>6717500</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B234" t="n">
-        <v>103.2900009155273</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="C234" t="n">
-        <v>103.6800003051758</v>
+        <v>104.9400024414062</v>
       </c>
       <c r="D234" t="n">
-        <v>102.0299987792969</v>
+        <v>103.4599990844727</v>
       </c>
       <c r="E234" t="n">
-        <v>103.2200012207031</v>
+        <v>104.8000030517578</v>
       </c>
       <c r="F234" t="n">
-        <v>6717500</v>
+        <v>7100000</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B235" t="n">
-        <v>103.8000030517578</v>
+        <v>104.9899978637695</v>
       </c>
       <c r="C235" t="n">
-        <v>104.9400024414062</v>
+        <v>107.1100006103516</v>
       </c>
       <c r="D235" t="n">
-        <v>103.4599990844727</v>
+        <v>104.9100036621094</v>
       </c>
       <c r="E235" t="n">
-        <v>104.8000030517578</v>
+        <v>106.8499984741211</v>
       </c>
       <c r="F235" t="n">
-        <v>7100000</v>
+        <v>8176900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B236" t="n">
-        <v>104.9899978637695</v>
+        <v>106.3300018310547</v>
       </c>
       <c r="C236" t="n">
-        <v>107.1100006103516</v>
+        <v>106.6399993896484</v>
       </c>
       <c r="D236" t="n">
-        <v>104.9100036621094</v>
+        <v>103.4599990844727</v>
       </c>
       <c r="E236" t="n">
-        <v>106.8499984741211</v>
+        <v>103.5</v>
       </c>
       <c r="F236" t="n">
-        <v>8176900</v>
+        <v>7635000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B237" t="n">
-        <v>106.3300018310547</v>
+        <v>104.1900024414062</v>
       </c>
       <c r="C237" t="n">
-        <v>106.6399993896484</v>
+        <v>105.2099990844727</v>
       </c>
       <c r="D237" t="n">
-        <v>103.4599990844727</v>
+        <v>103.629997253418</v>
       </c>
       <c r="E237" t="n">
-        <v>103.5</v>
+        <v>103.9499969482422</v>
       </c>
       <c r="F237" t="n">
-        <v>7635000</v>
+        <v>6149900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B238" t="n">
-        <v>104.1900024414062</v>
+        <v>104.0599975585938</v>
       </c>
       <c r="C238" t="n">
-        <v>105.2099990844727</v>
+        <v>107.0599975585938</v>
       </c>
       <c r="D238" t="n">
-        <v>103.629997253418</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="E238" t="n">
-        <v>103.9499969482422</v>
+        <v>106.9300003051758</v>
       </c>
       <c r="F238" t="n">
-        <v>6149900</v>
+        <v>8046100</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B239" t="n">
-        <v>104.0599975585938</v>
+        <v>106.879997253418</v>
       </c>
       <c r="C239" t="n">
-        <v>107.0599975585938</v>
+        <v>108.6900024414062</v>
       </c>
       <c r="D239" t="n">
-        <v>103.9599990844727</v>
+        <v>106.4199981689453</v>
       </c>
       <c r="E239" t="n">
-        <v>106.9300003051758</v>
+        <v>107.3199996948242</v>
       </c>
       <c r="F239" t="n">
-        <v>8046100</v>
+        <v>7971500</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B240" t="n">
-        <v>106.879997253418</v>
+        <v>107.5699996948242</v>
       </c>
       <c r="C240" t="n">
-        <v>108.6900024414062</v>
+        <v>108.4100036621094</v>
       </c>
       <c r="D240" t="n">
-        <v>106.4199981689453</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="E240" t="n">
-        <v>107.3199996948242</v>
+        <v>107.7799987792969</v>
       </c>
       <c r="F240" t="n">
-        <v>7971500</v>
+        <v>6840800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B241" t="n">
-        <v>107.5699996948242</v>
+        <v>108.3899993896484</v>
       </c>
       <c r="C241" t="n">
-        <v>108.4100036621094</v>
+        <v>111.870002746582</v>
       </c>
       <c r="D241" t="n">
-        <v>106.9700012207031</v>
+        <v>108.0800018310547</v>
       </c>
       <c r="E241" t="n">
-        <v>107.7799987792969</v>
+        <v>110.6100006103516</v>
       </c>
       <c r="F241" t="n">
-        <v>6840800</v>
+        <v>12658400</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B242" t="n">
-        <v>108.3899993896484</v>
+        <v>110.5</v>
       </c>
       <c r="C242" t="n">
-        <v>111.870002746582</v>
+        <v>111.5999984741211</v>
       </c>
       <c r="D242" t="n">
-        <v>108.0800018310547</v>
+        <v>109.7600021362305</v>
       </c>
       <c r="E242" t="n">
-        <v>110.6100006103516</v>
+        <v>111.25</v>
       </c>
       <c r="F242" t="n">
-        <v>12658400</v>
+        <v>6747100</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B243" t="n">
-        <v>110.5</v>
+        <v>111.3000030517578</v>
       </c>
       <c r="C243" t="n">
-        <v>111.5999984741211</v>
+        <v>111.5199966430664</v>
       </c>
       <c r="D243" t="n">
-        <v>109.7600021362305</v>
+        <v>109.4499969482422</v>
       </c>
       <c r="E243" t="n">
-        <v>111.25</v>
+        <v>109.629997253418</v>
       </c>
       <c r="F243" t="n">
-        <v>6747100</v>
+        <v>8524600</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B244" t="n">
-        <v>111.3000030517578</v>
+        <v>108.7799987792969</v>
       </c>
       <c r="C244" t="n">
-        <v>111.5199966430664</v>
+        <v>108.870002746582</v>
       </c>
       <c r="D244" t="n">
-        <v>109.4499969482422</v>
+        <v>106.7399978637695</v>
       </c>
       <c r="E244" t="n">
-        <v>109.629997253418</v>
+        <v>106.8199996948242</v>
       </c>
       <c r="F244" t="n">
-        <v>8524600</v>
+        <v>8699500</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B245" t="n">
-        <v>108.7799987792969</v>
+        <v>107.25</v>
       </c>
       <c r="C245" t="n">
-        <v>108.870002746582</v>
+        <v>108.1999969482422</v>
       </c>
       <c r="D245" t="n">
-        <v>106.7399978637695</v>
+        <v>107.0299987792969</v>
       </c>
       <c r="E245" t="n">
-        <v>106.8199996948242</v>
+        <v>108.0999984741211</v>
       </c>
       <c r="F245" t="n">
-        <v>8699500</v>
+        <v>5465900</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B246" t="n">
-        <v>107.25</v>
+        <v>107.7799987792969</v>
       </c>
       <c r="C246" t="n">
-        <v>108.1999969482422</v>
+        <v>108.0899963378906</v>
       </c>
       <c r="D246" t="n">
-        <v>107.0299987792969</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="E246" t="n">
-        <v>108.0999984741211</v>
+        <v>107.5500030517578</v>
       </c>
       <c r="F246" t="n">
-        <v>5465900</v>
+        <v>8728700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B247" t="n">
-        <v>107.7799987792969</v>
+        <v>107.2399978637695</v>
       </c>
       <c r="C247" t="n">
-        <v>108.0899963378906</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D247" t="n">
-        <v>106.9700012207031</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="E247" t="n">
-        <v>107.5500030517578</v>
+        <v>106.2200012207031</v>
       </c>
       <c r="F247" t="n">
-        <v>8728700</v>
+        <v>7033700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B248" t="n">
-        <v>107.2399978637695</v>
+        <v>106.7099990844727</v>
       </c>
       <c r="C248" t="n">
-        <v>108.9499969482422</v>
+        <v>108.9899978637695</v>
       </c>
       <c r="D248" t="n">
-        <v>106.1399993896484</v>
+        <v>106.3300018310547</v>
       </c>
       <c r="E248" t="n">
-        <v>106.2200012207031</v>
+        <v>107.9800033569336</v>
       </c>
       <c r="F248" t="n">
-        <v>7033700</v>
+        <v>7555300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B249" t="n">
-        <v>106.7099990844727</v>
+        <v>108.620002746582</v>
       </c>
       <c r="C249" t="n">
-        <v>108.9899978637695</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="D249" t="n">
-        <v>106.3300018310547</v>
+        <v>106.9000015258789</v>
       </c>
       <c r="E249" t="n">
-        <v>107.9800033569336</v>
+        <v>107.1600036621094</v>
       </c>
       <c r="F249" t="n">
-        <v>7555300</v>
+        <v>6241300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B250" t="n">
-        <v>108.620002746582</v>
+        <v>106.4899978637695</v>
       </c>
       <c r="C250" t="n">
-        <v>109.1999969482422</v>
+        <v>106.879997253418</v>
       </c>
       <c r="D250" t="n">
-        <v>106.9000015258789</v>
+        <v>105.1699981689453</v>
       </c>
       <c r="E250" t="n">
-        <v>107.1600036621094</v>
+        <v>105.3099975585938</v>
       </c>
       <c r="F250" t="n">
-        <v>6241300</v>
+        <v>6103700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B251" t="n">
-        <v>106.4899978637695</v>
+        <v>104.6800003051758</v>
       </c>
       <c r="C251" t="n">
-        <v>106.879997253418</v>
+        <v>105.1100006103516</v>
       </c>
       <c r="D251" t="n">
-        <v>105.1699981689453</v>
+        <v>103.7099990844727</v>
       </c>
       <c r="E251" t="n">
-        <v>105.3099975585938</v>
+        <v>105.0599975585938</v>
       </c>
       <c r="F251" t="n">
-        <v>6103700</v>
+        <v>7395400</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46274</v>
+      </c>
+      <c r="B252" t="n">
+        <v>104.4499969482422</v>
+      </c>
+      <c r="C252" t="n">
+        <v>104.9300003051758</v>
+      </c>
+      <c r="D252" t="n">
+        <v>102.9899978637695</v>
+      </c>
+      <c r="E252" t="n">
+        <v>104.1800003051758</v>
+      </c>
       <c r="F252" t="n">
-        <v>7332699</v>
+        <v>7038100</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -11120,40 +11128,40 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>104.18</v>
+      </c>
+      <c r="D2" t="n">
         <v>105.06</v>
       </c>
-      <c r="D2" t="n">
-        <v>105.31</v>
-      </c>
       <c r="E2" t="n">
-        <v>104.68</v>
+        <v>104.45</v>
       </c>
       <c r="F2" t="n">
-        <v>105.1</v>
+        <v>104.93</v>
       </c>
       <c r="G2" t="n">
-        <v>103.71</v>
+        <v>102.99</v>
       </c>
       <c r="H2" t="n">
-        <v>7332699</v>
+        <v>7036870</v>
       </c>
       <c r="I2" t="n">
-        <v>10420983</v>
+        <v>10456372</v>
       </c>
       <c r="J2" t="n">
-        <v>181405712384</v>
+        <v>179886243840</v>
       </c>
       <c r="K2" t="n">
-        <v>21.661856</v>
+        <v>21.659044</v>
       </c>
       <c r="L2" t="n">
-        <v>14.055394</v>
+        <v>13.937665</v>
       </c>
       <c r="M2" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="N2" t="n">
-        <v>119.05</v>
+        <v>117.17</v>
       </c>
       <c r="O2" t="n">
         <v>92.19</v>
@@ -11162,7 +11170,7 @@
         <v>1.409</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R2" t="n">
         <v>0.08699000599999999</v>
@@ -11186,7 +11194,7 @@
         <v>63.602</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.6518347</v>
+        <v>1.6379988</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.483</v>
@@ -11198,7 +11206,7 @@
         <v>98860998656</v>
       </c>
       <c r="AC2" t="n">
-        <v>229071732736</v>
+        <v>227552247808</v>
       </c>
       <c r="AD2" t="n">
         <v>20963000320</v>
@@ -11225,7 +11233,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15:36</t>
+          <t>2026-09-10 18:59:54</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B2" t="n">
-        <v>115.1821357107481</v>
+        <v>113.8021202611286</v>
       </c>
       <c r="C2" t="n">
-        <v>115.8327187862414</v>
+        <v>115.4975710271905</v>
       </c>
       <c r="D2" t="n">
-        <v>112.8656800265299</v>
+        <v>112.9938248401568</v>
       </c>
       <c r="E2" t="n">
-        <v>114.1372680664062</v>
+        <v>115.4088592529297</v>
       </c>
       <c r="F2" t="n">
-        <v>7484900</v>
+        <v>8399100</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B3" t="n">
-        <v>113.8021202611286</v>
+        <v>114.6005686850037</v>
       </c>
       <c r="C3" t="n">
-        <v>115.4975710271905</v>
+        <v>115.3398635838033</v>
       </c>
       <c r="D3" t="n">
-        <v>112.9938248401568</v>
+        <v>113.4571222983551</v>
       </c>
       <c r="E3" t="n">
-        <v>115.4088592529297</v>
+        <v>114.3048477172852</v>
       </c>
       <c r="F3" t="n">
-        <v>8399100</v>
+        <v>7640900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>114.6005686850037</v>
+        <v>114.452707566448</v>
       </c>
       <c r="C4" t="n">
-        <v>115.3398635838033</v>
+        <v>115.0835719416188</v>
       </c>
       <c r="D4" t="n">
-        <v>113.4571222983551</v>
+        <v>113.3585505206524</v>
       </c>
       <c r="E4" t="n">
-        <v>114.3048477172852</v>
+        <v>113.9697036743164</v>
       </c>
       <c r="F4" t="n">
-        <v>7640900</v>
+        <v>7150900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>114.452707566448</v>
+        <v>113.8021272666058</v>
       </c>
       <c r="C5" t="n">
-        <v>115.0835719416188</v>
+        <v>114.196419390973</v>
       </c>
       <c r="D5" t="n">
-        <v>113.3585505206524</v>
+        <v>113.0726917248494</v>
       </c>
       <c r="E5" t="n">
-        <v>113.9697036743164</v>
+        <v>113.5852737426758</v>
       </c>
       <c r="F5" t="n">
-        <v>7150900</v>
+        <v>6844900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>113.8021272666058</v>
+        <v>113.595115218382</v>
       </c>
       <c r="C6" t="n">
-        <v>114.196419390973</v>
+        <v>114.9948525080674</v>
       </c>
       <c r="D6" t="n">
-        <v>113.0726917248494</v>
+        <v>113.5754039981875</v>
       </c>
       <c r="E6" t="n">
-        <v>113.5852737426758</v>
+        <v>114.4428405761719</v>
       </c>
       <c r="F6" t="n">
-        <v>6844900</v>
+        <v>7333900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>113.595115218382</v>
+        <v>113.6838355517382</v>
       </c>
       <c r="C7" t="n">
-        <v>114.9948525080674</v>
+        <v>114.1274094548904</v>
       </c>
       <c r="D7" t="n">
-        <v>113.5754039981875</v>
+        <v>112.4221068738425</v>
       </c>
       <c r="E7" t="n">
-        <v>114.4428405761719</v>
+        <v>113.2205429077148</v>
       </c>
       <c r="F7" t="n">
-        <v>7333900</v>
+        <v>9460500</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B8" t="n">
-        <v>113.6838355517382</v>
+        <v>112.9642523554146</v>
       </c>
       <c r="C8" t="n">
-        <v>114.1274094548904</v>
+        <v>112.9642523554146</v>
       </c>
       <c r="D8" t="n">
-        <v>112.4221068738425</v>
+        <v>110.3323644761722</v>
       </c>
       <c r="E8" t="n">
-        <v>113.2205429077148</v>
+        <v>112.1362457275391</v>
       </c>
       <c r="F8" t="n">
-        <v>9460500</v>
+        <v>23398400</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>112.9642523554146</v>
+        <v>110.1647924763258</v>
       </c>
       <c r="C9" t="n">
-        <v>112.9642523554146</v>
+        <v>112.0080961635035</v>
       </c>
       <c r="D9" t="n">
-        <v>110.3323644761722</v>
+        <v>109.9282127085895</v>
       </c>
       <c r="E9" t="n">
-        <v>112.1362457275391</v>
+        <v>110.953369140625</v>
       </c>
       <c r="F9" t="n">
-        <v>23398400</v>
+        <v>15479800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>110.1647924763258</v>
+        <v>111.1110969379416</v>
       </c>
       <c r="C10" t="n">
-        <v>112.0080961635035</v>
+        <v>111.9982523292055</v>
       </c>
       <c r="D10" t="n">
-        <v>109.9282127085895</v>
+        <v>110.0070805043135</v>
       </c>
       <c r="E10" t="n">
-        <v>110.953369140625</v>
+        <v>110.6478042602539</v>
       </c>
       <c r="F10" t="n">
-        <v>15479800</v>
+        <v>13145000</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>111.1110969379416</v>
+        <v>110.8055211263376</v>
       </c>
       <c r="C11" t="n">
-        <v>111.9982523292055</v>
+        <v>112.5206831561622</v>
       </c>
       <c r="D11" t="n">
-        <v>110.0070805043135</v>
+        <v>110.5985119402154</v>
       </c>
       <c r="E11" t="n">
-        <v>110.6478042602539</v>
+        <v>111.8109588623047</v>
       </c>
       <c r="F11" t="n">
-        <v>13145000</v>
+        <v>8755200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>110.8055211263376</v>
+        <v>111.1012331951749</v>
       </c>
       <c r="C12" t="n">
-        <v>112.5206831561622</v>
+        <v>112.4221106191933</v>
       </c>
       <c r="D12" t="n">
-        <v>110.5985119402154</v>
+        <v>111.0420920115833</v>
       </c>
       <c r="E12" t="n">
-        <v>111.8109588623047</v>
+        <v>111.3772354125977</v>
       </c>
       <c r="F12" t="n">
-        <v>8755200</v>
+        <v>6365500</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B13" t="n">
-        <v>111.1012331951749</v>
+        <v>111.5152366513407</v>
       </c>
       <c r="C13" t="n">
-        <v>112.4221106191933</v>
+        <v>111.9489587195086</v>
       </c>
       <c r="D13" t="n">
-        <v>111.0420920115833</v>
+        <v>111.1505226581053</v>
       </c>
       <c r="E13" t="n">
-        <v>111.3772354125977</v>
+        <v>111.8503875732422</v>
       </c>
       <c r="F13" t="n">
-        <v>6365500</v>
+        <v>6145700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>111.5152366513407</v>
+        <v>111.8503861885936</v>
       </c>
       <c r="C14" t="n">
-        <v>111.9489587195086</v>
+        <v>113.3684058878927</v>
       </c>
       <c r="D14" t="n">
-        <v>111.1505226581053</v>
+        <v>111.7123850814297</v>
       </c>
       <c r="E14" t="n">
-        <v>111.8503875732422</v>
+        <v>113.1416854858398</v>
       </c>
       <c r="F14" t="n">
-        <v>6145700</v>
+        <v>9304100</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>111.8503861885936</v>
+        <v>112.8952551010659</v>
       </c>
       <c r="C15" t="n">
-        <v>113.3684058878927</v>
+        <v>113.2402578727591</v>
       </c>
       <c r="D15" t="n">
-        <v>111.7123850814297</v>
+        <v>111.7222381568123</v>
       </c>
       <c r="E15" t="n">
-        <v>113.1416854858398</v>
+        <v>112.8656845092773</v>
       </c>
       <c r="F15" t="n">
-        <v>9304100</v>
+        <v>9303700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>112.8952551010659</v>
+        <v>112.4516824751333</v>
       </c>
       <c r="C16" t="n">
-        <v>113.2402578727591</v>
+        <v>114.4034167605612</v>
       </c>
       <c r="D16" t="n">
-        <v>111.7222381568123</v>
+        <v>111.1800943701441</v>
       </c>
       <c r="E16" t="n">
-        <v>112.8656845092773</v>
+        <v>111.3378067016602</v>
       </c>
       <c r="F16" t="n">
-        <v>9303700</v>
+        <v>9736300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>112.4516824751333</v>
+        <v>111.3673818357084</v>
       </c>
       <c r="C17" t="n">
-        <v>114.4034167605612</v>
+        <v>111.5546647543437</v>
       </c>
       <c r="D17" t="n">
-        <v>111.1800943701441</v>
+        <v>109.1987790515154</v>
       </c>
       <c r="E17" t="n">
-        <v>111.3378067016602</v>
+        <v>110.5393676757812</v>
       </c>
       <c r="F17" t="n">
-        <v>9736300</v>
+        <v>8695100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B18" t="n">
-        <v>111.3673818357084</v>
+        <v>110.4407994688091</v>
       </c>
       <c r="C18" t="n">
-        <v>111.5546647543437</v>
+        <v>111.9489598311001</v>
       </c>
       <c r="D18" t="n">
-        <v>109.1987790515154</v>
+        <v>109.9676474333371</v>
       </c>
       <c r="E18" t="n">
-        <v>110.5393676757812</v>
+        <v>110.8646621704102</v>
       </c>
       <c r="F18" t="n">
-        <v>8695100</v>
+        <v>7148400</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>110.4407994688091</v>
+        <v>111.0815219633868</v>
       </c>
       <c r="C19" t="n">
-        <v>111.9489598311001</v>
+        <v>111.4955252894808</v>
       </c>
       <c r="D19" t="n">
-        <v>109.9676474333371</v>
+        <v>109.8592156856383</v>
       </c>
       <c r="E19" t="n">
-        <v>110.8646621704102</v>
+        <v>111.1406631469727</v>
       </c>
       <c r="F19" t="n">
-        <v>7148400</v>
+        <v>6141200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>111.0815219633868</v>
+        <v>111.0223763857341</v>
       </c>
       <c r="C20" t="n">
-        <v>111.4955252894808</v>
+        <v>111.7813900254436</v>
       </c>
       <c r="D20" t="n">
-        <v>109.8592156856383</v>
+        <v>110.20422908127</v>
       </c>
       <c r="E20" t="n">
-        <v>111.1406631469727</v>
+        <v>110.9238052368164</v>
       </c>
       <c r="F20" t="n">
-        <v>6141200</v>
+        <v>5409800</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>111.0223763857341</v>
+        <v>111.1998048136618</v>
       </c>
       <c r="C21" t="n">
-        <v>111.7813900254436</v>
+        <v>111.584237549633</v>
       </c>
       <c r="D21" t="n">
-        <v>110.20422908127</v>
+        <v>110.0563659765542</v>
       </c>
       <c r="E21" t="n">
-        <v>110.9238052368164</v>
+        <v>110.2929382324219</v>
       </c>
       <c r="F21" t="n">
-        <v>5409800</v>
+        <v>7074400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>111.1998048136618</v>
+        <v>110.2239317389327</v>
       </c>
       <c r="C22" t="n">
-        <v>111.584237549633</v>
+        <v>111.3870892549816</v>
       </c>
       <c r="D22" t="n">
-        <v>110.0563659765542</v>
+        <v>109.2973464660052</v>
       </c>
       <c r="E22" t="n">
-        <v>110.2929382324219</v>
+        <v>109.4057769775391</v>
       </c>
       <c r="F22" t="n">
-        <v>7074400</v>
+        <v>6502400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B23" t="n">
-        <v>110.2239317389327</v>
+        <v>109.9380737221385</v>
       </c>
       <c r="C23" t="n">
-        <v>111.3870892549816</v>
+        <v>111.0716606845381</v>
       </c>
       <c r="D23" t="n">
-        <v>109.2973464660052</v>
+        <v>107.5526174321997</v>
       </c>
       <c r="E23" t="n">
-        <v>109.4057769775391</v>
+        <v>107.631477355957</v>
       </c>
       <c r="F23" t="n">
-        <v>6502400</v>
+        <v>9635200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>109.9380737221385</v>
+        <v>108.8143500705835</v>
       </c>
       <c r="C24" t="n">
-        <v>111.0716606845381</v>
+        <v>109.3762138868319</v>
       </c>
       <c r="D24" t="n">
-        <v>107.5526174321997</v>
+        <v>107.8187641784603</v>
       </c>
       <c r="E24" t="n">
-        <v>107.631477355957</v>
+        <v>108.6960601806641</v>
       </c>
       <c r="F24" t="n">
-        <v>9635200</v>
+        <v>7435100</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>108.8143500705835</v>
+        <v>108.0849128268841</v>
       </c>
       <c r="C25" t="n">
-        <v>109.3762138868319</v>
+        <v>110.2436487598859</v>
       </c>
       <c r="D25" t="n">
-        <v>107.8187641784603</v>
+        <v>107.641331387133</v>
       </c>
       <c r="E25" t="n">
-        <v>108.6960601806641</v>
+        <v>109.5832138061523</v>
       </c>
       <c r="F25" t="n">
-        <v>7435100</v>
+        <v>7898000</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>108.0849128268841</v>
+        <v>109.8789291603083</v>
       </c>
       <c r="C26" t="n">
-        <v>110.2436487598859</v>
+        <v>111.0716572685961</v>
       </c>
       <c r="D26" t="n">
-        <v>107.641331387133</v>
+        <v>109.5536376251855</v>
       </c>
       <c r="E26" t="n">
-        <v>109.5832138061523</v>
+        <v>110.1155014038086</v>
       </c>
       <c r="F26" t="n">
-        <v>7898000</v>
+        <v>7012600</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>109.8789291603083</v>
+        <v>110.1943638011324</v>
       </c>
       <c r="C27" t="n">
-        <v>111.0716572685961</v>
+        <v>110.4900772320282</v>
       </c>
       <c r="D27" t="n">
-        <v>109.5536376251855</v>
+        <v>106.9611821588295</v>
       </c>
       <c r="E27" t="n">
-        <v>110.1155014038086</v>
+        <v>108.3116226196289</v>
       </c>
       <c r="F27" t="n">
-        <v>7012600</v>
+        <v>7531200</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B28" t="n">
-        <v>110.1943638011324</v>
+        <v>108.1736213665725</v>
       </c>
       <c r="C28" t="n">
-        <v>110.4900772320282</v>
+        <v>109.8690721085103</v>
       </c>
       <c r="D28" t="n">
-        <v>106.9611821588295</v>
+        <v>107.877907936081</v>
       </c>
       <c r="E28" t="n">
-        <v>108.3116226196289</v>
+        <v>109.0903472900391</v>
       </c>
       <c r="F28" t="n">
-        <v>7531200</v>
+        <v>10090500</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>108.1736213665725</v>
+        <v>109.4452125270959</v>
       </c>
       <c r="C29" t="n">
-        <v>109.8690721085103</v>
+        <v>110.6478000651592</v>
       </c>
       <c r="D29" t="n">
-        <v>107.877907936081</v>
+        <v>109.0213498295899</v>
       </c>
       <c r="E29" t="n">
-        <v>109.0903472900391</v>
+        <v>110.3619384765625</v>
       </c>
       <c r="F29" t="n">
-        <v>10090500</v>
+        <v>8047500</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>109.4452125270959</v>
+        <v>110.6477986393913</v>
       </c>
       <c r="C30" t="n">
-        <v>110.6478000651592</v>
+        <v>112.9051132067436</v>
       </c>
       <c r="D30" t="n">
-        <v>109.0213498295899</v>
+        <v>110.4407969786948</v>
       </c>
       <c r="E30" t="n">
-        <v>110.3619384765625</v>
+        <v>112.6685409545898</v>
       </c>
       <c r="F30" t="n">
-        <v>8047500</v>
+        <v>8163200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>110.6477986393913</v>
+        <v>112.3728165513869</v>
       </c>
       <c r="C31" t="n">
-        <v>112.9051132067436</v>
+        <v>112.6488187571811</v>
       </c>
       <c r="D31" t="n">
-        <v>110.4407969786948</v>
+        <v>111.3673788702085</v>
       </c>
       <c r="E31" t="n">
-        <v>112.6685409545898</v>
+        <v>111.465950012207</v>
       </c>
       <c r="F31" t="n">
-        <v>8163200</v>
+        <v>7569200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>112.3728165513869</v>
+        <v>111.5546652306962</v>
       </c>
       <c r="C32" t="n">
-        <v>112.6488187571811</v>
+        <v>112.2052483248811</v>
       </c>
       <c r="D32" t="n">
-        <v>111.3673788702085</v>
+        <v>110.3027958955931</v>
       </c>
       <c r="E32" t="n">
-        <v>111.465950012207</v>
+        <v>111.4166641235352</v>
       </c>
       <c r="F32" t="n">
-        <v>7569200</v>
+        <v>6945400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B33" t="n">
-        <v>111.5546652306962</v>
+        <v>111.6138166065038</v>
       </c>
       <c r="C33" t="n">
-        <v>112.2052483248811</v>
+        <v>112.0278199378997</v>
       </c>
       <c r="D33" t="n">
-        <v>110.3027958955931</v>
+        <v>109.9972182029886</v>
       </c>
       <c r="E33" t="n">
-        <v>111.4166641235352</v>
+        <v>110.0859375</v>
       </c>
       <c r="F33" t="n">
-        <v>6945400</v>
+        <v>6235200</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>111.6138166065038</v>
+        <v>110.34222664747</v>
       </c>
       <c r="C34" t="n">
-        <v>112.0278199378997</v>
+        <v>110.992802225815</v>
       </c>
       <c r="D34" t="n">
-        <v>109.9972182029886</v>
+        <v>109.721214140304</v>
       </c>
       <c r="E34" t="n">
-        <v>110.0859375</v>
+        <v>110.7365112304688</v>
       </c>
       <c r="F34" t="n">
-        <v>6235200</v>
+        <v>6029600</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>110.34222664747</v>
+        <v>110.3126569642538</v>
       </c>
       <c r="C35" t="n">
-        <v>110.992802225815</v>
+        <v>110.8745207722</v>
       </c>
       <c r="D35" t="n">
-        <v>109.721214140304</v>
+        <v>109.8690755239826</v>
       </c>
       <c r="E35" t="n">
-        <v>110.7365112304688</v>
+        <v>110.0563659667969</v>
       </c>
       <c r="F35" t="n">
-        <v>6029600</v>
+        <v>6839400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>110.3126569642538</v>
+        <v>109.5930739758994</v>
       </c>
       <c r="C36" t="n">
-        <v>110.8745207722</v>
+        <v>109.9380767512234</v>
       </c>
       <c r="D36" t="n">
-        <v>109.8690755239826</v>
+        <v>108.4397757610322</v>
       </c>
       <c r="E36" t="n">
-        <v>110.0563659667969</v>
+        <v>108.6664886474609</v>
       </c>
       <c r="F36" t="n">
-        <v>6839400</v>
+        <v>7097100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>109.5930739758994</v>
+        <v>108.5580608670909</v>
       </c>
       <c r="C37" t="n">
-        <v>109.9380767512234</v>
+        <v>111.9588219337512</v>
       </c>
       <c r="D37" t="n">
-        <v>108.4397757610322</v>
+        <v>107.9863451909205</v>
       </c>
       <c r="E37" t="n">
-        <v>108.6664886474609</v>
+        <v>110.24365234375</v>
       </c>
       <c r="F37" t="n">
-        <v>7097100</v>
+        <v>8311300</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B38" t="n">
-        <v>108.5580608670909</v>
+        <v>109.9873709449201</v>
       </c>
       <c r="C38" t="n">
-        <v>111.9588219337512</v>
+        <v>111.4856720013147</v>
       </c>
       <c r="D38" t="n">
-        <v>107.9863451909205</v>
+        <v>108.9523550527189</v>
       </c>
       <c r="E38" t="n">
-        <v>110.24365234375</v>
+        <v>111.0125274658203</v>
       </c>
       <c r="F38" t="n">
-        <v>8311300</v>
+        <v>8700600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B39" t="n">
-        <v>109.9873709449201</v>
+        <v>110.9435236572715</v>
       </c>
       <c r="C39" t="n">
-        <v>111.4856720013147</v>
+        <v>111.1998071396153</v>
       </c>
       <c r="D39" t="n">
-        <v>108.9523550527189</v>
+        <v>109.4452151242777</v>
       </c>
       <c r="E39" t="n">
-        <v>111.0125274658203</v>
+        <v>110.519660949707</v>
       </c>
       <c r="F39" t="n">
-        <v>8700600</v>
+        <v>8542300</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B40" t="n">
-        <v>110.9435236572715</v>
+        <v>109.3860735058741</v>
       </c>
       <c r="C40" t="n">
-        <v>111.1998071396153</v>
+        <v>110.1943689542488</v>
       </c>
       <c r="D40" t="n">
-        <v>109.4452151242777</v>
+        <v>109.0607819482302</v>
       </c>
       <c r="E40" t="n">
-        <v>110.519660949707</v>
+        <v>109.8789367675781</v>
       </c>
       <c r="F40" t="n">
-        <v>8542300</v>
+        <v>7950100</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B41" t="n">
-        <v>109.3860735058741</v>
+        <v>109.7606408126771</v>
       </c>
       <c r="C41" t="n">
-        <v>110.1943689542488</v>
+        <v>110.3717939308002</v>
       </c>
       <c r="D41" t="n">
-        <v>109.0607819482302</v>
+        <v>109.0213459609701</v>
       </c>
       <c r="E41" t="n">
-        <v>109.8789367675781</v>
+        <v>109.7705001831055</v>
       </c>
       <c r="F41" t="n">
-        <v>7950100</v>
+        <v>5746000</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B42" t="n">
-        <v>109.7606408126771</v>
+        <v>109.5832124067878</v>
       </c>
       <c r="C42" t="n">
-        <v>110.3717939308002</v>
+        <v>110.115505615394</v>
       </c>
       <c r="D42" t="n">
-        <v>109.0213459609701</v>
+        <v>107.6216187917271</v>
       </c>
       <c r="E42" t="n">
-        <v>109.7705001831055</v>
+        <v>108.9129180908203</v>
       </c>
       <c r="F42" t="n">
-        <v>5746000</v>
+        <v>10291800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B43" t="n">
-        <v>109.5832124067878</v>
+        <v>108.6862106348567</v>
       </c>
       <c r="C43" t="n">
-        <v>110.115505615394</v>
+        <v>109.8395088841645</v>
       </c>
       <c r="D43" t="n">
-        <v>107.6216187917271</v>
+        <v>108.4693495923209</v>
       </c>
       <c r="E43" t="n">
-        <v>108.9129180908203</v>
+        <v>109.1593551635742</v>
       </c>
       <c r="F43" t="n">
-        <v>10291800</v>
+        <v>8782100</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B44" t="n">
-        <v>108.6862106348567</v>
+        <v>109.5635011857433</v>
       </c>
       <c r="C44" t="n">
-        <v>109.8395088841645</v>
+        <v>111.1800920323978</v>
       </c>
       <c r="D44" t="n">
-        <v>108.4693495923209</v>
+        <v>109.4452112992212</v>
       </c>
       <c r="E44" t="n">
-        <v>109.1593551635742</v>
+        <v>110.637939453125</v>
       </c>
       <c r="F44" t="n">
-        <v>8782100</v>
+        <v>9158700</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B45" t="n">
-        <v>109.5635011857433</v>
+        <v>111.0420904629071</v>
       </c>
       <c r="C45" t="n">
-        <v>111.1800920323978</v>
+        <v>113.3289756160103</v>
       </c>
       <c r="D45" t="n">
-        <v>109.4452112992212</v>
+        <v>110.815370061474</v>
       </c>
       <c r="E45" t="n">
-        <v>110.637939453125</v>
+        <v>113.2106857299805</v>
       </c>
       <c r="F45" t="n">
-        <v>9158700</v>
+        <v>9713300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B46" t="n">
-        <v>111.0420904629071</v>
+        <v>112.9346876340564</v>
       </c>
       <c r="C46" t="n">
-        <v>113.3289756160103</v>
+        <v>115.4187151672819</v>
       </c>
       <c r="D46" t="n">
-        <v>110.815370061474</v>
+        <v>112.7572565587906</v>
       </c>
       <c r="E46" t="n">
-        <v>113.2106857299805</v>
+        <v>114.9850006103516</v>
       </c>
       <c r="F46" t="n">
-        <v>9713300</v>
+        <v>15248700</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B47" t="n">
-        <v>112.9346876340564</v>
+        <v>107.3357567169709</v>
       </c>
       <c r="C47" t="n">
-        <v>115.4187151672819</v>
+        <v>107.7990493697842</v>
       </c>
       <c r="D47" t="n">
-        <v>112.7572565587906</v>
+        <v>103.4125695047362</v>
       </c>
       <c r="E47" t="n">
-        <v>114.9850006103516</v>
+        <v>106.0740280151367</v>
       </c>
       <c r="F47" t="n">
-        <v>15248700</v>
+        <v>44045400</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B48" t="n">
-        <v>107.3357567169709</v>
+        <v>105.9853067984581</v>
       </c>
       <c r="C48" t="n">
-        <v>107.7990493697842</v>
+        <v>107.178042445792</v>
       </c>
       <c r="D48" t="n">
-        <v>103.4125695047362</v>
+        <v>103.797000351179</v>
       </c>
       <c r="E48" t="n">
-        <v>106.0740280151367</v>
+        <v>104.2898635864258</v>
       </c>
       <c r="F48" t="n">
-        <v>44045400</v>
+        <v>16691400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B49" t="n">
-        <v>105.9853067984581</v>
+        <v>104.2405758139031</v>
       </c>
       <c r="C49" t="n">
-        <v>107.178042445792</v>
+        <v>106.1331688606407</v>
       </c>
       <c r="D49" t="n">
-        <v>103.797000351179</v>
+        <v>103.6195708355819</v>
       </c>
       <c r="E49" t="n">
-        <v>104.2898635864258</v>
+        <v>104.1814346313477</v>
       </c>
       <c r="F49" t="n">
-        <v>16691400</v>
+        <v>12296400</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B50" t="n">
-        <v>104.2405758139031</v>
+        <v>103.5998505812639</v>
       </c>
       <c r="C50" t="n">
-        <v>106.1331688606407</v>
+        <v>105.5515923025468</v>
       </c>
       <c r="D50" t="n">
-        <v>103.6195708355819</v>
+        <v>103.501279438279</v>
       </c>
       <c r="E50" t="n">
-        <v>104.1814346313477</v>
+        <v>104.7630081176758</v>
       </c>
       <c r="F50" t="n">
-        <v>12296400</v>
+        <v>11796200</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B51" t="n">
-        <v>103.5998505812639</v>
+        <v>104.5658651685615</v>
       </c>
       <c r="C51" t="n">
-        <v>105.5515923025468</v>
+        <v>106.0543067153343</v>
       </c>
       <c r="D51" t="n">
-        <v>103.501279438279</v>
+        <v>102.5944122393827</v>
       </c>
       <c r="E51" t="n">
-        <v>104.7630081176758</v>
+        <v>103.1759872436523</v>
       </c>
       <c r="F51" t="n">
-        <v>11796200</v>
+        <v>12790000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B52" t="n">
-        <v>104.5658651685615</v>
+        <v>103.8660034269339</v>
       </c>
       <c r="C52" t="n">
-        <v>106.0543067153343</v>
+        <v>104.2898661203646</v>
       </c>
       <c r="D52" t="n">
-        <v>102.5944122393827</v>
+        <v>101.0369656805012</v>
       </c>
       <c r="E52" t="n">
-        <v>103.1759872436523</v>
+        <v>101.2341079711914</v>
       </c>
       <c r="F52" t="n">
-        <v>12790000</v>
+        <v>12609900</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B53" t="n">
-        <v>103.8660034269339</v>
+        <v>102.0029806312501</v>
       </c>
       <c r="C53" t="n">
-        <v>104.2898661203646</v>
+        <v>103.2844205576738</v>
       </c>
       <c r="D53" t="n">
-        <v>101.0369656805012</v>
+        <v>101.2242558006444</v>
       </c>
       <c r="E53" t="n">
-        <v>101.2341079711914</v>
+        <v>102.7915573120117</v>
       </c>
       <c r="F53" t="n">
-        <v>12609900</v>
+        <v>10785400</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B54" t="n">
-        <v>102.0029806312501</v>
+        <v>102.6042684356238</v>
       </c>
       <c r="C54" t="n">
-        <v>103.2844205576738</v>
+        <v>102.85070006221</v>
       </c>
       <c r="D54" t="n">
-        <v>101.2242558006444</v>
+        <v>100.4356731298631</v>
       </c>
       <c r="E54" t="n">
-        <v>102.7915573120117</v>
+        <v>100.4849624633789</v>
       </c>
       <c r="F54" t="n">
-        <v>10785400</v>
+        <v>15024800</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B55" t="n">
-        <v>102.6042684356238</v>
+        <v>101.0271004353643</v>
       </c>
       <c r="C55" t="n">
-        <v>102.85070006221</v>
+        <v>102.4366895412752</v>
       </c>
       <c r="D55" t="n">
-        <v>100.4356731298631</v>
+        <v>100.5440965869111</v>
       </c>
       <c r="E55" t="n">
-        <v>100.4849624633789</v>
+        <v>101.8353958129883</v>
       </c>
       <c r="F55" t="n">
-        <v>15024800</v>
+        <v>10574500</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B56" t="n">
-        <v>101.0271004353643</v>
+        <v>101.8452666826232</v>
       </c>
       <c r="C56" t="n">
-        <v>102.4366895412752</v>
+        <v>102.7619926734798</v>
       </c>
       <c r="D56" t="n">
-        <v>100.5440965869111</v>
+        <v>101.4115445947565</v>
       </c>
       <c r="E56" t="n">
-        <v>101.8353958129883</v>
+        <v>101.9536972045898</v>
       </c>
       <c r="F56" t="n">
-        <v>10574500</v>
+        <v>10130200</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B57" t="n">
-        <v>101.8452666826232</v>
+        <v>101.8255530884873</v>
       </c>
       <c r="C57" t="n">
-        <v>102.7619926734798</v>
+        <v>103.2449941712158</v>
       </c>
       <c r="D57" t="n">
-        <v>101.4115445947565</v>
+        <v>101.7664043830219</v>
       </c>
       <c r="E57" t="n">
-        <v>101.9536972045898</v>
+        <v>102.9788513183594</v>
       </c>
       <c r="F57" t="n">
-        <v>10130200</v>
+        <v>6525500</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>101.8255530884873</v>
+        <v>103.4224248942611</v>
       </c>
       <c r="C58" t="n">
-        <v>103.2449941712158</v>
+        <v>105.3051661613186</v>
       </c>
       <c r="D58" t="n">
-        <v>101.7664043830219</v>
+        <v>102.9788509675128</v>
       </c>
       <c r="E58" t="n">
-        <v>102.9788513183594</v>
+        <v>105.2460174560547</v>
       </c>
       <c r="F58" t="n">
-        <v>6525500</v>
+        <v>12628900</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>103.4224248942611</v>
+        <v>105.0094494941518</v>
       </c>
       <c r="C59" t="n">
-        <v>105.3051661613186</v>
+        <v>105.0488794591093</v>
       </c>
       <c r="D59" t="n">
-        <v>102.9788509675128</v>
+        <v>103.3238579748278</v>
       </c>
       <c r="E59" t="n">
-        <v>105.2460174560547</v>
+        <v>103.3337173461914</v>
       </c>
       <c r="F59" t="n">
-        <v>12628900</v>
+        <v>8548200</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>105.0094494941518</v>
+        <v>103.4027138498727</v>
       </c>
       <c r="C60" t="n">
-        <v>105.0488794591093</v>
+        <v>104.3391510392764</v>
       </c>
       <c r="D60" t="n">
-        <v>103.3238579748278</v>
+        <v>102.9788511438223</v>
       </c>
       <c r="E60" t="n">
-        <v>103.3337173461914</v>
+        <v>104.2307205200195</v>
       </c>
       <c r="F60" t="n">
-        <v>8548200</v>
+        <v>10177800</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>103.4027138498727</v>
+        <v>104.3292907185565</v>
       </c>
       <c r="C61" t="n">
-        <v>104.3391510392764</v>
+        <v>104.7038716073053</v>
       </c>
       <c r="D61" t="n">
-        <v>102.9788511438223</v>
+        <v>103.0182801694252</v>
       </c>
       <c r="E61" t="n">
-        <v>104.2307205200195</v>
+        <v>103.9645767211914</v>
       </c>
       <c r="F61" t="n">
-        <v>10177800</v>
+        <v>11471400</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B62" t="n">
-        <v>104.3292907185565</v>
+        <v>103.6787148109135</v>
       </c>
       <c r="C62" t="n">
-        <v>104.7038716073053</v>
+        <v>104.6545819518468</v>
       </c>
       <c r="D62" t="n">
-        <v>103.0182801694252</v>
+        <v>103.0675616662248</v>
       </c>
       <c r="E62" t="n">
-        <v>103.9645767211914</v>
+        <v>103.797004699707</v>
       </c>
       <c r="F62" t="n">
-        <v>11471400</v>
+        <v>10680100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>103.6787148109135</v>
+        <v>103.7970053004195</v>
       </c>
       <c r="C63" t="n">
-        <v>104.6545819518468</v>
+        <v>106.5077532235307</v>
       </c>
       <c r="D63" t="n">
-        <v>103.0675616662248</v>
+        <v>103.3337126339174</v>
       </c>
       <c r="E63" t="n">
-        <v>103.797004699707</v>
+        <v>106.0937423706055</v>
       </c>
       <c r="F63" t="n">
-        <v>10680100</v>
+        <v>13727700</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>103.7970053004195</v>
+        <v>106.0543107045445</v>
       </c>
       <c r="C64" t="n">
-        <v>106.5077532235307</v>
+        <v>106.2120305546496</v>
       </c>
       <c r="D64" t="n">
-        <v>103.3337126339174</v>
+        <v>105.0291617608474</v>
       </c>
       <c r="E64" t="n">
-        <v>106.0937423706055</v>
+        <v>105.4924468994141</v>
       </c>
       <c r="F64" t="n">
-        <v>13727700</v>
+        <v>8549400</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>106.0543107045445</v>
+        <v>105.5910275110776</v>
       </c>
       <c r="C65" t="n">
-        <v>106.2120305546496</v>
+        <v>108.1046256243346</v>
       </c>
       <c r="D65" t="n">
-        <v>105.0291617608474</v>
+        <v>105.0587342879123</v>
       </c>
       <c r="E65" t="n">
-        <v>105.4924468994141</v>
+        <v>107.2766189575195</v>
       </c>
       <c r="F65" t="n">
-        <v>8549400</v>
+        <v>11237900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>105.5910275110776</v>
+        <v>107.6413280220333</v>
       </c>
       <c r="C66" t="n">
-        <v>108.1046256243346</v>
+        <v>109.9676431038136</v>
       </c>
       <c r="D66" t="n">
-        <v>105.0587342879123</v>
+        <v>107.5526162491543</v>
       </c>
       <c r="E66" t="n">
-        <v>107.2766189575195</v>
+        <v>109.8690719604492</v>
       </c>
       <c r="F66" t="n">
-        <v>11237900</v>
+        <v>13281400</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B67" t="n">
-        <v>107.6413280220333</v>
+        <v>110.1352217028325</v>
       </c>
       <c r="C67" t="n">
-        <v>109.9676431038136</v>
+        <v>111.7222343992454</v>
       </c>
       <c r="D67" t="n">
-        <v>107.5526162491543</v>
+        <v>109.5634985458288</v>
       </c>
       <c r="E67" t="n">
-        <v>109.8690719604492</v>
+        <v>110.0070724487305</v>
       </c>
       <c r="F67" t="n">
-        <v>13281400</v>
+        <v>13059100</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,25 +2185,25 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>110.1352217028325</v>
+        <v>109.8582130022918</v>
       </c>
       <c r="C68" t="n">
-        <v>111.7222343992454</v>
+        <v>110.7017554968497</v>
       </c>
       <c r="D68" t="n">
-        <v>109.5634985458288</v>
+        <v>107.7245680705396</v>
       </c>
       <c r="E68" t="n">
-        <v>110.0070724487305</v>
+        <v>109.6498107910156</v>
       </c>
       <c r="F68" t="n">
-        <v>13059100</v>
+        <v>14318000</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2211,25 +2211,25 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>109.8582130022918</v>
+        <v>110.3742651303662</v>
       </c>
       <c r="C69" t="n">
-        <v>110.7017554968497</v>
+        <v>111.991867603266</v>
       </c>
       <c r="D69" t="n">
-        <v>107.7245680705396</v>
+        <v>110.0170020268064</v>
       </c>
       <c r="E69" t="n">
-        <v>109.6498107910156</v>
+        <v>110.7712249755859</v>
       </c>
       <c r="F69" t="n">
-        <v>14318000</v>
+        <v>15580200</v>
       </c>
       <c r="G69" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>110.3742651303662</v>
+        <v>110.2154802113721</v>
       </c>
       <c r="C70" t="n">
-        <v>111.991867603266</v>
+        <v>111.2773434635197</v>
       </c>
       <c r="D70" t="n">
-        <v>110.0170020268064</v>
+        <v>109.6200442181698</v>
       </c>
       <c r="E70" t="n">
-        <v>110.7712249755859</v>
+        <v>109.7887496948242</v>
       </c>
       <c r="F70" t="n">
-        <v>15580200</v>
+        <v>12142500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>110.2154802113721</v>
+        <v>109.6895108947102</v>
       </c>
       <c r="C71" t="n">
-        <v>111.2773434635197</v>
+        <v>111.9422536896534</v>
       </c>
       <c r="D71" t="n">
-        <v>109.6200442181698</v>
+        <v>109.5803467466885</v>
       </c>
       <c r="E71" t="n">
-        <v>109.7887496948242</v>
+        <v>111.0193252563477</v>
       </c>
       <c r="F71" t="n">
-        <v>12142500</v>
+        <v>12913900</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B72" t="n">
-        <v>109.6895108947102</v>
+        <v>111.4659009625997</v>
       </c>
       <c r="C72" t="n">
-        <v>111.9422536896534</v>
+        <v>112.6170837765976</v>
       </c>
       <c r="D72" t="n">
-        <v>109.5803467466885</v>
+        <v>110.076545265884</v>
       </c>
       <c r="E72" t="n">
-        <v>111.0193252563477</v>
+        <v>110.3941116333008</v>
       </c>
       <c r="F72" t="n">
-        <v>12913900</v>
+        <v>21138400</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>111.4659009625997</v>
+        <v>110.5628188428948</v>
       </c>
       <c r="C73" t="n">
-        <v>112.6170837765976</v>
+        <v>111.9422483883379</v>
       </c>
       <c r="D73" t="n">
-        <v>110.076545265884</v>
+        <v>110.3047938169375</v>
       </c>
       <c r="E73" t="n">
-        <v>110.3941116333008</v>
+        <v>111.5254364013672</v>
       </c>
       <c r="F73" t="n">
-        <v>21138400</v>
+        <v>8803300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>110.5628188428948</v>
+        <v>111.4361261613625</v>
       </c>
       <c r="C74" t="n">
-        <v>111.9422483883379</v>
+        <v>112.4483665538656</v>
       </c>
       <c r="D74" t="n">
-        <v>110.3047938169375</v>
+        <v>111.1880272094238</v>
       </c>
       <c r="E74" t="n">
-        <v>111.5254364013672</v>
+        <v>112.3590545654297</v>
       </c>
       <c r="F74" t="n">
-        <v>8803300</v>
+        <v>7634500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>111.4361261613625</v>
+        <v>112.0811837460467</v>
       </c>
       <c r="C75" t="n">
-        <v>112.4483665538656</v>
+        <v>113.6590894291559</v>
       </c>
       <c r="D75" t="n">
-        <v>111.1880272094238</v>
+        <v>111.9422489401646</v>
       </c>
       <c r="E75" t="n">
-        <v>112.3590545654297</v>
+        <v>113.6094741821289</v>
       </c>
       <c r="F75" t="n">
-        <v>7634500</v>
+        <v>4606700</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B76" t="n">
-        <v>112.0811837460467</v>
+        <v>113.2819819972415</v>
       </c>
       <c r="C76" t="n">
-        <v>113.6590894291559</v>
+        <v>113.8674918845297</v>
       </c>
       <c r="D76" t="n">
-        <v>111.9422489401646</v>
+        <v>112.4086688482299</v>
       </c>
       <c r="E76" t="n">
-        <v>113.6094741821289</v>
+        <v>112.6964645385742</v>
       </c>
       <c r="F76" t="n">
-        <v>4606700</v>
+        <v>5428900</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>113.2819819972415</v>
+        <v>112.4582910949776</v>
       </c>
       <c r="C77" t="n">
-        <v>113.8674918845297</v>
+        <v>113.6193923570513</v>
       </c>
       <c r="D77" t="n">
-        <v>112.4086688482299</v>
+        <v>112.4483650170496</v>
       </c>
       <c r="E77" t="n">
-        <v>112.6964645385742</v>
+        <v>113.3216781616211</v>
       </c>
       <c r="F77" t="n">
-        <v>5428900</v>
+        <v>7966000</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>112.4582910949776</v>
+        <v>113.2323587361736</v>
       </c>
       <c r="C78" t="n">
-        <v>113.6193923570513</v>
+        <v>114.4033860775522</v>
       </c>
       <c r="D78" t="n">
-        <v>112.4483650170496</v>
+        <v>113.2323587361736</v>
       </c>
       <c r="E78" t="n">
-        <v>113.3216781616211</v>
+        <v>113.9171142578125</v>
       </c>
       <c r="F78" t="n">
-        <v>7966000</v>
+        <v>6883900</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>113.2323587361736</v>
+        <v>113.8972648993226</v>
       </c>
       <c r="C79" t="n">
-        <v>114.4033860775522</v>
+        <v>114.0163551233871</v>
       </c>
       <c r="D79" t="n">
-        <v>113.2323587361736</v>
+        <v>112.6865483592072</v>
       </c>
       <c r="E79" t="n">
-        <v>113.9171142578125</v>
+        <v>112.9048690795898</v>
       </c>
       <c r="F79" t="n">
-        <v>6883900</v>
+        <v>6608000</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B80" t="n">
-        <v>113.8972648993226</v>
+        <v>112.5773868999257</v>
       </c>
       <c r="C80" t="n">
-        <v>114.0163551233871</v>
+        <v>112.5773868999257</v>
       </c>
       <c r="D80" t="n">
-        <v>112.6865483592072</v>
+        <v>110.7712267677642</v>
       </c>
       <c r="E80" t="n">
-        <v>112.9048690795898</v>
+        <v>110.9994735717773</v>
       </c>
       <c r="F80" t="n">
-        <v>6608000</v>
+        <v>8906200</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>112.5773868999257</v>
+        <v>110.5727405037633</v>
       </c>
       <c r="C81" t="n">
-        <v>112.5773868999257</v>
+        <v>115.1476858420111</v>
       </c>
       <c r="D81" t="n">
-        <v>110.7712267677642</v>
+        <v>110.5330437623775</v>
       </c>
       <c r="E81" t="n">
-        <v>110.9994735717773</v>
+        <v>113.2025909423828</v>
       </c>
       <c r="F81" t="n">
-        <v>8906200</v>
+        <v>12029000</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>110.5727405037633</v>
+        <v>112.9247239572814</v>
       </c>
       <c r="C82" t="n">
-        <v>115.1476858420111</v>
+        <v>113.8873491370408</v>
       </c>
       <c r="D82" t="n">
-        <v>110.5330437623775</v>
+        <v>112.2498944807456</v>
       </c>
       <c r="E82" t="n">
-        <v>113.2025909423828</v>
+        <v>113.6987915039062</v>
       </c>
       <c r="F82" t="n">
-        <v>12029000</v>
+        <v>7388300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>112.9247239572814</v>
+        <v>113.58962345171</v>
       </c>
       <c r="C83" t="n">
-        <v>113.8873491370408</v>
+        <v>114.0957474345631</v>
       </c>
       <c r="D83" t="n">
-        <v>112.2498944807456</v>
+        <v>111.6544546516531</v>
       </c>
       <c r="E83" t="n">
-        <v>113.6987915039062</v>
+        <v>112.0514144897461</v>
       </c>
       <c r="F83" t="n">
-        <v>7388300</v>
+        <v>8296300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>113.58962345171</v>
+        <v>111.6941501294552</v>
       </c>
       <c r="C84" t="n">
-        <v>114.0957474345631</v>
+        <v>114.1155907288179</v>
       </c>
       <c r="D84" t="n">
-        <v>111.6544546516531</v>
+        <v>111.6941501294552</v>
       </c>
       <c r="E84" t="n">
-        <v>112.0514144897461</v>
+        <v>113.3018264770508</v>
       </c>
       <c r="F84" t="n">
-        <v>8296300</v>
+        <v>9778200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B85" t="n">
-        <v>111.6941501294552</v>
+        <v>113.4407639362947</v>
       </c>
       <c r="C85" t="n">
-        <v>114.1155907288179</v>
+        <v>115.0980707124986</v>
       </c>
       <c r="D85" t="n">
-        <v>111.6941501294552</v>
+        <v>113.0338855865844</v>
       </c>
       <c r="E85" t="n">
-        <v>113.3018264770508</v>
+        <v>114.9988250732422</v>
       </c>
       <c r="F85" t="n">
-        <v>9778200</v>
+        <v>8935200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>113.4407639362947</v>
+        <v>113.7583311963079</v>
       </c>
       <c r="C86" t="n">
-        <v>115.0980707124986</v>
+        <v>114.0659790519541</v>
       </c>
       <c r="D86" t="n">
-        <v>113.0338855865844</v>
+        <v>111.6941536254426</v>
       </c>
       <c r="E86" t="n">
-        <v>114.9988250732422</v>
+        <v>111.9620971679688</v>
       </c>
       <c r="F86" t="n">
-        <v>8935200</v>
+        <v>10833800</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>113.7583311963079</v>
+        <v>111.9819377501375</v>
       </c>
       <c r="C87" t="n">
-        <v>114.0659790519541</v>
+        <v>112.3590529975045</v>
       </c>
       <c r="D87" t="n">
-        <v>111.6941536254426</v>
+        <v>110.7612951636049</v>
       </c>
       <c r="E87" t="n">
-        <v>111.9620971679688</v>
+        <v>112.1208801269531</v>
       </c>
       <c r="F87" t="n">
-        <v>10833800</v>
+        <v>8945700</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>111.9819377501375</v>
+        <v>111.9521684493894</v>
       </c>
       <c r="C88" t="n">
-        <v>112.3590529975045</v>
+        <v>112.7262359666306</v>
       </c>
       <c r="D88" t="n">
-        <v>110.7612951636049</v>
+        <v>111.4063552989297</v>
       </c>
       <c r="E88" t="n">
-        <v>112.1208801269531</v>
+        <v>112.6666946411133</v>
       </c>
       <c r="F88" t="n">
-        <v>8945700</v>
+        <v>8950900</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>111.9521684493894</v>
+        <v>112.8453292583326</v>
       </c>
       <c r="C89" t="n">
-        <v>112.7262359666306</v>
+        <v>113.242289105796</v>
       </c>
       <c r="D89" t="n">
-        <v>111.4063552989297</v>
+        <v>111.3170387669949</v>
       </c>
       <c r="E89" t="n">
-        <v>112.6666946411133</v>
+        <v>112.5476150512695</v>
       </c>
       <c r="F89" t="n">
-        <v>8950900</v>
+        <v>7958500</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B90" t="n">
-        <v>112.8453292583326</v>
+        <v>112.339199834173</v>
       </c>
       <c r="C90" t="n">
-        <v>113.242289105796</v>
+        <v>112.9842586087029</v>
       </c>
       <c r="D90" t="n">
-        <v>111.3170387669949</v>
+        <v>110.2750223556077</v>
       </c>
       <c r="E90" t="n">
-        <v>112.5476150512695</v>
+        <v>110.3544082641602</v>
       </c>
       <c r="F90" t="n">
-        <v>7958500</v>
+        <v>12049600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B91" t="n">
-        <v>112.339199834173</v>
+        <v>108.8261317696502</v>
       </c>
       <c r="C91" t="n">
-        <v>112.9842586087029</v>
+        <v>110.2452505565117</v>
       </c>
       <c r="D91" t="n">
-        <v>110.2750223556077</v>
+        <v>107.9726707390225</v>
       </c>
       <c r="E91" t="n">
-        <v>110.3544082641602</v>
+        <v>109.5009536743164</v>
       </c>
       <c r="F91" t="n">
-        <v>12049600</v>
+        <v>9818200</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B92" t="n">
-        <v>108.8261317696502</v>
+        <v>109.7292049082389</v>
       </c>
       <c r="C92" t="n">
-        <v>110.2452505565117</v>
+        <v>112.3888259939984</v>
       </c>
       <c r="D92" t="n">
-        <v>107.9726707390225</v>
+        <v>109.6597375040779</v>
       </c>
       <c r="E92" t="n">
-        <v>109.5009536743164</v>
+        <v>112.3292846679688</v>
       </c>
       <c r="F92" t="n">
-        <v>9818200</v>
+        <v>10041400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B93" t="n">
-        <v>109.7292049082389</v>
+        <v>112.3094319821855</v>
       </c>
       <c r="C93" t="n">
-        <v>112.3888259939984</v>
+        <v>113.4209180149001</v>
       </c>
       <c r="D93" t="n">
-        <v>109.6597375040779</v>
+        <v>111.317036172348</v>
       </c>
       <c r="E93" t="n">
-        <v>112.3292846679688</v>
+        <v>112.3491287231445</v>
       </c>
       <c r="F93" t="n">
-        <v>10041400</v>
+        <v>12437700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B94" t="n">
-        <v>112.3094319821855</v>
+        <v>111.8330891095483</v>
       </c>
       <c r="C94" t="n">
-        <v>113.4209180149001</v>
+        <v>112.0911065753488</v>
       </c>
       <c r="D94" t="n">
-        <v>111.317036172348</v>
+        <v>109.7093626275885</v>
       </c>
       <c r="E94" t="n">
-        <v>112.3491287231445</v>
+        <v>110.1360931396484</v>
       </c>
       <c r="F94" t="n">
-        <v>12437700</v>
+        <v>10819800</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B95" t="n">
-        <v>111.8330891095483</v>
+        <v>110.8307664528259</v>
       </c>
       <c r="C95" t="n">
-        <v>112.0911065753488</v>
+        <v>111.5552187391887</v>
       </c>
       <c r="D95" t="n">
-        <v>109.7093626275885</v>
+        <v>110.2849457184854</v>
       </c>
       <c r="E95" t="n">
-        <v>110.1360931396484</v>
+        <v>110.4635772705078</v>
       </c>
       <c r="F95" t="n">
-        <v>10819800</v>
+        <v>8859800</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B96" t="n">
-        <v>110.8307664528259</v>
+        <v>110.6521373409646</v>
       </c>
       <c r="C96" t="n">
-        <v>111.5552187391887</v>
+        <v>110.9498591246939</v>
       </c>
       <c r="D96" t="n">
-        <v>110.2849457184854</v>
+        <v>109.1933142291742</v>
       </c>
       <c r="E96" t="n">
-        <v>110.4635772705078</v>
+        <v>109.7689056396484</v>
       </c>
       <c r="F96" t="n">
-        <v>8859800</v>
+        <v>8956900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B97" t="n">
-        <v>110.6521373409646</v>
+        <v>109.4414091319104</v>
       </c>
       <c r="C97" t="n">
-        <v>110.9498591246939</v>
+        <v>110.5826658320299</v>
       </c>
       <c r="D97" t="n">
-        <v>109.1933142291742</v>
+        <v>108.1711437016965</v>
       </c>
       <c r="E97" t="n">
-        <v>109.7689056396484</v>
+        <v>108.7268829345703</v>
       </c>
       <c r="F97" t="n">
-        <v>8956900</v>
+        <v>9016600</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B98" t="n">
-        <v>109.4414091319104</v>
+        <v>108.7963528121511</v>
       </c>
       <c r="C98" t="n">
-        <v>110.5826658320299</v>
+        <v>110.8208412268483</v>
       </c>
       <c r="D98" t="n">
-        <v>108.1711437016965</v>
+        <v>107.932973280219</v>
       </c>
       <c r="E98" t="n">
-        <v>108.7268829345703</v>
+        <v>110.7315292358398</v>
       </c>
       <c r="F98" t="n">
-        <v>9016600</v>
+        <v>11079000</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B99" t="n">
-        <v>108.7963528121511</v>
+        <v>110.5132006888762</v>
       </c>
       <c r="C99" t="n">
-        <v>110.8208412268483</v>
+        <v>112.0911064308015</v>
       </c>
       <c r="D99" t="n">
-        <v>107.932973280219</v>
+        <v>110.1460115045699</v>
       </c>
       <c r="E99" t="n">
-        <v>110.7315292358398</v>
+        <v>111.942253112793</v>
       </c>
       <c r="F99" t="n">
-        <v>11079000</v>
+        <v>17895200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B100" t="n">
-        <v>110.5132006888762</v>
+        <v>103.219089824791</v>
       </c>
       <c r="C100" t="n">
-        <v>112.0911064308015</v>
+        <v>107.7841090146985</v>
       </c>
       <c r="D100" t="n">
-        <v>110.1460115045699</v>
+        <v>102.961064795438</v>
       </c>
       <c r="E100" t="n">
-        <v>111.942253112793</v>
+        <v>103.6557388305664</v>
       </c>
       <c r="F100" t="n">
-        <v>17895200</v>
+        <v>37778500</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B101" t="n">
-        <v>103.219089824791</v>
+        <v>103.9832294528008</v>
       </c>
       <c r="C101" t="n">
-        <v>107.7841090146985</v>
+        <v>104.1916316597105</v>
       </c>
       <c r="D101" t="n">
-        <v>102.961064795438</v>
+        <v>101.5617813072958</v>
       </c>
       <c r="E101" t="n">
-        <v>103.6557388305664</v>
+        <v>103.427490234375</v>
       </c>
       <c r="F101" t="n">
-        <v>37778500</v>
+        <v>24827100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B102" t="n">
-        <v>103.9832294528008</v>
+        <v>103.4076429857971</v>
       </c>
       <c r="C102" t="n">
-        <v>104.1916316597105</v>
+        <v>107.7741861743833</v>
       </c>
       <c r="D102" t="n">
-        <v>101.5617813072958</v>
+        <v>102.841977662662</v>
       </c>
       <c r="E102" t="n">
-        <v>103.427490234375</v>
+        <v>106.2359771728516</v>
       </c>
       <c r="F102" t="n">
-        <v>24827100</v>
+        <v>19070400</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B103" t="n">
-        <v>103.4076429857971</v>
+        <v>106.2359762120697</v>
       </c>
       <c r="C103" t="n">
-        <v>107.7741861743833</v>
+        <v>107.5062416580512</v>
       </c>
       <c r="D103" t="n">
-        <v>102.841977662662</v>
+        <v>104.0130041102228</v>
       </c>
       <c r="E103" t="n">
-        <v>106.2359771728516</v>
+        <v>104.1717910766602</v>
       </c>
       <c r="F103" t="n">
-        <v>19070400</v>
+        <v>11859500</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B104" t="n">
-        <v>106.2359762120697</v>
+        <v>105.3229638054753</v>
       </c>
       <c r="C104" t="n">
-        <v>107.5062416580512</v>
+        <v>108.1314457439972</v>
       </c>
       <c r="D104" t="n">
-        <v>104.0130041102228</v>
+        <v>104.5687484468834</v>
       </c>
       <c r="E104" t="n">
-        <v>104.1717910766602</v>
+        <v>107.873420715332</v>
       </c>
       <c r="F104" t="n">
-        <v>11859500</v>
+        <v>12105600</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B105" t="n">
-        <v>105.3229638054753</v>
+        <v>107.8635036441641</v>
       </c>
       <c r="C105" t="n">
-        <v>108.1314457439972</v>
+        <v>108.09175044183</v>
       </c>
       <c r="D105" t="n">
-        <v>104.5687484468834</v>
+        <v>105.9580979235442</v>
       </c>
       <c r="E105" t="n">
-        <v>107.873420715332</v>
+        <v>106.3153610229492</v>
       </c>
       <c r="F105" t="n">
-        <v>12105600</v>
+        <v>10515400</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B106" t="n">
-        <v>107.8635036441641</v>
+        <v>106.7817856582252</v>
       </c>
       <c r="C106" t="n">
-        <v>108.09175044183</v>
+        <v>110.265097006608</v>
       </c>
       <c r="D106" t="n">
-        <v>105.9580979235442</v>
+        <v>106.7817856582252</v>
       </c>
       <c r="E106" t="n">
-        <v>106.3153610229492</v>
+        <v>109.1238403320312</v>
       </c>
       <c r="F106" t="n">
-        <v>10515400</v>
+        <v>9815500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B107" t="n">
-        <v>106.7817856582252</v>
+        <v>108.1016744764874</v>
       </c>
       <c r="C107" t="n">
-        <v>110.265097006608</v>
+        <v>109.0345289485641</v>
       </c>
       <c r="D107" t="n">
-        <v>106.7817856582252</v>
+        <v>106.9802699515072</v>
       </c>
       <c r="E107" t="n">
-        <v>109.1238403320312</v>
+        <v>107.2978363037109</v>
       </c>
       <c r="F107" t="n">
-        <v>9815500</v>
+        <v>9374900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B108" t="n">
-        <v>108.1016744764874</v>
+        <v>107.1092782571758</v>
       </c>
       <c r="C108" t="n">
-        <v>109.0345289485641</v>
+        <v>107.3375326210063</v>
       </c>
       <c r="D108" t="n">
-        <v>106.9802699515072</v>
+        <v>100.2518196922704</v>
       </c>
       <c r="E108" t="n">
-        <v>107.2978363037109</v>
+        <v>101.6014785766602</v>
       </c>
       <c r="F108" t="n">
-        <v>9374900</v>
+        <v>25319600</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B109" t="n">
-        <v>107.1092782571758</v>
+        <v>100.6289339445357</v>
       </c>
       <c r="C109" t="n">
-        <v>107.3375326210063</v>
+        <v>104.7175997261971</v>
       </c>
       <c r="D109" t="n">
-        <v>100.2518196922704</v>
+        <v>100.4304502450412</v>
       </c>
       <c r="E109" t="n">
-        <v>101.6014785766602</v>
+        <v>104.6481323242188</v>
       </c>
       <c r="F109" t="n">
-        <v>25319600</v>
+        <v>12845300</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B110" t="n">
-        <v>100.6289339445357</v>
+        <v>105.7596186239472</v>
       </c>
       <c r="C110" t="n">
-        <v>104.7175997261971</v>
+        <v>106.4642187235269</v>
       </c>
       <c r="D110" t="n">
-        <v>100.4304502450412</v>
+        <v>103.576350923035</v>
       </c>
       <c r="E110" t="n">
-        <v>104.6481323242188</v>
+        <v>104.6382141113281</v>
       </c>
       <c r="F110" t="n">
-        <v>12845300</v>
+        <v>10467400</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B111" t="n">
-        <v>105.7596186239472</v>
+        <v>105.1542604930163</v>
       </c>
       <c r="C111" t="n">
-        <v>106.4642187235269</v>
+        <v>106.9108053396402</v>
       </c>
       <c r="D111" t="n">
-        <v>103.576350923035</v>
+        <v>105.0053996052954</v>
       </c>
       <c r="E111" t="n">
-        <v>104.6382141113281</v>
+        <v>106.2855911254883</v>
       </c>
       <c r="F111" t="n">
-        <v>10467400</v>
+        <v>8791600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B112" t="n">
-        <v>105.1542604930163</v>
+        <v>106.2955144080048</v>
       </c>
       <c r="C112" t="n">
-        <v>106.9108053396402</v>
+        <v>106.9504916968191</v>
       </c>
       <c r="D112" t="n">
-        <v>105.0053996052954</v>
+        <v>104.6481337509456</v>
       </c>
       <c r="E112" t="n">
-        <v>106.2855911254883</v>
+        <v>105.1939544677734</v>
       </c>
       <c r="F112" t="n">
-        <v>8791600</v>
+        <v>7492900</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B113" t="n">
-        <v>106.2955144080048</v>
+        <v>104.8069236784645</v>
       </c>
       <c r="C113" t="n">
-        <v>106.9504916968191</v>
+        <v>105.3924335809217</v>
       </c>
       <c r="D113" t="n">
-        <v>104.6481337509456</v>
+        <v>103.8542245950799</v>
       </c>
       <c r="E113" t="n">
-        <v>105.1939544677734</v>
+        <v>104.7771530151367</v>
       </c>
       <c r="F113" t="n">
-        <v>7492900</v>
+        <v>9043600</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B114" t="n">
-        <v>104.8069236784645</v>
+        <v>104.1817160321379</v>
       </c>
       <c r="C114" t="n">
-        <v>105.3924335809217</v>
+        <v>104.3901182448065</v>
       </c>
       <c r="D114" t="n">
-        <v>103.8542245950799</v>
+        <v>102.1770722450568</v>
       </c>
       <c r="E114" t="n">
-        <v>104.7771530151367</v>
+        <v>103.6160507202148</v>
       </c>
       <c r="F114" t="n">
-        <v>9043600</v>
+        <v>10626500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B115" t="n">
-        <v>104.1817160321379</v>
+        <v>103.6557367363695</v>
       </c>
       <c r="C115" t="n">
-        <v>104.3901182448065</v>
+        <v>106.4146033792047</v>
       </c>
       <c r="D115" t="n">
-        <v>102.1770722450568</v>
+        <v>103.1893170772804</v>
       </c>
       <c r="E115" t="n">
-        <v>103.6160507202148</v>
+        <v>105.2435760498047</v>
       </c>
       <c r="F115" t="n">
-        <v>10626500</v>
+        <v>13594800</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B116" t="n">
-        <v>103.6557367363695</v>
+        <v>105.193955544271</v>
       </c>
       <c r="C116" t="n">
-        <v>106.4146033792047</v>
+        <v>105.9084817367471</v>
       </c>
       <c r="D116" t="n">
-        <v>103.1893170772804</v>
+        <v>103.7152879117953</v>
       </c>
       <c r="E116" t="n">
-        <v>105.2435760498047</v>
+        <v>104.2511825561523</v>
       </c>
       <c r="F116" t="n">
-        <v>13594800</v>
+        <v>8556500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B117" t="n">
-        <v>105.193955544271</v>
+        <v>104.6679896339684</v>
       </c>
       <c r="C117" t="n">
-        <v>105.9084817367471</v>
+        <v>105.9580996730059</v>
       </c>
       <c r="D117" t="n">
-        <v>103.7152879117953</v>
+        <v>104.519128744862</v>
       </c>
       <c r="E117" t="n">
-        <v>104.2511825561523</v>
+        <v>104.7473831176758</v>
       </c>
       <c r="F117" t="n">
-        <v>8556500</v>
+        <v>9578500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B118" t="n">
-        <v>104.6679896339684</v>
+        <v>103.9832293953731</v>
       </c>
       <c r="C118" t="n">
-        <v>105.9580996730059</v>
+        <v>105.5313644009208</v>
       </c>
       <c r="D118" t="n">
-        <v>104.519128744862</v>
+        <v>103.1396944903344</v>
       </c>
       <c r="E118" t="n">
-        <v>104.7473831176758</v>
+        <v>105.2336502075195</v>
       </c>
       <c r="F118" t="n">
-        <v>9578500</v>
+        <v>13954000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B119" t="n">
-        <v>103.9832293953731</v>
+        <v>103.8145288629893</v>
       </c>
       <c r="C119" t="n">
-        <v>105.5313644009208</v>
+        <v>103.8145288629893</v>
       </c>
       <c r="D119" t="n">
-        <v>103.1396944903344</v>
+        <v>102.0778361524432</v>
       </c>
       <c r="E119" t="n">
-        <v>105.2336502075195</v>
+        <v>103.5366592407227</v>
       </c>
       <c r="F119" t="n">
-        <v>13954000</v>
+        <v>14178600</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B120" t="n">
-        <v>103.8145288629893</v>
+        <v>102.0579794936243</v>
       </c>
       <c r="C120" t="n">
-        <v>103.8145288629893</v>
+        <v>103.5168025175497</v>
       </c>
       <c r="D120" t="n">
-        <v>102.0778361524432</v>
+        <v>101.3732315464965</v>
       </c>
       <c r="E120" t="n">
-        <v>103.5366592407227</v>
+        <v>102.5144882202148</v>
       </c>
       <c r="F120" t="n">
-        <v>14178600</v>
+        <v>13608400</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B121" t="n">
-        <v>102.0579794936243</v>
+        <v>102.3854784619134</v>
       </c>
       <c r="C121" t="n">
-        <v>103.5168025175497</v>
+        <v>103.0503818671043</v>
       </c>
       <c r="D121" t="n">
-        <v>101.3732315464965</v>
+        <v>101.8595098706018</v>
       </c>
       <c r="E121" t="n">
-        <v>102.5144882202148</v>
+        <v>102.2564697265625</v>
       </c>
       <c r="F121" t="n">
-        <v>13608400</v>
+        <v>9672300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B122" t="n">
-        <v>102.3854784619134</v>
+        <v>102.3160040474863</v>
       </c>
       <c r="C122" t="n">
-        <v>103.0503818671043</v>
+        <v>103.7549824803676</v>
       </c>
       <c r="D122" t="n">
-        <v>101.8595098706018</v>
+        <v>100.8174842902717</v>
       </c>
       <c r="E122" t="n">
-        <v>102.2564697265625</v>
+        <v>101.6312561035156</v>
       </c>
       <c r="F122" t="n">
-        <v>9672300</v>
+        <v>11751500</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B123" t="n">
-        <v>102.3160040474863</v>
+        <v>100.6190147793836</v>
       </c>
       <c r="C123" t="n">
-        <v>103.7549824803676</v>
+        <v>101.0358192198888</v>
       </c>
       <c r="D123" t="n">
-        <v>100.8174842902717</v>
+        <v>99.18996233036073</v>
       </c>
       <c r="E123" t="n">
-        <v>101.6312561035156</v>
+        <v>100.7678756713867</v>
       </c>
       <c r="F123" t="n">
-        <v>11751500</v>
+        <v>10448600</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B124" t="n">
-        <v>100.6190147793836</v>
+        <v>99.78540292258373</v>
       </c>
       <c r="C124" t="n">
-        <v>101.0358192198888</v>
+        <v>101.0953651046626</v>
       </c>
       <c r="D124" t="n">
-        <v>99.18996233036073</v>
+        <v>97.70136563944882</v>
       </c>
       <c r="E124" t="n">
-        <v>100.7678756713867</v>
+        <v>100.886962890625</v>
       </c>
       <c r="F124" t="n">
-        <v>10448600</v>
+        <v>11715100</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B125" t="n">
-        <v>99.78540292258373</v>
+        <v>100.9762757982457</v>
       </c>
       <c r="C125" t="n">
-        <v>101.0953651046626</v>
+        <v>101.4625476354206</v>
       </c>
       <c r="D125" t="n">
-        <v>97.70136563944882</v>
+        <v>99.47775597353863</v>
       </c>
       <c r="E125" t="n">
-        <v>100.886962890625</v>
+        <v>100.5495452880859</v>
       </c>
       <c r="F125" t="n">
-        <v>11715100</v>
+        <v>7833100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B126" t="n">
-        <v>100.9762757982457</v>
+        <v>100.6289343352219</v>
       </c>
       <c r="C126" t="n">
-        <v>101.4625476354206</v>
+        <v>101.1152061509584</v>
       </c>
       <c r="D126" t="n">
-        <v>99.47775597353863</v>
+        <v>99.63653854803313</v>
       </c>
       <c r="E126" t="n">
-        <v>100.5495452880859</v>
+        <v>100.1228103637695</v>
       </c>
       <c r="F126" t="n">
-        <v>7833100</v>
+        <v>8152800</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B127" t="n">
-        <v>100.6289343352219</v>
+        <v>99.33882308016651</v>
       </c>
       <c r="C127" t="n">
-        <v>101.1152061509584</v>
+        <v>100.1128906318194</v>
       </c>
       <c r="D127" t="n">
-        <v>99.63653854803313</v>
+        <v>98.61437834957015</v>
       </c>
       <c r="E127" t="n">
-        <v>100.1228103637695</v>
+        <v>98.67391967773438</v>
       </c>
       <c r="F127" t="n">
-        <v>8152800</v>
+        <v>10309400</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B128" t="n">
-        <v>99.33882308016651</v>
+        <v>99.07087541929553</v>
       </c>
       <c r="C128" t="n">
-        <v>100.1128906318194</v>
+        <v>100.0037223311207</v>
       </c>
       <c r="D128" t="n">
-        <v>98.61437834957015</v>
+        <v>98.4059720444657</v>
       </c>
       <c r="E128" t="n">
-        <v>98.67391967773438</v>
+        <v>98.53498077392578</v>
       </c>
       <c r="F128" t="n">
-        <v>10309400</v>
+        <v>9551500</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B129" t="n">
-        <v>99.07087541929553</v>
+        <v>98.71361296789499</v>
       </c>
       <c r="C129" t="n">
-        <v>100.0037223311207</v>
+        <v>98.93194125870065</v>
       </c>
       <c r="D129" t="n">
-        <v>98.4059720444657</v>
+        <v>97.71129107436866</v>
       </c>
       <c r="E129" t="n">
-        <v>98.53498077392578</v>
+        <v>97.90977478027344</v>
       </c>
       <c r="F129" t="n">
-        <v>9551500</v>
+        <v>11578500</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B130" t="n">
-        <v>98.71361296789499</v>
+        <v>98.41588802886785</v>
       </c>
       <c r="C130" t="n">
-        <v>98.93194125870065</v>
+        <v>99.94417844396594</v>
       </c>
       <c r="D130" t="n">
-        <v>97.71129107436866</v>
+        <v>98.26702714707265</v>
       </c>
       <c r="E130" t="n">
-        <v>97.90977478027344</v>
+        <v>99.53730010986328</v>
       </c>
       <c r="F130" t="n">
-        <v>11578500</v>
+        <v>11785600</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B131" t="n">
-        <v>98.41588802886785</v>
+        <v>99.08079827635559</v>
       </c>
       <c r="C131" t="n">
-        <v>99.94417844396594</v>
+        <v>100.2518256851255</v>
       </c>
       <c r="D131" t="n">
-        <v>98.26702714707265</v>
+        <v>98.24718939454284</v>
       </c>
       <c r="E131" t="n">
-        <v>99.53730010986328</v>
+        <v>98.66399383544922</v>
       </c>
       <c r="F131" t="n">
-        <v>11785600</v>
+        <v>12615100</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B132" t="n">
-        <v>99.08079827635559</v>
+        <v>98.2769579779315</v>
       </c>
       <c r="C132" t="n">
-        <v>100.2518256851255</v>
+        <v>100.0136506829842</v>
       </c>
       <c r="D132" t="n">
-        <v>98.24718939454284</v>
+        <v>97.69144807163296</v>
       </c>
       <c r="E132" t="n">
-        <v>98.66399383544922</v>
+        <v>98.44566345214844</v>
       </c>
       <c r="F132" t="n">
-        <v>12615100</v>
+        <v>14793800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B133" t="n">
-        <v>98.2769579779315</v>
+        <v>98.25711324225701</v>
       </c>
       <c r="C133" t="n">
-        <v>100.0136506829842</v>
+        <v>99.269353657388</v>
       </c>
       <c r="D133" t="n">
-        <v>97.69144807163296</v>
+        <v>97.64182510199821</v>
       </c>
       <c r="E133" t="n">
-        <v>98.44566345214844</v>
+        <v>98.75331115722656</v>
       </c>
       <c r="F133" t="n">
-        <v>14793800</v>
+        <v>27544200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B134" t="n">
-        <v>98.25711324225701</v>
+        <v>99.45791247863863</v>
       </c>
       <c r="C134" t="n">
-        <v>99.269353657388</v>
+        <v>99.83502017283372</v>
       </c>
       <c r="D134" t="n">
-        <v>97.64182510199821</v>
+        <v>97.11585768623267</v>
       </c>
       <c r="E134" t="n">
-        <v>98.75331115722656</v>
+        <v>97.20516967773438</v>
       </c>
       <c r="F134" t="n">
-        <v>27544200</v>
+        <v>11373000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B135" t="n">
-        <v>99.45791247863863</v>
+        <v>96.99676871718921</v>
       </c>
       <c r="C135" t="n">
-        <v>99.83502017283372</v>
+        <v>97.30441658068045</v>
       </c>
       <c r="D135" t="n">
-        <v>97.11585768623267</v>
+        <v>95.5181010136908</v>
       </c>
       <c r="E135" t="n">
-        <v>97.20516967773438</v>
+        <v>95.65703582763672</v>
       </c>
       <c r="F135" t="n">
-        <v>11373000</v>
+        <v>9155700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B136" t="n">
-        <v>96.99676871718921</v>
+        <v>96.08376214252051</v>
       </c>
       <c r="C136" t="n">
-        <v>97.30441658068045</v>
+        <v>96.44102524028141</v>
       </c>
       <c r="D136" t="n">
-        <v>95.5181010136908</v>
+        <v>94.33714339473161</v>
       </c>
       <c r="E136" t="n">
-        <v>95.65703582763672</v>
+        <v>95.22037506103516</v>
       </c>
       <c r="F136" t="n">
-        <v>9155700</v>
+        <v>8467500</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B137" t="n">
-        <v>96.08376214252051</v>
+        <v>94.3966920435457</v>
       </c>
       <c r="C137" t="n">
-        <v>96.44102524028141</v>
+        <v>95.66695746718439</v>
       </c>
       <c r="D137" t="n">
-        <v>94.33714339473161</v>
+        <v>93.87071590500793</v>
       </c>
       <c r="E137" t="n">
-        <v>95.22037506103516</v>
+        <v>94.02950286865234</v>
       </c>
       <c r="F137" t="n">
-        <v>8467500</v>
+        <v>8548800</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B138" t="n">
-        <v>94.3966920435457</v>
+        <v>93.47376126842354</v>
       </c>
       <c r="C138" t="n">
-        <v>95.66695746718439</v>
+        <v>93.47376126842354</v>
       </c>
       <c r="D138" t="n">
-        <v>93.87071590500793</v>
+        <v>91.48896970147202</v>
       </c>
       <c r="E138" t="n">
-        <v>94.02950286865234</v>
+        <v>91.71721649169922</v>
       </c>
       <c r="F138" t="n">
-        <v>8548800</v>
+        <v>12475900</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B139" t="n">
-        <v>93.47376126842354</v>
+        <v>92.18364921591858</v>
       </c>
       <c r="C139" t="n">
-        <v>93.47376126842354</v>
+        <v>94.46616268251262</v>
       </c>
       <c r="D139" t="n">
-        <v>91.48896970147202</v>
+        <v>92.18364921591858</v>
       </c>
       <c r="E139" t="n">
-        <v>91.71721649169922</v>
+        <v>93.60277557373047</v>
       </c>
       <c r="F139" t="n">
-        <v>12475900</v>
+        <v>10592600</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B140" t="n">
-        <v>92.18364921591858</v>
+        <v>94.61501738536155</v>
       </c>
       <c r="C140" t="n">
-        <v>94.46616268251262</v>
+        <v>96.15323399247868</v>
       </c>
       <c r="D140" t="n">
-        <v>92.18364921591858</v>
+        <v>93.47376820675542</v>
       </c>
       <c r="E140" t="n">
-        <v>93.60277557373047</v>
+        <v>95.64710998535156</v>
       </c>
       <c r="F140" t="n">
-        <v>10592600</v>
+        <v>11180200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B141" t="n">
-        <v>94.61501738536155</v>
+        <v>96.52041860940267</v>
       </c>
       <c r="C141" t="n">
-        <v>96.15323399247868</v>
+        <v>97.61205248622655</v>
       </c>
       <c r="D141" t="n">
-        <v>93.47376820675542</v>
+        <v>95.75626959566054</v>
       </c>
       <c r="E141" t="n">
-        <v>95.64710998535156</v>
+        <v>95.82573699951172</v>
       </c>
       <c r="F141" t="n">
-        <v>11180200</v>
+        <v>8518600</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B142" t="n">
-        <v>96.52041860940267</v>
+        <v>95.26999653948798</v>
       </c>
       <c r="C142" t="n">
-        <v>97.61205248622655</v>
+        <v>96.43109780518201</v>
       </c>
       <c r="D142" t="n">
-        <v>95.75626959566054</v>
+        <v>94.36691272969546</v>
       </c>
       <c r="E142" t="n">
-        <v>95.82573699951172</v>
+        <v>95.87535858154297</v>
       </c>
       <c r="F142" t="n">
-        <v>8518600</v>
+        <v>6379100</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B143" t="n">
-        <v>95.26999653948798</v>
+        <v>95.76619510964362</v>
       </c>
       <c r="C143" t="n">
-        <v>96.43109780518201</v>
+        <v>96.4211799747073</v>
       </c>
       <c r="D143" t="n">
-        <v>94.36691272969546</v>
+        <v>95.389087429727</v>
       </c>
       <c r="E143" t="n">
-        <v>95.87535858154297</v>
+        <v>95.54786682128906</v>
       </c>
       <c r="F143" t="n">
-        <v>6379100</v>
+        <v>5882200</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B144" t="n">
-        <v>95.76619510964362</v>
+        <v>95.07152604625539</v>
       </c>
       <c r="C144" t="n">
-        <v>96.4211799747073</v>
+        <v>96.05399582384246</v>
       </c>
       <c r="D144" t="n">
-        <v>95.389087429727</v>
+        <v>94.60509878245135</v>
       </c>
       <c r="E144" t="n">
-        <v>95.54786682128906</v>
+        <v>95.05167388916016</v>
       </c>
       <c r="F144" t="n">
-        <v>5882200</v>
+        <v>7913000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B145" t="n">
-        <v>95.07152604625539</v>
+        <v>97.3540300760944</v>
       </c>
       <c r="C145" t="n">
-        <v>96.05399582384246</v>
+        <v>98.43574547532691</v>
       </c>
       <c r="D145" t="n">
-        <v>94.60509878245135</v>
+        <v>96.94715172012246</v>
       </c>
       <c r="E145" t="n">
-        <v>95.05167388916016</v>
+        <v>98.42581939697266</v>
       </c>
       <c r="F145" t="n">
-        <v>7913000</v>
+        <v>10821000</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B146" t="n">
-        <v>97.3540300760944</v>
+        <v>97.9097767670043</v>
       </c>
       <c r="C146" t="n">
-        <v>98.43574547532691</v>
+        <v>99.46783792592092</v>
       </c>
       <c r="D146" t="n">
-        <v>96.94715172012246</v>
+        <v>96.93722551678441</v>
       </c>
       <c r="E146" t="n">
-        <v>98.42581939697266</v>
+        <v>99.03118133544922</v>
       </c>
       <c r="F146" t="n">
-        <v>10821000</v>
+        <v>8918300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B147" t="n">
-        <v>97.9097767670043</v>
+        <v>99.08079694980933</v>
       </c>
       <c r="C147" t="n">
-        <v>99.46783792592092</v>
+        <v>99.39837088687223</v>
       </c>
       <c r="D147" t="n">
-        <v>96.93722551678441</v>
+        <v>98.06855652524918</v>
       </c>
       <c r="E147" t="n">
-        <v>99.03118133544922</v>
+        <v>98.4158935546875</v>
       </c>
       <c r="F147" t="n">
-        <v>8918300</v>
+        <v>6359600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B148" t="n">
-        <v>99.08079694980933</v>
+        <v>97.78075602521236</v>
       </c>
       <c r="C148" t="n">
-        <v>99.39837088687223</v>
+        <v>100.4999183711592</v>
       </c>
       <c r="D148" t="n">
-        <v>98.06855652524918</v>
+        <v>97.78075602521236</v>
       </c>
       <c r="E148" t="n">
-        <v>98.4158935546875</v>
+        <v>100.4106063842773</v>
       </c>
       <c r="F148" t="n">
-        <v>6359600</v>
+        <v>6790300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B149" t="n">
-        <v>97.78075602521236</v>
+        <v>100.5693883478159</v>
       </c>
       <c r="C149" t="n">
-        <v>100.4999183711592</v>
+        <v>102.3160071037648</v>
       </c>
       <c r="D149" t="n">
-        <v>97.78075602521236</v>
+        <v>100.1327393373631</v>
       </c>
       <c r="E149" t="n">
-        <v>100.4106063842773</v>
+        <v>101.8098831176758</v>
       </c>
       <c r="F149" t="n">
-        <v>6790300</v>
+        <v>9997400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B150" t="n">
-        <v>100.5693883478159</v>
+        <v>101.8198131278678</v>
       </c>
       <c r="C150" t="n">
-        <v>102.3160071037648</v>
+        <v>102.5938806827324</v>
       </c>
       <c r="D150" t="n">
-        <v>100.1327393373631</v>
+        <v>101.0159749087976</v>
       </c>
       <c r="E150" t="n">
-        <v>101.8098831176758</v>
+        <v>102.2564697265625</v>
       </c>
       <c r="F150" t="n">
-        <v>9997400</v>
+        <v>7035300</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B151" t="n">
-        <v>101.8198131278678</v>
+        <v>102.832054706031</v>
       </c>
       <c r="C151" t="n">
-        <v>102.5938806827324</v>
+        <v>103.7351309397506</v>
       </c>
       <c r="D151" t="n">
-        <v>101.0159749087976</v>
+        <v>101.9984383035261</v>
       </c>
       <c r="E151" t="n">
-        <v>102.2564697265625</v>
+        <v>103.1099243164062</v>
       </c>
       <c r="F151" t="n">
-        <v>7035300</v>
+        <v>8145900</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B152" t="n">
-        <v>102.832054706031</v>
+        <v>103.8939187225915</v>
       </c>
       <c r="C152" t="n">
-        <v>103.7351309397506</v>
+        <v>105.5214472288459</v>
       </c>
       <c r="D152" t="n">
-        <v>101.9984383035261</v>
+        <v>103.8939187225915</v>
       </c>
       <c r="E152" t="n">
-        <v>103.1099243164062</v>
+        <v>105.4817504882812</v>
       </c>
       <c r="F152" t="n">
-        <v>8145900</v>
+        <v>10506200</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B153" t="n">
-        <v>103.8939187225915</v>
+        <v>105.1046425751499</v>
       </c>
       <c r="C153" t="n">
-        <v>105.5214472288459</v>
+        <v>106.2955145039117</v>
       </c>
       <c r="D153" t="n">
-        <v>103.8939187225915</v>
+        <v>105.1046425751499</v>
       </c>
       <c r="E153" t="n">
-        <v>105.4817504882812</v>
+        <v>105.4916763305664</v>
       </c>
       <c r="F153" t="n">
-        <v>10506200</v>
+        <v>6423400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B154" t="n">
-        <v>105.1046425751499</v>
+        <v>105.3825171192469</v>
       </c>
       <c r="C154" t="n">
-        <v>106.2955145039117</v>
+        <v>106.0672651032121</v>
       </c>
       <c r="D154" t="n">
-        <v>105.1046425751499</v>
+        <v>103.1793971336853</v>
       </c>
       <c r="E154" t="n">
-        <v>105.4916763305664</v>
+        <v>103.4969635009766</v>
       </c>
       <c r="F154" t="n">
-        <v>6423400</v>
+        <v>7784500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B155" t="n">
-        <v>105.3825171192469</v>
+        <v>104.2313285377519</v>
       </c>
       <c r="C155" t="n">
-        <v>106.0672651032121</v>
+        <v>105.4718232743649</v>
       </c>
       <c r="D155" t="n">
-        <v>103.1793971336853</v>
+        <v>103.437416449147</v>
       </c>
       <c r="E155" t="n">
-        <v>103.4969635009766</v>
+        <v>104.0229263305664</v>
       </c>
       <c r="F155" t="n">
-        <v>7784500</v>
+        <v>6886600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B156" t="n">
-        <v>104.2313285377519</v>
+        <v>104.1420232238167</v>
       </c>
       <c r="C156" t="n">
-        <v>105.4718232743649</v>
+        <v>104.4000406941716</v>
       </c>
       <c r="D156" t="n">
-        <v>103.437416449147</v>
+        <v>101.7701977411496</v>
       </c>
       <c r="E156" t="n">
-        <v>104.0229263305664</v>
+        <v>102.8618316650391</v>
       </c>
       <c r="F156" t="n">
-        <v>6886600</v>
+        <v>6147000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B157" t="n">
-        <v>104.1420232238167</v>
+        <v>102.81220477355</v>
       </c>
       <c r="C157" t="n">
-        <v>104.4000406941716</v>
+        <v>102.851901514659</v>
       </c>
       <c r="D157" t="n">
-        <v>101.7701977411496</v>
+        <v>101.1946023230963</v>
       </c>
       <c r="E157" t="n">
-        <v>102.8618316650391</v>
+        <v>101.8198089599609</v>
       </c>
       <c r="F157" t="n">
-        <v>6147000</v>
+        <v>5974500</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B158" t="n">
-        <v>102.81220477355</v>
+        <v>101.839659785339</v>
       </c>
       <c r="C158" t="n">
-        <v>102.851901514659</v>
+        <v>103.0206056395392</v>
       </c>
       <c r="D158" t="n">
-        <v>101.1946023230963</v>
+        <v>101.2839129884539</v>
       </c>
       <c r="E158" t="n">
-        <v>101.8198089599609</v>
+        <v>101.5717086791992</v>
       </c>
       <c r="F158" t="n">
-        <v>5974500</v>
+        <v>6524300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B159" t="n">
-        <v>101.839659785339</v>
+        <v>101.8793558222072</v>
       </c>
       <c r="C159" t="n">
-        <v>103.0206056395392</v>
+        <v>102.5045624465828</v>
       </c>
       <c r="D159" t="n">
-        <v>101.2839129884539</v>
+        <v>99.84494141643668</v>
       </c>
       <c r="E159" t="n">
-        <v>101.5717086791992</v>
+        <v>100.6984024047852</v>
       </c>
       <c r="F159" t="n">
-        <v>6524300</v>
+        <v>6409300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B160" t="n">
-        <v>101.8793558222072</v>
+        <v>100.1724381261774</v>
       </c>
       <c r="C160" t="n">
-        <v>102.5045624465828</v>
+        <v>100.7083327862765</v>
       </c>
       <c r="D160" t="n">
-        <v>99.84494141643668</v>
+        <v>99.83501960476121</v>
       </c>
       <c r="E160" t="n">
-        <v>100.6984024047852</v>
+        <v>100.5297012329102</v>
       </c>
       <c r="F160" t="n">
-        <v>6409300</v>
+        <v>5533700</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B161" t="n">
-        <v>100.1724381261774</v>
+        <v>100.1426666812253</v>
       </c>
       <c r="C161" t="n">
-        <v>100.7083327862765</v>
+        <v>103.328256381923</v>
       </c>
       <c r="D161" t="n">
-        <v>99.83501960476121</v>
+        <v>99.65638727390106</v>
       </c>
       <c r="E161" t="n">
-        <v>100.5297012329102</v>
+        <v>102.961067199707</v>
       </c>
       <c r="F161" t="n">
-        <v>5533700</v>
+        <v>9203500</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B162" t="n">
-        <v>100.1426666812253</v>
+        <v>103.6061276781693</v>
       </c>
       <c r="C162" t="n">
-        <v>103.328256381923</v>
+        <v>104.0328581941516</v>
       </c>
       <c r="D162" t="n">
-        <v>99.65638727390106</v>
+        <v>102.1870013177053</v>
       </c>
       <c r="E162" t="n">
-        <v>102.961067199707</v>
+        <v>102.2961654663086</v>
       </c>
       <c r="F162" t="n">
-        <v>9203500</v>
+        <v>5956900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B163" t="n">
-        <v>103.6061276781693</v>
+        <v>101.9587457902329</v>
       </c>
       <c r="C163" t="n">
-        <v>104.0328581941516</v>
+        <v>102.2663936470847</v>
       </c>
       <c r="D163" t="n">
-        <v>102.1870013177053</v>
+        <v>100.4999227039044</v>
       </c>
       <c r="E163" t="n">
-        <v>102.2961654663086</v>
+        <v>100.5396194458008</v>
       </c>
       <c r="F163" t="n">
-        <v>5956900</v>
+        <v>8400100</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B164" t="n">
-        <v>101.9587457902329</v>
+        <v>100.7579458156174</v>
       </c>
       <c r="C164" t="n">
-        <v>102.2663936470847</v>
+        <v>100.9564295213072</v>
       </c>
       <c r="D164" t="n">
-        <v>100.4999227039044</v>
+        <v>99.29912275715898</v>
       </c>
       <c r="E164" t="n">
-        <v>100.5396194458008</v>
+        <v>99.71593475341797</v>
       </c>
       <c r="F164" t="n">
-        <v>8400100</v>
+        <v>14314700</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B165" t="n">
-        <v>100.7579458156174</v>
+        <v>105.7099984223796</v>
       </c>
       <c r="C165" t="n">
-        <v>100.9564295213072</v>
+        <v>108.3100781720615</v>
       </c>
       <c r="D165" t="n">
-        <v>99.29912275715898</v>
+        <v>104.5092004000206</v>
       </c>
       <c r="E165" t="n">
-        <v>99.71593475341797</v>
+        <v>107.2382888793945</v>
       </c>
       <c r="F165" t="n">
-        <v>14314700</v>
+        <v>23219500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B166" t="n">
-        <v>105.7099984223796</v>
+        <v>108.2207663660894</v>
       </c>
       <c r="C166" t="n">
-        <v>108.3100781720615</v>
+        <v>109.6398926806152</v>
       </c>
       <c r="D166" t="n">
-        <v>104.5092004000206</v>
+        <v>106.2756639110559</v>
       </c>
       <c r="E166" t="n">
-        <v>107.2382888793945</v>
+        <v>107.8337326049805</v>
       </c>
       <c r="F166" t="n">
-        <v>23219500</v>
+        <v>14309200</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B167" t="n">
-        <v>108.2207663660894</v>
+        <v>108.2009150377847</v>
       </c>
       <c r="C167" t="n">
-        <v>109.6398926806152</v>
+        <v>108.3795465882309</v>
       </c>
       <c r="D167" t="n">
-        <v>106.2756639110559</v>
+        <v>106.7222473860446</v>
       </c>
       <c r="E167" t="n">
-        <v>107.8337326049805</v>
+        <v>107.1985931396484</v>
       </c>
       <c r="F167" t="n">
-        <v>14309200</v>
+        <v>8370000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B168" t="n">
-        <v>108.2009150377847</v>
+        <v>107.1787478525936</v>
       </c>
       <c r="C168" t="n">
-        <v>108.3795465882309</v>
+        <v>107.5657816141287</v>
       </c>
       <c r="D168" t="n">
-        <v>106.7222473860446</v>
+        <v>103.5862722822083</v>
       </c>
       <c r="E168" t="n">
-        <v>107.1985931396484</v>
+        <v>103.9236907958984</v>
       </c>
       <c r="F168" t="n">
-        <v>8370000</v>
+        <v>10562300</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B169" t="n">
-        <v>107.1787478525936</v>
+        <v>104.1916361796018</v>
       </c>
       <c r="C169" t="n">
-        <v>107.5657816141287</v>
+        <v>105.4619016318964</v>
       </c>
       <c r="D169" t="n">
-        <v>103.5862722822083</v>
+        <v>103.4274947211174</v>
       </c>
       <c r="E169" t="n">
-        <v>103.9236907958984</v>
+        <v>105.3527450561523</v>
       </c>
       <c r="F169" t="n">
-        <v>10562300</v>
+        <v>8178500</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B170" t="n">
-        <v>104.1916361796018</v>
+        <v>104.5489005402277</v>
       </c>
       <c r="C170" t="n">
-        <v>105.4619016318964</v>
+        <v>105.0748691255691</v>
       </c>
       <c r="D170" t="n">
-        <v>103.4274947211174</v>
+        <v>103.0702328542224</v>
       </c>
       <c r="E170" t="n">
-        <v>105.3527450561523</v>
+        <v>104.1023254394531</v>
       </c>
       <c r="F170" t="n">
-        <v>8178500</v>
+        <v>7605900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B171" t="n">
-        <v>104.5489005402277</v>
+        <v>104.7374526473249</v>
       </c>
       <c r="C171" t="n">
-        <v>105.0748691255691</v>
+        <v>105.4817494902667</v>
       </c>
       <c r="D171" t="n">
-        <v>103.0702328542224</v>
+        <v>104.0526971289773</v>
       </c>
       <c r="E171" t="n">
-        <v>104.1023254394531</v>
+        <v>104.6183624267578</v>
       </c>
       <c r="F171" t="n">
-        <v>7605900</v>
+        <v>6144600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B172" t="n">
-        <v>104.7374526473249</v>
+        <v>104.2313280181917</v>
       </c>
       <c r="C172" t="n">
-        <v>105.4817494902667</v>
+        <v>104.6183617683755</v>
       </c>
       <c r="D172" t="n">
-        <v>104.0526971289773</v>
+        <v>101.5220917669058</v>
       </c>
       <c r="E172" t="n">
-        <v>104.6183624267578</v>
+        <v>101.9388961791992</v>
       </c>
       <c r="F172" t="n">
-        <v>6144600</v>
+        <v>9258600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B173" t="n">
-        <v>104.2313280181917</v>
+        <v>101.9091260836407</v>
       </c>
       <c r="C173" t="n">
-        <v>104.6183617683755</v>
+        <v>103.9038361698679</v>
       </c>
       <c r="D173" t="n">
-        <v>101.5220917669058</v>
+        <v>101.7701912787705</v>
       </c>
       <c r="E173" t="n">
-        <v>101.9388961791992</v>
+        <v>103.1198501586914</v>
       </c>
       <c r="F173" t="n">
-        <v>9258600</v>
+        <v>9037200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B174" t="n">
-        <v>101.9091260836407</v>
+        <v>102.9213691252704</v>
       </c>
       <c r="C174" t="n">
-        <v>103.9038361698679</v>
+        <v>103.1396974161188</v>
       </c>
       <c r="D174" t="n">
-        <v>101.7701912787705</v>
+        <v>101.1946025261468</v>
       </c>
       <c r="E174" t="n">
-        <v>103.1198501586914</v>
+        <v>101.5121688842773</v>
       </c>
       <c r="F174" t="n">
-        <v>9037200</v>
+        <v>7032600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B175" t="n">
-        <v>102.9213691252704</v>
+        <v>102.1274576654748</v>
       </c>
       <c r="C175" t="n">
-        <v>103.1396974161188</v>
+        <v>104.0626264896183</v>
       </c>
       <c r="D175" t="n">
-        <v>101.1946025261468</v>
+        <v>100.8274139902545</v>
       </c>
       <c r="E175" t="n">
-        <v>101.5121688842773</v>
+        <v>103.2885589599609</v>
       </c>
       <c r="F175" t="n">
-        <v>7032600</v>
+        <v>7941400</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B176" t="n">
-        <v>102.1274576654748</v>
+        <v>102.822129060906</v>
       </c>
       <c r="C176" t="n">
-        <v>104.0626264896183</v>
+        <v>103.8244509351605</v>
       </c>
       <c r="D176" t="n">
-        <v>100.8274139902545</v>
+        <v>101.8098811087023</v>
       </c>
       <c r="E176" t="n">
-        <v>103.2885589599609</v>
+        <v>102.7923583984375</v>
       </c>
       <c r="F176" t="n">
-        <v>7941400</v>
+        <v>8611200</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B177" t="n">
-        <v>102.822129060906</v>
+        <v>103.2488588874603</v>
       </c>
       <c r="C177" t="n">
-        <v>103.8244509351605</v>
+        <v>103.7053600422387</v>
       </c>
       <c r="D177" t="n">
-        <v>101.8098811087023</v>
+        <v>102.1969217730311</v>
       </c>
       <c r="E177" t="n">
-        <v>102.7923583984375</v>
+        <v>102.2167663574219</v>
       </c>
       <c r="F177" t="n">
-        <v>8611200</v>
+        <v>5693300</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B178" t="n">
-        <v>103.2488588874603</v>
+        <v>102.3160049896206</v>
       </c>
       <c r="C178" t="n">
-        <v>103.7053600422387</v>
+        <v>103.0106865892155</v>
       </c>
       <c r="D178" t="n">
-        <v>102.1969217730311</v>
+        <v>101.571708143084</v>
       </c>
       <c r="E178" t="n">
-        <v>102.2167663574219</v>
+        <v>102.4946365356445</v>
       </c>
       <c r="F178" t="n">
-        <v>5693300</v>
+        <v>6714400</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B179" t="n">
-        <v>102.3160049896206</v>
+        <v>102.5144889184559</v>
       </c>
       <c r="C179" t="n">
-        <v>103.0106865892155</v>
+        <v>104.4496576951832</v>
       </c>
       <c r="D179" t="n">
-        <v>101.571708143084</v>
+        <v>102.4747921779873</v>
       </c>
       <c r="E179" t="n">
-        <v>102.4946365356445</v>
+        <v>103.3877944946289</v>
       </c>
       <c r="F179" t="n">
-        <v>6714400</v>
+        <v>7360100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B180" t="n">
-        <v>102.5144889184559</v>
+        <v>103.0206090569662</v>
       </c>
       <c r="C180" t="n">
-        <v>104.4496576951832</v>
+        <v>103.6160526141937</v>
       </c>
       <c r="D180" t="n">
-        <v>102.4747921779873</v>
+        <v>102.3160089237181</v>
       </c>
       <c r="E180" t="n">
-        <v>103.3877944946289</v>
+        <v>102.9412231445312</v>
       </c>
       <c r="F180" t="n">
-        <v>7360100</v>
+        <v>6511100</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B181" t="n">
-        <v>103.0206090569662</v>
+        <v>102.8419796873618</v>
       </c>
       <c r="C181" t="n">
-        <v>103.6160526141937</v>
+        <v>102.9709959941437</v>
       </c>
       <c r="D181" t="n">
-        <v>102.3160089237181</v>
+        <v>101.0556716918945</v>
       </c>
       <c r="E181" t="n">
-        <v>102.9412231445312</v>
+        <v>101.0556716918945</v>
       </c>
       <c r="F181" t="n">
-        <v>6511100</v>
+        <v>13340300</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B182" t="n">
-        <v>102.8419796873618</v>
+        <v>100.8869633557317</v>
       </c>
       <c r="C182" t="n">
-        <v>102.9709959941437</v>
+        <v>102.2266962072239</v>
       </c>
       <c r="D182" t="n">
-        <v>101.0556716918945</v>
+        <v>99.53730442598828</v>
       </c>
       <c r="E182" t="n">
-        <v>101.0556716918945</v>
+        <v>102.0679092407227</v>
       </c>
       <c r="F182" t="n">
-        <v>13340300</v>
+        <v>8219000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B183" t="n">
-        <v>100.8869633557317</v>
+        <v>101.5717095216456</v>
       </c>
       <c r="C183" t="n">
-        <v>102.2266962072239</v>
+        <v>101.7106443291744</v>
       </c>
       <c r="D183" t="n">
-        <v>99.53730442598828</v>
+        <v>99.32889287365569</v>
       </c>
       <c r="E183" t="n">
-        <v>102.0679092407227</v>
+        <v>100.6388626098633</v>
       </c>
       <c r="F183" t="n">
-        <v>8219000</v>
+        <v>8397400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B184" t="n">
-        <v>101.5717095216456</v>
+        <v>99.67623490973834</v>
       </c>
       <c r="C184" t="n">
-        <v>101.7106443291744</v>
+        <v>100.4999176557305</v>
       </c>
       <c r="D184" t="n">
-        <v>99.32889287365569</v>
+        <v>98.495281504625</v>
       </c>
       <c r="E184" t="n">
-        <v>100.6388626098633</v>
+        <v>98.63421630859375</v>
       </c>
       <c r="F184" t="n">
-        <v>8397400</v>
+        <v>7471600</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B185" t="n">
-        <v>99.67623490973834</v>
+        <v>99.77547422442305</v>
       </c>
       <c r="C185" t="n">
-        <v>100.4999176557305</v>
+        <v>100.6984026174289</v>
       </c>
       <c r="D185" t="n">
-        <v>98.495281504625</v>
+        <v>98.25710986817649</v>
       </c>
       <c r="E185" t="n">
-        <v>98.63421630859375</v>
+        <v>98.5845947265625</v>
       </c>
       <c r="F185" t="n">
-        <v>7471600</v>
+        <v>9568000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B186" t="n">
-        <v>99.77547422442305</v>
+        <v>98.92201919170897</v>
       </c>
       <c r="C186" t="n">
-        <v>100.6984026174289</v>
+        <v>99.43806170522778</v>
       </c>
       <c r="D186" t="n">
-        <v>98.25710986817649</v>
+        <v>98.33650169977196</v>
       </c>
       <c r="E186" t="n">
-        <v>98.5845947265625</v>
+        <v>98.95178985595703</v>
       </c>
       <c r="F186" t="n">
-        <v>9568000</v>
+        <v>9501600</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B187" t="n">
-        <v>98.92201919170897</v>
+        <v>98.76323055949389</v>
       </c>
       <c r="C187" t="n">
-        <v>99.43806170522778</v>
+        <v>99.08079692509821</v>
       </c>
       <c r="D187" t="n">
-        <v>98.33650169977196</v>
+        <v>97.66167814394407</v>
       </c>
       <c r="E187" t="n">
-        <v>98.95178985595703</v>
+        <v>98.11817932128906</v>
       </c>
       <c r="F187" t="n">
-        <v>9501600</v>
+        <v>7559200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B188" t="n">
-        <v>98.76323055949389</v>
+        <v>98.29680690142362</v>
       </c>
       <c r="C188" t="n">
-        <v>99.08079692509821</v>
+        <v>99.32889186938023</v>
       </c>
       <c r="D188" t="n">
-        <v>97.66167814394407</v>
+        <v>97.7609122614967</v>
       </c>
       <c r="E188" t="n">
-        <v>98.11817932128906</v>
+        <v>98.57467651367188</v>
       </c>
       <c r="F188" t="n">
-        <v>7559200</v>
+        <v>8616300</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B189" t="n">
-        <v>98.29680690142362</v>
+        <v>98.7334588011272</v>
       </c>
       <c r="C189" t="n">
-        <v>99.32889186938023</v>
+        <v>99.00140991464168</v>
       </c>
       <c r="D189" t="n">
-        <v>97.7609122614967</v>
+        <v>97.20516831754395</v>
       </c>
       <c r="E189" t="n">
-        <v>98.57467651367188</v>
+        <v>97.86015319824219</v>
       </c>
       <c r="F189" t="n">
-        <v>8616300</v>
+        <v>7041400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B190" t="n">
-        <v>98.7334588011272</v>
+        <v>98.07848356908464</v>
       </c>
       <c r="C190" t="n">
-        <v>99.00140991464168</v>
+        <v>99.97395570346617</v>
       </c>
       <c r="D190" t="n">
-        <v>97.20516831754395</v>
+        <v>97.35403126794252</v>
       </c>
       <c r="E190" t="n">
-        <v>97.86015319824219</v>
+        <v>99.57699584960938</v>
       </c>
       <c r="F190" t="n">
-        <v>7041400</v>
+        <v>9264400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B191" t="n">
-        <v>98.07848356908464</v>
+        <v>100.2915220505157</v>
       </c>
       <c r="C191" t="n">
-        <v>99.97395570346617</v>
+        <v>100.9961221945534</v>
       </c>
       <c r="D191" t="n">
-        <v>97.35403126794252</v>
+        <v>98.78308369184245</v>
       </c>
       <c r="E191" t="n">
-        <v>99.57699584960938</v>
+        <v>99.27928161621094</v>
       </c>
       <c r="F191" t="n">
-        <v>9264400</v>
+        <v>8257200</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B192" t="n">
-        <v>100.2915220505157</v>
+        <v>100.1128870298928</v>
       </c>
       <c r="C192" t="n">
-        <v>100.9961221945534</v>
+        <v>101.6213329077368</v>
       </c>
       <c r="D192" t="n">
-        <v>98.78308369184245</v>
+        <v>99.82509133515438</v>
       </c>
       <c r="E192" t="n">
-        <v>99.27928161621094</v>
+        <v>100.9167327880859</v>
       </c>
       <c r="F192" t="n">
-        <v>8257200</v>
+        <v>10265100</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B193" t="n">
-        <v>100.1128870298928</v>
+        <v>100.658710438741</v>
       </c>
       <c r="C193" t="n">
-        <v>101.6213329077368</v>
+        <v>101.1549083591584</v>
       </c>
       <c r="D193" t="n">
-        <v>99.82509133515438</v>
+        <v>99.28920690408536</v>
       </c>
       <c r="E193" t="n">
-        <v>100.9167327880859</v>
+        <v>100.5098495483398</v>
       </c>
       <c r="F193" t="n">
-        <v>10265100</v>
+        <v>10694600</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B194" t="n">
-        <v>100.658710438741</v>
+        <v>99.90448284246082</v>
       </c>
       <c r="C194" t="n">
-        <v>101.1549083591584</v>
+        <v>101.581634158465</v>
       </c>
       <c r="D194" t="n">
-        <v>99.28920690408536</v>
+        <v>99.67623604963576</v>
       </c>
       <c r="E194" t="n">
-        <v>100.5098495483398</v>
+        <v>100.0930404663086</v>
       </c>
       <c r="F194" t="n">
-        <v>10694600</v>
+        <v>11168700</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B195" t="n">
-        <v>99.90448284246082</v>
+        <v>101.0258948980948</v>
       </c>
       <c r="C195" t="n">
-        <v>101.581634158465</v>
+        <v>103.4274909034028</v>
       </c>
       <c r="D195" t="n">
-        <v>99.67623604963576</v>
+        <v>100.0334991036985</v>
       </c>
       <c r="E195" t="n">
-        <v>100.0930404663086</v>
+        <v>103.0999984741211</v>
       </c>
       <c r="F195" t="n">
-        <v>11168700</v>
+        <v>22943600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B196" t="n">
-        <v>101.0258948980948</v>
+        <v>102.623658522444</v>
       </c>
       <c r="C196" t="n">
-        <v>103.4274909034028</v>
+        <v>103.5168087306858</v>
       </c>
       <c r="D196" t="n">
-        <v>100.0334991036985</v>
+        <v>100.7381048924391</v>
       </c>
       <c r="E196" t="n">
-        <v>103.0999984741211</v>
+        <v>101.6709518432617</v>
       </c>
       <c r="F196" t="n">
-        <v>22943600</v>
+        <v>17396300</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B197" t="n">
-        <v>102.623658522444</v>
+        <v>101.2442170259669</v>
       </c>
       <c r="C197" t="n">
-        <v>103.5168087306858</v>
+        <v>103.2488607985985</v>
       </c>
       <c r="D197" t="n">
-        <v>100.7381048924391</v>
+        <v>101.025896308111</v>
       </c>
       <c r="E197" t="n">
-        <v>101.6709518432617</v>
+        <v>102.7427368164062</v>
       </c>
       <c r="F197" t="n">
-        <v>17396300</v>
+        <v>14457400</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B198" t="n">
-        <v>101.2442170259669</v>
+        <v>102.3160060444983</v>
       </c>
       <c r="C198" t="n">
-        <v>103.2488607985985</v>
+        <v>103.7351323493811</v>
       </c>
       <c r="D198" t="n">
-        <v>101.025896308111</v>
+        <v>100.2716731077754</v>
       </c>
       <c r="E198" t="n">
-        <v>102.7427368164062</v>
+        <v>100.3510665893555</v>
       </c>
       <c r="F198" t="n">
-        <v>14457400</v>
+        <v>12215500</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B199" t="n">
-        <v>102.3160060444983</v>
+        <v>100.3411416176147</v>
       </c>
       <c r="C199" t="n">
-        <v>103.7351323493811</v>
+        <v>100.8075688628163</v>
       </c>
       <c r="D199" t="n">
-        <v>100.2716731077754</v>
+        <v>97.24486394426569</v>
       </c>
       <c r="E199" t="n">
-        <v>100.3510665893555</v>
+        <v>97.30441284179688</v>
       </c>
       <c r="F199" t="n">
-        <v>12215500</v>
+        <v>12054400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B200" t="n">
-        <v>100.3411416176147</v>
+        <v>97.30440945370802</v>
       </c>
       <c r="C200" t="n">
-        <v>100.8075688628163</v>
+        <v>98.69375749140566</v>
       </c>
       <c r="D200" t="n">
-        <v>97.24486394426569</v>
+        <v>97.15554857213215</v>
       </c>
       <c r="E200" t="n">
-        <v>97.30441284179688</v>
+        <v>98.03878021240234</v>
       </c>
       <c r="F200" t="n">
-        <v>12054400</v>
+        <v>13921400</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B201" t="n">
-        <v>97.30440945370802</v>
+        <v>98.95178655891404</v>
       </c>
       <c r="C201" t="n">
-        <v>98.69375749140566</v>
+        <v>99.27927899748993</v>
       </c>
       <c r="D201" t="n">
-        <v>97.15554857213215</v>
+        <v>97.75098852218167</v>
       </c>
       <c r="E201" t="n">
-        <v>98.03878021240234</v>
+        <v>97.87999725341797</v>
       </c>
       <c r="F201" t="n">
-        <v>13921400</v>
+        <v>10418100</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,25 +5669,25 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B202" t="n">
-        <v>98.95178655891404</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C202" t="n">
-        <v>99.27927899748993</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D202" t="n">
-        <v>97.75098852218167</v>
+        <v>95.98999786376953</v>
       </c>
       <c r="E202" t="n">
-        <v>97.87999725341797</v>
+        <v>96.25</v>
       </c>
       <c r="F202" t="n">
-        <v>10418100</v>
+        <v>12717800</v>
       </c>
       <c r="G202" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -5695,25 +5695,25 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B203" t="n">
-        <v>97.41000366210938</v>
+        <v>96.55000305175781</v>
       </c>
       <c r="C203" t="n">
-        <v>97.59999847412109</v>
+        <v>97.76000213623047</v>
       </c>
       <c r="D203" t="n">
-        <v>95.98999786376953</v>
+        <v>95.65000152587891</v>
       </c>
       <c r="E203" t="n">
-        <v>96.25</v>
+        <v>95.70999908447266</v>
       </c>
       <c r="F203" t="n">
-        <v>12717800</v>
+        <v>11590400</v>
       </c>
       <c r="G203" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B204" t="n">
-        <v>96.55000305175781</v>
+        <v>96.40000152587891</v>
       </c>
       <c r="C204" t="n">
-        <v>97.76000213623047</v>
+        <v>99.51999664306641</v>
       </c>
       <c r="D204" t="n">
-        <v>95.65000152587891</v>
+        <v>95.76999664306641</v>
       </c>
       <c r="E204" t="n">
-        <v>95.70999908447266</v>
+        <v>99.5</v>
       </c>
       <c r="F204" t="n">
-        <v>11590400</v>
+        <v>11297800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B205" t="n">
-        <v>96.40000152587891</v>
+        <v>98.84999847412109</v>
       </c>
       <c r="C205" t="n">
-        <v>99.51999664306641</v>
+        <v>99.44000244140625</v>
       </c>
       <c r="D205" t="n">
-        <v>95.76999664306641</v>
+        <v>97.01999664306641</v>
       </c>
       <c r="E205" t="n">
-        <v>99.5</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="F205" t="n">
-        <v>11297800</v>
+        <v>10171900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B206" t="n">
-        <v>98.84999847412109</v>
+        <v>98.13999938964844</v>
       </c>
       <c r="C206" t="n">
-        <v>99.44000244140625</v>
+        <v>99.04000091552734</v>
       </c>
       <c r="D206" t="n">
-        <v>97.01999664306641</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="E206" t="n">
-        <v>97.41000366210938</v>
+        <v>97.48000335693359</v>
       </c>
       <c r="F206" t="n">
-        <v>10171900</v>
+        <v>9936400</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B207" t="n">
-        <v>98.13999938964844</v>
+        <v>97.30000305175781</v>
       </c>
       <c r="C207" t="n">
-        <v>99.04000091552734</v>
+        <v>97.66000366210938</v>
       </c>
       <c r="D207" t="n">
-        <v>96.91999816894531</v>
+        <v>96.63999938964844</v>
       </c>
       <c r="E207" t="n">
-        <v>97.48000335693359</v>
+        <v>96.69999694824219</v>
       </c>
       <c r="F207" t="n">
-        <v>9936400</v>
+        <v>8720800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B208" t="n">
-        <v>97.30000305175781</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="C208" t="n">
-        <v>97.66000366210938</v>
+        <v>96.55000305175781</v>
       </c>
       <c r="D208" t="n">
-        <v>96.63999938964844</v>
+        <v>94.77999877929688</v>
       </c>
       <c r="E208" t="n">
-        <v>96.69999694824219</v>
+        <v>96.16999816894531</v>
       </c>
       <c r="F208" t="n">
-        <v>8720800</v>
+        <v>11448100</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B209" t="n">
-        <v>96.33999633789062</v>
+        <v>96.88999938964844</v>
       </c>
       <c r="C209" t="n">
-        <v>96.55000305175781</v>
+        <v>97.05000305175781</v>
       </c>
       <c r="D209" t="n">
-        <v>94.77999877929688</v>
+        <v>95.51999664306641</v>
       </c>
       <c r="E209" t="n">
-        <v>96.16999816894531</v>
+        <v>95.62000274658203</v>
       </c>
       <c r="F209" t="n">
-        <v>11448100</v>
+        <v>10678900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B210" t="n">
-        <v>96.88999938964844</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="C210" t="n">
-        <v>97.05000305175781</v>
+        <v>97.54000091552734</v>
       </c>
       <c r="D210" t="n">
-        <v>95.51999664306641</v>
+        <v>95.83000183105469</v>
       </c>
       <c r="E210" t="n">
-        <v>95.62000274658203</v>
+        <v>96</v>
       </c>
       <c r="F210" t="n">
-        <v>10678900</v>
+        <v>9304200</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>96.09999847412109</v>
+        <v>95.51000213623047</v>
       </c>
       <c r="C211" t="n">
-        <v>97.54000091552734</v>
+        <v>96.69000244140625</v>
       </c>
       <c r="D211" t="n">
-        <v>95.83000183105469</v>
+        <v>95.12999725341797</v>
       </c>
       <c r="E211" t="n">
-        <v>96</v>
+        <v>95.87000274658203</v>
       </c>
       <c r="F211" t="n">
-        <v>9304200</v>
+        <v>7651600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>95.51000213623047</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="C212" t="n">
-        <v>96.69000244140625</v>
+        <v>97.90000152587891</v>
       </c>
       <c r="D212" t="n">
-        <v>95.12999725341797</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="E212" t="n">
-        <v>95.87000274658203</v>
+        <v>97.15000152587891</v>
       </c>
       <c r="F212" t="n">
-        <v>7651600</v>
+        <v>10219200</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>96.09999847412109</v>
+        <v>97.27999877929688</v>
       </c>
       <c r="C213" t="n">
-        <v>97.90000152587891</v>
+        <v>99.84999847412109</v>
       </c>
       <c r="D213" t="n">
-        <v>96.09999847412109</v>
+        <v>97.27999877929688</v>
       </c>
       <c r="E213" t="n">
-        <v>97.15000152587891</v>
+        <v>99.70999908447266</v>
       </c>
       <c r="F213" t="n">
-        <v>10219200</v>
+        <v>7480000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B214" t="n">
-        <v>97.27999877929688</v>
+        <v>99.01000213623047</v>
       </c>
       <c r="C214" t="n">
-        <v>99.84999847412109</v>
+        <v>99.79000091552734</v>
       </c>
       <c r="D214" t="n">
-        <v>97.27999877929688</v>
+        <v>97.05000305175781</v>
       </c>
       <c r="E214" t="n">
-        <v>99.70999908447266</v>
+        <v>97.66999816894531</v>
       </c>
       <c r="F214" t="n">
-        <v>7480000</v>
+        <v>10496500</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B215" t="n">
-        <v>99.01000213623047</v>
+        <v>97.84999847412109</v>
       </c>
       <c r="C215" t="n">
-        <v>99.79000091552734</v>
+        <v>98.38999938964844</v>
       </c>
       <c r="D215" t="n">
-        <v>97.05000305175781</v>
+        <v>96</v>
       </c>
       <c r="E215" t="n">
-        <v>97.66999816894531</v>
+        <v>96.41000366210938</v>
       </c>
       <c r="F215" t="n">
-        <v>10496500</v>
+        <v>9861700</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B216" t="n">
-        <v>97.84999847412109</v>
+        <v>96</v>
       </c>
       <c r="C216" t="n">
-        <v>98.38999938964844</v>
+        <v>96.88999938964844</v>
       </c>
       <c r="D216" t="n">
-        <v>96</v>
+        <v>95.83999633789062</v>
       </c>
       <c r="E216" t="n">
-        <v>96.41000366210938</v>
+        <v>96.13999938964844</v>
       </c>
       <c r="F216" t="n">
-        <v>9861700</v>
+        <v>9745400</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B217" t="n">
-        <v>96</v>
+        <v>97.12000274658203</v>
       </c>
       <c r="C217" t="n">
-        <v>96.88999938964844</v>
+        <v>97.30000305175781</v>
       </c>
       <c r="D217" t="n">
-        <v>95.83999633789062</v>
+        <v>95.65000152587891</v>
       </c>
       <c r="E217" t="n">
-        <v>96.13999938964844</v>
+        <v>95.87000274658203</v>
       </c>
       <c r="F217" t="n">
-        <v>9745400</v>
+        <v>9119200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B218" t="n">
-        <v>97.12000274658203</v>
+        <v>94.80999755859375</v>
       </c>
       <c r="C218" t="n">
-        <v>97.30000305175781</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D218" t="n">
-        <v>95.65000152587891</v>
+        <v>92.48999786376953</v>
       </c>
       <c r="E218" t="n">
-        <v>95.87000274658203</v>
+        <v>92.83000183105469</v>
       </c>
       <c r="F218" t="n">
-        <v>9119200</v>
+        <v>13562500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B219" t="n">
-        <v>94.80999755859375</v>
+        <v>93.26000213623047</v>
       </c>
       <c r="C219" t="n">
-        <v>94.81999969482422</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="D219" t="n">
-        <v>92.48999786376953</v>
+        <v>93</v>
       </c>
       <c r="E219" t="n">
-        <v>92.83000183105469</v>
+        <v>94.84999847412109</v>
       </c>
       <c r="F219" t="n">
-        <v>13562500</v>
+        <v>12153100</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B220" t="n">
-        <v>93.26000213623047</v>
+        <v>95.51000213623047</v>
       </c>
       <c r="C220" t="n">
-        <v>96.29000091552734</v>
+        <v>97.19000244140625</v>
       </c>
       <c r="D220" t="n">
-        <v>93</v>
+        <v>95.51000213623047</v>
       </c>
       <c r="E220" t="n">
-        <v>94.84999847412109</v>
+        <v>96.65000152587891</v>
       </c>
       <c r="F220" t="n">
-        <v>12153100</v>
+        <v>10593900</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B221" t="n">
-        <v>95.51000213623047</v>
+        <v>97</v>
       </c>
       <c r="C221" t="n">
-        <v>97.19000244140625</v>
+        <v>99.23000335693359</v>
       </c>
       <c r="D221" t="n">
-        <v>95.51000213623047</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="E221" t="n">
-        <v>96.65000152587891</v>
+        <v>98.88999938964844</v>
       </c>
       <c r="F221" t="n">
-        <v>10593900</v>
+        <v>11389300</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B222" t="n">
-        <v>97</v>
+        <v>98.33999633789062</v>
       </c>
       <c r="C222" t="n">
-        <v>99.23000335693359</v>
+        <v>99.41000366210938</v>
       </c>
       <c r="D222" t="n">
-        <v>96.97000122070312</v>
+        <v>97.98999786376953</v>
       </c>
       <c r="E222" t="n">
-        <v>98.88999938964844</v>
+        <v>98.48000335693359</v>
       </c>
       <c r="F222" t="n">
-        <v>11389300</v>
+        <v>11070100</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B223" t="n">
-        <v>98.33999633789062</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C223" t="n">
-        <v>99.41000366210938</v>
+        <v>97.48000335693359</v>
       </c>
       <c r="D223" t="n">
-        <v>97.98999786376953</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E223" t="n">
-        <v>98.48000335693359</v>
+        <v>96.16000366210938</v>
       </c>
       <c r="F223" t="n">
-        <v>11070100</v>
+        <v>21112400</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B224" t="n">
-        <v>97.41000366210938</v>
+        <v>96.08000183105469</v>
       </c>
       <c r="C224" t="n">
-        <v>97.48000335693359</v>
+        <v>96.58999633789062</v>
       </c>
       <c r="D224" t="n">
-        <v>94.45999908447266</v>
+        <v>95.59999847412109</v>
       </c>
       <c r="E224" t="n">
-        <v>96.16000366210938</v>
+        <v>96.19000244140625</v>
       </c>
       <c r="F224" t="n">
-        <v>21112400</v>
+        <v>11193000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B225" t="n">
-        <v>96.08000183105469</v>
+        <v>97.62000274658203</v>
       </c>
       <c r="C225" t="n">
-        <v>96.58999633789062</v>
+        <v>99.05000305175781</v>
       </c>
       <c r="D225" t="n">
-        <v>95.59999847412109</v>
+        <v>97.20999908447266</v>
       </c>
       <c r="E225" t="n">
-        <v>96.19000244140625</v>
+        <v>98.13999938964844</v>
       </c>
       <c r="F225" t="n">
-        <v>11193000</v>
+        <v>11480300</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B226" t="n">
-        <v>97.62000274658203</v>
+        <v>97.87000274658203</v>
       </c>
       <c r="C226" t="n">
-        <v>99.05000305175781</v>
+        <v>98.56999969482422</v>
       </c>
       <c r="D226" t="n">
-        <v>97.20999908447266</v>
+        <v>97.37999725341797</v>
       </c>
       <c r="E226" t="n">
-        <v>98.13999938964844</v>
+        <v>98.18000030517578</v>
       </c>
       <c r="F226" t="n">
-        <v>11480300</v>
+        <v>16796800</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B227" t="n">
-        <v>97.87000274658203</v>
+        <v>101.9899978637695</v>
       </c>
       <c r="C227" t="n">
-        <v>98.56999969482422</v>
+        <v>103.2099990844727</v>
       </c>
       <c r="D227" t="n">
-        <v>97.37999725341797</v>
+        <v>99.69000244140625</v>
       </c>
       <c r="E227" t="n">
-        <v>98.18000030517578</v>
+        <v>101.7600021362305</v>
       </c>
       <c r="F227" t="n">
-        <v>16796800</v>
+        <v>20809000</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B228" t="n">
-        <v>101.9899978637695</v>
+        <v>102.5400009155273</v>
       </c>
       <c r="C228" t="n">
-        <v>103.2099990844727</v>
+        <v>104.7300033569336</v>
       </c>
       <c r="D228" t="n">
-        <v>99.69000244140625</v>
+        <v>102.5199966430664</v>
       </c>
       <c r="E228" t="n">
-        <v>101.7600021362305</v>
+        <v>104.6800003051758</v>
       </c>
       <c r="F228" t="n">
-        <v>20809000</v>
+        <v>14047200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B229" t="n">
-        <v>102.5400009155273</v>
+        <v>104.4199981689453</v>
       </c>
       <c r="C229" t="n">
-        <v>104.7300033569336</v>
+        <v>105.25</v>
       </c>
       <c r="D229" t="n">
-        <v>102.5199966430664</v>
+        <v>103.6999969482422</v>
       </c>
       <c r="E229" t="n">
-        <v>104.6800003051758</v>
+        <v>104.9100036621094</v>
       </c>
       <c r="F229" t="n">
-        <v>14047200</v>
+        <v>10929700</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B230" t="n">
-        <v>104.4199981689453</v>
+        <v>104.6100006103516</v>
       </c>
       <c r="C230" t="n">
-        <v>105.25</v>
+        <v>104.8000030517578</v>
       </c>
       <c r="D230" t="n">
-        <v>103.6999969482422</v>
+        <v>102.8000030517578</v>
       </c>
       <c r="E230" t="n">
-        <v>104.9100036621094</v>
+        <v>103.1800003051758</v>
       </c>
       <c r="F230" t="n">
-        <v>10929700</v>
+        <v>8631900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B231" t="n">
-        <v>104.6100006103516</v>
+        <v>102.9499969482422</v>
       </c>
       <c r="C231" t="n">
-        <v>104.8000030517578</v>
+        <v>104.0899963378906</v>
       </c>
       <c r="D231" t="n">
-        <v>102.8000030517578</v>
+        <v>102.7900009155273</v>
       </c>
       <c r="E231" t="n">
-        <v>103.1800003051758</v>
+        <v>103.5299987792969</v>
       </c>
       <c r="F231" t="n">
-        <v>8631900</v>
+        <v>6781600</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B232" t="n">
-        <v>102.9499969482422</v>
+        <v>103.2900009155273</v>
       </c>
       <c r="C232" t="n">
-        <v>104.0899963378906</v>
+        <v>103.6800003051758</v>
       </c>
       <c r="D232" t="n">
-        <v>102.7900009155273</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E232" t="n">
-        <v>103.5299987792969</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F232" t="n">
-        <v>6781600</v>
+        <v>6717500</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B233" t="n">
-        <v>103.2900009155273</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="C233" t="n">
-        <v>103.6800003051758</v>
+        <v>104.9400024414062</v>
       </c>
       <c r="D233" t="n">
-        <v>102.0299987792969</v>
+        <v>103.4599990844727</v>
       </c>
       <c r="E233" t="n">
-        <v>103.2200012207031</v>
+        <v>104.8000030517578</v>
       </c>
       <c r="F233" t="n">
-        <v>6717500</v>
+        <v>7100000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="n">
-        <v>103.8000030517578</v>
+        <v>104.9899978637695</v>
       </c>
       <c r="C234" t="n">
-        <v>104.9400024414062</v>
+        <v>107.1100006103516</v>
       </c>
       <c r="D234" t="n">
-        <v>103.4599990844727</v>
+        <v>104.9100036621094</v>
       </c>
       <c r="E234" t="n">
-        <v>104.8000030517578</v>
+        <v>106.8499984741211</v>
       </c>
       <c r="F234" t="n">
-        <v>7100000</v>
+        <v>8176900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B235" t="n">
-        <v>104.9899978637695</v>
+        <v>106.3300018310547</v>
       </c>
       <c r="C235" t="n">
-        <v>107.1100006103516</v>
+        <v>106.6399993896484</v>
       </c>
       <c r="D235" t="n">
-        <v>104.9100036621094</v>
+        <v>103.4599990844727</v>
       </c>
       <c r="E235" t="n">
-        <v>106.8499984741211</v>
+        <v>103.5</v>
       </c>
       <c r="F235" t="n">
-        <v>8176900</v>
+        <v>7635000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B236" t="n">
-        <v>106.3300018310547</v>
+        <v>104.1900024414062</v>
       </c>
       <c r="C236" t="n">
-        <v>106.6399993896484</v>
+        <v>105.2099990844727</v>
       </c>
       <c r="D236" t="n">
-        <v>103.4599990844727</v>
+        <v>103.629997253418</v>
       </c>
       <c r="E236" t="n">
-        <v>103.5</v>
+        <v>103.9499969482422</v>
       </c>
       <c r="F236" t="n">
-        <v>7635000</v>
+        <v>6149900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B237" t="n">
-        <v>104.1900024414062</v>
+        <v>104.0599975585938</v>
       </c>
       <c r="C237" t="n">
-        <v>105.2099990844727</v>
+        <v>107.0599975585938</v>
       </c>
       <c r="D237" t="n">
-        <v>103.629997253418</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="E237" t="n">
-        <v>103.9499969482422</v>
+        <v>106.9300003051758</v>
       </c>
       <c r="F237" t="n">
-        <v>6149900</v>
+        <v>8046100</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B238" t="n">
-        <v>104.0599975585938</v>
+        <v>106.879997253418</v>
       </c>
       <c r="C238" t="n">
-        <v>107.0599975585938</v>
+        <v>108.6900024414062</v>
       </c>
       <c r="D238" t="n">
-        <v>103.9599990844727</v>
+        <v>106.4199981689453</v>
       </c>
       <c r="E238" t="n">
-        <v>106.9300003051758</v>
+        <v>107.3199996948242</v>
       </c>
       <c r="F238" t="n">
-        <v>8046100</v>
+        <v>7971500</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B239" t="n">
-        <v>106.879997253418</v>
+        <v>107.5699996948242</v>
       </c>
       <c r="C239" t="n">
-        <v>108.6900024414062</v>
+        <v>108.4100036621094</v>
       </c>
       <c r="D239" t="n">
-        <v>106.4199981689453</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="E239" t="n">
-        <v>107.3199996948242</v>
+        <v>107.7799987792969</v>
       </c>
       <c r="F239" t="n">
-        <v>7971500</v>
+        <v>6840800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B240" t="n">
-        <v>107.5699996948242</v>
+        <v>108.3899993896484</v>
       </c>
       <c r="C240" t="n">
-        <v>108.4100036621094</v>
+        <v>111.870002746582</v>
       </c>
       <c r="D240" t="n">
-        <v>106.9700012207031</v>
+        <v>108.0800018310547</v>
       </c>
       <c r="E240" t="n">
-        <v>107.7799987792969</v>
+        <v>110.6100006103516</v>
       </c>
       <c r="F240" t="n">
-        <v>6840800</v>
+        <v>12658400</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B241" t="n">
-        <v>108.3899993896484</v>
+        <v>110.5</v>
       </c>
       <c r="C241" t="n">
-        <v>111.870002746582</v>
+        <v>111.5999984741211</v>
       </c>
       <c r="D241" t="n">
-        <v>108.0800018310547</v>
+        <v>109.7600021362305</v>
       </c>
       <c r="E241" t="n">
-        <v>110.6100006103516</v>
+        <v>111.25</v>
       </c>
       <c r="F241" t="n">
-        <v>12658400</v>
+        <v>6747100</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B242" t="n">
-        <v>110.5</v>
+        <v>111.3000030517578</v>
       </c>
       <c r="C242" t="n">
-        <v>111.5999984741211</v>
+        <v>111.5199966430664</v>
       </c>
       <c r="D242" t="n">
-        <v>109.7600021362305</v>
+        <v>109.4499969482422</v>
       </c>
       <c r="E242" t="n">
-        <v>111.25</v>
+        <v>109.629997253418</v>
       </c>
       <c r="F242" t="n">
-        <v>6747100</v>
+        <v>8524600</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B243" t="n">
-        <v>111.3000030517578</v>
+        <v>108.7799987792969</v>
       </c>
       <c r="C243" t="n">
-        <v>111.5199966430664</v>
+        <v>108.870002746582</v>
       </c>
       <c r="D243" t="n">
-        <v>109.4499969482422</v>
+        <v>106.7399978637695</v>
       </c>
       <c r="E243" t="n">
-        <v>109.629997253418</v>
+        <v>106.8199996948242</v>
       </c>
       <c r="F243" t="n">
-        <v>8524600</v>
+        <v>8699500</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B244" t="n">
-        <v>108.7799987792969</v>
+        <v>107.25</v>
       </c>
       <c r="C244" t="n">
-        <v>108.870002746582</v>
+        <v>108.1999969482422</v>
       </c>
       <c r="D244" t="n">
-        <v>106.7399978637695</v>
+        <v>107.0299987792969</v>
       </c>
       <c r="E244" t="n">
-        <v>106.8199996948242</v>
+        <v>108.0999984741211</v>
       </c>
       <c r="F244" t="n">
-        <v>8699500</v>
+        <v>5465900</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B245" t="n">
-        <v>107.25</v>
+        <v>107.7799987792969</v>
       </c>
       <c r="C245" t="n">
-        <v>108.1999969482422</v>
+        <v>108.0899963378906</v>
       </c>
       <c r="D245" t="n">
-        <v>107.0299987792969</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="E245" t="n">
-        <v>108.0999984741211</v>
+        <v>107.5500030517578</v>
       </c>
       <c r="F245" t="n">
-        <v>5465900</v>
+        <v>8728700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B246" t="n">
-        <v>107.7799987792969</v>
+        <v>107.2399978637695</v>
       </c>
       <c r="C246" t="n">
-        <v>108.0899963378906</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D246" t="n">
-        <v>106.9700012207031</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="E246" t="n">
-        <v>107.5500030517578</v>
+        <v>106.2200012207031</v>
       </c>
       <c r="F246" t="n">
-        <v>8728700</v>
+        <v>7033700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B247" t="n">
-        <v>107.2399978637695</v>
+        <v>106.7099990844727</v>
       </c>
       <c r="C247" t="n">
-        <v>108.9499969482422</v>
+        <v>108.9899978637695</v>
       </c>
       <c r="D247" t="n">
-        <v>106.1399993896484</v>
+        <v>106.3300018310547</v>
       </c>
       <c r="E247" t="n">
-        <v>106.2200012207031</v>
+        <v>107.9800033569336</v>
       </c>
       <c r="F247" t="n">
-        <v>7033700</v>
+        <v>7555300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B248" t="n">
-        <v>106.7099990844727</v>
+        <v>108.620002746582</v>
       </c>
       <c r="C248" t="n">
-        <v>108.9899978637695</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="D248" t="n">
-        <v>106.3300018310547</v>
+        <v>106.9000015258789</v>
       </c>
       <c r="E248" t="n">
-        <v>107.9800033569336</v>
+        <v>107.1600036621094</v>
       </c>
       <c r="F248" t="n">
-        <v>7555300</v>
+        <v>6241300</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B249" t="n">
-        <v>108.620002746582</v>
+        <v>106.4899978637695</v>
       </c>
       <c r="C249" t="n">
-        <v>109.1999969482422</v>
+        <v>106.879997253418</v>
       </c>
       <c r="D249" t="n">
-        <v>106.9000015258789</v>
+        <v>105.1699981689453</v>
       </c>
       <c r="E249" t="n">
-        <v>107.1600036621094</v>
+        <v>105.3099975585938</v>
       </c>
       <c r="F249" t="n">
-        <v>6241300</v>
+        <v>6103700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B250" t="n">
-        <v>106.4899978637695</v>
+        <v>104.6800003051758</v>
       </c>
       <c r="C250" t="n">
-        <v>106.879997253418</v>
+        <v>105.1100006103516</v>
       </c>
       <c r="D250" t="n">
-        <v>105.1699981689453</v>
+        <v>103.7099990844727</v>
       </c>
       <c r="E250" t="n">
-        <v>105.3099975585938</v>
+        <v>105.0599975585938</v>
       </c>
       <c r="F250" t="n">
-        <v>6103700</v>
+        <v>7395400</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B251" t="n">
-        <v>104.6800003051758</v>
+        <v>104.4499969482422</v>
       </c>
       <c r="C251" t="n">
-        <v>105.1100006103516</v>
+        <v>104.9300003051758</v>
       </c>
       <c r="D251" t="n">
-        <v>103.7099990844727</v>
+        <v>102.9899978637695</v>
       </c>
       <c r="E251" t="n">
-        <v>105.0599975585938</v>
+        <v>104.1800003051758</v>
       </c>
       <c r="F251" t="n">
-        <v>7395400</v>
+        <v>7038100</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B252" t="n">
-        <v>104.4499969482422</v>
+        <v>103.6900024414062</v>
       </c>
       <c r="C252" t="n">
-        <v>104.9300003051758</v>
+        <v>106.120002746582</v>
       </c>
       <c r="D252" t="n">
-        <v>102.9899978637695</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="E252" t="n">
-        <v>104.1800003051758</v>
+        <v>105.8199996948242</v>
       </c>
       <c r="F252" t="n">
-        <v>7038100</v>
+        <v>7607600</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -11128,37 +11128,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>105.82</v>
+      </c>
+      <c r="D2" t="n">
         <v>104.18</v>
       </c>
-      <c r="D2" t="n">
-        <v>105.06</v>
-      </c>
       <c r="E2" t="n">
-        <v>104.45</v>
+        <v>103.69</v>
       </c>
       <c r="F2" t="n">
-        <v>104.93</v>
+        <v>105.86</v>
       </c>
       <c r="G2" t="n">
-        <v>102.99</v>
+        <v>103.57</v>
       </c>
       <c r="H2" t="n">
-        <v>7036870</v>
+        <v>7387622</v>
       </c>
       <c r="I2" t="n">
-        <v>10456372</v>
+        <v>10419875</v>
       </c>
       <c r="J2" t="n">
-        <v>179886243840</v>
+        <v>182718005248</v>
       </c>
       <c r="K2" t="n">
-        <v>21.659044</v>
+        <v>21.464504</v>
       </c>
       <c r="L2" t="n">
-        <v>13.937665</v>
+        <v>14.157071</v>
       </c>
       <c r="M2" t="n">
-        <v>4.81</v>
+        <v>4.93</v>
       </c>
       <c r="N2" t="n">
         <v>117.17</v>
@@ -11194,7 +11194,7 @@
         <v>63.602</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.6379988</v>
+        <v>1.6637841</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.483</v>
@@ -11206,7 +11206,7 @@
         <v>98860998656</v>
       </c>
       <c r="AC2" t="n">
-        <v>227552247808</v>
+        <v>230384009216</v>
       </c>
       <c r="AD2" t="n">
         <v>20963000320</v>
@@ -11233,7 +11233,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:59:54</t>
+          <t>2026-09-11 19:03:29</t>
         </is>
       </c>
     </row>

--- a/data/DIS_data.xlsx
+++ b/data/DIS_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B2" t="n">
-        <v>113.8021202611286</v>
+        <v>114.6005610358709</v>
       </c>
       <c r="C2" t="n">
-        <v>115.4975710271905</v>
+        <v>115.3398558853256</v>
       </c>
       <c r="D2" t="n">
-        <v>112.9938248401568</v>
+        <v>113.4571147255429</v>
       </c>
       <c r="E2" t="n">
-        <v>115.4088592529297</v>
+        <v>114.3048400878906</v>
       </c>
       <c r="F2" t="n">
-        <v>8399100</v>
+        <v>7640900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B3" t="n">
-        <v>114.6005686850037</v>
+        <v>114.45269990472</v>
       </c>
       <c r="C3" t="n">
-        <v>115.3398635838033</v>
+        <v>115.0835642376594</v>
       </c>
       <c r="D3" t="n">
-        <v>113.4571222983551</v>
+        <v>113.3585429321699</v>
       </c>
       <c r="E3" t="n">
-        <v>114.3048477172852</v>
+        <v>113.9696960449219</v>
       </c>
       <c r="F3" t="n">
-        <v>7640900</v>
+        <v>7150900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B4" t="n">
-        <v>114.452707566448</v>
+        <v>113.8021196226455</v>
       </c>
       <c r="C4" t="n">
-        <v>115.0835719416188</v>
+        <v>114.1964117205285</v>
       </c>
       <c r="D4" t="n">
-        <v>113.3585505206524</v>
+        <v>113.0726841298844</v>
       </c>
       <c r="E4" t="n">
-        <v>113.9697036743164</v>
+        <v>113.5852661132812</v>
       </c>
       <c r="F4" t="n">
-        <v>7150900</v>
+        <v>6844900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B5" t="n">
-        <v>113.8021272666058</v>
+        <v>113.5951227912625</v>
       </c>
       <c r="C5" t="n">
-        <v>114.196419390973</v>
+        <v>114.9948601742622</v>
       </c>
       <c r="D5" t="n">
-        <v>113.0726917248494</v>
+        <v>113.5754115697539</v>
       </c>
       <c r="E5" t="n">
-        <v>113.5852737426758</v>
+        <v>114.4428482055664</v>
       </c>
       <c r="F5" t="n">
-        <v>6844900</v>
+        <v>7333900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B6" t="n">
-        <v>113.595115218382</v>
+        <v>113.6838432123518</v>
       </c>
       <c r="C6" t="n">
-        <v>114.9948525080674</v>
+        <v>114.1274171453944</v>
       </c>
       <c r="D6" t="n">
-        <v>113.5754039981875</v>
+        <v>112.4221144494342</v>
       </c>
       <c r="E6" t="n">
-        <v>114.4428405761719</v>
+        <v>113.2205505371094</v>
       </c>
       <c r="F6" t="n">
-        <v>7333900</v>
+        <v>9460500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B7" t="n">
-        <v>113.6838355517382</v>
+        <v>112.9642523554146</v>
       </c>
       <c r="C7" t="n">
-        <v>114.1274094548904</v>
+        <v>112.9642523554146</v>
       </c>
       <c r="D7" t="n">
-        <v>112.4221068738425</v>
+        <v>110.3323644761722</v>
       </c>
       <c r="E7" t="n">
-        <v>113.2205429077148</v>
+        <v>112.1362457275391</v>
       </c>
       <c r="F7" t="n">
-        <v>9460500</v>
+        <v>23398400</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B8" t="n">
-        <v>112.9642523554146</v>
+        <v>110.1647924763258</v>
       </c>
       <c r="C8" t="n">
-        <v>112.9642523554146</v>
+        <v>112.0080961635035</v>
       </c>
       <c r="D8" t="n">
-        <v>110.3323644761722</v>
+        <v>109.9282127085895</v>
       </c>
       <c r="E8" t="n">
-        <v>112.1362457275391</v>
+        <v>110.953369140625</v>
       </c>
       <c r="F8" t="n">
-        <v>23398400</v>
+        <v>15479800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B9" t="n">
-        <v>110.1647924763258</v>
+        <v>111.111089276602</v>
       </c>
       <c r="C9" t="n">
-        <v>112.0080961635035</v>
+        <v>111.9982446066948</v>
       </c>
       <c r="D9" t="n">
-        <v>109.9282127085895</v>
+        <v>110.0070729190981</v>
       </c>
       <c r="E9" t="n">
-        <v>110.953369140625</v>
+        <v>110.6477966308594</v>
       </c>
       <c r="F9" t="n">
-        <v>15479800</v>
+        <v>13145000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B10" t="n">
-        <v>111.1110969379416</v>
+        <v>110.8055211263376</v>
       </c>
       <c r="C10" t="n">
-        <v>111.9982523292055</v>
+        <v>112.5206831561622</v>
       </c>
       <c r="D10" t="n">
-        <v>110.0070805043135</v>
+        <v>110.5985119402154</v>
       </c>
       <c r="E10" t="n">
-        <v>110.6478042602539</v>
+        <v>111.8109588623047</v>
       </c>
       <c r="F10" t="n">
-        <v>13145000</v>
+        <v>8755200</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B11" t="n">
-        <v>110.8055211263376</v>
+        <v>111.1012331951749</v>
       </c>
       <c r="C11" t="n">
-        <v>112.5206831561622</v>
+        <v>112.4221106191933</v>
       </c>
       <c r="D11" t="n">
-        <v>110.5985119402154</v>
+        <v>111.0420920115833</v>
       </c>
       <c r="E11" t="n">
-        <v>111.8109588623047</v>
+        <v>111.3772354125977</v>
       </c>
       <c r="F11" t="n">
-        <v>8755200</v>
+        <v>6365500</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B12" t="n">
-        <v>111.1012331951749</v>
+        <v>111.5152366513407</v>
       </c>
       <c r="C12" t="n">
-        <v>112.4221106191933</v>
+        <v>111.9489587195086</v>
       </c>
       <c r="D12" t="n">
-        <v>111.0420920115833</v>
+        <v>111.1505226581053</v>
       </c>
       <c r="E12" t="n">
-        <v>111.3772354125977</v>
+        <v>111.8503875732422</v>
       </c>
       <c r="F12" t="n">
-        <v>6365500</v>
+        <v>6145700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B13" t="n">
-        <v>111.5152366513407</v>
+        <v>111.8503861885936</v>
       </c>
       <c r="C13" t="n">
-        <v>111.9489587195086</v>
+        <v>113.3684058878927</v>
       </c>
       <c r="D13" t="n">
-        <v>111.1505226581053</v>
+        <v>111.7123850814297</v>
       </c>
       <c r="E13" t="n">
-        <v>111.8503875732422</v>
+        <v>113.1416854858398</v>
       </c>
       <c r="F13" t="n">
-        <v>6145700</v>
+        <v>9304100</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B14" t="n">
-        <v>111.8503861885936</v>
+        <v>112.8952551010659</v>
       </c>
       <c r="C14" t="n">
-        <v>113.3684058878927</v>
+        <v>113.2402578727591</v>
       </c>
       <c r="D14" t="n">
-        <v>111.7123850814297</v>
+        <v>111.7222381568123</v>
       </c>
       <c r="E14" t="n">
-        <v>113.1416854858398</v>
+        <v>112.8656845092773</v>
       </c>
       <c r="F14" t="n">
-        <v>9304100</v>
+        <v>9303700</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B15" t="n">
-        <v>112.8952551010659</v>
+        <v>112.4516824751333</v>
       </c>
       <c r="C15" t="n">
-        <v>113.2402578727591</v>
+        <v>114.4034167605612</v>
       </c>
       <c r="D15" t="n">
-        <v>111.7222381568123</v>
+        <v>111.1800943701441</v>
       </c>
       <c r="E15" t="n">
-        <v>112.8656845092773</v>
+        <v>111.3378067016602</v>
       </c>
       <c r="F15" t="n">
-        <v>9303700</v>
+        <v>9736300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B16" t="n">
-        <v>112.4516824751333</v>
+        <v>111.3673895222522</v>
       </c>
       <c r="C16" t="n">
-        <v>114.4034167605612</v>
+        <v>111.5546724538137</v>
       </c>
       <c r="D16" t="n">
-        <v>111.1800943701441</v>
+        <v>109.1987865883829</v>
       </c>
       <c r="E16" t="n">
-        <v>111.3378067016602</v>
+        <v>110.5393753051758</v>
       </c>
       <c r="F16" t="n">
-        <v>9736300</v>
+        <v>8695100</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B17" t="n">
-        <v>111.3673818357084</v>
+        <v>110.4407994688091</v>
       </c>
       <c r="C17" t="n">
-        <v>111.5546647543437</v>
+        <v>111.9489598311001</v>
       </c>
       <c r="D17" t="n">
-        <v>109.1987790515154</v>
+        <v>109.9676474333371</v>
       </c>
       <c r="E17" t="n">
-        <v>110.5393676757812</v>
+        <v>110.8646621704102</v>
       </c>
       <c r="F17" t="n">
-        <v>8695100</v>
+        <v>7148400</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B18" t="n">
-        <v>110.4407994688091</v>
+        <v>111.0815219633868</v>
       </c>
       <c r="C18" t="n">
-        <v>111.9489598311001</v>
+        <v>111.4955252894808</v>
       </c>
       <c r="D18" t="n">
-        <v>109.9676474333371</v>
+        <v>109.8592156856383</v>
       </c>
       <c r="E18" t="n">
-        <v>110.8646621704102</v>
+        <v>111.1406631469727</v>
       </c>
       <c r="F18" t="n">
-        <v>7148400</v>
+        <v>6141200</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B19" t="n">
-        <v>111.0815219633868</v>
+        <v>111.0223763857341</v>
       </c>
       <c r="C19" t="n">
-        <v>111.4955252894808</v>
+        <v>111.7813900254436</v>
       </c>
       <c r="D19" t="n">
-        <v>109.8592156856383</v>
+        <v>110.20422908127</v>
       </c>
       <c r="E19" t="n">
-        <v>111.1406631469727</v>
+        <v>110.9238052368164</v>
       </c>
       <c r="F19" t="n">
-        <v>6141200</v>
+        <v>5409800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B20" t="n">
-        <v>111.0223763857341</v>
+        <v>111.1998048136618</v>
       </c>
       <c r="C20" t="n">
-        <v>111.7813900254436</v>
+        <v>111.584237549633</v>
       </c>
       <c r="D20" t="n">
-        <v>110.20422908127</v>
+        <v>110.0563659765542</v>
       </c>
       <c r="E20" t="n">
-        <v>110.9238052368164</v>
+        <v>110.2929382324219</v>
       </c>
       <c r="F20" t="n">
-        <v>5409800</v>
+        <v>7074400</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B21" t="n">
-        <v>111.1998048136618</v>
+        <v>110.2239394253812</v>
       </c>
       <c r="C21" t="n">
-        <v>111.584237549633</v>
+        <v>111.3870970225426</v>
       </c>
       <c r="D21" t="n">
-        <v>110.0563659765542</v>
+        <v>109.2973540878383</v>
       </c>
       <c r="E21" t="n">
-        <v>110.2929382324219</v>
+        <v>109.4057846069336</v>
       </c>
       <c r="F21" t="n">
-        <v>7074400</v>
+        <v>6502400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B22" t="n">
-        <v>110.2239317389327</v>
+        <v>109.9380737221385</v>
       </c>
       <c r="C22" t="n">
-        <v>111.3870892549816</v>
+        <v>111.0716606845381</v>
       </c>
       <c r="D22" t="n">
-        <v>109.2973464660052</v>
+        <v>107.5526174321997</v>
       </c>
       <c r="E22" t="n">
-        <v>109.4057769775391</v>
+        <v>107.631477355957</v>
       </c>
       <c r="F22" t="n">
-        <v>6502400</v>
+        <v>9635200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B23" t="n">
-        <v>109.9380737221385</v>
+        <v>108.8143424328862</v>
       </c>
       <c r="C23" t="n">
-        <v>111.0716606845381</v>
+        <v>109.3762062096973</v>
       </c>
       <c r="D23" t="n">
-        <v>107.5526174321997</v>
+        <v>107.8187566106434</v>
       </c>
       <c r="E23" t="n">
-        <v>107.631477355957</v>
+        <v>108.6960525512695</v>
       </c>
       <c r="F23" t="n">
-        <v>9635200</v>
+        <v>7435100</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B24" t="n">
-        <v>108.8143500705835</v>
+        <v>108.0849128268841</v>
       </c>
       <c r="C24" t="n">
-        <v>109.3762138868319</v>
+        <v>110.2436487598859</v>
       </c>
       <c r="D24" t="n">
-        <v>107.8187641784603</v>
+        <v>107.641331387133</v>
       </c>
       <c r="E24" t="n">
-        <v>108.6960601806641</v>
+        <v>109.5832138061523</v>
       </c>
       <c r="F24" t="n">
-        <v>7435100</v>
+        <v>7898000</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B25" t="n">
-        <v>108.0849128268841</v>
+        <v>109.8789291603083</v>
       </c>
       <c r="C25" t="n">
-        <v>110.2436487598859</v>
+        <v>111.0716572685961</v>
       </c>
       <c r="D25" t="n">
-        <v>107.641331387133</v>
+        <v>109.5536376251855</v>
       </c>
       <c r="E25" t="n">
-        <v>109.5832138061523</v>
+        <v>110.1155014038086</v>
       </c>
       <c r="F25" t="n">
-        <v>7898000</v>
+        <v>7012600</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B26" t="n">
-        <v>109.8789291603083</v>
+        <v>110.1943638011324</v>
       </c>
       <c r="C26" t="n">
-        <v>111.0716572685961</v>
+        <v>110.4900772320282</v>
       </c>
       <c r="D26" t="n">
-        <v>109.5536376251855</v>
+        <v>106.9611821588295</v>
       </c>
       <c r="E26" t="n">
-        <v>110.1155014038086</v>
+        <v>108.3116226196289</v>
       </c>
       <c r="F26" t="n">
-        <v>7012600</v>
+        <v>7531200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B27" t="n">
-        <v>110.1943638011324</v>
+        <v>108.1736289318545</v>
       </c>
       <c r="C27" t="n">
-        <v>110.4900772320282</v>
+        <v>109.8690797923661</v>
       </c>
       <c r="D27" t="n">
-        <v>106.9611821588295</v>
+        <v>107.8779154806818</v>
       </c>
       <c r="E27" t="n">
-        <v>108.3116226196289</v>
+        <v>109.0903549194336</v>
       </c>
       <c r="F27" t="n">
-        <v>7531200</v>
+        <v>10090500</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B28" t="n">
-        <v>108.1736213665725</v>
+        <v>109.4452125270959</v>
       </c>
       <c r="C28" t="n">
-        <v>109.8690721085103</v>
+        <v>110.6478000651592</v>
       </c>
       <c r="D28" t="n">
-        <v>107.877907936081</v>
+        <v>109.0213498295899</v>
       </c>
       <c r="E28" t="n">
-        <v>109.0903472900391</v>
+        <v>110.3619384765625</v>
       </c>
       <c r="F28" t="n">
-        <v>10090500</v>
+        <v>8047500</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B29" t="n">
-        <v>109.4452125270959</v>
+        <v>110.6477986393913</v>
       </c>
       <c r="C29" t="n">
-        <v>110.6478000651592</v>
+        <v>112.9051132067436</v>
       </c>
       <c r="D29" t="n">
-        <v>109.0213498295899</v>
+        <v>110.4407969786948</v>
       </c>
       <c r="E29" t="n">
-        <v>110.3619384765625</v>
+        <v>112.6685409545898</v>
       </c>
       <c r="F29" t="n">
-        <v>8047500</v>
+        <v>8163200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B30" t="n">
-        <v>110.6477986393913</v>
+        <v>112.3728242428528</v>
       </c>
       <c r="C30" t="n">
-        <v>112.9051132067436</v>
+        <v>112.6488264675382</v>
       </c>
       <c r="D30" t="n">
-        <v>110.4407969786948</v>
+        <v>111.3673864928563</v>
       </c>
       <c r="E30" t="n">
-        <v>112.6685409545898</v>
+        <v>111.4659576416016</v>
       </c>
       <c r="F30" t="n">
-        <v>8163200</v>
+        <v>7569200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B31" t="n">
-        <v>112.3728165513869</v>
+        <v>111.5546728695406</v>
       </c>
       <c r="C31" t="n">
-        <v>112.6488187571811</v>
+        <v>112.2052560082749</v>
       </c>
       <c r="D31" t="n">
-        <v>111.3673788702085</v>
+        <v>110.3028034487141</v>
       </c>
       <c r="E31" t="n">
-        <v>111.465950012207</v>
+        <v>111.4166717529297</v>
       </c>
       <c r="F31" t="n">
-        <v>7569200</v>
+        <v>6945400</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B32" t="n">
-        <v>111.5546652306962</v>
+        <v>111.6138166065038</v>
       </c>
       <c r="C32" t="n">
-        <v>112.2052483248811</v>
+        <v>112.0278199378997</v>
       </c>
       <c r="D32" t="n">
-        <v>110.3027958955931</v>
+        <v>109.9972182029886</v>
       </c>
       <c r="E32" t="n">
-        <v>111.4166641235352</v>
+        <v>110.0859375</v>
       </c>
       <c r="F32" t="n">
-        <v>6945400</v>
+        <v>6235200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B33" t="n">
-        <v>111.6138166065038</v>
+        <v>110.34222664747</v>
       </c>
       <c r="C33" t="n">
-        <v>112.0278199378997</v>
+        <v>110.992802225815</v>
       </c>
       <c r="D33" t="n">
-        <v>109.9972182029886</v>
+        <v>109.721214140304</v>
       </c>
       <c r="E33" t="n">
-        <v>110.0859375</v>
+        <v>110.7365112304688</v>
       </c>
       <c r="F33" t="n">
-        <v>6235200</v>
+        <v>6029600</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B34" t="n">
-        <v>110.34222664747</v>
+        <v>110.3126569642538</v>
       </c>
       <c r="C34" t="n">
-        <v>110.992802225815</v>
+        <v>110.8745207722</v>
       </c>
       <c r="D34" t="n">
-        <v>109.721214140304</v>
+        <v>109.8690755239826</v>
       </c>
       <c r="E34" t="n">
-        <v>110.7365112304688</v>
+        <v>110.0563659667969</v>
       </c>
       <c r="F34" t="n">
-        <v>6029600</v>
+        <v>6839400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B35" t="n">
-        <v>110.3126569642538</v>
+        <v>109.59306628145</v>
       </c>
       <c r="C35" t="n">
-        <v>110.8745207722</v>
+        <v>109.9380690325516</v>
       </c>
       <c r="D35" t="n">
-        <v>109.8690755239826</v>
+        <v>108.4397681475551</v>
       </c>
       <c r="E35" t="n">
-        <v>110.0563659667969</v>
+        <v>108.6664810180664</v>
       </c>
       <c r="F35" t="n">
-        <v>6839400</v>
+        <v>7097100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B36" t="n">
-        <v>109.5930739758994</v>
+        <v>108.5580608670909</v>
       </c>
       <c r="C36" t="n">
-        <v>109.9380767512234</v>
+        <v>111.9588219337512</v>
       </c>
       <c r="D36" t="n">
-        <v>108.4397757610322</v>
+        <v>107.9863451909205</v>
       </c>
       <c r="E36" t="n">
-        <v>108.6664886474609</v>
+        <v>110.24365234375</v>
       </c>
       <c r="F36" t="n">
-        <v>7097100</v>
+        <v>8311300</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B37" t="n">
-        <v>108.5580608670909</v>
+        <v>109.98736338598</v>
       </c>
       <c r="C37" t="n">
-        <v>111.9588219337512</v>
+        <v>111.485664339403</v>
       </c>
       <c r="D37" t="n">
-        <v>107.9863451909205</v>
+        <v>108.9523475649108</v>
       </c>
       <c r="E37" t="n">
-        <v>110.24365234375</v>
+        <v>111.0125198364258</v>
       </c>
       <c r="F37" t="n">
-        <v>8311300</v>
+        <v>8700600</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>109.9873709449201</v>
+        <v>110.9435236572715</v>
       </c>
       <c r="C38" t="n">
-        <v>111.4856720013147</v>
+        <v>111.1998071396153</v>
       </c>
       <c r="D38" t="n">
-        <v>108.9523550527189</v>
+        <v>109.4452151242777</v>
       </c>
       <c r="E38" t="n">
-        <v>111.0125274658203</v>
+        <v>110.519660949707</v>
       </c>
       <c r="F38" t="n">
-        <v>8700600</v>
+        <v>8542300</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>110.9435236572715</v>
+        <v>109.3860659107013</v>
       </c>
       <c r="C39" t="n">
-        <v>111.1998071396153</v>
+        <v>110.1943613029524</v>
       </c>
       <c r="D39" t="n">
-        <v>109.4452151242777</v>
+        <v>109.0607743756439</v>
       </c>
       <c r="E39" t="n">
-        <v>110.519660949707</v>
+        <v>109.8789291381836</v>
       </c>
       <c r="F39" t="n">
-        <v>8542300</v>
+        <v>7950100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>109.3860735058741</v>
+        <v>109.7606408126771</v>
       </c>
       <c r="C40" t="n">
-        <v>110.1943689542488</v>
+        <v>110.3717939308002</v>
       </c>
       <c r="D40" t="n">
-        <v>109.0607819482302</v>
+        <v>109.0213459609701</v>
       </c>
       <c r="E40" t="n">
-        <v>109.8789367675781</v>
+        <v>109.7705001831055</v>
       </c>
       <c r="F40" t="n">
-        <v>7950100</v>
+        <v>5746000</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>109.7606408126771</v>
+        <v>109.5832124067878</v>
       </c>
       <c r="C41" t="n">
-        <v>110.3717939308002</v>
+        <v>110.115505615394</v>
       </c>
       <c r="D41" t="n">
-        <v>109.0213459609701</v>
+        <v>107.6216187917271</v>
       </c>
       <c r="E41" t="n">
-        <v>109.7705001831055</v>
+        <v>108.9129180908203</v>
       </c>
       <c r="F41" t="n">
-        <v>5746000</v>
+        <v>10291800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B42" t="n">
-        <v>109.5832124067878</v>
+        <v>108.6862030385313</v>
       </c>
       <c r="C42" t="n">
-        <v>110.115505615394</v>
+        <v>109.8395012072324</v>
       </c>
       <c r="D42" t="n">
-        <v>107.6216187917271</v>
+        <v>108.4693420111524</v>
       </c>
       <c r="E42" t="n">
-        <v>108.9129180908203</v>
+        <v>109.1593475341797</v>
       </c>
       <c r="F42" t="n">
-        <v>10291800</v>
+        <v>8782100</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>108.6862106348567</v>
+        <v>109.5635011857433</v>
       </c>
       <c r="C43" t="n">
-        <v>109.8395088841645</v>
+        <v>111.1800920323978</v>
       </c>
       <c r="D43" t="n">
-        <v>108.4693495923209</v>
+        <v>109.4452112992212</v>
       </c>
       <c r="E43" t="n">
-        <v>109.1593551635742</v>
+        <v>110.637939453125</v>
       </c>
       <c r="F43" t="n">
-        <v>8782100</v>
+        <v>9158700</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>109.5635011857433</v>
+        <v>111.0420979461576</v>
       </c>
       <c r="C44" t="n">
-        <v>111.1800920323978</v>
+        <v>113.3289832533765</v>
       </c>
       <c r="D44" t="n">
-        <v>109.4452112992212</v>
+        <v>110.8153775294455</v>
       </c>
       <c r="E44" t="n">
-        <v>110.637939453125</v>
+        <v>113.210693359375</v>
       </c>
       <c r="F44" t="n">
-        <v>9158700</v>
+        <v>9713300</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>111.0420904629071</v>
+        <v>112.9346801407027</v>
       </c>
       <c r="C45" t="n">
-        <v>113.3289756160103</v>
+        <v>115.4187075091099</v>
       </c>
       <c r="D45" t="n">
-        <v>110.815370061474</v>
+        <v>112.7572490772096</v>
       </c>
       <c r="E45" t="n">
-        <v>113.2106857299805</v>
+        <v>114.984992980957</v>
       </c>
       <c r="F45" t="n">
-        <v>9713300</v>
+        <v>15248700</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>112.9346876340564</v>
+        <v>107.3357644371155</v>
       </c>
       <c r="C46" t="n">
-        <v>115.4187151672819</v>
+        <v>107.7990571232513</v>
       </c>
       <c r="D46" t="n">
-        <v>112.7572565587906</v>
+        <v>103.4125769427048</v>
       </c>
       <c r="E46" t="n">
-        <v>114.9850006103516</v>
+        <v>106.0740356445312</v>
       </c>
       <c r="F46" t="n">
-        <v>15248700</v>
+        <v>44045400</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B47" t="n">
-        <v>107.3357567169709</v>
+        <v>105.9853145518839</v>
       </c>
       <c r="C47" t="n">
-        <v>107.7990493697842</v>
+        <v>107.1780502864732</v>
       </c>
       <c r="D47" t="n">
-        <v>103.4125695047362</v>
+        <v>103.7970079445177</v>
       </c>
       <c r="E47" t="n">
-        <v>106.0740280151367</v>
+        <v>104.2898712158203</v>
       </c>
       <c r="F47" t="n">
-        <v>44045400</v>
+        <v>16691400</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>105.9853067984581</v>
+        <v>104.2405758139031</v>
       </c>
       <c r="C48" t="n">
-        <v>107.178042445792</v>
+        <v>106.1331688606407</v>
       </c>
       <c r="D48" t="n">
-        <v>103.797000351179</v>
+        <v>103.6195708355819</v>
       </c>
       <c r="E48" t="n">
-        <v>104.2898635864258</v>
+        <v>104.1814346313477</v>
       </c>
       <c r="F48" t="n">
-        <v>16691400</v>
+        <v>12296400</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>104.2405758139031</v>
+        <v>103.5998505812639</v>
       </c>
       <c r="C49" t="n">
-        <v>106.1331688606407</v>
+        <v>105.5515923025468</v>
       </c>
       <c r="D49" t="n">
-        <v>103.6195708355819</v>
+        <v>103.501279438279</v>
       </c>
       <c r="E49" t="n">
-        <v>104.1814346313477</v>
+        <v>104.7630081176758</v>
       </c>
       <c r="F49" t="n">
-        <v>12296400</v>
+        <v>11796200</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>103.5998505812639</v>
+        <v>104.5658729007312</v>
       </c>
       <c r="C50" t="n">
-        <v>105.5515923025468</v>
+        <v>106.0543145575675</v>
       </c>
       <c r="D50" t="n">
-        <v>103.501279438279</v>
+        <v>102.5944198257724</v>
       </c>
       <c r="E50" t="n">
-        <v>104.7630081176758</v>
+        <v>103.1759948730469</v>
       </c>
       <c r="F50" t="n">
-        <v>11796200</v>
+        <v>12790000</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>104.5658651685615</v>
+        <v>103.8660034269339</v>
       </c>
       <c r="C51" t="n">
-        <v>106.0543067153343</v>
+        <v>104.2898661203646</v>
       </c>
       <c r="D51" t="n">
-        <v>102.5944122393827</v>
+        <v>101.0369656805012</v>
       </c>
       <c r="E51" t="n">
-        <v>103.1759872436523</v>
+        <v>101.2341079711914</v>
       </c>
       <c r="F51" t="n">
-        <v>12790000</v>
+        <v>12609900</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B52" t="n">
-        <v>103.8660034269339</v>
+        <v>102.0029806312501</v>
       </c>
       <c r="C52" t="n">
-        <v>104.2898661203646</v>
+        <v>103.2844205576738</v>
       </c>
       <c r="D52" t="n">
-        <v>101.0369656805012</v>
+        <v>101.2242558006444</v>
       </c>
       <c r="E52" t="n">
-        <v>101.2341079711914</v>
+        <v>102.7915573120117</v>
       </c>
       <c r="F52" t="n">
-        <v>12609900</v>
+        <v>10785400</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>102.0029806312501</v>
+        <v>102.6042684356238</v>
       </c>
       <c r="C53" t="n">
-        <v>103.2844205576738</v>
+        <v>102.85070006221</v>
       </c>
       <c r="D53" t="n">
-        <v>101.2242558006444</v>
+        <v>100.4356731298631</v>
       </c>
       <c r="E53" t="n">
-        <v>102.7915573120117</v>
+        <v>100.4849624633789</v>
       </c>
       <c r="F53" t="n">
-        <v>10785400</v>
+        <v>15024800</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>102.6042684356238</v>
+        <v>101.0271004353643</v>
       </c>
       <c r="C54" t="n">
-        <v>102.85070006221</v>
+        <v>102.4366895412752</v>
       </c>
       <c r="D54" t="n">
-        <v>100.4356731298631</v>
+        <v>100.5440965869111</v>
       </c>
       <c r="E54" t="n">
-        <v>100.4849624633789</v>
+        <v>101.8353958129883</v>
       </c>
       <c r="F54" t="n">
-        <v>15024800</v>
+        <v>10574500</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>101.0271004353643</v>
+        <v>101.8452666826232</v>
       </c>
       <c r="C55" t="n">
-        <v>102.4366895412752</v>
+        <v>102.7619926734798</v>
       </c>
       <c r="D55" t="n">
-        <v>100.5440965869111</v>
+        <v>101.4115445947565</v>
       </c>
       <c r="E55" t="n">
-        <v>101.8353958129883</v>
+        <v>101.9536972045898</v>
       </c>
       <c r="F55" t="n">
-        <v>10574500</v>
+        <v>10130200</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B56" t="n">
-        <v>101.8452666826232</v>
+        <v>101.8255455445372</v>
       </c>
       <c r="C56" t="n">
-        <v>102.7619926734798</v>
+        <v>103.2449865221035</v>
       </c>
       <c r="D56" t="n">
-        <v>101.4115445947565</v>
+        <v>101.7663968434539</v>
       </c>
       <c r="E56" t="n">
-        <v>101.9536972045898</v>
+        <v>102.9788436889648</v>
       </c>
       <c r="F56" t="n">
-        <v>10130200</v>
+        <v>6525500</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B57" t="n">
-        <v>101.8255530884873</v>
+        <v>103.4224248942611</v>
       </c>
       <c r="C57" t="n">
-        <v>103.2449941712158</v>
+        <v>105.3051661613186</v>
       </c>
       <c r="D57" t="n">
-        <v>101.7664043830219</v>
+        <v>102.9788509675128</v>
       </c>
       <c r="E57" t="n">
-        <v>102.9788513183594</v>
+        <v>105.2460174560547</v>
       </c>
       <c r="F57" t="n">
-        <v>6525500</v>
+        <v>12628900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B58" t="n">
-        <v>103.4224248942611</v>
+        <v>105.0094417410337</v>
       </c>
       <c r="C58" t="n">
-        <v>105.3051661613186</v>
+        <v>105.0488717030799</v>
       </c>
       <c r="D58" t="n">
-        <v>102.9788509675128</v>
+        <v>103.3238503461612</v>
       </c>
       <c r="E58" t="n">
-        <v>105.2460174560547</v>
+        <v>103.3337097167969</v>
       </c>
       <c r="F58" t="n">
-        <v>12628900</v>
+        <v>8548200</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B59" t="n">
-        <v>105.0094494941518</v>
+        <v>103.4027062810859</v>
       </c>
       <c r="C59" t="n">
-        <v>105.0488794591093</v>
+        <v>104.339143401945</v>
       </c>
       <c r="D59" t="n">
-        <v>103.3238579748278</v>
+        <v>102.978843606061</v>
       </c>
       <c r="E59" t="n">
-        <v>103.3337173461914</v>
+        <v>104.230712890625</v>
       </c>
       <c r="F59" t="n">
-        <v>8548200</v>
+        <v>10177800</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B60" t="n">
-        <v>103.4027138498727</v>
+        <v>104.3292907185565</v>
       </c>
       <c r="C60" t="n">
-        <v>104.3391510392764</v>
+        <v>104.7038716073053</v>
       </c>
       <c r="D60" t="n">
-        <v>102.9788511438223</v>
+        <v>103.0182801694252</v>
       </c>
       <c r="E60" t="n">
-        <v>104.2307205200195</v>
+        <v>103.9645767211914</v>
       </c>
       <c r="F60" t="n">
-        <v>10177800</v>
+        <v>11471400</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B61" t="n">
-        <v>104.3292907185565</v>
+        <v>103.6787148109135</v>
       </c>
       <c r="C61" t="n">
-        <v>104.7038716073053</v>
+        <v>104.6545819518468</v>
       </c>
       <c r="D61" t="n">
-        <v>103.0182801694252</v>
+        <v>103.0675616662248</v>
       </c>
       <c r="E61" t="n">
-        <v>103.9645767211914</v>
+        <v>103.797004699707</v>
       </c>
       <c r="F61" t="n">
-        <v>11471400</v>
+        <v>10680100</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B62" t="n">
-        <v>103.6787148109135</v>
+        <v>103.7970053004195</v>
       </c>
       <c r="C62" t="n">
-        <v>104.6545819518468</v>
+        <v>106.5077532235307</v>
       </c>
       <c r="D62" t="n">
-        <v>103.0675616662248</v>
+        <v>103.3337126339174</v>
       </c>
       <c r="E62" t="n">
-        <v>103.797004699707</v>
+        <v>106.0937423706055</v>
       </c>
       <c r="F62" t="n">
-        <v>10680100</v>
+        <v>13727700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B63" t="n">
-        <v>103.7970053004195</v>
+        <v>106.0543107045445</v>
       </c>
       <c r="C63" t="n">
-        <v>106.5077532235307</v>
+        <v>106.2120305546496</v>
       </c>
       <c r="D63" t="n">
-        <v>103.3337126339174</v>
+        <v>105.0291617608474</v>
       </c>
       <c r="E63" t="n">
-        <v>106.0937423706055</v>
+        <v>105.4924468994141</v>
       </c>
       <c r="F63" t="n">
-        <v>13727700</v>
+        <v>8549400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B64" t="n">
-        <v>106.0543107045445</v>
+        <v>105.5910275110776</v>
       </c>
       <c r="C64" t="n">
-        <v>106.2120305546496</v>
+        <v>108.1046256243346</v>
       </c>
       <c r="D64" t="n">
-        <v>105.0291617608474</v>
+        <v>105.0587342879123</v>
       </c>
       <c r="E64" t="n">
-        <v>105.4924468994141</v>
+        <v>107.2766189575195</v>
       </c>
       <c r="F64" t="n">
-        <v>8549400</v>
+        <v>11237900</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B65" t="n">
-        <v>105.5910275110776</v>
+        <v>107.6413280220333</v>
       </c>
       <c r="C65" t="n">
-        <v>108.1046256243346</v>
+        <v>109.9676431038136</v>
       </c>
       <c r="D65" t="n">
-        <v>105.0587342879123</v>
+        <v>107.5526162491543</v>
       </c>
       <c r="E65" t="n">
-        <v>107.2766189575195</v>
+        <v>109.8690719604492</v>
       </c>
       <c r="F65" t="n">
-        <v>11237900</v>
+        <v>13281400</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B66" t="n">
-        <v>107.6413280220333</v>
+        <v>110.1352293411146</v>
       </c>
       <c r="C66" t="n">
-        <v>109.9676431038136</v>
+        <v>111.7222421475927</v>
       </c>
       <c r="D66" t="n">
-        <v>107.5526162491543</v>
+        <v>109.5635061444599</v>
       </c>
       <c r="E66" t="n">
-        <v>109.8690719604492</v>
+        <v>110.007080078125</v>
       </c>
       <c r="F66" t="n">
-        <v>13281400</v>
+        <v>13059100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,25 +2159,25 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B67" t="n">
-        <v>110.1352217028325</v>
+        <v>109.8582130022918</v>
       </c>
       <c r="C67" t="n">
-        <v>111.7222343992454</v>
+        <v>110.7017554968497</v>
       </c>
       <c r="D67" t="n">
-        <v>109.5634985458288</v>
+        <v>107.7245680705396</v>
       </c>
       <c r="E67" t="n">
-        <v>110.0070724487305</v>
+        <v>109.6498107910156</v>
       </c>
       <c r="F67" t="n">
-        <v>13059100</v>
+        <v>14318000</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2185,25 +2185,25 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B68" t="n">
-        <v>109.8582130022918</v>
+        <v>110.3742651303662</v>
       </c>
       <c r="C68" t="n">
-        <v>110.7017554968497</v>
+        <v>111.991867603266</v>
       </c>
       <c r="D68" t="n">
-        <v>107.7245680705396</v>
+        <v>110.0170020268064</v>
       </c>
       <c r="E68" t="n">
-        <v>109.6498107910156</v>
+        <v>110.7712249755859</v>
       </c>
       <c r="F68" t="n">
-        <v>14318000</v>
+        <v>15580200</v>
       </c>
       <c r="G68" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B69" t="n">
-        <v>110.3742651303662</v>
+        <v>110.2154802113721</v>
       </c>
       <c r="C69" t="n">
-        <v>111.991867603266</v>
+        <v>111.2773434635197</v>
       </c>
       <c r="D69" t="n">
-        <v>110.0170020268064</v>
+        <v>109.6200442181698</v>
       </c>
       <c r="E69" t="n">
-        <v>110.7712249755859</v>
+        <v>109.7887496948242</v>
       </c>
       <c r="F69" t="n">
-        <v>15580200</v>
+        <v>12142500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B70" t="n">
-        <v>110.2154802113721</v>
+        <v>109.6895108947102</v>
       </c>
       <c r="C70" t="n">
-        <v>111.2773434635197</v>
+        <v>111.9422536896534</v>
       </c>
       <c r="D70" t="n">
-        <v>109.6200442181698</v>
+        <v>109.5803467466885</v>
       </c>
       <c r="E70" t="n">
-        <v>109.7887496948242</v>
+        <v>111.0193252563477</v>
       </c>
       <c r="F70" t="n">
-        <v>12142500</v>
+        <v>12913900</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B71" t="n">
-        <v>109.6895108947102</v>
+        <v>111.4659009625997</v>
       </c>
       <c r="C71" t="n">
-        <v>111.9422536896534</v>
+        <v>112.6170837765976</v>
       </c>
       <c r="D71" t="n">
-        <v>109.5803467466885</v>
+        <v>110.076545265884</v>
       </c>
       <c r="E71" t="n">
-        <v>111.0193252563477</v>
+        <v>110.3941116333008</v>
       </c>
       <c r="F71" t="n">
-        <v>12913900</v>
+        <v>21138400</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B72" t="n">
-        <v>111.4659009625997</v>
+        <v>110.5628188428948</v>
       </c>
       <c r="C72" t="n">
-        <v>112.6170837765976</v>
+        <v>111.9422483883379</v>
       </c>
       <c r="D72" t="n">
-        <v>110.076545265884</v>
+        <v>110.3047938169375</v>
       </c>
       <c r="E72" t="n">
-        <v>110.3941116333008</v>
+        <v>111.5254364013672</v>
       </c>
       <c r="F72" t="n">
-        <v>21138400</v>
+        <v>8803300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B73" t="n">
-        <v>110.5628188428948</v>
+        <v>111.4361261613625</v>
       </c>
       <c r="C73" t="n">
-        <v>111.9422483883379</v>
+        <v>112.4483665538656</v>
       </c>
       <c r="D73" t="n">
-        <v>110.3047938169375</v>
+        <v>111.1880272094238</v>
       </c>
       <c r="E73" t="n">
-        <v>111.5254364013672</v>
+        <v>112.3590545654297</v>
       </c>
       <c r="F73" t="n">
-        <v>8803300</v>
+        <v>7634500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B74" t="n">
-        <v>111.4361261613625</v>
+        <v>112.0811837460467</v>
       </c>
       <c r="C74" t="n">
-        <v>112.4483665538656</v>
+        <v>113.6590894291559</v>
       </c>
       <c r="D74" t="n">
-        <v>111.1880272094238</v>
+        <v>111.9422489401646</v>
       </c>
       <c r="E74" t="n">
-        <v>112.3590545654297</v>
+        <v>113.6094741821289</v>
       </c>
       <c r="F74" t="n">
-        <v>7634500</v>
+        <v>4606700</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B75" t="n">
-        <v>112.0811837460467</v>
+        <v>113.2819819972415</v>
       </c>
       <c r="C75" t="n">
-        <v>113.6590894291559</v>
+        <v>113.8674918845297</v>
       </c>
       <c r="D75" t="n">
-        <v>111.9422489401646</v>
+        <v>112.4086688482299</v>
       </c>
       <c r="E75" t="n">
-        <v>113.6094741821289</v>
+        <v>112.6964645385742</v>
       </c>
       <c r="F75" t="n">
-        <v>4606700</v>
+        <v>5428900</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B76" t="n">
-        <v>113.2819819972415</v>
+        <v>112.4582910949776</v>
       </c>
       <c r="C76" t="n">
-        <v>113.8674918845297</v>
+        <v>113.6193923570513</v>
       </c>
       <c r="D76" t="n">
-        <v>112.4086688482299</v>
+        <v>112.4483650170496</v>
       </c>
       <c r="E76" t="n">
-        <v>112.6964645385742</v>
+        <v>113.3216781616211</v>
       </c>
       <c r="F76" t="n">
-        <v>5428900</v>
+        <v>7966000</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B77" t="n">
-        <v>112.4582910949776</v>
+        <v>113.2323587361736</v>
       </c>
       <c r="C77" t="n">
-        <v>113.6193923570513</v>
+        <v>114.4033860775522</v>
       </c>
       <c r="D77" t="n">
-        <v>112.4483650170496</v>
+        <v>113.2323587361736</v>
       </c>
       <c r="E77" t="n">
-        <v>113.3216781616211</v>
+        <v>113.9171142578125</v>
       </c>
       <c r="F77" t="n">
-        <v>7966000</v>
+        <v>6883900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B78" t="n">
-        <v>113.2323587361736</v>
+        <v>113.8972648993226</v>
       </c>
       <c r="C78" t="n">
-        <v>114.4033860775522</v>
+        <v>114.0163551233871</v>
       </c>
       <c r="D78" t="n">
-        <v>113.2323587361736</v>
+        <v>112.6865483592072</v>
       </c>
       <c r="E78" t="n">
-        <v>113.9171142578125</v>
+        <v>112.9048690795898</v>
       </c>
       <c r="F78" t="n">
-        <v>6883900</v>
+        <v>6608000</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B79" t="n">
-        <v>113.8972648993226</v>
+        <v>112.5773868999257</v>
       </c>
       <c r="C79" t="n">
-        <v>114.0163551233871</v>
+        <v>112.5773868999257</v>
       </c>
       <c r="D79" t="n">
-        <v>112.6865483592072</v>
+        <v>110.7712267677642</v>
       </c>
       <c r="E79" t="n">
-        <v>112.9048690795898</v>
+        <v>110.9994735717773</v>
       </c>
       <c r="F79" t="n">
-        <v>6608000</v>
+        <v>8906200</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B80" t="n">
-        <v>112.5773868999257</v>
+        <v>110.5727405037633</v>
       </c>
       <c r="C80" t="n">
-        <v>112.5773868999257</v>
+        <v>115.1476858420111</v>
       </c>
       <c r="D80" t="n">
-        <v>110.7712267677642</v>
+        <v>110.5330437623775</v>
       </c>
       <c r="E80" t="n">
-        <v>110.9994735717773</v>
+        <v>113.2025909423828</v>
       </c>
       <c r="F80" t="n">
-        <v>8906200</v>
+        <v>12029000</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B81" t="n">
-        <v>110.5727405037633</v>
+        <v>112.9247239572814</v>
       </c>
       <c r="C81" t="n">
-        <v>115.1476858420111</v>
+        <v>113.8873491370408</v>
       </c>
       <c r="D81" t="n">
-        <v>110.5330437623775</v>
+        <v>112.2498944807456</v>
       </c>
       <c r="E81" t="n">
-        <v>113.2025909423828</v>
+        <v>113.6987915039062</v>
       </c>
       <c r="F81" t="n">
-        <v>12029000</v>
+        <v>7388300</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B82" t="n">
-        <v>112.9247239572814</v>
+        <v>113.58962345171</v>
       </c>
       <c r="C82" t="n">
-        <v>113.8873491370408</v>
+        <v>114.0957474345631</v>
       </c>
       <c r="D82" t="n">
-        <v>112.2498944807456</v>
+        <v>111.6544546516531</v>
       </c>
       <c r="E82" t="n">
-        <v>113.6987915039062</v>
+        <v>112.0514144897461</v>
       </c>
       <c r="F82" t="n">
-        <v>7388300</v>
+        <v>8296300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B83" t="n">
-        <v>113.58962345171</v>
+        <v>111.6941501294552</v>
       </c>
       <c r="C83" t="n">
-        <v>114.0957474345631</v>
+        <v>114.1155907288179</v>
       </c>
       <c r="D83" t="n">
-        <v>111.6544546516531</v>
+        <v>111.6941501294552</v>
       </c>
       <c r="E83" t="n">
-        <v>112.0514144897461</v>
+        <v>113.3018264770508</v>
       </c>
       <c r="F83" t="n">
-        <v>8296300</v>
+        <v>9778200</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B84" t="n">
-        <v>111.6941501294552</v>
+        <v>113.4407639362947</v>
       </c>
       <c r="C84" t="n">
-        <v>114.1155907288179</v>
+        <v>115.0980707124986</v>
       </c>
       <c r="D84" t="n">
-        <v>111.6941501294552</v>
+        <v>113.0338855865844</v>
       </c>
       <c r="E84" t="n">
-        <v>113.3018264770508</v>
+        <v>114.9988250732422</v>
       </c>
       <c r="F84" t="n">
-        <v>9778200</v>
+        <v>8935200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B85" t="n">
-        <v>113.4407639362947</v>
+        <v>113.7583311963079</v>
       </c>
       <c r="C85" t="n">
-        <v>115.0980707124986</v>
+        <v>114.0659790519541</v>
       </c>
       <c r="D85" t="n">
-        <v>113.0338855865844</v>
+        <v>111.6941536254426</v>
       </c>
       <c r="E85" t="n">
-        <v>114.9988250732422</v>
+        <v>111.9620971679688</v>
       </c>
       <c r="F85" t="n">
-        <v>8935200</v>
+        <v>10833800</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B86" t="n">
-        <v>113.7583311963079</v>
+        <v>111.9819377501375</v>
       </c>
       <c r="C86" t="n">
-        <v>114.0659790519541</v>
+        <v>112.3590529975045</v>
       </c>
       <c r="D86" t="n">
-        <v>111.6941536254426</v>
+        <v>110.7612951636049</v>
       </c>
       <c r="E86" t="n">
-        <v>111.9620971679688</v>
+        <v>112.1208801269531</v>
       </c>
       <c r="F86" t="n">
-        <v>10833800</v>
+        <v>8945700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B87" t="n">
-        <v>111.9819377501375</v>
+        <v>111.9521684493894</v>
       </c>
       <c r="C87" t="n">
-        <v>112.3590529975045</v>
+        <v>112.7262359666306</v>
       </c>
       <c r="D87" t="n">
-        <v>110.7612951636049</v>
+        <v>111.4063552989297</v>
       </c>
       <c r="E87" t="n">
-        <v>112.1208801269531</v>
+        <v>112.6666946411133</v>
       </c>
       <c r="F87" t="n">
-        <v>8945700</v>
+        <v>8950900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B88" t="n">
-        <v>111.9521684493894</v>
+        <v>112.8453292583326</v>
       </c>
       <c r="C88" t="n">
-        <v>112.7262359666306</v>
+        <v>113.242289105796</v>
       </c>
       <c r="D88" t="n">
-        <v>111.4063552989297</v>
+        <v>111.3170387669949</v>
       </c>
       <c r="E88" t="n">
-        <v>112.6666946411133</v>
+        <v>112.5476150512695</v>
       </c>
       <c r="F88" t="n">
-        <v>8950900</v>
+        <v>7958500</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B89" t="n">
-        <v>112.8453292583326</v>
+        <v>112.339199834173</v>
       </c>
       <c r="C89" t="n">
-        <v>113.242289105796</v>
+        <v>112.9842586087029</v>
       </c>
       <c r="D89" t="n">
-        <v>111.3170387669949</v>
+        <v>110.2750223556077</v>
       </c>
       <c r="E89" t="n">
-        <v>112.5476150512695</v>
+        <v>110.3544082641602</v>
       </c>
       <c r="F89" t="n">
-        <v>7958500</v>
+        <v>12049600</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B90" t="n">
-        <v>112.339199834173</v>
+        <v>108.8261317696502</v>
       </c>
       <c r="C90" t="n">
-        <v>112.9842586087029</v>
+        <v>110.2452505565117</v>
       </c>
       <c r="D90" t="n">
-        <v>110.2750223556077</v>
+        <v>107.9726707390225</v>
       </c>
       <c r="E90" t="n">
-        <v>110.3544082641602</v>
+        <v>109.5009536743164</v>
       </c>
       <c r="F90" t="n">
-        <v>12049600</v>
+        <v>9818200</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B91" t="n">
-        <v>108.8261317696502</v>
+        <v>109.7292049082389</v>
       </c>
       <c r="C91" t="n">
-        <v>110.2452505565117</v>
+        <v>112.3888259939984</v>
       </c>
       <c r="D91" t="n">
-        <v>107.9726707390225</v>
+        <v>109.6597375040779</v>
       </c>
       <c r="E91" t="n">
-        <v>109.5009536743164</v>
+        <v>112.3292846679688</v>
       </c>
       <c r="F91" t="n">
-        <v>9818200</v>
+        <v>10041400</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B92" t="n">
-        <v>109.7292049082389</v>
+        <v>112.3094319821855</v>
       </c>
       <c r="C92" t="n">
-        <v>112.3888259939984</v>
+        <v>113.4209180149001</v>
       </c>
       <c r="D92" t="n">
-        <v>109.6597375040779</v>
+        <v>111.317036172348</v>
       </c>
       <c r="E92" t="n">
-        <v>112.3292846679688</v>
+        <v>112.3491287231445</v>
       </c>
       <c r="F92" t="n">
-        <v>10041400</v>
+        <v>12437700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B93" t="n">
-        <v>112.3094319821855</v>
+        <v>111.8330891095483</v>
       </c>
       <c r="C93" t="n">
-        <v>113.4209180149001</v>
+        <v>112.0911065753488</v>
       </c>
       <c r="D93" t="n">
-        <v>111.317036172348</v>
+        <v>109.7093626275885</v>
       </c>
       <c r="E93" t="n">
-        <v>112.3491287231445</v>
+        <v>110.1360931396484</v>
       </c>
       <c r="F93" t="n">
-        <v>12437700</v>
+        <v>10819800</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B94" t="n">
-        <v>111.8330891095483</v>
+        <v>110.8307664528259</v>
       </c>
       <c r="C94" t="n">
-        <v>112.0911065753488</v>
+        <v>111.5552187391887</v>
       </c>
       <c r="D94" t="n">
-        <v>109.7093626275885</v>
+        <v>110.2849457184854</v>
       </c>
       <c r="E94" t="n">
-        <v>110.1360931396484</v>
+        <v>110.4635772705078</v>
       </c>
       <c r="F94" t="n">
-        <v>10819800</v>
+        <v>8859800</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B95" t="n">
-        <v>110.8307664528259</v>
+        <v>110.6521373409646</v>
       </c>
       <c r="C95" t="n">
-        <v>111.5552187391887</v>
+        <v>110.9498591246939</v>
       </c>
       <c r="D95" t="n">
-        <v>110.2849457184854</v>
+        <v>109.1933142291742</v>
       </c>
       <c r="E95" t="n">
-        <v>110.4635772705078</v>
+        <v>109.7689056396484</v>
       </c>
       <c r="F95" t="n">
-        <v>8859800</v>
+        <v>8956900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B96" t="n">
-        <v>110.6521373409646</v>
+        <v>109.4414091319104</v>
       </c>
       <c r="C96" t="n">
-        <v>110.9498591246939</v>
+        <v>110.5826658320299</v>
       </c>
       <c r="D96" t="n">
-        <v>109.1933142291742</v>
+        <v>108.1711437016965</v>
       </c>
       <c r="E96" t="n">
-        <v>109.7689056396484</v>
+        <v>108.7268829345703</v>
       </c>
       <c r="F96" t="n">
-        <v>8956900</v>
+        <v>9016600</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B97" t="n">
-        <v>109.4414091319104</v>
+        <v>108.7963528121511</v>
       </c>
       <c r="C97" t="n">
-        <v>110.5826658320299</v>
+        <v>110.8208412268483</v>
       </c>
       <c r="D97" t="n">
-        <v>108.1711437016965</v>
+        <v>107.932973280219</v>
       </c>
       <c r="E97" t="n">
-        <v>108.7268829345703</v>
+        <v>110.7315292358398</v>
       </c>
       <c r="F97" t="n">
-        <v>9016600</v>
+        <v>11079000</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B98" t="n">
-        <v>108.7963528121511</v>
+        <v>110.5132006888762</v>
       </c>
       <c r="C98" t="n">
-        <v>110.8208412268483</v>
+        <v>112.0911064308015</v>
       </c>
       <c r="D98" t="n">
-        <v>107.932973280219</v>
+        <v>110.1460115045699</v>
       </c>
       <c r="E98" t="n">
-        <v>110.7315292358398</v>
+        <v>111.942253112793</v>
       </c>
       <c r="F98" t="n">
-        <v>11079000</v>
+        <v>17895200</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B99" t="n">
-        <v>110.5132006888762</v>
+        <v>103.219089824791</v>
       </c>
       <c r="C99" t="n">
-        <v>112.0911064308015</v>
+        <v>107.7841090146985</v>
       </c>
       <c r="D99" t="n">
-        <v>110.1460115045699</v>
+        <v>102.961064795438</v>
       </c>
       <c r="E99" t="n">
-        <v>111.942253112793</v>
+        <v>103.6557388305664</v>
       </c>
       <c r="F99" t="n">
-        <v>17895200</v>
+        <v>37778500</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B100" t="n">
-        <v>103.219089824791</v>
+        <v>103.9832294528008</v>
       </c>
       <c r="C100" t="n">
-        <v>107.7841090146985</v>
+        <v>104.1916316597105</v>
       </c>
       <c r="D100" t="n">
-        <v>102.961064795438</v>
+        <v>101.5617813072958</v>
       </c>
       <c r="E100" t="n">
-        <v>103.6557388305664</v>
+        <v>103.427490234375</v>
       </c>
       <c r="F100" t="n">
-        <v>37778500</v>
+        <v>24827100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B101" t="n">
-        <v>103.9832294528008</v>
+        <v>103.4076429857971</v>
       </c>
       <c r="C101" t="n">
-        <v>104.1916316597105</v>
+        <v>107.7741861743833</v>
       </c>
       <c r="D101" t="n">
-        <v>101.5617813072958</v>
+        <v>102.841977662662</v>
       </c>
       <c r="E101" t="n">
-        <v>103.427490234375</v>
+        <v>106.2359771728516</v>
       </c>
       <c r="F101" t="n">
-        <v>24827100</v>
+        <v>19070400</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B102" t="n">
-        <v>103.4076429857971</v>
+        <v>106.2359762120697</v>
       </c>
       <c r="C102" t="n">
-        <v>107.7741861743833</v>
+        <v>107.5062416580512</v>
       </c>
       <c r="D102" t="n">
-        <v>102.841977662662</v>
+        <v>104.0130041102228</v>
       </c>
       <c r="E102" t="n">
-        <v>106.2359771728516</v>
+        <v>104.1717910766602</v>
       </c>
       <c r="F102" t="n">
-        <v>19070400</v>
+        <v>11859500</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B103" t="n">
-        <v>106.2359762120697</v>
+        <v>105.3229638054753</v>
       </c>
       <c r="C103" t="n">
-        <v>107.5062416580512</v>
+        <v>108.1314457439972</v>
       </c>
       <c r="D103" t="n">
-        <v>104.0130041102228</v>
+        <v>104.5687484468834</v>
       </c>
       <c r="E103" t="n">
-        <v>104.1717910766602</v>
+        <v>107.873420715332</v>
       </c>
       <c r="F103" t="n">
-        <v>11859500</v>
+        <v>12105600</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B104" t="n">
-        <v>105.3229638054753</v>
+        <v>107.8635036441641</v>
       </c>
       <c r="C104" t="n">
-        <v>108.1314457439972</v>
+        <v>108.09175044183</v>
       </c>
       <c r="D104" t="n">
-        <v>104.5687484468834</v>
+        <v>105.9580979235442</v>
       </c>
       <c r="E104" t="n">
-        <v>107.873420715332</v>
+        <v>106.3153610229492</v>
       </c>
       <c r="F104" t="n">
-        <v>12105600</v>
+        <v>10515400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B105" t="n">
-        <v>107.8635036441641</v>
+        <v>106.7817856582252</v>
       </c>
       <c r="C105" t="n">
-        <v>108.09175044183</v>
+        <v>110.265097006608</v>
       </c>
       <c r="D105" t="n">
-        <v>105.9580979235442</v>
+        <v>106.7817856582252</v>
       </c>
       <c r="E105" t="n">
-        <v>106.3153610229492</v>
+        <v>109.1238403320312</v>
       </c>
       <c r="F105" t="n">
-        <v>10515400</v>
+        <v>9815500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B106" t="n">
-        <v>106.7817856582252</v>
+        <v>108.1016744764874</v>
       </c>
       <c r="C106" t="n">
-        <v>110.265097006608</v>
+        <v>109.0345289485641</v>
       </c>
       <c r="D106" t="n">
-        <v>106.7817856582252</v>
+        <v>106.9802699515072</v>
       </c>
       <c r="E106" t="n">
-        <v>109.1238403320312</v>
+        <v>107.2978363037109</v>
       </c>
       <c r="F106" t="n">
-        <v>9815500</v>
+        <v>9374900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B107" t="n">
-        <v>108.1016744764874</v>
+        <v>107.1092782571758</v>
       </c>
       <c r="C107" t="n">
-        <v>109.0345289485641</v>
+        <v>107.3375326210063</v>
       </c>
       <c r="D107" t="n">
-        <v>106.9802699515072</v>
+        <v>100.2518196922704</v>
       </c>
       <c r="E107" t="n">
-        <v>107.2978363037109</v>
+        <v>101.6014785766602</v>
       </c>
       <c r="F107" t="n">
-        <v>9374900</v>
+        <v>25319600</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B108" t="n">
-        <v>107.1092782571758</v>
+        <v>100.6289339445357</v>
       </c>
       <c r="C108" t="n">
-        <v>107.3375326210063</v>
+        <v>104.7175997261971</v>
       </c>
       <c r="D108" t="n">
-        <v>100.2518196922704</v>
+        <v>100.4304502450412</v>
       </c>
       <c r="E108" t="n">
-        <v>101.6014785766602</v>
+        <v>104.6481323242188</v>
       </c>
       <c r="F108" t="n">
-        <v>25319600</v>
+        <v>12845300</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B109" t="n">
-        <v>100.6289339445357</v>
+        <v>105.7596186239472</v>
       </c>
       <c r="C109" t="n">
-        <v>104.7175997261971</v>
+        <v>106.4642187235269</v>
       </c>
       <c r="D109" t="n">
-        <v>100.4304502450412</v>
+        <v>103.576350923035</v>
       </c>
       <c r="E109" t="n">
-        <v>104.6481323242188</v>
+        <v>104.6382141113281</v>
       </c>
       <c r="F109" t="n">
-        <v>12845300</v>
+        <v>10467400</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B110" t="n">
-        <v>105.7596186239472</v>
+        <v>105.1542604930163</v>
       </c>
       <c r="C110" t="n">
-        <v>106.4642187235269</v>
+        <v>106.9108053396402</v>
       </c>
       <c r="D110" t="n">
-        <v>103.576350923035</v>
+        <v>105.0053996052954</v>
       </c>
       <c r="E110" t="n">
-        <v>104.6382141113281</v>
+        <v>106.2855911254883</v>
       </c>
       <c r="F110" t="n">
-        <v>10467400</v>
+        <v>8791600</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B111" t="n">
-        <v>105.1542604930163</v>
+        <v>106.2955144080048</v>
       </c>
       <c r="C111" t="n">
-        <v>106.9108053396402</v>
+        <v>106.9504916968191</v>
       </c>
       <c r="D111" t="n">
-        <v>105.0053996052954</v>
+        <v>104.6481337509456</v>
       </c>
       <c r="E111" t="n">
-        <v>106.2855911254883</v>
+        <v>105.1939544677734</v>
       </c>
       <c r="F111" t="n">
-        <v>8791600</v>
+        <v>7492900</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B112" t="n">
-        <v>106.2955144080048</v>
+        <v>104.8069236784645</v>
       </c>
       <c r="C112" t="n">
-        <v>106.9504916968191</v>
+        <v>105.3924335809217</v>
       </c>
       <c r="D112" t="n">
-        <v>104.6481337509456</v>
+        <v>103.8542245950799</v>
       </c>
       <c r="E112" t="n">
-        <v>105.1939544677734</v>
+        <v>104.7771530151367</v>
       </c>
       <c r="F112" t="n">
-        <v>7492900</v>
+        <v>9043600</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B113" t="n">
-        <v>104.8069236784645</v>
+        <v>104.1817160321379</v>
       </c>
       <c r="C113" t="n">
-        <v>105.3924335809217</v>
+        <v>104.3901182448065</v>
       </c>
       <c r="D113" t="n">
-        <v>103.8542245950799</v>
+        <v>102.1770722450568</v>
       </c>
       <c r="E113" t="n">
-        <v>104.7771530151367</v>
+        <v>103.6160507202148</v>
       </c>
       <c r="F113" t="n">
-        <v>9043600</v>
+        <v>10626500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B114" t="n">
-        <v>104.1817160321379</v>
+        <v>103.6557367363695</v>
       </c>
       <c r="C114" t="n">
-        <v>104.3901182448065</v>
+        <v>106.4146033792047</v>
       </c>
       <c r="D114" t="n">
-        <v>102.1770722450568</v>
+        <v>103.1893170772804</v>
       </c>
       <c r="E114" t="n">
-        <v>103.6160507202148</v>
+        <v>105.2435760498047</v>
       </c>
       <c r="F114" t="n">
-        <v>10626500</v>
+        <v>13594800</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B115" t="n">
-        <v>103.6557367363695</v>
+        <v>105.193955544271</v>
       </c>
       <c r="C115" t="n">
-        <v>106.4146033792047</v>
+        <v>105.9084817367471</v>
       </c>
       <c r="D115" t="n">
-        <v>103.1893170772804</v>
+        <v>103.7152879117953</v>
       </c>
       <c r="E115" t="n">
-        <v>105.2435760498047</v>
+        <v>104.2511825561523</v>
       </c>
       <c r="F115" t="n">
-        <v>13594800</v>
+        <v>8556500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B116" t="n">
-        <v>105.193955544271</v>
+        <v>104.6679896339684</v>
       </c>
       <c r="C116" t="n">
-        <v>105.9084817367471</v>
+        <v>105.9580996730059</v>
       </c>
       <c r="D116" t="n">
-        <v>103.7152879117953</v>
+        <v>104.519128744862</v>
       </c>
       <c r="E116" t="n">
-        <v>104.2511825561523</v>
+        <v>104.7473831176758</v>
       </c>
       <c r="F116" t="n">
-        <v>8556500</v>
+        <v>9578500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B117" t="n">
-        <v>104.6679896339684</v>
+        <v>103.9832293953731</v>
       </c>
       <c r="C117" t="n">
-        <v>105.9580996730059</v>
+        <v>105.5313644009208</v>
       </c>
       <c r="D117" t="n">
-        <v>104.519128744862</v>
+        <v>103.1396944903344</v>
       </c>
       <c r="E117" t="n">
-        <v>104.7473831176758</v>
+        <v>105.2336502075195</v>
       </c>
       <c r="F117" t="n">
-        <v>9578500</v>
+        <v>13954000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B118" t="n">
-        <v>103.9832293953731</v>
+        <v>103.8145288629893</v>
       </c>
       <c r="C118" t="n">
-        <v>105.5313644009208</v>
+        <v>103.8145288629893</v>
       </c>
       <c r="D118" t="n">
-        <v>103.1396944903344</v>
+        <v>102.0778361524432</v>
       </c>
       <c r="E118" t="n">
-        <v>105.2336502075195</v>
+        <v>103.5366592407227</v>
       </c>
       <c r="F118" t="n">
-        <v>13954000</v>
+        <v>14178600</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B119" t="n">
-        <v>103.8145288629893</v>
+        <v>102.0579794936243</v>
       </c>
       <c r="C119" t="n">
-        <v>103.8145288629893</v>
+        <v>103.5168025175497</v>
       </c>
       <c r="D119" t="n">
-        <v>102.0778361524432</v>
+        <v>101.3732315464965</v>
       </c>
       <c r="E119" t="n">
-        <v>103.5366592407227</v>
+        <v>102.5144882202148</v>
       </c>
       <c r="F119" t="n">
-        <v>14178600</v>
+        <v>13608400</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B120" t="n">
-        <v>102.0579794936243</v>
+        <v>102.3854784619134</v>
       </c>
       <c r="C120" t="n">
-        <v>103.5168025175497</v>
+        <v>103.0503818671043</v>
       </c>
       <c r="D120" t="n">
-        <v>101.3732315464965</v>
+        <v>101.8595098706018</v>
       </c>
       <c r="E120" t="n">
-        <v>102.5144882202148</v>
+        <v>102.2564697265625</v>
       </c>
       <c r="F120" t="n">
-        <v>13608400</v>
+        <v>9672300</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B121" t="n">
-        <v>102.3854784619134</v>
+        <v>102.3160040474863</v>
       </c>
       <c r="C121" t="n">
-        <v>103.0503818671043</v>
+        <v>103.7549824803676</v>
       </c>
       <c r="D121" t="n">
-        <v>101.8595098706018</v>
+        <v>100.8174842902717</v>
       </c>
       <c r="E121" t="n">
-        <v>102.2564697265625</v>
+        <v>101.6312561035156</v>
       </c>
       <c r="F121" t="n">
-        <v>9672300</v>
+        <v>11751500</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B122" t="n">
-        <v>102.3160040474863</v>
+        <v>100.6190147793836</v>
       </c>
       <c r="C122" t="n">
-        <v>103.7549824803676</v>
+        <v>101.0358192198888</v>
       </c>
       <c r="D122" t="n">
-        <v>100.8174842902717</v>
+        <v>99.18996233036073</v>
       </c>
       <c r="E122" t="n">
-        <v>101.6312561035156</v>
+        <v>100.7678756713867</v>
       </c>
       <c r="F122" t="n">
-        <v>11751500</v>
+        <v>10448600</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B123" t="n">
-        <v>100.6190147793836</v>
+        <v>99.78540292258373</v>
       </c>
       <c r="C123" t="n">
-        <v>101.0358192198888</v>
+        <v>101.0953651046626</v>
       </c>
       <c r="D123" t="n">
-        <v>99.18996233036073</v>
+        <v>97.70136563944882</v>
       </c>
       <c r="E123" t="n">
-        <v>100.7678756713867</v>
+        <v>100.886962890625</v>
       </c>
       <c r="F123" t="n">
-        <v>10448600</v>
+        <v>11715100</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B124" t="n">
-        <v>99.78540292258373</v>
+        <v>100.9762757982457</v>
       </c>
       <c r="C124" t="n">
-        <v>101.0953651046626</v>
+        <v>101.4625476354206</v>
       </c>
       <c r="D124" t="n">
-        <v>97.70136563944882</v>
+        <v>99.47775597353863</v>
       </c>
       <c r="E124" t="n">
-        <v>100.886962890625</v>
+        <v>100.5495452880859</v>
       </c>
       <c r="F124" t="n">
-        <v>11715100</v>
+        <v>7833100</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B125" t="n">
-        <v>100.9762757982457</v>
+        <v>100.6289343352219</v>
       </c>
       <c r="C125" t="n">
-        <v>101.4625476354206</v>
+        <v>101.1152061509584</v>
       </c>
       <c r="D125" t="n">
-        <v>99.47775597353863</v>
+        <v>99.63653854803313</v>
       </c>
       <c r="E125" t="n">
-        <v>100.5495452880859</v>
+        <v>100.1228103637695</v>
       </c>
       <c r="F125" t="n">
-        <v>7833100</v>
+        <v>8152800</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B126" t="n">
-        <v>100.6289343352219</v>
+        <v>99.33882308016651</v>
       </c>
       <c r="C126" t="n">
-        <v>101.1152061509584</v>
+        <v>100.1128906318194</v>
       </c>
       <c r="D126" t="n">
-        <v>99.63653854803313</v>
+        <v>98.61437834957015</v>
       </c>
       <c r="E126" t="n">
-        <v>100.1228103637695</v>
+        <v>98.67391967773438</v>
       </c>
       <c r="F126" t="n">
-        <v>8152800</v>
+        <v>10309400</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B127" t="n">
-        <v>99.33882308016651</v>
+        <v>99.07087541929553</v>
       </c>
       <c r="C127" t="n">
-        <v>100.1128906318194</v>
+        <v>100.0037223311207</v>
       </c>
       <c r="D127" t="n">
-        <v>98.61437834957015</v>
+        <v>98.4059720444657</v>
       </c>
       <c r="E127" t="n">
-        <v>98.67391967773438</v>
+        <v>98.53498077392578</v>
       </c>
       <c r="F127" t="n">
-        <v>10309400</v>
+        <v>9551500</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B128" t="n">
-        <v>99.07087541929553</v>
+        <v>98.71361296789499</v>
       </c>
       <c r="C128" t="n">
-        <v>100.0037223311207</v>
+        <v>98.93194125870065</v>
       </c>
       <c r="D128" t="n">
-        <v>98.4059720444657</v>
+        <v>97.71129107436866</v>
       </c>
       <c r="E128" t="n">
-        <v>98.53498077392578</v>
+        <v>97.90977478027344</v>
       </c>
       <c r="F128" t="n">
-        <v>9551500</v>
+        <v>11578500</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B129" t="n">
-        <v>98.71361296789499</v>
+        <v>98.41588802886785</v>
       </c>
       <c r="C129" t="n">
-        <v>98.93194125870065</v>
+        <v>99.94417844396594</v>
       </c>
       <c r="D129" t="n">
-        <v>97.71129107436866</v>
+        <v>98.26702714707265</v>
       </c>
       <c r="E129" t="n">
-        <v>97.90977478027344</v>
+        <v>99.53730010986328</v>
       </c>
       <c r="F129" t="n">
-        <v>11578500</v>
+        <v>11785600</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B130" t="n">
-        <v>98.41588802886785</v>
+        <v>99.08079827635559</v>
       </c>
       <c r="C130" t="n">
-        <v>99.94417844396594</v>
+        <v>100.2518256851255</v>
       </c>
       <c r="D130" t="n">
-        <v>98.26702714707265</v>
+        <v>98.24718939454284</v>
       </c>
       <c r="E130" t="n">
-        <v>99.53730010986328</v>
+        <v>98.66399383544922</v>
       </c>
       <c r="F130" t="n">
-        <v>11785600</v>
+        <v>12615100</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B131" t="n">
-        <v>99.08079827635559</v>
+        <v>98.2769579779315</v>
       </c>
       <c r="C131" t="n">
-        <v>100.2518256851255</v>
+        <v>100.0136506829842</v>
       </c>
       <c r="D131" t="n">
-        <v>98.24718939454284</v>
+        <v>97.69144807163296</v>
       </c>
       <c r="E131" t="n">
-        <v>98.66399383544922</v>
+        <v>98.44566345214844</v>
       </c>
       <c r="F131" t="n">
-        <v>12615100</v>
+        <v>14793800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B132" t="n">
-        <v>98.2769579779315</v>
+        <v>98.25711324225701</v>
       </c>
       <c r="C132" t="n">
-        <v>100.0136506829842</v>
+        <v>99.269353657388</v>
       </c>
       <c r="D132" t="n">
-        <v>97.69144807163296</v>
+        <v>97.64182510199821</v>
       </c>
       <c r="E132" t="n">
-        <v>98.44566345214844</v>
+        <v>98.75331115722656</v>
       </c>
       <c r="F132" t="n">
-        <v>14793800</v>
+        <v>27544200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B133" t="n">
-        <v>98.25711324225701</v>
+        <v>99.45791247863863</v>
       </c>
       <c r="C133" t="n">
-        <v>99.269353657388</v>
+        <v>99.83502017283372</v>
       </c>
       <c r="D133" t="n">
-        <v>97.64182510199821</v>
+        <v>97.11585768623267</v>
       </c>
       <c r="E133" t="n">
-        <v>98.75331115722656</v>
+        <v>97.20516967773438</v>
       </c>
       <c r="F133" t="n">
-        <v>27544200</v>
+        <v>11373000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>99.45791247863863</v>
+        <v>96.99676871718921</v>
       </c>
       <c r="C134" t="n">
-        <v>99.83502017283372</v>
+        <v>97.30441658068045</v>
       </c>
       <c r="D134" t="n">
-        <v>97.11585768623267</v>
+        <v>95.5181010136908</v>
       </c>
       <c r="E134" t="n">
-        <v>97.20516967773438</v>
+        <v>95.65703582763672</v>
       </c>
       <c r="F134" t="n">
-        <v>11373000</v>
+        <v>9155700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>96.99676871718921</v>
+        <v>96.08376214252051</v>
       </c>
       <c r="C135" t="n">
-        <v>97.30441658068045</v>
+        <v>96.44102524028141</v>
       </c>
       <c r="D135" t="n">
-        <v>95.5181010136908</v>
+        <v>94.33714339473161</v>
       </c>
       <c r="E135" t="n">
-        <v>95.65703582763672</v>
+        <v>95.22037506103516</v>
       </c>
       <c r="F135" t="n">
-        <v>9155700</v>
+        <v>8467500</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>96.08376214252051</v>
+        <v>94.3966920435457</v>
       </c>
       <c r="C136" t="n">
-        <v>96.44102524028141</v>
+        <v>95.66695746718439</v>
       </c>
       <c r="D136" t="n">
-        <v>94.33714339473161</v>
+        <v>93.87071590500793</v>
       </c>
       <c r="E136" t="n">
-        <v>95.22037506103516</v>
+        <v>94.02950286865234</v>
       </c>
       <c r="F136" t="n">
-        <v>8467500</v>
+        <v>8548800</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B137" t="n">
-        <v>94.3966920435457</v>
+        <v>93.47376126842354</v>
       </c>
       <c r="C137" t="n">
-        <v>95.66695746718439</v>
+        <v>93.47376126842354</v>
       </c>
       <c r="D137" t="n">
-        <v>93.87071590500793</v>
+        <v>91.48896970147202</v>
       </c>
       <c r="E137" t="n">
-        <v>94.02950286865234</v>
+        <v>91.71721649169922</v>
       </c>
       <c r="F137" t="n">
-        <v>8548800</v>
+        <v>12475900</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>93.47376126842354</v>
+        <v>92.18364921591858</v>
       </c>
       <c r="C138" t="n">
-        <v>93.47376126842354</v>
+        <v>94.46616268251262</v>
       </c>
       <c r="D138" t="n">
-        <v>91.48896970147202</v>
+        <v>92.18364921591858</v>
       </c>
       <c r="E138" t="n">
-        <v>91.71721649169922</v>
+        <v>93.60277557373047</v>
       </c>
       <c r="F138" t="n">
-        <v>12475900</v>
+        <v>10592600</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>92.18364921591858</v>
+        <v>94.61501738536155</v>
       </c>
       <c r="C139" t="n">
-        <v>94.46616268251262</v>
+        <v>96.15323399247868</v>
       </c>
       <c r="D139" t="n">
-        <v>92.18364921591858</v>
+        <v>93.47376820675542</v>
       </c>
       <c r="E139" t="n">
-        <v>93.60277557373047</v>
+        <v>95.64710998535156</v>
       </c>
       <c r="F139" t="n">
-        <v>10592600</v>
+        <v>11180200</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>94.61501738536155</v>
+        <v>96.52041860940267</v>
       </c>
       <c r="C140" t="n">
-        <v>96.15323399247868</v>
+        <v>97.61205248622655</v>
       </c>
       <c r="D140" t="n">
-        <v>93.47376820675542</v>
+        <v>95.75626959566054</v>
       </c>
       <c r="E140" t="n">
-        <v>95.64710998535156</v>
+        <v>95.82573699951172</v>
       </c>
       <c r="F140" t="n">
-        <v>11180200</v>
+        <v>8518600</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>96.52041860940267</v>
+        <v>95.26999653948798</v>
       </c>
       <c r="C141" t="n">
-        <v>97.61205248622655</v>
+        <v>96.43109780518201</v>
       </c>
       <c r="D141" t="n">
-        <v>95.75626959566054</v>
+        <v>94.36691272969546</v>
       </c>
       <c r="E141" t="n">
-        <v>95.82573699951172</v>
+        <v>95.87535858154297</v>
       </c>
       <c r="F141" t="n">
-        <v>8518600</v>
+        <v>6379100</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B142" t="n">
-        <v>95.26999653948798</v>
+        <v>95.76619510964362</v>
       </c>
       <c r="C142" t="n">
-        <v>96.43109780518201</v>
+        <v>96.4211799747073</v>
       </c>
       <c r="D142" t="n">
-        <v>94.36691272969546</v>
+        <v>95.389087429727</v>
       </c>
       <c r="E142" t="n">
-        <v>95.87535858154297</v>
+        <v>95.54786682128906</v>
       </c>
       <c r="F142" t="n">
-        <v>6379100</v>
+        <v>5882200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B143" t="n">
-        <v>95.76619510964362</v>
+        <v>95.07152604625539</v>
       </c>
       <c r="C143" t="n">
-        <v>96.4211799747073</v>
+        <v>96.05399582384246</v>
       </c>
       <c r="D143" t="n">
-        <v>95.389087429727</v>
+        <v>94.60509878245135</v>
       </c>
       <c r="E143" t="n">
-        <v>95.54786682128906</v>
+        <v>95.05167388916016</v>
       </c>
       <c r="F143" t="n">
-        <v>5882200</v>
+        <v>7913000</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B144" t="n">
-        <v>95.07152604625539</v>
+        <v>97.3540300760944</v>
       </c>
       <c r="C144" t="n">
-        <v>96.05399582384246</v>
+        <v>98.43574547532691</v>
       </c>
       <c r="D144" t="n">
-        <v>94.60509878245135</v>
+        <v>96.94715172012246</v>
       </c>
       <c r="E144" t="n">
-        <v>95.05167388916016</v>
+        <v>98.42581939697266</v>
       </c>
       <c r="F144" t="n">
-        <v>7913000</v>
+        <v>10821000</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B145" t="n">
-        <v>97.3540300760944</v>
+        <v>97.9097767670043</v>
       </c>
       <c r="C145" t="n">
-        <v>98.43574547532691</v>
+        <v>99.46783792592092</v>
       </c>
       <c r="D145" t="n">
-        <v>96.94715172012246</v>
+        <v>96.93722551678441</v>
       </c>
       <c r="E145" t="n">
-        <v>98.42581939697266</v>
+        <v>99.03118133544922</v>
       </c>
       <c r="F145" t="n">
-        <v>10821000</v>
+        <v>8918300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B146" t="n">
-        <v>97.9097767670043</v>
+        <v>99.08079694980933</v>
       </c>
       <c r="C146" t="n">
-        <v>99.46783792592092</v>
+        <v>99.39837088687223</v>
       </c>
       <c r="D146" t="n">
-        <v>96.93722551678441</v>
+        <v>98.06855652524918</v>
       </c>
       <c r="E146" t="n">
-        <v>99.03118133544922</v>
+        <v>98.4158935546875</v>
       </c>
       <c r="F146" t="n">
-        <v>8918300</v>
+        <v>6359600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B147" t="n">
-        <v>99.08079694980933</v>
+        <v>97.78075602521236</v>
       </c>
       <c r="C147" t="n">
-        <v>99.39837088687223</v>
+        <v>100.4999183711592</v>
       </c>
       <c r="D147" t="n">
-        <v>98.06855652524918</v>
+        <v>97.78075602521236</v>
       </c>
       <c r="E147" t="n">
-        <v>98.4158935546875</v>
+        <v>100.4106063842773</v>
       </c>
       <c r="F147" t="n">
-        <v>6359600</v>
+        <v>6790300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B148" t="n">
-        <v>97.78075602521236</v>
+        <v>100.5693883478159</v>
       </c>
       <c r="C148" t="n">
-        <v>100.4999183711592</v>
+        <v>102.3160071037648</v>
       </c>
       <c r="D148" t="n">
-        <v>97.78075602521236</v>
+        <v>100.1327393373631</v>
       </c>
       <c r="E148" t="n">
-        <v>100.4106063842773</v>
+        <v>101.8098831176758</v>
       </c>
       <c r="F148" t="n">
-        <v>6790300</v>
+        <v>9997400</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B149" t="n">
-        <v>100.5693883478159</v>
+        <v>101.8198131278678</v>
       </c>
       <c r="C149" t="n">
-        <v>102.3160071037648</v>
+        <v>102.5938806827324</v>
       </c>
       <c r="D149" t="n">
-        <v>100.1327393373631</v>
+        <v>101.0159749087976</v>
       </c>
       <c r="E149" t="n">
-        <v>101.8098831176758</v>
+        <v>102.2564697265625</v>
       </c>
       <c r="F149" t="n">
-        <v>9997400</v>
+        <v>7035300</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B150" t="n">
-        <v>101.8198131278678</v>
+        <v>102.832054706031</v>
       </c>
       <c r="C150" t="n">
-        <v>102.5938806827324</v>
+        <v>103.7351309397506</v>
       </c>
       <c r="D150" t="n">
-        <v>101.0159749087976</v>
+        <v>101.9984383035261</v>
       </c>
       <c r="E150" t="n">
-        <v>102.2564697265625</v>
+        <v>103.1099243164062</v>
       </c>
       <c r="F150" t="n">
-        <v>7035300</v>
+        <v>8145900</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B151" t="n">
-        <v>102.832054706031</v>
+        <v>103.8939187225915</v>
       </c>
       <c r="C151" t="n">
-        <v>103.7351309397506</v>
+        <v>105.5214472288459</v>
       </c>
       <c r="D151" t="n">
-        <v>101.9984383035261</v>
+        <v>103.8939187225915</v>
       </c>
       <c r="E151" t="n">
-        <v>103.1099243164062</v>
+        <v>105.4817504882812</v>
       </c>
       <c r="F151" t="n">
-        <v>8145900</v>
+        <v>10506200</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="n">
-        <v>103.8939187225915</v>
+        <v>105.1046425751499</v>
       </c>
       <c r="C152" t="n">
-        <v>105.5214472288459</v>
+        <v>106.2955145039117</v>
       </c>
       <c r="D152" t="n">
-        <v>103.8939187225915</v>
+        <v>105.1046425751499</v>
       </c>
       <c r="E152" t="n">
-        <v>105.4817504882812</v>
+        <v>105.4916763305664</v>
       </c>
       <c r="F152" t="n">
-        <v>10506200</v>
+        <v>6423400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B153" t="n">
-        <v>105.1046425751499</v>
+        <v>105.3825171192469</v>
       </c>
       <c r="C153" t="n">
-        <v>106.2955145039117</v>
+        <v>106.0672651032121</v>
       </c>
       <c r="D153" t="n">
-        <v>105.1046425751499</v>
+        <v>103.1793971336853</v>
       </c>
       <c r="E153" t="n">
-        <v>105.4916763305664</v>
+        <v>103.4969635009766</v>
       </c>
       <c r="F153" t="n">
-        <v>6423400</v>
+        <v>7784500</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B154" t="n">
-        <v>105.3825171192469</v>
+        <v>104.2313285377519</v>
       </c>
       <c r="C154" t="n">
-        <v>106.0672651032121</v>
+        <v>105.4718232743649</v>
       </c>
       <c r="D154" t="n">
-        <v>103.1793971336853</v>
+        <v>103.437416449147</v>
       </c>
       <c r="E154" t="n">
-        <v>103.4969635009766</v>
+        <v>104.0229263305664</v>
       </c>
       <c r="F154" t="n">
-        <v>7784500</v>
+        <v>6886600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B155" t="n">
-        <v>104.2313285377519</v>
+        <v>104.1420232238167</v>
       </c>
       <c r="C155" t="n">
-        <v>105.4718232743649</v>
+        <v>104.4000406941716</v>
       </c>
       <c r="D155" t="n">
-        <v>103.437416449147</v>
+        <v>101.7701977411496</v>
       </c>
       <c r="E155" t="n">
-        <v>104.0229263305664</v>
+        <v>102.8618316650391</v>
       </c>
       <c r="F155" t="n">
-        <v>6886600</v>
+        <v>6147000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B156" t="n">
-        <v>104.1420232238167</v>
+        <v>102.81220477355</v>
       </c>
       <c r="C156" t="n">
-        <v>104.4000406941716</v>
+        <v>102.851901514659</v>
       </c>
       <c r="D156" t="n">
-        <v>101.7701977411496</v>
+        <v>101.1946023230963</v>
       </c>
       <c r="E156" t="n">
-        <v>102.8618316650391</v>
+        <v>101.8198089599609</v>
       </c>
       <c r="F156" t="n">
-        <v>6147000</v>
+        <v>5974500</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B157" t="n">
-        <v>102.81220477355</v>
+        <v>101.839659785339</v>
       </c>
       <c r="C157" t="n">
-        <v>102.851901514659</v>
+        <v>103.0206056395392</v>
       </c>
       <c r="D157" t="n">
-        <v>101.1946023230963</v>
+        <v>101.2839129884539</v>
       </c>
       <c r="E157" t="n">
-        <v>101.8198089599609</v>
+        <v>101.5717086791992</v>
       </c>
       <c r="F157" t="n">
-        <v>5974500</v>
+        <v>6524300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B158" t="n">
-        <v>101.839659785339</v>
+        <v>101.8793558222072</v>
       </c>
       <c r="C158" t="n">
-        <v>103.0206056395392</v>
+        <v>102.5045624465828</v>
       </c>
       <c r="D158" t="n">
-        <v>101.2839129884539</v>
+        <v>99.84494141643668</v>
       </c>
       <c r="E158" t="n">
-        <v>101.5717086791992</v>
+        <v>100.6984024047852</v>
       </c>
       <c r="F158" t="n">
-        <v>6524300</v>
+        <v>6409300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B159" t="n">
-        <v>101.8793558222072</v>
+        <v>100.1724381261774</v>
       </c>
       <c r="C159" t="n">
-        <v>102.5045624465828</v>
+        <v>100.7083327862765</v>
       </c>
       <c r="D159" t="n">
-        <v>99.84494141643668</v>
+        <v>99.83501960476121</v>
       </c>
       <c r="E159" t="n">
-        <v>100.6984024047852</v>
+        <v>100.5297012329102</v>
       </c>
       <c r="F159" t="n">
-        <v>6409300</v>
+        <v>5533700</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B160" t="n">
-        <v>100.1724381261774</v>
+        <v>100.1426666812253</v>
       </c>
       <c r="C160" t="n">
-        <v>100.7083327862765</v>
+        <v>103.328256381923</v>
       </c>
       <c r="D160" t="n">
-        <v>99.83501960476121</v>
+        <v>99.65638727390106</v>
       </c>
       <c r="E160" t="n">
-        <v>100.5297012329102</v>
+        <v>102.961067199707</v>
       </c>
       <c r="F160" t="n">
-        <v>5533700</v>
+        <v>9203500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B161" t="n">
-        <v>100.1426666812253</v>
+        <v>103.6061276781693</v>
       </c>
       <c r="C161" t="n">
-        <v>103.328256381923</v>
+        <v>104.0328581941516</v>
       </c>
       <c r="D161" t="n">
-        <v>99.65638727390106</v>
+        <v>102.1870013177053</v>
       </c>
       <c r="E161" t="n">
-        <v>102.961067199707</v>
+        <v>102.2961654663086</v>
       </c>
       <c r="F161" t="n">
-        <v>9203500</v>
+        <v>5956900</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B162" t="n">
-        <v>103.6061276781693</v>
+        <v>101.9587457902329</v>
       </c>
       <c r="C162" t="n">
-        <v>104.0328581941516</v>
+        <v>102.2663936470847</v>
       </c>
       <c r="D162" t="n">
-        <v>102.1870013177053</v>
+        <v>100.4999227039044</v>
       </c>
       <c r="E162" t="n">
-        <v>102.2961654663086</v>
+        <v>100.5396194458008</v>
       </c>
       <c r="F162" t="n">
-        <v>5956900</v>
+        <v>8400100</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B163" t="n">
-        <v>101.9587457902329</v>
+        <v>100.7579458156174</v>
       </c>
       <c r="C163" t="n">
-        <v>102.2663936470847</v>
+        <v>100.9564295213072</v>
       </c>
       <c r="D163" t="n">
-        <v>100.4999227039044</v>
+        <v>99.29912275715898</v>
       </c>
       <c r="E163" t="n">
-        <v>100.5396194458008</v>
+        <v>99.71593475341797</v>
       </c>
       <c r="F163" t="n">
-        <v>8400100</v>
+        <v>14314700</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B164" t="n">
-        <v>100.7579458156174</v>
+        <v>105.7099984223796</v>
       </c>
       <c r="C164" t="n">
-        <v>100.9564295213072</v>
+        <v>108.3100781720615</v>
       </c>
       <c r="D164" t="n">
-        <v>99.29912275715898</v>
+        <v>104.5092004000206</v>
       </c>
       <c r="E164" t="n">
-        <v>99.71593475341797</v>
+        <v>107.2382888793945</v>
       </c>
       <c r="F164" t="n">
-        <v>14314700</v>
+        <v>23219500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B165" t="n">
-        <v>105.7099984223796</v>
+        <v>108.2207663660894</v>
       </c>
       <c r="C165" t="n">
-        <v>108.3100781720615</v>
+        <v>109.6398926806152</v>
       </c>
       <c r="D165" t="n">
-        <v>104.5092004000206</v>
+        <v>106.2756639110559</v>
       </c>
       <c r="E165" t="n">
-        <v>107.2382888793945</v>
+        <v>107.8337326049805</v>
       </c>
       <c r="F165" t="n">
-        <v>23219500</v>
+        <v>14309200</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B166" t="n">
-        <v>108.2207663660894</v>
+        <v>108.2009150377847</v>
       </c>
       <c r="C166" t="n">
-        <v>109.6398926806152</v>
+        <v>108.3795465882309</v>
       </c>
       <c r="D166" t="n">
-        <v>106.2756639110559</v>
+        <v>106.7222473860446</v>
       </c>
       <c r="E166" t="n">
-        <v>107.8337326049805</v>
+        <v>107.1985931396484</v>
       </c>
       <c r="F166" t="n">
-        <v>14309200</v>
+        <v>8370000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B167" t="n">
-        <v>108.2009150377847</v>
+        <v>107.1787478525936</v>
       </c>
       <c r="C167" t="n">
-        <v>108.3795465882309</v>
+        <v>107.5657816141287</v>
       </c>
       <c r="D167" t="n">
-        <v>106.7222473860446</v>
+        <v>103.5862722822083</v>
       </c>
       <c r="E167" t="n">
-        <v>107.1985931396484</v>
+        <v>103.9236907958984</v>
       </c>
       <c r="F167" t="n">
-        <v>8370000</v>
+        <v>10562300</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B168" t="n">
-        <v>107.1787478525936</v>
+        <v>104.1916361796018</v>
       </c>
       <c r="C168" t="n">
-        <v>107.5657816141287</v>
+        <v>105.4619016318964</v>
       </c>
       <c r="D168" t="n">
-        <v>103.5862722822083</v>
+        <v>103.4274947211174</v>
       </c>
       <c r="E168" t="n">
-        <v>103.9236907958984</v>
+        <v>105.3527450561523</v>
       </c>
       <c r="F168" t="n">
-        <v>10562300</v>
+        <v>8178500</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B169" t="n">
-        <v>104.1916361796018</v>
+        <v>104.5489005402277</v>
       </c>
       <c r="C169" t="n">
-        <v>105.4619016318964</v>
+        <v>105.0748691255691</v>
       </c>
       <c r="D169" t="n">
-        <v>103.4274947211174</v>
+        <v>103.0702328542224</v>
       </c>
       <c r="E169" t="n">
-        <v>105.3527450561523</v>
+        <v>104.1023254394531</v>
       </c>
       <c r="F169" t="n">
-        <v>8178500</v>
+        <v>7605900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B170" t="n">
-        <v>104.5489005402277</v>
+        <v>104.7374526473249</v>
       </c>
       <c r="C170" t="n">
-        <v>105.0748691255691</v>
+        <v>105.4817494902667</v>
       </c>
       <c r="D170" t="n">
-        <v>103.0702328542224</v>
+        <v>104.0526971289773</v>
       </c>
       <c r="E170" t="n">
-        <v>104.1023254394531</v>
+        <v>104.6183624267578</v>
       </c>
       <c r="F170" t="n">
-        <v>7605900</v>
+        <v>6144600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B171" t="n">
-        <v>104.7374526473249</v>
+        <v>104.2313280181917</v>
       </c>
       <c r="C171" t="n">
-        <v>105.4817494902667</v>
+        <v>104.6183617683755</v>
       </c>
       <c r="D171" t="n">
-        <v>104.0526971289773</v>
+        <v>101.5220917669058</v>
       </c>
       <c r="E171" t="n">
-        <v>104.6183624267578</v>
+        <v>101.9388961791992</v>
       </c>
       <c r="F171" t="n">
-        <v>6144600</v>
+        <v>9258600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B172" t="n">
-        <v>104.2313280181917</v>
+        <v>101.9091260836407</v>
       </c>
       <c r="C172" t="n">
-        <v>104.6183617683755</v>
+        <v>103.9038361698679</v>
       </c>
       <c r="D172" t="n">
-        <v>101.5220917669058</v>
+        <v>101.7701912787705</v>
       </c>
       <c r="E172" t="n">
-        <v>101.9388961791992</v>
+        <v>103.1198501586914</v>
       </c>
       <c r="F172" t="n">
-        <v>9258600</v>
+        <v>9037200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B173" t="n">
-        <v>101.9091260836407</v>
+        <v>102.9213691252704</v>
       </c>
       <c r="C173" t="n">
-        <v>103.9038361698679</v>
+        <v>103.1396974161188</v>
       </c>
       <c r="D173" t="n">
-        <v>101.7701912787705</v>
+        <v>101.1946025261468</v>
       </c>
       <c r="E173" t="n">
-        <v>103.1198501586914</v>
+        <v>101.5121688842773</v>
       </c>
       <c r="F173" t="n">
-        <v>9037200</v>
+        <v>7032600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B174" t="n">
-        <v>102.9213691252704</v>
+        <v>102.1274576654748</v>
       </c>
       <c r="C174" t="n">
-        <v>103.1396974161188</v>
+        <v>104.0626264896183</v>
       </c>
       <c r="D174" t="n">
-        <v>101.1946025261468</v>
+        <v>100.8274139902545</v>
       </c>
       <c r="E174" t="n">
-        <v>101.5121688842773</v>
+        <v>103.2885589599609</v>
       </c>
       <c r="F174" t="n">
-        <v>7032600</v>
+        <v>7941400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B175" t="n">
-        <v>102.1274576654748</v>
+        <v>102.822129060906</v>
       </c>
       <c r="C175" t="n">
-        <v>104.0626264896183</v>
+        <v>103.8244509351605</v>
       </c>
       <c r="D175" t="n">
-        <v>100.8274139902545</v>
+        <v>101.8098811087023</v>
       </c>
       <c r="E175" t="n">
-        <v>103.2885589599609</v>
+        <v>102.7923583984375</v>
       </c>
       <c r="F175" t="n">
-        <v>7941400</v>
+        <v>8611200</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B176" t="n">
-        <v>102.822129060906</v>
+        <v>103.2488588874603</v>
       </c>
       <c r="C176" t="n">
-        <v>103.8244509351605</v>
+        <v>103.7053600422387</v>
       </c>
       <c r="D176" t="n">
-        <v>101.8098811087023</v>
+        <v>102.1969217730311</v>
       </c>
       <c r="E176" t="n">
-        <v>102.7923583984375</v>
+        <v>102.2167663574219</v>
       </c>
       <c r="F176" t="n">
-        <v>8611200</v>
+        <v>5693300</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B177" t="n">
-        <v>103.2488588874603</v>
+        <v>102.3160049896206</v>
       </c>
       <c r="C177" t="n">
-        <v>103.7053600422387</v>
+        <v>103.0106865892155</v>
       </c>
       <c r="D177" t="n">
-        <v>102.1969217730311</v>
+        <v>101.571708143084</v>
       </c>
       <c r="E177" t="n">
-        <v>102.2167663574219</v>
+        <v>102.4946365356445</v>
       </c>
       <c r="F177" t="n">
-        <v>5693300</v>
+        <v>6714400</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B178" t="n">
-        <v>102.3160049896206</v>
+        <v>102.5144889184559</v>
       </c>
       <c r="C178" t="n">
-        <v>103.0106865892155</v>
+        <v>104.4496576951832</v>
       </c>
       <c r="D178" t="n">
-        <v>101.571708143084</v>
+        <v>102.4747921779873</v>
       </c>
       <c r="E178" t="n">
-        <v>102.4946365356445</v>
+        <v>103.3877944946289</v>
       </c>
       <c r="F178" t="n">
-        <v>6714400</v>
+        <v>7360100</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B179" t="n">
-        <v>102.5144889184559</v>
+        <v>103.0206090569662</v>
       </c>
       <c r="C179" t="n">
-        <v>104.4496576951832</v>
+        <v>103.6160526141937</v>
       </c>
       <c r="D179" t="n">
-        <v>102.4747921779873</v>
+        <v>102.3160089237181</v>
       </c>
       <c r="E179" t="n">
-        <v>103.3877944946289</v>
+        <v>102.9412231445312</v>
       </c>
       <c r="F179" t="n">
-        <v>7360100</v>
+        <v>6511100</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B180" t="n">
-        <v>103.0206090569662</v>
+        <v>102.8419796873618</v>
       </c>
       <c r="C180" t="n">
-        <v>103.6160526141937</v>
+        <v>102.9709959941437</v>
       </c>
       <c r="D180" t="n">
-        <v>102.3160089237181</v>
+        <v>101.0556716918945</v>
       </c>
       <c r="E180" t="n">
-        <v>102.9412231445312</v>
+        <v>101.0556716918945</v>
       </c>
       <c r="F180" t="n">
-        <v>6511100</v>
+        <v>13340300</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B181" t="n">
-        <v>102.8419796873618</v>
+        <v>100.8869633557317</v>
       </c>
       <c r="C181" t="n">
-        <v>102.9709959941437</v>
+        <v>102.2266962072239</v>
       </c>
       <c r="D181" t="n">
-        <v>101.0556716918945</v>
+        <v>99.53730442598828</v>
       </c>
       <c r="E181" t="n">
-        <v>101.0556716918945</v>
+        <v>102.0679092407227</v>
       </c>
       <c r="F181" t="n">
-        <v>13340300</v>
+        <v>8219000</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B182" t="n">
-        <v>100.8869633557317</v>
+        <v>101.5717095216456</v>
       </c>
       <c r="C182" t="n">
-        <v>102.2266962072239</v>
+        <v>101.7106443291744</v>
       </c>
       <c r="D182" t="n">
-        <v>99.53730442598828</v>
+        <v>99.32889287365569</v>
       </c>
       <c r="E182" t="n">
-        <v>102.0679092407227</v>
+        <v>100.6388626098633</v>
       </c>
       <c r="F182" t="n">
-        <v>8219000</v>
+        <v>8397400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B183" t="n">
-        <v>101.5717095216456</v>
+        <v>99.67623490973834</v>
       </c>
       <c r="C183" t="n">
-        <v>101.7106443291744</v>
+        <v>100.4999176557305</v>
       </c>
       <c r="D183" t="n">
-        <v>99.32889287365569</v>
+        <v>98.495281504625</v>
       </c>
       <c r="E183" t="n">
-        <v>100.6388626098633</v>
+        <v>98.63421630859375</v>
       </c>
       <c r="F183" t="n">
-        <v>8397400</v>
+        <v>7471600</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B184" t="n">
-        <v>99.67623490973834</v>
+        <v>99.77547422442305</v>
       </c>
       <c r="C184" t="n">
-        <v>100.4999176557305</v>
+        <v>100.6984026174289</v>
       </c>
       <c r="D184" t="n">
-        <v>98.495281504625</v>
+        <v>98.25710986817649</v>
       </c>
       <c r="E184" t="n">
-        <v>98.63421630859375</v>
+        <v>98.5845947265625</v>
       </c>
       <c r="F184" t="n">
-        <v>7471600</v>
+        <v>9568000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B185" t="n">
-        <v>99.77547422442305</v>
+        <v>98.92201919170897</v>
       </c>
       <c r="C185" t="n">
-        <v>100.6984026174289</v>
+        <v>99.43806170522778</v>
       </c>
       <c r="D185" t="n">
-        <v>98.25710986817649</v>
+        <v>98.33650169977196</v>
       </c>
       <c r="E185" t="n">
-        <v>98.5845947265625</v>
+        <v>98.95178985595703</v>
       </c>
       <c r="F185" t="n">
-        <v>9568000</v>
+        <v>9501600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B186" t="n">
-        <v>98.92201919170897</v>
+        <v>98.76323055949389</v>
       </c>
       <c r="C186" t="n">
-        <v>99.43806170522778</v>
+        <v>99.08079692509821</v>
       </c>
       <c r="D186" t="n">
-        <v>98.33650169977196</v>
+        <v>97.66167814394407</v>
       </c>
       <c r="E186" t="n">
-        <v>98.95178985595703</v>
+        <v>98.11817932128906</v>
       </c>
       <c r="F186" t="n">
-        <v>9501600</v>
+        <v>7559200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B187" t="n">
-        <v>98.76323055949389</v>
+        <v>98.29680690142362</v>
       </c>
       <c r="C187" t="n">
-        <v>99.08079692509821</v>
+        <v>99.32889186938023</v>
       </c>
       <c r="D187" t="n">
-        <v>97.66167814394407</v>
+        <v>97.7609122614967</v>
       </c>
       <c r="E187" t="n">
-        <v>98.11817932128906</v>
+        <v>98.57467651367188</v>
       </c>
       <c r="F187" t="n">
-        <v>7559200</v>
+        <v>8616300</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B188" t="n">
-        <v>98.29680690142362</v>
+        <v>98.7334588011272</v>
       </c>
       <c r="C188" t="n">
-        <v>99.32889186938023</v>
+        <v>99.00140991464168</v>
       </c>
       <c r="D188" t="n">
-        <v>97.7609122614967</v>
+        <v>97.20516831754395</v>
       </c>
       <c r="E188" t="n">
-        <v>98.57467651367188</v>
+        <v>97.86015319824219</v>
       </c>
       <c r="F188" t="n">
-        <v>8616300</v>
+        <v>7041400</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B189" t="n">
-        <v>98.7334588011272</v>
+        <v>98.07848356908464</v>
       </c>
       <c r="C189" t="n">
-        <v>99.00140991464168</v>
+        <v>99.97395570346617</v>
       </c>
       <c r="D189" t="n">
-        <v>97.20516831754395</v>
+        <v>97.35403126794252</v>
       </c>
       <c r="E189" t="n">
-        <v>97.86015319824219</v>
+        <v>99.57699584960938</v>
       </c>
       <c r="F189" t="n">
-        <v>7041400</v>
+        <v>9264400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B190" t="n">
-        <v>98.07848356908464</v>
+        <v>100.2915220505157</v>
       </c>
       <c r="C190" t="n">
-        <v>99.97395570346617</v>
+        <v>100.9961221945534</v>
       </c>
       <c r="D190" t="n">
-        <v>97.35403126794252</v>
+        <v>98.78308369184245</v>
       </c>
       <c r="E190" t="n">
-        <v>99.57699584960938</v>
+        <v>99.27928161621094</v>
       </c>
       <c r="F190" t="n">
-        <v>9264400</v>
+        <v>8257200</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B191" t="n">
-        <v>100.2915220505157</v>
+        <v>100.1128870298928</v>
       </c>
       <c r="C191" t="n">
-        <v>100.9961221945534</v>
+        <v>101.6213329077368</v>
       </c>
       <c r="D191" t="n">
-        <v>98.78308369184245</v>
+        <v>99.82509133515438</v>
       </c>
       <c r="E191" t="n">
-        <v>99.27928161621094</v>
+        <v>100.9167327880859</v>
       </c>
       <c r="F191" t="n">
-        <v>8257200</v>
+        <v>10265100</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B192" t="n">
-        <v>100.1128870298928</v>
+        <v>100.658710438741</v>
       </c>
       <c r="C192" t="n">
-        <v>101.6213329077368</v>
+        <v>101.1549083591584</v>
       </c>
       <c r="D192" t="n">
-        <v>99.82509133515438</v>
+        <v>99.28920690408536</v>
       </c>
       <c r="E192" t="n">
-        <v>100.9167327880859</v>
+        <v>100.5098495483398</v>
       </c>
       <c r="F192" t="n">
-        <v>10265100</v>
+        <v>10694600</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B193" t="n">
-        <v>100.658710438741</v>
+        <v>99.90448284246082</v>
       </c>
       <c r="C193" t="n">
-        <v>101.1549083591584</v>
+        <v>101.581634158465</v>
       </c>
       <c r="D193" t="n">
-        <v>99.28920690408536</v>
+        <v>99.67623604963576</v>
       </c>
       <c r="E193" t="n">
-        <v>100.5098495483398</v>
+        <v>100.0930404663086</v>
       </c>
       <c r="F193" t="n">
-        <v>10694600</v>
+        <v>11168700</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B194" t="n">
-        <v>99.90448284246082</v>
+        <v>101.0258948980948</v>
       </c>
       <c r="C194" t="n">
-        <v>101.581634158465</v>
+        <v>103.4274909034028</v>
       </c>
       <c r="D194" t="n">
-        <v>99.67623604963576</v>
+        <v>100.0334991036985</v>
       </c>
       <c r="E194" t="n">
-        <v>100.0930404663086</v>
+        <v>103.0999984741211</v>
       </c>
       <c r="F194" t="n">
-        <v>11168700</v>
+        <v>22943600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B195" t="n">
-        <v>101.0258948980948</v>
+        <v>102.623658522444</v>
       </c>
       <c r="C195" t="n">
-        <v>103.4274909034028</v>
+        <v>103.5168087306858</v>
       </c>
       <c r="D195" t="n">
-        <v>100.0334991036985</v>
+        <v>100.7381048924391</v>
       </c>
       <c r="E195" t="n">
-        <v>103.0999984741211</v>
+        <v>101.6709518432617</v>
       </c>
       <c r="F195" t="n">
-        <v>22943600</v>
+        <v>17396300</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B196" t="n">
-        <v>102.623658522444</v>
+        <v>101.2442170259669</v>
       </c>
       <c r="C196" t="n">
-        <v>103.5168087306858</v>
+        <v>103.2488607985985</v>
       </c>
       <c r="D196" t="n">
-        <v>100.7381048924391</v>
+        <v>101.025896308111</v>
       </c>
       <c r="E196" t="n">
-        <v>101.6709518432617</v>
+        <v>102.7427368164062</v>
       </c>
       <c r="F196" t="n">
-        <v>17396300</v>
+        <v>14457400</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B197" t="n">
-        <v>101.2442170259669</v>
+        <v>102.3160060444983</v>
       </c>
       <c r="C197" t="n">
-        <v>103.2488607985985</v>
+        <v>103.7351323493811</v>
       </c>
       <c r="D197" t="n">
-        <v>101.025896308111</v>
+        <v>100.2716731077754</v>
       </c>
       <c r="E197" t="n">
-        <v>102.7427368164062</v>
+        <v>100.3510665893555</v>
       </c>
       <c r="F197" t="n">
-        <v>14457400</v>
+        <v>12215500</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B198" t="n">
-        <v>102.3160060444983</v>
+        <v>100.3411416176147</v>
       </c>
       <c r="C198" t="n">
-        <v>103.7351323493811</v>
+        <v>100.8075688628163</v>
       </c>
       <c r="D198" t="n">
-        <v>100.2716731077754</v>
+        <v>97.24486394426569</v>
       </c>
       <c r="E198" t="n">
-        <v>100.3510665893555</v>
+        <v>97.30441284179688</v>
       </c>
       <c r="F198" t="n">
-        <v>12215500</v>
+        <v>12054400</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B199" t="n">
-        <v>100.3411416176147</v>
+        <v>97.30440945370802</v>
       </c>
       <c r="C199" t="n">
-        <v>100.8075688628163</v>
+        <v>98.69375749140566</v>
       </c>
       <c r="D199" t="n">
-        <v>97.24486394426569</v>
+        <v>97.15554857213215</v>
       </c>
       <c r="E199" t="n">
-        <v>97.30441284179688</v>
+        <v>98.03878021240234</v>
       </c>
       <c r="F199" t="n">
-        <v>12054400</v>
+        <v>13921400</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B200" t="n">
-        <v>97.30440945370802</v>
+        <v>98.95178655891404</v>
       </c>
       <c r="C200" t="n">
-        <v>98.69375749140566</v>
+        <v>99.27927899748993</v>
       </c>
       <c r="D200" t="n">
-        <v>97.15554857213215</v>
+        <v>97.75098852218167</v>
       </c>
       <c r="E200" t="n">
-        <v>98.03878021240234</v>
+        <v>97.87999725341797</v>
       </c>
       <c r="F200" t="n">
-        <v>13921400</v>
+        <v>10418100</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,25 +5643,25 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B201" t="n">
-        <v>98.95178655891404</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C201" t="n">
-        <v>99.27927899748993</v>
+        <v>97.59999847412109</v>
       </c>
       <c r="D201" t="n">
-        <v>97.75098852218167</v>
+        <v>95.98999786376953</v>
       </c>
       <c r="E201" t="n">
-        <v>97.87999725341797</v>
+        <v>96.25</v>
       </c>
       <c r="F201" t="n">
-        <v>10418100</v>
+        <v>12717800</v>
       </c>
       <c r="G201" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -5669,25 +5669,25 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B202" t="n">
-        <v>97.41000366210938</v>
+        <v>96.55000305175781</v>
       </c>
       <c r="C202" t="n">
-        <v>97.59999847412109</v>
+        <v>97.76000213623047</v>
       </c>
       <c r="D202" t="n">
-        <v>95.98999786376953</v>
+        <v>95.65000152587891</v>
       </c>
       <c r="E202" t="n">
-        <v>96.25</v>
+        <v>95.70999908447266</v>
       </c>
       <c r="F202" t="n">
-        <v>12717800</v>
+        <v>11590400</v>
       </c>
       <c r="G202" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B203" t="n">
-        <v>96.55000305175781</v>
+        <v>96.40000152587891</v>
       </c>
       <c r="C203" t="n">
-        <v>97.76000213623047</v>
+        <v>99.51999664306641</v>
       </c>
       <c r="D203" t="n">
-        <v>95.65000152587891</v>
+        <v>95.76999664306641</v>
       </c>
       <c r="E203" t="n">
-        <v>95.70999908447266</v>
+        <v>99.5</v>
       </c>
       <c r="F203" t="n">
-        <v>11590400</v>
+        <v>11297800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B204" t="n">
-        <v>96.40000152587891</v>
+        <v>98.84999847412109</v>
       </c>
       <c r="C204" t="n">
-        <v>99.51999664306641</v>
+        <v>99.44000244140625</v>
       </c>
       <c r="D204" t="n">
-        <v>95.76999664306641</v>
+        <v>97.01999664306641</v>
       </c>
       <c r="E204" t="n">
-        <v>99.5</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="F204" t="n">
-        <v>11297800</v>
+        <v>10171900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B205" t="n">
-        <v>98.84999847412109</v>
+        <v>98.13999938964844</v>
       </c>
       <c r="C205" t="n">
-        <v>99.44000244140625</v>
+        <v>99.04000091552734</v>
       </c>
       <c r="D205" t="n">
-        <v>97.01999664306641</v>
+        <v>96.91999816894531</v>
       </c>
       <c r="E205" t="n">
-        <v>97.41000366210938</v>
+        <v>97.48000335693359</v>
       </c>
       <c r="F205" t="n">
-        <v>10171900</v>
+        <v>9936400</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B206" t="n">
-        <v>98.13999938964844</v>
+        <v>97.30000305175781</v>
       </c>
       <c r="C206" t="n">
-        <v>99.04000091552734</v>
+        <v>97.66000366210938</v>
       </c>
       <c r="D206" t="n">
-        <v>96.91999816894531</v>
+        <v>96.63999938964844</v>
       </c>
       <c r="E206" t="n">
-        <v>97.48000335693359</v>
+        <v>96.69999694824219</v>
       </c>
       <c r="F206" t="n">
-        <v>9936400</v>
+        <v>8720800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B207" t="n">
-        <v>97.30000305175781</v>
+        <v>96.33999633789062</v>
       </c>
       <c r="C207" t="n">
-        <v>97.66000366210938</v>
+        <v>96.55000305175781</v>
       </c>
       <c r="D207" t="n">
-        <v>96.63999938964844</v>
+        <v>94.77999877929688</v>
       </c>
       <c r="E207" t="n">
-        <v>96.69999694824219</v>
+        <v>96.16999816894531</v>
       </c>
       <c r="F207" t="n">
-        <v>8720800</v>
+        <v>11448100</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B208" t="n">
-        <v>96.33999633789062</v>
+        <v>96.88999938964844</v>
       </c>
       <c r="C208" t="n">
-        <v>96.55000305175781</v>
+        <v>97.05000305175781</v>
       </c>
       <c r="D208" t="n">
-        <v>94.77999877929688</v>
+        <v>95.51999664306641</v>
       </c>
       <c r="E208" t="n">
-        <v>96.16999816894531</v>
+        <v>95.62000274658203</v>
       </c>
       <c r="F208" t="n">
-        <v>11448100</v>
+        <v>10678900</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B209" t="n">
-        <v>96.88999938964844</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="C209" t="n">
-        <v>97.05000305175781</v>
+        <v>97.54000091552734</v>
       </c>
       <c r="D209" t="n">
-        <v>95.51999664306641</v>
+        <v>95.83000183105469</v>
       </c>
       <c r="E209" t="n">
-        <v>95.62000274658203</v>
+        <v>96</v>
       </c>
       <c r="F209" t="n">
-        <v>10678900</v>
+        <v>9304200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>96.09999847412109</v>
+        <v>95.51000213623047</v>
       </c>
       <c r="C210" t="n">
-        <v>97.54000091552734</v>
+        <v>96.69000244140625</v>
       </c>
       <c r="D210" t="n">
-        <v>95.83000183105469</v>
+        <v>95.12999725341797</v>
       </c>
       <c r="E210" t="n">
-        <v>96</v>
+        <v>95.87000274658203</v>
       </c>
       <c r="F210" t="n">
-        <v>9304200</v>
+        <v>7651600</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>95.51000213623047</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="C211" t="n">
-        <v>96.69000244140625</v>
+        <v>97.90000152587891</v>
       </c>
       <c r="D211" t="n">
-        <v>95.12999725341797</v>
+        <v>96.09999847412109</v>
       </c>
       <c r="E211" t="n">
-        <v>95.87000274658203</v>
+        <v>97.15000152587891</v>
       </c>
       <c r="F211" t="n">
-        <v>7651600</v>
+        <v>10219200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>96.09999847412109</v>
+        <v>97.27999877929688</v>
       </c>
       <c r="C212" t="n">
-        <v>97.90000152587891</v>
+        <v>99.84999847412109</v>
       </c>
       <c r="D212" t="n">
-        <v>96.09999847412109</v>
+        <v>97.27999877929688</v>
       </c>
       <c r="E212" t="n">
-        <v>97.15000152587891</v>
+        <v>99.70999908447266</v>
       </c>
       <c r="F212" t="n">
-        <v>10219200</v>
+        <v>7480000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B213" t="n">
-        <v>97.27999877929688</v>
+        <v>99.01000213623047</v>
       </c>
       <c r="C213" t="n">
-        <v>99.84999847412109</v>
+        <v>99.79000091552734</v>
       </c>
       <c r="D213" t="n">
-        <v>97.27999877929688</v>
+        <v>97.05000305175781</v>
       </c>
       <c r="E213" t="n">
-        <v>99.70999908447266</v>
+        <v>97.66999816894531</v>
       </c>
       <c r="F213" t="n">
-        <v>7480000</v>
+        <v>10496500</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B214" t="n">
-        <v>99.01000213623047</v>
+        <v>97.84999847412109</v>
       </c>
       <c r="C214" t="n">
-        <v>99.79000091552734</v>
+        <v>98.38999938964844</v>
       </c>
       <c r="D214" t="n">
-        <v>97.05000305175781</v>
+        <v>96</v>
       </c>
       <c r="E214" t="n">
-        <v>97.66999816894531</v>
+        <v>96.41000366210938</v>
       </c>
       <c r="F214" t="n">
-        <v>10496500</v>
+        <v>9861700</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B215" t="n">
-        <v>97.84999847412109</v>
+        <v>96</v>
       </c>
       <c r="C215" t="n">
-        <v>98.38999938964844</v>
+        <v>96.88999938964844</v>
       </c>
       <c r="D215" t="n">
-        <v>96</v>
+        <v>95.83999633789062</v>
       </c>
       <c r="E215" t="n">
-        <v>96.41000366210938</v>
+        <v>96.13999938964844</v>
       </c>
       <c r="F215" t="n">
-        <v>9861700</v>
+        <v>9745400</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B216" t="n">
-        <v>96</v>
+        <v>97.12000274658203</v>
       </c>
       <c r="C216" t="n">
-        <v>96.88999938964844</v>
+        <v>97.30000305175781</v>
       </c>
       <c r="D216" t="n">
-        <v>95.83999633789062</v>
+        <v>95.65000152587891</v>
       </c>
       <c r="E216" t="n">
-        <v>96.13999938964844</v>
+        <v>95.87000274658203</v>
       </c>
       <c r="F216" t="n">
-        <v>9745400</v>
+        <v>9119200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B217" t="n">
-        <v>97.12000274658203</v>
+        <v>94.80999755859375</v>
       </c>
       <c r="C217" t="n">
-        <v>97.30000305175781</v>
+        <v>94.81999969482422</v>
       </c>
       <c r="D217" t="n">
-        <v>95.65000152587891</v>
+        <v>92.48999786376953</v>
       </c>
       <c r="E217" t="n">
-        <v>95.87000274658203</v>
+        <v>92.83000183105469</v>
       </c>
       <c r="F217" t="n">
-        <v>9119200</v>
+        <v>13562500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B218" t="n">
-        <v>94.80999755859375</v>
+        <v>93.26000213623047</v>
       </c>
       <c r="C218" t="n">
-        <v>94.81999969482422</v>
+        <v>96.29000091552734</v>
       </c>
       <c r="D218" t="n">
-        <v>92.48999786376953</v>
+        <v>93</v>
       </c>
       <c r="E218" t="n">
-        <v>92.83000183105469</v>
+        <v>94.84999847412109</v>
       </c>
       <c r="F218" t="n">
-        <v>13562500</v>
+        <v>12153100</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B219" t="n">
-        <v>93.26000213623047</v>
+        <v>95.51000213623047</v>
       </c>
       <c r="C219" t="n">
-        <v>96.29000091552734</v>
+        <v>97.19000244140625</v>
       </c>
       <c r="D219" t="n">
-        <v>93</v>
+        <v>95.51000213623047</v>
       </c>
       <c r="E219" t="n">
-        <v>94.84999847412109</v>
+        <v>96.65000152587891</v>
       </c>
       <c r="F219" t="n">
-        <v>12153100</v>
+        <v>10593900</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B220" t="n">
-        <v>95.51000213623047</v>
+        <v>97</v>
       </c>
       <c r="C220" t="n">
-        <v>97.19000244140625</v>
+        <v>99.23000335693359</v>
       </c>
       <c r="D220" t="n">
-        <v>95.51000213623047</v>
+        <v>96.97000122070312</v>
       </c>
       <c r="E220" t="n">
-        <v>96.65000152587891</v>
+        <v>98.88999938964844</v>
       </c>
       <c r="F220" t="n">
-        <v>10593900</v>
+        <v>11389300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B221" t="n">
-        <v>97</v>
+        <v>98.33999633789062</v>
       </c>
       <c r="C221" t="n">
-        <v>99.23000335693359</v>
+        <v>99.41000366210938</v>
       </c>
       <c r="D221" t="n">
-        <v>96.97000122070312</v>
+        <v>97.98999786376953</v>
       </c>
       <c r="E221" t="n">
-        <v>98.88999938964844</v>
+        <v>98.48000335693359</v>
       </c>
       <c r="F221" t="n">
-        <v>11389300</v>
+        <v>11070100</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B222" t="n">
-        <v>98.33999633789062</v>
+        <v>97.41000366210938</v>
       </c>
       <c r="C222" t="n">
-        <v>99.41000366210938</v>
+        <v>97.48000335693359</v>
       </c>
       <c r="D222" t="n">
-        <v>97.98999786376953</v>
+        <v>94.45999908447266</v>
       </c>
       <c r="E222" t="n">
-        <v>98.48000335693359</v>
+        <v>96.16000366210938</v>
       </c>
       <c r="F222" t="n">
-        <v>11070100</v>
+        <v>21112400</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B223" t="n">
-        <v>97.41000366210938</v>
+        <v>96.08000183105469</v>
       </c>
       <c r="C223" t="n">
-        <v>97.48000335693359</v>
+        <v>96.58999633789062</v>
       </c>
       <c r="D223" t="n">
-        <v>94.45999908447266</v>
+        <v>95.59999847412109</v>
       </c>
       <c r="E223" t="n">
-        <v>96.16000366210938</v>
+        <v>96.19000244140625</v>
       </c>
       <c r="F223" t="n">
-        <v>21112400</v>
+        <v>11193000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B224" t="n">
-        <v>96.08000183105469</v>
+        <v>97.62000274658203</v>
       </c>
       <c r="C224" t="n">
-        <v>96.58999633789062</v>
+        <v>99.05000305175781</v>
       </c>
       <c r="D224" t="n">
-        <v>95.59999847412109</v>
+        <v>97.20999908447266</v>
       </c>
       <c r="E224" t="n">
-        <v>96.19000244140625</v>
+        <v>98.13999938964844</v>
       </c>
       <c r="F224" t="n">
-        <v>11193000</v>
+        <v>11480300</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B225" t="n">
-        <v>97.62000274658203</v>
+        <v>97.87000274658203</v>
       </c>
       <c r="C225" t="n">
-        <v>99.05000305175781</v>
+        <v>98.56999969482422</v>
       </c>
       <c r="D225" t="n">
-        <v>97.20999908447266</v>
+        <v>97.37999725341797</v>
       </c>
       <c r="E225" t="n">
-        <v>98.13999938964844</v>
+        <v>98.18000030517578</v>
       </c>
       <c r="F225" t="n">
-        <v>11480300</v>
+        <v>16796800</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B226" t="n">
-        <v>97.87000274658203</v>
+        <v>101.9899978637695</v>
       </c>
       <c r="C226" t="n">
-        <v>98.56999969482422</v>
+        <v>103.2099990844727</v>
       </c>
       <c r="D226" t="n">
-        <v>97.37999725341797</v>
+        <v>99.69000244140625</v>
       </c>
       <c r="E226" t="n">
-        <v>98.18000030517578</v>
+        <v>101.7600021362305</v>
       </c>
       <c r="F226" t="n">
-        <v>16796800</v>
+        <v>20809000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B227" t="n">
-        <v>101.9899978637695</v>
+        <v>102.5400009155273</v>
       </c>
       <c r="C227" t="n">
-        <v>103.2099990844727</v>
+        <v>104.7300033569336</v>
       </c>
       <c r="D227" t="n">
-        <v>99.69000244140625</v>
+        <v>102.5199966430664</v>
       </c>
       <c r="E227" t="n">
-        <v>101.7600021362305</v>
+        <v>104.6800003051758</v>
       </c>
       <c r="F227" t="n">
-        <v>20809000</v>
+        <v>14047200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B228" t="n">
-        <v>102.5400009155273</v>
+        <v>104.4199981689453</v>
       </c>
       <c r="C228" t="n">
-        <v>104.7300033569336</v>
+        <v>105.25</v>
       </c>
       <c r="D228" t="n">
-        <v>102.5199966430664</v>
+        <v>103.6999969482422</v>
       </c>
       <c r="E228" t="n">
-        <v>104.6800003051758</v>
+        <v>104.9100036621094</v>
       </c>
       <c r="F228" t="n">
-        <v>14047200</v>
+        <v>10929700</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B229" t="n">
-        <v>104.4199981689453</v>
+        <v>104.6100006103516</v>
       </c>
       <c r="C229" t="n">
-        <v>105.25</v>
+        <v>104.8000030517578</v>
       </c>
       <c r="D229" t="n">
-        <v>103.6999969482422</v>
+        <v>102.8000030517578</v>
       </c>
       <c r="E229" t="n">
-        <v>104.9100036621094</v>
+        <v>103.1800003051758</v>
       </c>
       <c r="F229" t="n">
-        <v>10929700</v>
+        <v>8631900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B230" t="n">
-        <v>104.6100006103516</v>
+        <v>102.9499969482422</v>
       </c>
       <c r="C230" t="n">
-        <v>104.8000030517578</v>
+        <v>104.0899963378906</v>
       </c>
       <c r="D230" t="n">
-        <v>102.8000030517578</v>
+        <v>102.7900009155273</v>
       </c>
       <c r="E230" t="n">
-        <v>103.1800003051758</v>
+        <v>103.5299987792969</v>
       </c>
       <c r="F230" t="n">
-        <v>8631900</v>
+        <v>6781600</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B231" t="n">
-        <v>102.9499969482422</v>
+        <v>103.2900009155273</v>
       </c>
       <c r="C231" t="n">
-        <v>104.0899963378906</v>
+        <v>103.6800003051758</v>
       </c>
       <c r="D231" t="n">
-        <v>102.7900009155273</v>
+        <v>102.0299987792969</v>
       </c>
       <c r="E231" t="n">
-        <v>103.5299987792969</v>
+        <v>103.2200012207031</v>
       </c>
       <c r="F231" t="n">
-        <v>6781600</v>
+        <v>6717500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B232" t="n">
-        <v>103.2900009155273</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="C232" t="n">
-        <v>103.6800003051758</v>
+        <v>104.9400024414062</v>
       </c>
       <c r="D232" t="n">
-        <v>102.0299987792969</v>
+        <v>103.4599990844727</v>
       </c>
       <c r="E232" t="n">
-        <v>103.2200012207031</v>
+        <v>104.8000030517578</v>
       </c>
       <c r="F232" t="n">
-        <v>6717500</v>
+        <v>7100000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B233" t="n">
-        <v>103.8000030517578</v>
+        <v>104.9899978637695</v>
       </c>
       <c r="C233" t="n">
-        <v>104.9400024414062</v>
+        <v>107.1100006103516</v>
       </c>
       <c r="D233" t="n">
-        <v>103.4599990844727</v>
+        <v>104.9100036621094</v>
       </c>
       <c r="E233" t="n">
-        <v>104.8000030517578</v>
+        <v>106.8499984741211</v>
       </c>
       <c r="F233" t="n">
-        <v>7100000</v>
+        <v>8176900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B234" t="n">
-        <v>104.9899978637695</v>
+        <v>106.3300018310547</v>
       </c>
       <c r="C234" t="n">
-        <v>107.1100006103516</v>
+        <v>106.6399993896484</v>
       </c>
       <c r="D234" t="n">
-        <v>104.9100036621094</v>
+        <v>103.4599990844727</v>
       </c>
       <c r="E234" t="n">
-        <v>106.8499984741211</v>
+        <v>103.5</v>
       </c>
       <c r="F234" t="n">
-        <v>8176900</v>
+        <v>7635000</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B235" t="n">
-        <v>106.3300018310547</v>
+        <v>104.1900024414062</v>
       </c>
       <c r="C235" t="n">
-        <v>106.6399993896484</v>
+        <v>105.2099990844727</v>
       </c>
       <c r="D235" t="n">
-        <v>103.4599990844727</v>
+        <v>103.629997253418</v>
       </c>
       <c r="E235" t="n">
-        <v>103.5</v>
+        <v>103.9499969482422</v>
       </c>
       <c r="F235" t="n">
-        <v>7635000</v>
+        <v>6149900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B236" t="n">
-        <v>104.1900024414062</v>
+        <v>104.0599975585938</v>
       </c>
       <c r="C236" t="n">
-        <v>105.2099990844727</v>
+        <v>107.0599975585938</v>
       </c>
       <c r="D236" t="n">
-        <v>103.629997253418</v>
+        <v>103.9599990844727</v>
       </c>
       <c r="E236" t="n">
-        <v>103.9499969482422</v>
+        <v>106.9300003051758</v>
       </c>
       <c r="F236" t="n">
-        <v>6149900</v>
+        <v>8046100</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B237" t="n">
-        <v>104.0599975585938</v>
+        <v>106.879997253418</v>
       </c>
       <c r="C237" t="n">
-        <v>107.0599975585938</v>
+        <v>108.6900024414062</v>
       </c>
       <c r="D237" t="n">
-        <v>103.9599990844727</v>
+        <v>106.4199981689453</v>
       </c>
       <c r="E237" t="n">
-        <v>106.9300003051758</v>
+        <v>107.3199996948242</v>
       </c>
       <c r="F237" t="n">
-        <v>8046100</v>
+        <v>7971500</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B238" t="n">
-        <v>106.879997253418</v>
+        <v>107.5699996948242</v>
       </c>
       <c r="C238" t="n">
-        <v>108.6900024414062</v>
+        <v>108.4100036621094</v>
       </c>
       <c r="D238" t="n">
-        <v>106.4199981689453</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="E238" t="n">
-        <v>107.3199996948242</v>
+        <v>107.7799987792969</v>
       </c>
       <c r="F238" t="n">
-        <v>7971500</v>
+        <v>6840800</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B239" t="n">
-        <v>107.5699996948242</v>
+        <v>108.3899993896484</v>
       </c>
       <c r="C239" t="n">
-        <v>108.4100036621094</v>
+        <v>111.870002746582</v>
       </c>
       <c r="D239" t="n">
-        <v>106.9700012207031</v>
+        <v>108.0800018310547</v>
       </c>
       <c r="E239" t="n">
-        <v>107.7799987792969</v>
+        <v>110.6100006103516</v>
       </c>
       <c r="F239" t="n">
-        <v>6840800</v>
+        <v>12658400</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B240" t="n">
-        <v>108.3899993896484</v>
+        <v>110.5</v>
       </c>
       <c r="C240" t="n">
-        <v>111.870002746582</v>
+        <v>111.5999984741211</v>
       </c>
       <c r="D240" t="n">
-        <v>108.0800018310547</v>
+        <v>109.7600021362305</v>
       </c>
       <c r="E240" t="n">
-        <v>110.6100006103516</v>
+        <v>111.25</v>
       </c>
       <c r="F240" t="n">
-        <v>12658400</v>
+        <v>6747100</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B241" t="n">
-        <v>110.5</v>
+        <v>111.3000030517578</v>
       </c>
       <c r="C241" t="n">
-        <v>111.5999984741211</v>
+        <v>111.5199966430664</v>
       </c>
       <c r="D241" t="n">
-        <v>109.7600021362305</v>
+        <v>109.4499969482422</v>
       </c>
       <c r="E241" t="n">
-        <v>111.25</v>
+        <v>109.629997253418</v>
       </c>
       <c r="F241" t="n">
-        <v>6747100</v>
+        <v>8524600</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B242" t="n">
-        <v>111.3000030517578</v>
+        <v>108.7799987792969</v>
       </c>
       <c r="C242" t="n">
-        <v>111.5199966430664</v>
+        <v>108.870002746582</v>
       </c>
       <c r="D242" t="n">
-        <v>109.4499969482422</v>
+        <v>106.7399978637695</v>
       </c>
       <c r="E242" t="n">
-        <v>109.629997253418</v>
+        <v>106.8199996948242</v>
       </c>
       <c r="F242" t="n">
-        <v>8524600</v>
+        <v>8699500</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B243" t="n">
-        <v>108.7799987792969</v>
+        <v>107.25</v>
       </c>
       <c r="C243" t="n">
-        <v>108.870002746582</v>
+        <v>108.1999969482422</v>
       </c>
       <c r="D243" t="n">
-        <v>106.7399978637695</v>
+        <v>107.0299987792969</v>
       </c>
       <c r="E243" t="n">
-        <v>106.8199996948242</v>
+        <v>108.0999984741211</v>
       </c>
       <c r="F243" t="n">
-        <v>8699500</v>
+        <v>5465900</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B244" t="n">
-        <v>107.25</v>
+        <v>107.7799987792969</v>
       </c>
       <c r="C244" t="n">
-        <v>108.1999969482422</v>
+        <v>108.0899963378906</v>
       </c>
       <c r="D244" t="n">
-        <v>107.0299987792969</v>
+        <v>106.9700012207031</v>
       </c>
       <c r="E244" t="n">
-        <v>108.0999984741211</v>
+        <v>107.5500030517578</v>
       </c>
       <c r="F244" t="n">
-        <v>5465900</v>
+        <v>8728700</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B245" t="n">
-        <v>107.7799987792969</v>
+        <v>107.2399978637695</v>
       </c>
       <c r="C245" t="n">
-        <v>108.0899963378906</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="D245" t="n">
-        <v>106.9700012207031</v>
+        <v>106.1399993896484</v>
       </c>
       <c r="E245" t="n">
-        <v>107.5500030517578</v>
+        <v>106.2200012207031</v>
       </c>
       <c r="F245" t="n">
-        <v>8728700</v>
+        <v>7033700</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B246" t="n">
-        <v>107.2399978637695</v>
+        <v>106.7099990844727</v>
       </c>
       <c r="C246" t="n">
-        <v>108.9499969482422</v>
+        <v>108.9899978637695</v>
       </c>
       <c r="D246" t="n">
-        <v>106.1399993896484</v>
+        <v>106.3300018310547</v>
       </c>
       <c r="E246" t="n">
-        <v>106.2200012207031</v>
+        <v>107.9800033569336</v>
       </c>
       <c r="F246" t="n">
-        <v>7033700</v>
+        <v>7555300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B247" t="n">
-        <v>106.7099990844727</v>
+        <v>108.620002746582</v>
       </c>
       <c r="C247" t="n">
-        <v>108.9899978637695</v>
+        <v>109.1999969482422</v>
       </c>
       <c r="D247" t="n">
-        <v>106.3300018310547</v>
+        <v>106.9000015258789</v>
       </c>
       <c r="E247" t="n">
-        <v>107.9800033569336</v>
+        <v>107.1600036621094</v>
       </c>
       <c r="F247" t="n">
-        <v>7555300</v>
+        <v>6241300</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B248" t="n">
-        <v>108.620002746582</v>
+        <v>106.4899978637695</v>
       </c>
       <c r="C248" t="n">
-        <v>109.1999969482422</v>
+        <v>106.879997253418</v>
       </c>
       <c r="D248" t="n">
-        <v>106.9000015258789</v>
+        <v>105.1699981689453</v>
       </c>
       <c r="E248" t="n">
-        <v>107.1600036621094</v>
+        <v>105.3099975585938</v>
       </c>
       <c r="F248" t="n">
-        <v>6241300</v>
+        <v>6103700</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B249" t="n">
-        <v>106.4899978637695</v>
+        <v>104.6800003051758</v>
       </c>
       <c r="C249" t="n">
-        <v>106.879997253418</v>
+        <v>105.1100006103516</v>
       </c>
       <c r="D249" t="n">
-        <v>105.1699981689453</v>
+        <v>103.7099990844727</v>
       </c>
       <c r="E249" t="n">
-        <v>105.3099975585938</v>
+        <v>105.0599975585938</v>
       </c>
       <c r="F249" t="n">
-        <v>6103700</v>
+        <v>7395400</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B250" t="n">
-        <v>104.6800003051758</v>
+        <v>104.4499969482422</v>
       </c>
       <c r="C250" t="n">
-        <v>105.1100006103516</v>
+        <v>104.9300003051758</v>
       </c>
       <c r="D250" t="n">
-        <v>103.7099990844727</v>
+        <v>102.9899978637695</v>
       </c>
       <c r="E250" t="n">
-        <v>105.0599975585938</v>
+        <v>104.1800003051758</v>
       </c>
       <c r="F250" t="n">
-        <v>7395400</v>
+        <v>7038100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B251" t="n">
-        <v>104.4499969482422</v>
+        <v>103.6900024414062</v>
       </c>
       <c r="C251" t="n">
-        <v>104.9300003051758</v>
+        <v>106.120002746582</v>
       </c>
       <c r="D251" t="n">
-        <v>102.9899978637695</v>
+        <v>103.5699996948242</v>
       </c>
       <c r="E251" t="n">
-        <v>104.1800003051758</v>
+        <v>105.8199996948242</v>
       </c>
       <c r="F251" t="n">
-        <v>7038100</v>
+        <v>7607600</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B252" t="n">
-        <v>103.6900024414062</v>
+        <v>106.7399978637695</v>
       </c>
       <c r="C252" t="n">
-        <v>106.120002746582</v>
+        <v>107.3600006103516</v>
       </c>
       <c r="D252" t="n">
-        <v>103.5699996948242</v>
+        <v>105.6399993896484</v>
       </c>
       <c r="E252" t="n">
-        <v>105.8199996948242</v>
+        <v>106.5500030517578</v>
       </c>
       <c r="F252" t="n">
-        <v>7607600</v>
+        <v>7255200</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -11128,40 +11128,40 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="D2" t="n">
         <v>105.82</v>
       </c>
-      <c r="D2" t="n">
-        <v>104.18</v>
-      </c>
       <c r="E2" t="n">
-        <v>103.69</v>
+        <v>106.74</v>
       </c>
       <c r="F2" t="n">
-        <v>105.86</v>
+        <v>107.36</v>
       </c>
       <c r="G2" t="n">
-        <v>103.57</v>
+        <v>105.64</v>
       </c>
       <c r="H2" t="n">
-        <v>7387622</v>
+        <v>7105108</v>
       </c>
       <c r="I2" t="n">
-        <v>10419875</v>
+        <v>10358354</v>
       </c>
       <c r="J2" t="n">
-        <v>182718005248</v>
+        <v>183978491904</v>
       </c>
       <c r="K2" t="n">
-        <v>21.464504</v>
+        <v>21.969072</v>
       </c>
       <c r="L2" t="n">
-        <v>14.157071</v>
+        <v>14.268364</v>
       </c>
       <c r="M2" t="n">
-        <v>4.93</v>
+        <v>4.85</v>
       </c>
       <c r="N2" t="n">
-        <v>117.17</v>
+        <v>117.09</v>
       </c>
       <c r="O2" t="n">
         <v>92.19</v>
@@ -11170,7 +11170,7 @@
         <v>1.409</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="R2" t="n">
         <v>0.08699000599999999</v>
@@ -11194,7 +11194,7 @@
         <v>63.602</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.6637841</v>
+        <v>1.6752619</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.483</v>
@@ -11206,7 +11206,7 @@
         <v>98860998656</v>
       </c>
       <c r="AC2" t="n">
-        <v>230384009216</v>
+        <v>231644495872</v>
       </c>
       <c r="AD2" t="n">
         <v>20963000320</v>
@@ -11233,7 +11233,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:03:29</t>
+          <t>2026-09-12 21:47:32</t>
         </is>
       </c>
     </row>
